--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.228945968244615e-05</v>
+        <v>1.228945968244608e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.968721593784019e-06</v>
+        <v>6.968721593784014e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.275464753444331e-06</v>
+        <v>7.275464753444258e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.382736107896336e-06</v>
+        <v>7.382736107896361e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.229137500954861e-06</v>
+        <v>7.229137500954746e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.069687948445687e-06</v>
+        <v>8.069687948445713e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.236452748646633e-06</v>
+        <v>7.236452748646518e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.178939896203683e-06</v>
+        <v>7.178939896203706e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.239769411113025e-06</v>
+        <v>8.239769411113023e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>7.101519469518682e-06</v>
+        <v>7.101519469518613e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.187813394397674e-06</v>
+        <v>9.187813394397832e-06</v>
       </c>
       <c r="M2" t="n">
         <v>1.035464068071486e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>6.966356627391151e-06</v>
+        <v>6.966356627391098e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.087868693706598e-05</v>
+        <v>1.087868693706594e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.168389778829759e-06</v>
+        <v>8.168389778829793e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.149815786141985e-06</v>
+        <v>7.14981578614196e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>7.123365068185206e-06</v>
+        <v>7.123365068185098e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.410926557125703e-06</v>
+        <v>8.410926557125632e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>7.351803991894242e-06</v>
+        <v>7.351803991894183e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.388281242662358e-05</v>
+        <v>1.388281242662367e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.750679398606816e-06</v>
+        <v>7.750679398606803e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.083736675503358e-05</v>
+        <v>1.083736675503371e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>7.851096569616602e-06</v>
+        <v>7.851096569616658e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.845519315999275e-06</v>
+        <v>7.84551931599918e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.838355037143171e-06</v>
+        <v>9.838355037143129e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.225711699844088e-06</v>
+        <v>9.225711699844246e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.079406225430908e-05</v>
+        <v>1.079406225430906e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.47744394087472e-05</v>
+        <v>4.477443940874727e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.951955000028342e-06</v>
+        <v>6.951955000028341e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.152325041578437e-06</v>
+        <v>9.152325041578368e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>9.901632858227166e-06</v>
+        <v>9.901632858227305e-06</v>
       </c>
       <c r="F3" t="n">
         <v>8.825019937680705e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.479009203241295e-05</v>
+        <v>1.479009203241284e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.88066285153379e-06</v>
+        <v>8.88066285153402e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.463002322168923e-06</v>
+        <v>8.463002322168894e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.601690874430053e-05</v>
+        <v>1.601690874430062e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.906213351255533e-06</v>
+        <v>7.906213351255472e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.27881819424783e-05</v>
+        <v>2.278818194247838e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.112858632567576e-05</v>
+        <v>3.112858632567574e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>6.938235826392491e-06</v>
+        <v>6.938235826392438e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.810123270218434e-05</v>
+        <v>1.810123270218436e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.548686110002264e-05</v>
+        <v>1.548686110002279e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.250441154670783e-06</v>
+        <v>8.250441154670912e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>8.066477713766237e-06</v>
+        <v>8.066477713766252e-06</v>
       </c>
       <c r="S3" t="n">
         <v>1.722166392100421e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>9.699668040361544e-06</v>
+        <v>9.699668040361617e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>4.258110698712415e-05</v>
+        <v>4.258110698712409e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.251450705131552e-05</v>
+        <v>1.251450705131566e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.990072412196333e-05</v>
+        <v>1.990072412196339e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.326782713115313e-05</v>
+        <v>1.326782713115312e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.321439050959038e-05</v>
+        <v>1.321439050959037e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.882974256492578e-05</v>
+        <v>1.88297425649258e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.307299674719653e-05</v>
+        <v>2.307299674719661e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.421088086187374e-05</v>
+        <v>3.421088086187367e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.976893981076717e-05</v>
+        <v>6.976893981076721e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.640523820340777e-06</v>
+        <v>9.640523820340772e-06</v>
       </c>
       <c r="D4" t="n">
         <v>1.313356053606796e-05</v>
@@ -777,13 +777,13 @@
         <v>1.261027290761035e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.210467688432884e-05</v>
+        <v>2.210467688432887e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.269290199546918e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.204326786990731e-05</v>
+        <v>1.20432678699073e-05</v>
       </c>
       <c r="J4" t="n">
         <v>2.400808884108893e-05</v>
@@ -792,55 +792,55 @@
         <v>1.116876853534392e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.473441815947496e-05</v>
+        <v>3.473441815947494e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.775856814932677e-05</v>
+        <v>4.775856814932675e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>9.642042055534177e-06</v>
+        <v>9.642042055534175e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.939978695595601e-05</v>
+        <v>1.9399786955956e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.321955946360268e-05</v>
+        <v>2.321955946360271e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.171429764900724e-05</v>
+        <v>1.171429764900723e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.141552462175405e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.595912394688516e-05</v>
+        <v>2.595912394688513e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.399584735214457e-05</v>
+        <v>1.399584735214455e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.953050761042472e-05</v>
+        <v>5.953050761042464e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.838630868702927e-05</v>
+        <v>1.838630868702926e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.317157162752399e-05</v>
+        <v>2.317157162752395e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.963558670345293e-05</v>
+        <v>1.96355867034529e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.949986825717709e-05</v>
+        <v>1.949986825717707e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.441845195210234e-05</v>
+        <v>2.441845195210231e-05</v>
       </c>
       <c r="AA4" t="n">
         <v>3.516249695357418e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.250676921350102e-05</v>
+        <v>5.250676921350093e-05</v>
       </c>
     </row>
     <row r="5">
@@ -853,82 +853,82 @@
         <v>0.001158023498315678</v>
       </c>
       <c r="C5" t="n">
-        <v>4.008014489637595e-05</v>
+        <v>4.008014489637593e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000114398123054267</v>
+        <v>0.0001143981230542671</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001291148863952736</v>
+        <v>0.0001291148863952734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000105842277130829</v>
+        <v>0.0001058422771308287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000276844127540221</v>
+        <v>0.0002768441275402212</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001095470240817366</v>
+        <v>0.0001095470240817365</v>
       </c>
       <c r="I5" t="n">
-        <v>9.219234625307751e-05</v>
+        <v>9.219234625307733e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003232031903506424</v>
+        <v>0.0003232031903506423</v>
       </c>
       <c r="K5" t="n">
-        <v>7.206442694923516e-05</v>
+        <v>7.206442694923501e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005418621159432184</v>
+        <v>0.0005418621159432192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008619679357105151</v>
+        <v>0.000861967935710516</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0009705962460628222</v>
+        <v>0.0009705962460628203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002153466983960905</v>
+        <v>0.0002153466983960909</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002947363171777805</v>
+        <v>0.0002947363171777802</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.277359003395105e-05</v>
+        <v>8.277359003395087e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>7.961971949346712e-05</v>
+        <v>7.961971949346714e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003521671956628991</v>
+        <v>0.0003521671956628983</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001332521938777992</v>
+        <v>0.0001332521938777987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001020557432418716</v>
+        <v>0.001020557432418715</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002048756367154673</v>
+        <v>0.000204875636715467</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003125135317667298</v>
+        <v>0.0003125135317667296</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002496077966241422</v>
+        <v>0.0002496077966241416</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002402372907231263</v>
+        <v>0.0002402372907231254</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003212442468040271</v>
+        <v>0.0003212442468040263</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0005590013437763994</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009950781578811807</v>
+        <v>0.0009950781578811773</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.109903076425295e-05</v>
+        <v>7.45200483930405e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.439163240261418e-05</v>
+        <v>1.439163240261416e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.446365148955378e-05</v>
+        <v>1.446365148955376e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.909634841413793e-05</v>
+        <v>1.567533078535031e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.394036386109616e-05</v>
+        <v>1.736138148988373e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.343476783781467e-05</v>
+        <v>2.685578546660225e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.744401057774258e-05</v>
+        <v>1.744401057774256e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67943764521807e-05</v>
+        <v>1.337335882339312e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.533817979457472e-05</v>
+        <v>2.875919742336232e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.249885948882974e-05</v>
+        <v>1.249885948882973e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.948552674174836e-05</v>
+        <v>3.606450911296075e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.908865910281248e-05</v>
+        <v>4.908865910281261e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.10758405811103e-05</v>
+        <v>1.107584058111049e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.415490740346724e-05</v>
+        <v>2.415490740346725e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.797467716681909e-05</v>
+        <v>2.797467716681907e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.304438860249305e-05</v>
+        <v>1.304438860249304e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.616663320402745e-05</v>
+        <v>1.274561557523984e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.071023252915856e-05</v>
+        <v>3.071023252915853e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.532593830563037e-05</v>
+        <v>1.532593830563036e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>6.093331936491425e-05</v>
+        <v>6.093331936491424e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.313741726930267e-05</v>
+        <v>2.313741726930264e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.467003324327808e-05</v>
+        <v>2.792669108557208e-05</v>
       </c>
       <c r="X6" t="n">
         <v>2.438669528572628e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.109299166255219e-05</v>
+        <v>2.109299166255234e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.574854290558818e-05</v>
+        <v>2.574854290558816e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.991360553584754e-05</v>
+        <v>3.649258790705996e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.408077941640343e-05</v>
+        <v>5.408077941640338e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,34 +1026,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.411805919695543e-05</v>
+        <v>7.411805919695539e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.398964320652902e-05</v>
+        <v>1.398964320652899e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.748267992225621e-05</v>
+        <v>1.748267992225617e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.869435921805277e-05</v>
+        <v>1.869435921805274e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.695939229379857e-05</v>
+        <v>1.695939229379856e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.645379627051706e-05</v>
+        <v>2.645379627051708e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.70420213816574e-05</v>
+        <v>1.704202138165739e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.639238725609555e-05</v>
+        <v>1.639238725609554e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.835720822727717e-05</v>
+        <v>2.835720822727715e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.551788792153217e-05</v>
+        <v>1.551788792153215e-05</v>
       </c>
       <c r="L7" t="n">
         <v>3.908353754566318e-05</v>
@@ -1062,49 +1062,49 @@
         <v>5.210768753551502e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.399116144172242e-05</v>
+        <v>1.399116144172239e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.37472590389588e-05</v>
+        <v>2.374725903895877e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.756703154660551e-05</v>
+        <v>2.756703154660548e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.606341703519549e-05</v>
+        <v>1.606341703519545e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.576464400794227e-05</v>
+        <v>1.576464400794226e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.030824333307339e-05</v>
+        <v>3.030824333307332e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83449667383328e-05</v>
+        <v>1.834496673833278e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>6.394916320572448e-05</v>
+        <v>6.394916320572455e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.273542807321751e-05</v>
+        <v>2.273542807321748e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.752069101371222e-05</v>
+        <v>2.752069101371218e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.398470608964113e-05</v>
+        <v>2.398470608964111e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.392170844436907e-05</v>
+        <v>2.392170844436902e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.876757133829059e-05</v>
+        <v>2.876757133829058e-05</v>
       </c>
       <c r="AA7" t="n">
         <v>3.951161633976234e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.685588859968924e-05</v>
+        <v>5.685588859968911e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.248431598584448e-05</v>
+        <v>8.248431598584454e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.103611530453692e-05</v>
+        <v>3.103611530453693e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.452915202026414e-05</v>
+        <v>3.452915202026415e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.574083131606067e-05</v>
+        <v>3.1118872714239e-05</v>
       </c>
       <c r="F8" t="n">
         <v>2.667792518007922e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.350026836852503e-05</v>
+        <v>4.530016755923204e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.408849347966532e-05</v>
+        <v>3.408849347966538e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.343885935410347e-05</v>
+        <v>3.343885935410348e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.540368032528513e-05</v>
+        <v>4.540368032528511e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.256436001954007e-05</v>
+        <v>3.25643600195401e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.613000964367116e-05</v>
+        <v>5.613000964367114e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.915415963352298e-05</v>
+        <v>6.915415963352336e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.430901450686718e-05</v>
+        <v>2.430901450686719e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.591584234130477e-05</v>
+        <v>3.591584234130478e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.92823599416977e-05</v>
+        <v>3.928235994169772e-05</v>
       </c>
       <c r="Q8" t="n">
         <v>2.272381339954166e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.281111610595017e-05</v>
+        <v>3.28111161059502e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.735471543108129e-05</v>
+        <v>4.735471543108131e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.539143883634073e-05</v>
+        <v>3.539143883634078e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>7.565634868509354e-05</v>
+        <v>7.676093129595725e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.978190017122545e-05</v>
+        <v>3.740815240929329e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.456886902305673e-05</v>
+        <v>4.456886902305675e-05</v>
       </c>
       <c r="X8" t="n">
         <v>3.144066143509995e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.959668297775115e-05</v>
+        <v>4.959668297775116e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.581404343629846e-05</v>
+        <v>3.697258867137682e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>5.655808843777031e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.296957141612523e-05</v>
+        <v>8.296957141612511e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.264551033341175e-05</v>
+        <v>9.264551033341176e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.910532222397858e-05</v>
+        <v>3.910532222397854e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.259835893970574e-05</v>
+        <v>4.259835893970577e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.381003823550234e-05</v>
+        <v>4.228949949246886e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.207507131124817e-05</v>
+        <v>2.688741239514896e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.156947528796664e-05</v>
+        <v>5.156947188056492e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.215770039910697e-05</v>
+        <v>4.215770039910693e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.150806627354513e-05</v>
+        <v>4.150806627354511e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.347288724472675e-05</v>
+        <v>5.347288724472672e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.063356693898177e-05</v>
+        <v>4.063356693898175e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>6.419921656311277e-05</v>
+        <v>6.419921656311274e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.722336655296452e-05</v>
+        <v>7.722336655296454e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.910684045917197e-05</v>
+        <v>3.910684045917195e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>5.10479109162203e-05</v>
+        <v>5.104791091622019e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.534252001390656e-05</v>
+        <v>5.534252001390658e-05</v>
       </c>
       <c r="Q9" t="n">
         <v>4.117909264524334e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.088032302539186e-05</v>
+        <v>4.088032302539187e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>5.542392235052295e-05</v>
+        <v>5.542392235052292e-05</v>
       </c>
       <c r="T9" t="n">
         <v>4.34606457557824e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>8.906802681506618e-05</v>
+        <v>8.906802681506614e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.785110709066712e-05</v>
+        <v>5.545376589404962e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>5.263637003116177e-05</v>
+        <v>5.263637003116179e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.910038510709069e-05</v>
+        <v>4.910038510709071e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.903738746181867e-05</v>
+        <v>4.903738746181862e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.388325035574017e-05</v>
+        <v>4.991113343854184e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.462729535721196e-05</v>
+        <v>6.462729535721194e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.197156761713878e-05</v>
+        <v>8.197156761713863e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.271323031437645e-06</v>
+        <v>4.271323031437632e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.344977211299949e-06</v>
+        <v>4.344977211299945e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.328958473075965e-06</v>
+        <v>4.328958473075953e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.283224311700281e-06</v>
+        <v>4.283224311700266e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.354687525821248e-06</v>
+        <v>4.354687525821228e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.484876223375599e-06</v>
+        <v>4.484876223375566e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.268670071379971e-06</v>
+        <v>4.268670071379963e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.356687363994994e-06</v>
+        <v>4.35668736399498e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.444330962014267e-06</v>
+        <v>4.444330962014268e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.834133211091207e-06</v>
+        <v>4.834133211091193e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.536234632023781e-06</v>
+        <v>4.536234632023764e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.455721862476977e-06</v>
+        <v>4.455721862476973e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.281710303743231e-06</v>
+        <v>4.281710303743211e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.87006614213116e-06</v>
+        <v>5.870066142131161e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.31217684818378e-06</v>
+        <v>4.312176848183761e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.341476083543771e-06</v>
+        <v>4.341476083543752e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.287309025475347e-06</v>
+        <v>4.287309025475328e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.642406886762285e-06</v>
+        <v>4.642406886762274e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.302561799827824e-06</v>
+        <v>4.302561799827793e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.34129179380128e-06</v>
+        <v>6.341291793801287e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.389192352580367e-06</v>
+        <v>4.389192352580347e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.266044631293076e-06</v>
+        <v>6.26604463129303e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.291928062880767e-06</v>
+        <v>6.291928062880772e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.514840916147776e-06</v>
+        <v>5.514840916147759e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.023369512384921e-06</v>
+        <v>5.023369512384902e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.476094917977924e-06</v>
+        <v>4.476094917977904e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.474450332637234e-06</v>
+        <v>4.474450332637227e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.245577169125797e-06</v>
+        <v>4.245577169125799e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.328874811851924e-06</v>
+        <v>4.328874811851921e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.659358153787603e-06</v>
+        <v>4.659358153787601e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.325809999386868e-06</v>
+        <v>4.32580999938686e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.843093356489337e-06</v>
+        <v>4.843093356489327e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.761972299064706e-06</v>
+        <v>5.761972299064684e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.228692780686973e-06</v>
+        <v>4.22869278068697e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.857496521021382e-06</v>
+        <v>4.857496521021381e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.477583933466319e-06</v>
+        <v>5.477583933466285e-06</v>
       </c>
       <c r="K3" t="n">
         <v>8.248114252763027e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.129314584171907e-06</v>
+        <v>6.129314584171927e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>5.587216967512276e-06</v>
+        <v>5.587216967512274e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.319333084665147e-06</v>
+        <v>4.319333084665143e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.050610102775743e-06</v>
+        <v>7.050610102775731e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.53587048323776e-06</v>
+        <v>4.535870483237765e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.746464677372418e-06</v>
+        <v>4.746464677372428e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.361121692563098e-06</v>
+        <v>4.361121692563102e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>6.879780568944859e-06</v>
+        <v>6.87978056894488e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.469698988927414e-06</v>
+        <v>4.469698988927398e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>9.695617076764389e-06</v>
+        <v>9.695617076764396e-06</v>
       </c>
       <c r="V3" t="n">
         <v>5.083850918835875e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.120133977175396e-06</v>
+        <v>8.120133977175379e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.864837649605273e-05</v>
+        <v>1.86483764960527e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.312809227963306e-05</v>
+        <v>1.312809227963305e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.575054314104606e-06</v>
+        <v>5.575054314104626e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.707207758081257e-06</v>
+        <v>5.707207758081268e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.697973301402309e-06</v>
+        <v>5.69797330140231e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.658950612102242e-06</v>
+        <v>4.658950612102253e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.57810979176273e-06</v>
+        <v>4.578109791762729e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.309969439020104e-06</v>
+        <v>5.309969439020118e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.793381047528194e-06</v>
+        <v>4.793381047528206e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.600590925727132e-06</v>
+        <v>5.600590925727142e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>7.071132154363068e-06</v>
+        <v>7.071132154363084e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.628984207828926e-06</v>
+        <v>4.628984207828934e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.623180017870589e-06</v>
+        <v>5.623180017870599e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>6.597746477363211e-06</v>
+        <v>6.597746477363216e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.101615049676316e-05</v>
+        <v>1.101615049676317e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.651249006079723e-06</v>
+        <v>7.651249006079731e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.781913343713004e-06</v>
+        <v>6.781913343713011e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>5.001735728902372e-06</v>
+        <v>5.001735728902383e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>5.120413265934008e-06</v>
+        <v>5.120413265934016e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.451361607639363e-06</v>
+        <v>5.451361607639369e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.839519768678643e-06</v>
+        <v>4.83951976867865e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.850513465001328e-06</v>
+        <v>8.850513465001337e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.011806871612559e-06</v>
+        <v>5.011806871612561e-06</v>
       </c>
       <c r="U4" t="n">
         <v>8.87581682420321e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.89081621757935e-06</v>
+        <v>5.890816217579371e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>5.858157841121684e-06</v>
+        <v>5.858157841121693e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.748261396649042e-05</v>
+        <v>2.748261396649044e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.871081540613277e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.838753916436107e-06</v>
+        <v>4.83875391643612e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.971943270296472e-06</v>
+        <v>6.971943270296488e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.943838758853872e-06</v>
+        <v>6.943838758853882e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1713,70 +1713,70 @@
         <v>1.442457645966381e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.459416715429791e-05</v>
+        <v>1.459416715429793e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.720025912272797e-05</v>
+        <v>2.720025912272798e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.436281319130812e-05</v>
+        <v>1.436281319130815e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.239514079897599e-05</v>
+        <v>3.239514079897597e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.307452026932165e-05</v>
+        <v>5.307452026932167e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.495689015276743e-05</v>
+        <v>1.495689015276741e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.286214927730997e-05</v>
+        <v>3.286214927730993e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.754247271229459e-05</v>
+        <v>4.754247271229448e-05</v>
       </c>
       <c r="K5" t="n">
         <v>0.0001194685181667533</v>
       </c>
       <c r="L5" t="n">
-        <v>6.37467094807735e-05</v>
+        <v>6.374670948077347e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.39381772089778e-05</v>
+        <v>5.393817720897775e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.023808505306236e-05</v>
+        <v>2.023808505306237e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.192172708492897e-05</v>
+        <v>2.19217270849289e-05</v>
       </c>
       <c r="Q5" t="n">
         <v>2.854418706487973e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.837054001402634e-05</v>
+        <v>1.837054001402636e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.11794648041338e-05</v>
+        <v>8.117946480413373e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.127131570366002e-05</v>
+        <v>2.127131570366005e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>8.203293692164723e-05</v>
+        <v>8.203293692164713e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>3.63360708217073e-05</v>
+        <v>3.633607082170737e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.533992422160963e-05</v>
+        <v>3.533992422160958e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004085843718868737</v>
+        <v>0.0004085843718868731</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0002667222015475371</v>
@@ -1785,10 +1785,10 @@
         <v>1.799528559469033e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.541835997313026e-05</v>
+        <v>5.541835997313039e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.890118507250555e-05</v>
+        <v>5.89011850725058e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.863724194373276e-06</v>
+        <v>5.1065147418428e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.782883374033768e-06</v>
+        <v>5.025673921503285e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.514743021291146e-06</v>
+        <v>7.514743021291163e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.998154629799235e-06</v>
+        <v>5.240945177268751e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.805364507998174e-06</v>
+        <v>6.048155055467698e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.51869628410363e-06</v>
+        <v>9.275905736634126e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>5.076548337569477e-06</v>
+        <v>6.833757790099973e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.070744147611146e-06</v>
+        <v>7.827953600141651e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.045310607103756e-06</v>
+        <v>8.802520059634254e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.322092407903421e-05</v>
+        <v>1.146371462650374e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.098813135820275e-06</v>
+        <v>9.856022588350769e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.229477473453557e-06</v>
+        <v>8.98668692598407e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>7.211278300856143e-06</v>
+        <v>7.211278300856154e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>5.529762073125976e-06</v>
+        <v>7.330334173296945e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.656135189910408e-06</v>
+        <v>7.656135189910415e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>5.28708389841919e-06</v>
+        <v>7.044293350949693e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>9.29807759474188e-06</v>
+        <v>1.105528704727238e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>7.216580453883587e-06</v>
+        <v>5.459371001353103e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>9.317622714203379e-06</v>
+        <v>1.107483216673389e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>6.338380347319894e-06</v>
+        <v>8.095589799850408e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.357271533841571e-06</v>
+        <v>6.357271533841575e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.7930178096231e-05</v>
+        <v>2.793017809623099e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.920404540708968e-05</v>
+        <v>1.920404540708967e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.043527498707156e-06</v>
+        <v>5.286318046176667e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.419507400037028e-06</v>
+        <v>7.419507400037043e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.404566169111887e-06</v>
+        <v>7.404566169111893e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.196066655620264e-06</v>
+        <v>7.196066655620269e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.115225835280763e-06</v>
+        <v>7.115225835280751e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.847085482538128e-06</v>
+        <v>7.847085482538123e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.330497091046224e-06</v>
+        <v>7.330497091046219e-06</v>
       </c>
       <c r="F7" t="n">
         <v>8.137706969245173e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.608248197881103e-06</v>
+        <v>9.608248197881108e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.166100251346955e-06</v>
+        <v>7.166100251346953e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.160296061388628e-06</v>
+        <v>8.160296061388624e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>9.134862520881228e-06</v>
+        <v>9.134862520881229e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.35532665402812e-05</v>
+        <v>1.355326654028121e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.018836504959774e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>9.319029387231033e-06</v>
+        <v>9.319029387231032e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>7.537422588512303e-06</v>
+        <v>7.537422588512296e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>7.656100125543933e-06</v>
+        <v>7.656100125543936e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.988477651157387e-06</v>
+        <v>7.98847765115739e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.376635812196665e-06</v>
+        <v>7.376635812196662e-06</v>
       </c>
       <c r="S7" t="n">
         <v>1.138762950851936e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>7.54892291513058e-06</v>
+        <v>7.548922915130574e-06</v>
       </c>
       <c r="U7" t="n">
         <v>1.141447491618778e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.427932261097378e-06</v>
+        <v>8.427932261097388e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.395273884639716e-06</v>
+        <v>8.395273884639713e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>3.001973001000846e-05</v>
+        <v>3.001973001000847e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.124217320991043e-05</v>
+        <v>2.124217320991044e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.375869959954141e-06</v>
+        <v>7.375869959954139e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.509059313814511e-06</v>
+        <v>9.509059313814514e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.480954802371889e-06</v>
+        <v>9.480954802371899e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.355265656765087e-05</v>
+        <v>1.35526565676509e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.942052195536892e-05</v>
+        <v>1.942052195536894e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015238160262624e-05</v>
+        <v>2.015238160262628e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.963579321113435e-05</v>
+        <v>1.646828263112165e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.54210357845499e-05</v>
+        <v>1.542103578454992e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.191354431796924e-05</v>
+        <v>2.314704730246064e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.947139637143505e-05</v>
+        <v>1.947139637143509e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.046559218147677e-05</v>
+        <v>2.046559218147679e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.144015864096936e-05</v>
+        <v>2.144015864096937e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.585856266036933e-05</v>
+        <v>2.585856266036935e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.249366116968587e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.162432550731915e-05</v>
+        <v>2.162432550731987e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.650011486467858e-05</v>
+        <v>1.65001148646786e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.630816873802401e-05</v>
+        <v>1.630816873802404e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.317601102061468e-05</v>
+        <v>1.317601102061471e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.96819319322848e-05</v>
+        <v>1.968193193228482e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.369292562860749e-05</v>
+        <v>2.36929256286075e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.985421903521868e-05</v>
+        <v>1.985421903521874e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.00582990406739e-05</v>
+        <v>2.081575177125701e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.073322838118548e-05</v>
+        <v>1.911481901578696e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.070173909637129e-05</v>
+        <v>2.070173909637133e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.575247412395046e-05</v>
+        <v>3.575247412395047e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.947370567478933e-05</v>
+        <v>3.947370567478937e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.968116608004225e-05</v>
+        <v>1.362195960007472e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.181435543390264e-05</v>
+        <v>2.181435543390266e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.800017197987436e-05</v>
+        <v>2.800017197987438e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2068,16 +2068,16 @@
         <v>1.724374551325694e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.797560516051431e-05</v>
+        <v>1.797560516051432e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.74590167690224e-05</v>
+        <v>1.680230433318779e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.826622664722134e-05</v>
+        <v>1.170674522652295e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.973676787585727e-05</v>
+        <v>1.973676795194386e-05</v>
       </c>
       <c r="H9" t="n">
         <v>1.729461992932312e-05</v>
@@ -2086,55 +2086,55 @@
         <v>1.828881573936479e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.926338219885744e-05</v>
+        <v>1.926338219885743e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.368178621825737e-05</v>
+        <v>2.368178621825739e-05</v>
       </c>
       <c r="L9" t="n">
         <v>2.031688472757393e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.944754906520719e-05</v>
+        <v>1.94475490652072e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.630355218413741e-05</v>
+        <v>1.630355218413735e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.861034168622112e-05</v>
+        <v>1.861034168622113e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.893409905433483e-05</v>
+        <v>1.893409905433482e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.811699740522015e-05</v>
+        <v>1.811699740522014e-05</v>
       </c>
       <c r="R9" t="n">
         <v>1.750515549017284e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151614918649554e-05</v>
+        <v>2.151614918649555e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.767744259310676e-05</v>
+        <v>1.767744259310675e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.153569430595705e-05</v>
+        <v>2.153569430595704e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.855645193907356e-05</v>
+        <v>2.184001107912946e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.852379356261589e-05</v>
+        <v>1.85237935626159e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.014824968798465e-05</v>
+        <v>4.014824968798464e-05</v>
       </c>
       <c r="Y9" t="n">
         <v>3.137069288788661e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.750438963793031e-05</v>
+        <v>1.578885139042964e-05</v>
       </c>
       <c r="AA9" t="n">
         <v>1.963757899179069e-05</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.121015144822268e-05</v>
+        <v>1.121015144822271e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.587388217380609e-06</v>
+        <v>6.587388217380602e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.460262558407075e-06</v>
+        <v>7.460262558407124e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.977872454095042e-06</v>
+        <v>6.97787245409505e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.923262331357495e-06</v>
+        <v>6.923262331357504e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.739586062119759e-06</v>
+        <v>7.73958606211981e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.607038993347808e-06</v>
+        <v>6.60703899334785e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.776611283340838e-06</v>
+        <v>6.776611283340867e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.860716438531747e-06</v>
+        <v>7.86071643853175e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.81837285004697e-06</v>
+        <v>6.81837285004696e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.006671204797983e-06</v>
+        <v>9.006671204798032e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>9.885508191097278e-06</v>
+        <v>9.885508191097283e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>6.729598403223525e-06</v>
+        <v>6.729598403223553e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.047725754346058e-05</v>
+        <v>1.047725754346055e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.1968810815506e-06</v>
+        <v>8.196881081550625e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.852740459296476e-06</v>
+        <v>6.852740459296484e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.615898941715901e-06</v>
+        <v>6.615898941715933e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.189442743370897e-06</v>
+        <v>8.189442743370948e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>7.18906419845704e-06</v>
+        <v>7.18906419845706e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.271132345393602e-05</v>
+        <v>1.271132345393601e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.095879944670696e-06</v>
+        <v>7.095879944670729e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.930135415107328e-06</v>
+        <v>9.930135415107289e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.793841863446388e-06</v>
+        <v>7.793841863446425e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.406449467153134e-06</v>
+        <v>7.406449467153199e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.098046154111835e-06</v>
+        <v>9.098046154111948e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.957179988042423e-06</v>
+        <v>7.957179988042525e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.040668576763919e-05</v>
+        <v>1.040668576763918e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.913382333810859e-05</v>
+        <v>3.913382333810874e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.245688382512734e-06</v>
+        <v>6.245688382512738e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.253403572545318e-05</v>
+        <v>1.253403572545331e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>9.063609466409448e-06</v>
+        <v>9.063609466409635e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.691748459048459e-06</v>
+        <v>8.691748459048445e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.448234151278027e-05</v>
+        <v>1.448234151278035e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.428558027956637e-06</v>
+        <v>6.428558027956757e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.641289598320575e-06</v>
+        <v>7.641289598320715e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.536410011236525e-05</v>
+        <v>1.536410011236532e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.935557057453267e-06</v>
+        <v>7.93555705745346e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.354692019927177e-05</v>
+        <v>2.35469201992719e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.981710161617076e-05</v>
+        <v>2.98171016161708e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>7.301035184466126e-06</v>
+        <v>7.301035184466264e-06</v>
       </c>
       <c r="O3" t="n">
         <v>1.772750458794723e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.773265110673852e-05</v>
+        <v>1.773265110673871e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.181837251654693e-06</v>
+        <v>8.181837251654649e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>6.490588296631694e-06</v>
+        <v>6.490588296631805e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.768528389783412e-05</v>
+        <v>1.768528389783413e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.059265148801406e-05</v>
+        <v>1.059265148801418e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>3.714487716509805e-05</v>
+        <v>3.714487716509796e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>9.896264259346078e-06</v>
+        <v>9.89626425934622e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.638268128953112e-05</v>
+        <v>1.638268128953115e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.491286588985322e-05</v>
+        <v>1.491286588985325e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.212924922827866e-05</v>
+        <v>1.212924922827875e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.659842086189352e-05</v>
+        <v>1.659842086189355e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.606260168973807e-05</v>
+        <v>1.606260168973802e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.348816430717336e-05</v>
+        <v>3.348816430717332e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.086226019423781e-05</v>
+        <v>6.086226019423789e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.543389807942069e-06</v>
+        <v>8.543389807942084e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.85055401496554e-05</v>
+        <v>1.850554014965544e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.305672201103932e-05</v>
+        <v>1.305672201103935e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.243987555282085e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.166062761925031e-05</v>
+        <v>2.166062761925027e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.867987480079379e-06</v>
+        <v>8.867987480079396e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.078338450265789e-05</v>
+        <v>1.07833845026579e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.300935298303648e-05</v>
+        <v>2.300935298303653e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.12551006098735e-05</v>
+        <v>1.125510060987351e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.597293719376441e-05</v>
+        <v>3.597293719376439e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.573674409142971e-05</v>
+        <v>4.573674409142977e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.025235239473949e-05</v>
+        <v>1.02523523947395e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.906144512970823e-05</v>
+        <v>1.906144512970825e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.682598522982349e-05</v>
+        <v>2.682598522982357e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.164329856622783e-05</v>
+        <v>1.164329856622785e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.968064672674476e-06</v>
+        <v>8.968064672674486e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.674196577827946e-05</v>
+        <v>2.674196577827951e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.544222991661032e-05</v>
+        <v>1.544222991661034e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.133139514083134e-05</v>
+        <v>5.133139514083143e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.426267741892082e-05</v>
+        <v>1.426267741892083e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.807370322915142e-05</v>
+        <v>1.807370322915143e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.227347185413618e-05</v>
+        <v>2.22734718541362e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.778256105726452e-05</v>
+        <v>1.778256105726454e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.139855668318674e-05</v>
+        <v>2.139855668318678e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.411845111069871e-05</v>
+        <v>2.411845111069872e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.140011649344546e-05</v>
+        <v>5.140011649344542e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2576,79 +2576,79 @@
         <v>2.483179884803366e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002226798421557124</v>
+        <v>0.0002226798421557117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001043131851150524</v>
+        <v>0.0001043131851150525</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001026017891431839</v>
+        <v>0.000102601789143184</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002571756160501704</v>
+        <v>0.0002571756160501707</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15673940177355e-05</v>
+        <v>3.156739401773554e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>6.916595630731333e-05</v>
+        <v>6.916595630731344e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002926172355293322</v>
+        <v>0.0002926172355293326</v>
       </c>
       <c r="K5" t="n">
-        <v>7.597901291513549e-05</v>
+        <v>7.597901291513547e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005396534903402463</v>
+        <v>0.0005396534903402466</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007723584521286188</v>
+        <v>0.0007723584521286206</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007721089146791037</v>
+        <v>0.0007721089146791041</v>
       </c>
       <c r="O5" t="n">
         <v>0.0002016877652980339</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000347373827329559</v>
+        <v>0.0003473738273295609</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.387342523081843e-05</v>
+        <v>8.387342523081862e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.27902455350103e-05</v>
+        <v>3.279024553501038e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003489667098455729</v>
+        <v>0.000348966709845574</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001615177968427878</v>
+        <v>0.0001615177968427873</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0008133030928966279</v>
+        <v>0.0008133030928966284</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000124066778974808</v>
+        <v>0.0001240667789748078</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002041800864204671</v>
+        <v>0.0002041800864204672</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000292843506667232</v>
+        <v>0.0002928435066672335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000199663439484198</v>
+        <v>0.0001996634394841983</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002527675924257582</v>
+        <v>0.000252767592425758</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003188205645466736</v>
+        <v>0.000318820564546674</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009199629683963495</v>
+        <v>0.0009199629683963473</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.500632794164099e-05</v>
+        <v>6.18663321631916e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.26874575553452e-05</v>
+        <v>1.268745755534521e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.950961211860918e-05</v>
+        <v>2.264960789705855e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.406079397999308e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.658394330022396e-05</v>
+        <v>1.34439475217746e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.580469536665341e-05</v>
+        <v>2.2664699588204e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.872059449033129e-06</v>
+        <v>1.30120552274825e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.178745647161165e-05</v>
+        <v>1.178745647161166e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.715342073043962e-05</v>
+        <v>2.715342073043961e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.225917257882727e-05</v>
+        <v>1.539916835727665e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.697700916271817e-05</v>
+        <v>3.697700916271825e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.674081606038348e-05</v>
+        <v>4.674081606038347e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.133250577119788e-05</v>
+        <v>1.133250577119792e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.320973623126431e-05</v>
+        <v>2.320973623126434e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.097443010326125e-05</v>
+        <v>3.097443010326137e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.264737053518159e-05</v>
+        <v>1.578736631363097e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>9.972136641628227e-06</v>
+        <v>1.31121324200776e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.774603774723324e-05</v>
+        <v>3.088603352568265e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.958629766401343e-05</v>
+        <v>1.644630188556407e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.559059835966727e-05</v>
+        <v>5.245060258121797e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.840674516632393e-05</v>
+        <v>1.840674516632396e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.222185561070129e-05</v>
+        <v>2.222185561070134e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.327754382308995e-05</v>
+        <v>2.641753960153935e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.903907075176441e-05</v>
+        <v>1.903907075176442e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.240262865214058e-05</v>
+        <v>2.554262443058995e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.826251885810185e-05</v>
+        <v>2.51225230796525e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.263345150029201e-05</v>
+        <v>5.263345150029194e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,76 +2746,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.477589288676419e-05</v>
+        <v>6.477589288676423e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.245702250046847e-05</v>
+        <v>1.245702250046846e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.241917284218181e-05</v>
+        <v>2.241917284218184e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.697035470356574e-05</v>
+        <v>1.697035470356575e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.635350824534724e-05</v>
+        <v>1.635350824534723e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.55742603117767e-05</v>
+        <v>2.557426031177666e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.278162017260579e-05</v>
+        <v>1.27816201726058e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.46970171951843e-05</v>
+        <v>1.469701719518432e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.692298567556291e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.516873330239992e-05</v>
+        <v>1.516873330239994e-05</v>
       </c>
       <c r="L7" t="n">
         <v>3.988656988629085e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.965037678395618e-05</v>
+        <v>4.965037678395615e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.416598508726589e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.29735390987117e-05</v>
+        <v>2.297353909871171e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.073807919882697e-05</v>
+        <v>3.073807919882706e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.555693125875422e-05</v>
+        <v>1.555693125875421e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.288169736520089e-05</v>
+        <v>1.288169736520088e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.065559847080588e-05</v>
+        <v>3.06555984708059e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.935586260913671e-05</v>
+        <v>1.935586260913672e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>5.535619820362483e-05</v>
+        <v>5.535619820362493e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.817631011144722e-05</v>
+        <v>1.817631011144725e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.198733592167785e-05</v>
+        <v>2.198733592167784e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.618710454666262e-05</v>
+        <v>2.618710454666264e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.181132922122373e-05</v>
+        <v>2.181132922122372e-05</v>
       </c>
       <c r="Z7" t="n">
         <v>2.531218937571319e-05</v>
@@ -2824,7 +2824,7 @@
         <v>2.803208380322513e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.531374918597183e-05</v>
+        <v>5.531374918597173e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.254010771146595e-05</v>
+        <v>7.254010771146578e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.819200275261802e-05</v>
+        <v>2.819200275261803e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.815415309433135e-05</v>
+        <v>3.815415309433136e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.270533495571527e-05</v>
+        <v>2.846113748842342e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.535947516738904e-05</v>
+        <v>2.535947516738905e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.130924056392628e-05</v>
+        <v>4.296203070004088e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.851660042475535e-05</v>
+        <v>2.851660042475532e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.043199744733385e-05</v>
+        <v>3.043199744733387e-05</v>
       </c>
       <c r="J8" t="n">
         <v>4.265796592771246e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.090371355454947e-05</v>
+        <v>3.09037135545495e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.562155013844039e-05</v>
+        <v>5.562155013844037e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.538535703610565e-05</v>
+        <v>6.538535703610578e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.372228865322575e-05</v>
+        <v>2.372228865322574e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42293353902702e-05</v>
+        <v>3.422933539027025e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.157766593613903e-05</v>
+        <v>4.157766593613914e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.175470875306344e-05</v>
+        <v>2.175470875306345e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.861667761735042e-05</v>
+        <v>2.861667761735044e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.639057872295537e-05</v>
+        <v>4.639057872295546e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.509084286128629e-05</v>
+        <v>3.509084286128628e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.618858388219965e-05</v>
+        <v>6.72028389534912e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.391129036359673e-05</v>
+        <v>3.173068598032e-05</v>
       </c>
       <c r="W8" t="n">
         <v>3.772388265792583e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.311541853072819e-05</v>
+        <v>3.311541853072827e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.54682433231817e-05</v>
+        <v>4.546824332318171e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.10471696278627e-05</v>
+        <v>3.292834314039427e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.376706405537465e-05</v>
+        <v>4.37670640553747e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.937486043190682e-05</v>
+        <v>7.937486043190676e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.95933963649961e-05</v>
+        <v>7.959339636499613e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.269445597597734e-05</v>
+        <v>3.269445597597735e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.265660631769063e-05</v>
+        <v>4.265660631769072e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.720778817907456e-05</v>
+        <v>3.595688797708598e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.659094172085607e-05</v>
+        <v>2.40965280226449e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.581169378728553e-05</v>
+        <v>4.581169058123875e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.301905364811466e-05</v>
+        <v>3.301905364811472e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.493445067069314e-05</v>
+        <v>3.49344506706932e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.716041915107172e-05</v>
+        <v>4.716041915107178e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.540616677790875e-05</v>
+        <v>3.54061667779088e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>6.012400336179964e-05</v>
+        <v>6.012400336179974e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>6.988781025946506e-05</v>
+        <v>6.988781025946508e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.440341856277473e-05</v>
+        <v>3.440341856277475e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.500866473354419e-05</v>
+        <v>4.500866473354421e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.316383808638435e-05</v>
+        <v>5.316383808638447e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.579436152821634e-05</v>
+        <v>3.57943615282163e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.311913084070973e-05</v>
+        <v>3.311913084070975e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>5.089303194631476e-05</v>
+        <v>5.089303194631484e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.95932960846456e-05</v>
+        <v>3.959329608464561e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>7.559759678029932e-05</v>
+        <v>7.55975967802995e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.841374358695611e-05</v>
+        <v>4.466821246863147e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.222476939718672e-05</v>
+        <v>4.222476939718678e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.642453802217147e-05</v>
+        <v>4.642453802217154e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.204876269673261e-05</v>
+        <v>4.204876269673263e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.554962285122206e-05</v>
+        <v>4.228188574875921e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.826951727873399e-05</v>
+        <v>4.826951727873402e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.555118266148068e-05</v>
+        <v>7.555118266148066e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.062154625500527e-05</v>
+        <v>1.062154625500508e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.795556347628087e-06</v>
+        <v>6.795556347628081e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.064700175460516e-06</v>
+        <v>8.06470017546036e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.135163818781825e-06</v>
+        <v>7.13516381878165e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.386453941988166e-06</v>
+        <v>7.386453941987961e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.953563746098963e-06</v>
+        <v>7.953563746098772e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.766194582325918e-06</v>
+        <v>6.766194582325719e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.801625550925728e-06</v>
+        <v>7.801625550925555e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.119563614515993e-06</v>
+        <v>8.119563614515835e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.508322898954886e-06</v>
+        <v>8.508322898954705e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.276652197153367e-06</v>
+        <v>9.276652197153162e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>9.860725848468524e-06</v>
+        <v>9.860725848468519e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>7.028390602685338e-06</v>
+        <v>7.028390602685117e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.061195930220759e-05</v>
+        <v>1.061195930220728e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.473527662166246e-06</v>
+        <v>8.473527662166052e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.114158268487216e-06</v>
+        <v>7.114158268486982e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.809898932090221e-06</v>
+        <v>6.809898932090035e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.46761299649084e-06</v>
+        <v>8.467612996490669e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>7.542288874222998e-06</v>
+        <v>7.542288874222833e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.104502539482179e-05</v>
+        <v>1.104502539482154e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.654939260242205e-06</v>
+        <v>7.654939260242001e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.002992958542746e-05</v>
+        <v>1.002992958542729e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>9.476200734250643e-06</v>
+        <v>9.476200734250443e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.576252603148612e-06</v>
+        <v>8.576252603148445e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.482921142135763e-06</v>
+        <v>9.482921142135531e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.985577102394786e-06</v>
+        <v>7.985577102394553e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.052192585550224e-05</v>
+        <v>1.052192585550223e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.367522776995896e-05</v>
+        <v>3.36752277699589e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.474451652606708e-06</v>
+        <v>6.474451652606715e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.554587167959908e-05</v>
+        <v>1.554587167959907e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.880673565628799e-06</v>
+        <v>8.880673565628648e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.069370579617573e-05</v>
+        <v>1.069370579617561e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.469722008245837e-05</v>
+        <v>1.469722008245827e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.256109068542088e-06</v>
+        <v>6.256109068542011e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.367100410656708e-05</v>
+        <v>1.367100410656698e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.590269465266733e-05</v>
+        <v>1.59026946526673e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.864757365587057e-05</v>
+        <v>1.864757365587056e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.416301380524342e-05</v>
+        <v>2.416301380524334e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.835527653500693e-05</v>
+        <v>2.835527653500691e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.128542809861538e-06</v>
+        <v>8.128542809861462e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.755369525446603e-05</v>
+        <v>1.755369525446587e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.839239828258793e-05</v>
+        <v>1.839239828258786e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.739880845177685e-06</v>
+        <v>8.73988084517764e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>6.568752786288555e-06</v>
+        <v>6.56875278628842e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.835787536194608e-05</v>
+        <v>1.835787536194602e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.181128320563098e-05</v>
+        <v>1.18112832056308e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.423245848893625e-05</v>
+        <v>2.423245848893626e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.256240362483999e-05</v>
+        <v>1.256240362483997e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.569548914607606e-05</v>
+        <v>1.569548914607585e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.562913388976529e-05</v>
+        <v>2.562913388976521e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.917156024750003e-05</v>
+        <v>1.917156024749986e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.755466166753029e-05</v>
+        <v>1.755466166753019e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.496025023055845e-05</v>
+        <v>1.496025023055835e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.302381157151342e-05</v>
+        <v>3.302381157151344e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.209138558051582e-05</v>
+        <v>5.209138558051581e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.86877315485766e-06</v>
+        <v>8.868773154857662e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.321063290475013e-05</v>
+        <v>2.321063290475014e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.271109214821409e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.554952968899763e-05</v>
+        <v>1.554952968899762e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.195529580982791e-05</v>
+        <v>2.195529580982788e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.543414888210028e-06</v>
+        <v>8.543414888210031e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.023908400032321e-05</v>
+        <v>2.023908400032322e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.381276687481847e-05</v>
+        <v>2.381276687481845e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.822155564315421e-05</v>
+        <v>2.822155564315424e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.690018851524556e-05</v>
+        <v>3.690018851524554e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.33796194214829e-05</v>
+        <v>4.337961942148289e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.150503955429797e-05</v>
+        <v>1.150503955429795e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.881475244348386e-05</v>
+        <v>1.88147524434839e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.782852743702689e-05</v>
+        <v>2.782852743702693e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24738247946058e-05</v>
+        <v>1.247382479460581e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>9.037075623792364e-06</v>
+        <v>9.037075623792356e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.776171856734267e-05</v>
+        <v>2.776171856734268e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.730975693620066e-05</v>
+        <v>1.730975693620071e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.100087387507076e-05</v>
+        <v>3.100087387507083e-05</v>
       </c>
       <c r="V4" t="n">
         <v>1.846823202942515e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.688645581688497e-05</v>
+        <v>1.688645581688494e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>3.915418103862165e-05</v>
+        <v>3.915418103862168e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.891837425699067e-05</v>
+        <v>2.89183742569907e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.268304288465012e-05</v>
+        <v>2.268304288465011e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.231690139606073e-05</v>
+        <v>2.231690139606074e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.061092552103766e-05</v>
+        <v>5.061092552103769e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007390432015790076</v>
+        <v>0.0007390432015790096</v>
       </c>
       <c r="C5" t="n">
-        <v>2.611206768606021e-05</v>
+        <v>2.61120676860602e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002898987608279489</v>
+        <v>0.0002898987608279491</v>
       </c>
       <c r="E5" t="n">
-        <v>8.810576758410324e-05</v>
+        <v>8.810576758410343e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001484457791058752</v>
+        <v>0.0001484457791058751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002389525342959439</v>
+        <v>0.0002389525342959427</v>
       </c>
       <c r="H5" t="n">
-        <v>1.894733309056148e-05</v>
+        <v>1.894733309056146e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002387459566884796</v>
+        <v>0.0002387459566884802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000282838550872269</v>
+        <v>0.0002828385508722687</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003451227587167159</v>
+        <v>0.0003451227587167158</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005151167190267097</v>
+        <v>0.0005151167190267102</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006752081809133821</v>
+        <v>0.0006752081809133827</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003823754720323925</v>
+        <v>0.0003823754720323937</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001801490474707396</v>
+        <v>0.00018014904747074</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003346267320764209</v>
+        <v>0.0003346267320764228</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.863807157540733e-05</v>
+        <v>8.863807157540764e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.80535224504462e-05</v>
+        <v>2.805352245044624e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003374304325700274</v>
+        <v>0.000337430432570028</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001823641382241786</v>
+        <v>0.0001823641382241793</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0004019417849974049</v>
+        <v>0.0004019417849974067</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001773562821128638</v>
+        <v>0.0001773562821128626</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001663281826568342</v>
+        <v>0.0001663281826568339</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005767126112093339</v>
+        <v>0.0005767126112093341</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003789919707540743</v>
+        <v>0.0003789919707540751</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000241189993335148</v>
+        <v>0.0002411899933351477</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002632523884866487</v>
+        <v>0.0002632523884866485</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0008437457036518718</v>
+        <v>0.0008437457036518711</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.616928562681285e-05</v>
+        <v>5.3153488844999e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.930876419340817e-06</v>
+        <v>9.930876419340834e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.728853295104717e-05</v>
+        <v>2.728853295104722e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.377319541269725e-05</v>
+        <v>1.377319541269729e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.661163295348078e-05</v>
+        <v>1.962742973529465e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.603319585612491e-05</v>
+        <v>2.301739907431104e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.605518152693188e-06</v>
+        <v>9.605518152693205e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.431698404662023e-05</v>
+        <v>2.130118726480645e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.789066692111545e-05</v>
+        <v>2.789066692111547e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.928365890763738e-05</v>
+        <v>3.229945568945127e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.097808856154253e-05</v>
+        <v>3.796229177972871e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.745751946777993e-05</v>
+        <v>4.745751946777996e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.262807843950829e-05</v>
+        <v>1.262807843950828e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.290882297032847e-05</v>
+        <v>1.993779132869417e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1922899132751e-05</v>
+        <v>3.192289913275112e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655172484090281e-05</v>
+        <v>1.655172484090286e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.311497567008938e-05</v>
+        <v>1.31149756700894e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.882382183182577e-05</v>
+        <v>2.882382183182583e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.837186020068385e-05</v>
+        <v>1.837186020068388e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.514925256560776e-05</v>
+        <v>3.213345578379401e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.254613207572216e-05</v>
+        <v>2.254613207572217e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.098039009361334e-05</v>
+        <v>1.806487207359312e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.021628430310478e-05</v>
+        <v>4.021628430310482e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.018382645102391e-05</v>
+        <v>3.018382645102395e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.67609429309471e-05</v>
+        <v>2.374514614913326e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.337900466054389e-05</v>
+        <v>2.639480144235778e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.188414573604773e-05</v>
+        <v>5.188414573604779e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.57490887638957e-05</v>
+        <v>5.574908876389575e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.25264763382376e-05</v>
+        <v>1.252647633823759e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.68683360881301e-05</v>
@@ -3618,28 +3618,28 @@
         <v>1.636879533159403e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.920723287237754e-05</v>
+        <v>1.920723287237756e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.561299899320785e-05</v>
+        <v>2.56129989932078e-05</v>
       </c>
       <c r="H7" t="n">
         <v>1.220111807158996e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.389678718370318e-05</v>
+        <v>2.389678718370321e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.747047005819842e-05</v>
+        <v>2.74704700581984e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.187925882653411e-05</v>
+        <v>3.187925882653416e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>4.055789169862545e-05</v>
+        <v>4.055789169862544e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.703732260486278e-05</v>
+        <v>4.703732260486284e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.516274273767792e-05</v>
@@ -3648,43 +3648,43 @@
         <v>2.247101343919396e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.148478843273692e-05</v>
+        <v>3.148478843273707e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.613152797798573e-05</v>
+        <v>1.613152797798574e-05</v>
       </c>
       <c r="R7" t="n">
         <v>1.269477880717229e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.141942175072257e-05</v>
+        <v>3.141942175072259e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.096746011958061e-05</v>
+        <v>2.096746011958063e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.473189695136638e-05</v>
+        <v>3.473189695136645e-05</v>
       </c>
       <c r="V7" t="n">
         <v>2.212593521280511e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.054415900026489e-05</v>
+        <v>2.054415900026487e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>4.281188422200161e-05</v>
+        <v>4.281188422200158e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.26465560846106e-05</v>
+        <v>3.264655608461064e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.634074606803006e-05</v>
+        <v>2.634074606803004e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.597460457944069e-05</v>
+        <v>2.59746045794407e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.426862870441762e-05</v>
+        <v>5.426862870441756e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.299449341544065e-05</v>
+        <v>6.299449341544067e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.721742590204969e-05</v>
+        <v>2.721742590204967e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.15592856519422e-05</v>
+        <v>4.155928565194214e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.105974489540618e-05</v>
+        <v>2.709521185942784e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.761256640336496e-05</v>
+        <v>2.761256640336494e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.030394855701994e-05</v>
+        <v>4.184783079781479e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.689206763540209e-05</v>
+        <v>2.689206763540207e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.858773674751532e-05</v>
+        <v>3.85877367475153e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.216141962201048e-05</v>
+        <v>4.216141962201044e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.657020839034624e-05</v>
+        <v>4.657020839034623e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.524884126243755e-05</v>
+        <v>5.524884126243749e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.172827216867496e-05</v>
+        <v>6.172827216867494e-05</v>
       </c>
       <c r="N8" t="n">
         <v>2.408214938201743e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.297793237905807e-05</v>
+        <v>3.29779323790581e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.160292326432857e-05</v>
+        <v>4.160292326432864e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.191371311796232e-05</v>
+        <v>2.191371311796231e-05</v>
       </c>
       <c r="R8" t="n">
         <v>2.738572837098442e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.611037131453464e-05</v>
+        <v>4.611037131453467e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.565840968339273e-05</v>
+        <v>3.565840968339275e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.484152161892718e-05</v>
+        <v>4.578925372754707e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.681688477661718e-05</v>
+        <v>3.478556646233666e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.523657182720828e-05</v>
+        <v>3.52365718272083e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.927646834783645e-05</v>
+        <v>4.927646834783643e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.474612028112885e-05</v>
+        <v>5.474612028112888e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.103169563184217e-05</v>
+        <v>3.344784590027423e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.066555414325277e-05</v>
+        <v>4.066555414325279e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.673707251561273e-05</v>
+        <v>7.673707251561272e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3785,79 +3785,79 @@
         <v>6.871540418636196e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.03156408725871e-05</v>
+        <v>3.031564087258707e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.46575006224795e-05</v>
+        <v>4.465750062247954e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.415795986594348e-05</v>
+        <v>3.304486420472049e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.699639740672707e-05</v>
+        <v>2.587841690699792e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.340216352755739e-05</v>
+        <v>4.340216124176683e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.99902826059395e-05</v>
+        <v>2.999028260593942e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.168595171805271e-05</v>
+        <v>4.168595171805268e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.525963459254791e-05</v>
+        <v>4.525963459254788e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.966842336088368e-05</v>
+        <v>4.966842336088366e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8347056232975e-05</v>
+        <v>5.834705623297492e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>6.482648713921237e-05</v>
+        <v>6.482648713921236e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.295190727202744e-05</v>
+        <v>3.295190727202737e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.185990299863205e-05</v>
+        <v>4.185990299863203e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.122127758450078e-05</v>
+        <v>5.122127758450087e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.392069022654478e-05</v>
+        <v>3.392069022654477e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.048394334152178e-05</v>
+        <v>3.048394334152176e-05</v>
       </c>
       <c r="S9" t="n">
         <v>4.920858628507208e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.875662465393012e-05</v>
+        <v>3.875662465393008e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>5.251822023704015e-05</v>
+        <v>5.251822023704026e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.991509974715461e-05</v>
+        <v>4.54805529544771e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.833332353461443e-05</v>
+        <v>3.83333235346144e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>6.060104875635109e-05</v>
+        <v>6.060104875635103e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.043572061896013e-05</v>
+        <v>5.043572061896008e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.412991060237954e-05</v>
+        <v>4.122216054472874e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.376376911379013e-05</v>
+        <v>4.376376911379007e-05</v>
       </c>
       <c r="AB9" t="n">
         <v>7.205779323876703e-05</v>
@@ -4026,82 +4026,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.046298928647919e-05</v>
+        <v>1.046298928647898e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.221991753652213e-06</v>
+        <v>7.221991753652202e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.33176565604007e-06</v>
+        <v>8.331765656039911e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.429746831538328e-06</v>
+        <v>7.429746831538261e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.886052548832028e-06</v>
+        <v>7.886052548831948e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.284998576724897e-06</v>
+        <v>8.284998576724714e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.158861956036713e-06</v>
+        <v>7.158861956036517e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>8.334146514837343e-06</v>
+        <v>8.33414651483725e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.53469030756126e-06</v>
+        <v>8.534690307561062e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>9.138625890441896e-06</v>
+        <v>9.138625890441605e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.346372394787665e-06</v>
+        <v>9.346372394787592e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>9.929347689165107e-06</v>
+        <v>9.929347689165091e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>7.380850010033711e-06</v>
+        <v>7.380850010033621e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.055953035484391e-05</v>
+        <v>1.055953035484369e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.776423986253458e-06</v>
+        <v>8.776423986253435e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.625037326526753e-06</v>
+        <v>7.625037326526697e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>7.374697747369287e-06</v>
+        <v>7.374697747369166e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.804873237724264e-06</v>
+        <v>8.804873237724188e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>7.98701514841058e-06</v>
+        <v>7.987015148410604e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.132540912702229e-05</v>
+        <v>1.132540912702256e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>8.83570869523149e-06</v>
+        <v>8.835708695231368e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.067623099679041e-05</v>
+        <v>1.067623099679071e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.057790221227064e-05</v>
+        <v>1.057790221227058e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.00687171985872e-05</v>
+        <v>1.006871719858707e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.001355177021491e-05</v>
+        <v>1.001355177021492e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.441880187967826e-06</v>
+        <v>8.441880187967673e-06</v>
       </c>
       <c r="AB2" t="n">
         <v>1.075609068273557e-05</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.015259208882597e-05</v>
+        <v>3.015259208882605e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.242806818218125e-06</v>
+        <v>7.242806818218119e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.506536493029063e-05</v>
+        <v>1.50653649302909e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.612978591038732e-06</v>
+        <v>8.612978591038759e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.189200728286967e-05</v>
+        <v>1.189200728286976e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.468548146534177e-05</v>
+        <v>1.468548146534172e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.691764776772812e-06</v>
+        <v>6.69176477677295e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.510045793904265e-05</v>
+        <v>1.51004579390427e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.648538983510464e-05</v>
+        <v>1.648538983510462e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.077360230846991e-05</v>
+        <v>2.077360230847016e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.22638147390865e-05</v>
+        <v>2.226381473908655e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.644558052364201e-05</v>
+        <v>2.644558052364198e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.277062661031434e-06</v>
+        <v>8.2770626610313e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.556731781675956e-05</v>
+        <v>1.556731781675961e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.817104471843136e-05</v>
+        <v>1.817104471843145e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.00155149743503e-05</v>
+        <v>1.001551497435035e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.238620669666854e-06</v>
+        <v>8.238620669666748e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.839149052649015e-05</v>
+        <v>1.839149052649009e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.262010343518877e-05</v>
+        <v>1.262010343518889e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.319259016142382e-05</v>
+        <v>2.319259016142386e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.858234746489024e-05</v>
+        <v>1.858234746489025e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.711188957261414e-05</v>
+        <v>1.711188957261426e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.109227087534539e-05</v>
+        <v>3.109227087534544e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.747691971848289e-05</v>
+        <v>2.747691971848294e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.824309928754133e-05</v>
+        <v>1.824309928754125e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.585284505835084e-05</v>
+        <v>1.585284505835085e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.231248791633187e-05</v>
+        <v>3.231248791633194e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.638859136146266e-05</v>
+        <v>4.638859136146267e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.964307193267656e-06</v>
+        <v>9.964307193267649e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.231544004434538e-05</v>
+        <v>2.231544004434541e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.21267224724385e-05</v>
+        <v>1.212672247243851e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.728090546027167e-05</v>
+        <v>1.728090546027165e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.178718436956096e-05</v>
+        <v>2.178718436956093e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>9.066953190447977e-06</v>
+        <v>9.066953190447966e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.234233293971025e-05</v>
+        <v>2.234233293971026e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.459533163029217e-05</v>
+        <v>2.459533163029218e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.14292975659587e-05</v>
+        <v>3.142929756595875e-05</v>
       </c>
       <c r="L4" t="n">
         <v>3.377588990065919e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.028221831111223e-05</v>
+        <v>4.028221831111222e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.157441037989495e-05</v>
+        <v>1.157441037989493e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.583588187640213e-05</v>
+        <v>1.583588187640215e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.733806043704331e-05</v>
+        <v>2.733806043704335e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.433261845139891e-05</v>
+        <v>1.43326184513989e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.150491774291875e-05</v>
+        <v>1.150491774291874e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.765940781970884e-05</v>
+        <v>2.765940781970887e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.842132446760242e-05</v>
+        <v>1.842132446760243e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>2.901349591084825e-05</v>
+        <v>2.901349591084829e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.792992855092706e-05</v>
+        <v>2.792992855092705e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.856580250383031e-05</v>
+        <v>1.856580250383029e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.768658572083537e-05</v>
+        <v>4.768658572083542e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.197197135087446e-05</v>
+        <v>4.197197135087457e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.33044507220927e-05</v>
+        <v>2.330445072209269e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.355923433765663e-05</v>
+        <v>2.35592343376567e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.936671174331395e-05</v>
+        <v>4.936671174331398e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000617942856942678</v>
+        <v>0.0006179428569426784</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75921268575727e-05</v>
+        <v>3.759212685757273e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002561298495483708</v>
+        <v>0.0002561298495483712</v>
       </c>
       <c r="E5" t="n">
-        <v>6.834237378307774e-05</v>
+        <v>6.834237378307813e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001710859836099083</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002228942925738232</v>
+        <v>0.0002228942925738237</v>
       </c>
       <c r="H5" t="n">
-        <v>2.049843874779529e-05</v>
+        <v>2.04984387477953e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002659857246346873</v>
+        <v>0.0002659857246346879</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002820134414798804</v>
+        <v>0.0002820134414798807</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003912234158758616</v>
+        <v>0.0003912234158758626</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004366213731852042</v>
+        <v>0.000436621373185205</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0005847446702435199</v>
+        <v>0.0005847446702435206</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003302240282170273</v>
+        <v>0.0003302240282170284</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000126931678655841</v>
+        <v>0.0001269316786558412</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003097918498241596</v>
+        <v>0.0003097918498241609</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001118857309218605</v>
+        <v>0.0001118857309218608</v>
       </c>
       <c r="R5" t="n">
-        <v>6.694750517828638e-05</v>
+        <v>6.694750517828665e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000324493596922472</v>
+        <v>0.000324493596922473</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001951537672064544</v>
+        <v>0.0001951537672064549</v>
       </c>
       <c r="U5" t="n">
         <v>0.0003476262491517078</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003154349845386896</v>
+        <v>0.0003154349845386898</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001886754135937091</v>
+        <v>0.0001886754135937087</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0007028483513076078</v>
+        <v>0.0007028483513076091</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006108290956789589</v>
+        <v>0.0006108290956789612</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000232818074572165</v>
+        <v>0.0002328180745721649</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002789509428330164</v>
+        <v>0.0002789509428330174</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007995096723928132</v>
+        <v>0.0007995096723928157</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.778916005021912e-05</v>
+        <v>5.085660861713667e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.136487588202413e-05</v>
+        <v>1.136487588202412e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.371600873310187e-05</v>
+        <v>2.371600873310189e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.352729116119497e-05</v>
+        <v>1.659473972811256e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.868147414902813e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.318775305831742e-05</v>
+        <v>2.625520162523497e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.353497044612204e-05</v>
+        <v>1.046752187920445e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.374290162846669e-05</v>
+        <v>2.37429016284667e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.599590031904868e-05</v>
+        <v>2.906334888596626e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.58973148216327e-05</v>
+        <v>3.589731482163276e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.517645858941565e-05</v>
+        <v>3.824390715633329e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.168278699986873e-05</v>
+        <v>4.168278699986867e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.306137171226072e-05</v>
+        <v>1.306137171226067e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.732284320876793e-05</v>
+        <v>2.034435117048261e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.184700839732305e-05</v>
+        <v>2.869782291458505e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.880063570707296e-05</v>
+        <v>1.880063570707297e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59729349985928e-05</v>
+        <v>1.597293499859281e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.212742507538291e-05</v>
+        <v>3.212742507538293e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.982189315635891e-05</v>
+        <v>2.288934172327653e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.344464857024903e-05</v>
+        <v>3.03772000033315e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>3.239794580660112e-05</v>
+        <v>2.933049723968348e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.307414194959237e-05</v>
+        <v>2.307414194959234e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.908715440959185e-05</v>
+        <v>4.90871544095919e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.353456678474828e-05</v>
+        <v>4.353456678474836e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>2.777246797776678e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.80272515933307e-05</v>
+        <v>2.802725159333073e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.097468479480463e-05</v>
+        <v>5.097468479480461e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4472,79 +4472,79 @@
         <v>1.374122981271971e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.609236266379745e-05</v>
+        <v>2.609236266379746e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.590364509189057e-05</v>
+        <v>1.590364509189056e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.105782807972373e-05</v>
+        <v>2.105782807972372e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.556410698901301e-05</v>
+        <v>2.556410698901298e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.284387580990005e-05</v>
+        <v>1.284387580990004e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.611925555916227e-05</v>
+        <v>2.611925555916231e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.837225424974426e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.520622018541072e-05</v>
+        <v>3.520622018541075e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.755281252011127e-05</v>
+        <v>3.75528125201113e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.405914093056426e-05</v>
+        <v>4.40591409305643e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.535133299934701e-05</v>
+        <v>1.535133299934702e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.961134366047678e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.111352222111798e-05</v>
+        <v>3.111352222111807e-05</v>
       </c>
       <c r="Q7" t="n">
         <v>1.810954107085098e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.528184036237082e-05</v>
+        <v>1.528184036237081e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.143633043916091e-05</v>
+        <v>3.143633043916092e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.219824708705448e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.277437831785956e-05</v>
+        <v>3.277437831785958e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>3.17068511703791e-05</v>
+        <v>3.170685117037908e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.234272512328239e-05</v>
+        <v>2.234272512328236e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.146350834028739e-05</v>
+        <v>5.146350834028742e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.571202937405331e-05</v>
+        <v>4.571202937405339e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.708137334154479e-05</v>
+        <v>2.708137334154476e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.733615695710868e-05</v>
+        <v>2.733615695710871e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.3143634362766e-05</v>
+        <v>5.314363436276605e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.742196723043304e-05</v>
+        <v>5.742196723043299e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.85392361166185e-05</v>
+        <v>2.853923611661845e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.089036896769627e-05</v>
+        <v>4.089036896769626e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.070165139578935e-05</v>
+        <v>2.668599685621057e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.948916715514232e-05</v>
+        <v>2.94891671551423e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.036211329291183e-05</v>
+        <v>4.192590344740938e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.764188211379884e-05</v>
+        <v>2.764188211379881e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.091726186306108e-05</v>
+        <v>4.091726186306109e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.317026055364303e-05</v>
+        <v>4.317026055364301e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.000422648930958e-05</v>
+        <v>5.000422648930963e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.235081882401009e-05</v>
+        <v>5.235081882401002e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>5.885714723446308e-05</v>
+        <v>5.885714723446381e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.430337401180061e-05</v>
+        <v>2.430337401180059e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.017136753014549e-05</v>
+        <v>3.017136753014546e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.127974872421513e-05</v>
+        <v>4.127974872421515e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.388390701760985e-05</v>
+        <v>2.388390701760986e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.007984666626962e-05</v>
+        <v>3.007984666626958e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.623433674305971e-05</v>
+        <v>4.623433674305972e-05</v>
       </c>
       <c r="T8" t="n">
         <v>3.699625339095328e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.292709790882226e-05</v>
+        <v>4.388789934597475e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>4.650485747427794e-05</v>
+        <v>4.446268616540838e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.714221355859333e-05</v>
+        <v>3.714221355859329e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.792907260985862e-05</v>
+        <v>5.792907260985865e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.803797502010689e-05</v>
+        <v>6.803797502010706e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.187937964544357e-05</v>
+        <v>3.419773837123226e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.21341632610075e-05</v>
+        <v>4.213416326100749e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.581942344649992e-05</v>
+        <v>7.581942344649987e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4645,82 +4645,82 @@
         <v>6.262724593755582e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.092499815242703e-05</v>
+        <v>3.092499815242699e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.32761310035048e-05</v>
+        <v>4.327613100350481e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.308741343159785e-05</v>
+        <v>3.199758489792756e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.824159641943106e-05</v>
+        <v>2.735601684029486e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.274787532872027e-05</v>
+        <v>4.274787299216225e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.002764414960737e-05</v>
+        <v>3.002764414960732e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.330302389886962e-05</v>
+        <v>4.330302389886958e-05</v>
       </c>
       <c r="J9" t="n">
         <v>4.555602258945152e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.238998852511809e-05</v>
+        <v>5.238998852511812e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.473658085981861e-05</v>
+        <v>5.473658085981858e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>6.124290927027158e-05</v>
+        <v>6.124290927027155e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.253510133905427e-05</v>
+        <v>3.253510133905425e-05</v>
       </c>
       <c r="O9" t="n">
         <v>3.836144639906147e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.020395861919869e-05</v>
+        <v>5.020395861919874e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.529330707400028e-05</v>
+        <v>3.529330707400031e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.246560870207814e-05</v>
+        <v>3.24656087020781e-05</v>
       </c>
       <c r="S9" t="n">
         <v>4.862009877886824e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.938201542676176e-05</v>
+        <v>3.938201542676181e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.993732227373432e-05</v>
+        <v>4.993732227373439e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.889061951008635e-05</v>
+        <v>5.433973918989052e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.952649346298973e-05</v>
+        <v>3.95264934629897e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>6.864727667999472e-05</v>
+        <v>6.864727667999481e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.289579771376062e-05</v>
+        <v>6.289579771376063e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.426514168125206e-05</v>
+        <v>4.141817271430109e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.451992529681593e-05</v>
+        <v>4.451992529681603e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.032740270247326e-05</v>
+        <v>7.032740270247334e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.089292761348081e-06</v>
+        <v>5.089292761348188e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.737834981561719e-06</v>
+        <v>4.737834981561714e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.734433454471906e-06</v>
+        <v>4.734433454471914e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.70941011275921e-06</v>
+        <v>4.709410112759249e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.696301861928403e-06</v>
+        <v>4.6963018619284e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.08055221288097e-06</v>
+        <v>5.080552212880991e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.708841957775537e-06</v>
+        <v>4.708841957775566e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.719399502876159e-06</v>
+        <v>4.719399502876174e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.025365103298258e-06</v>
+        <v>5.025365103298248e-06</v>
       </c>
       <c r="K2" t="n">
         <v>4.950245067021829e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.193054297939878e-06</v>
+        <v>5.193054297939889e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.711732322648369e-06</v>
+        <v>5.711732322648366e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.692708390621753e-06</v>
+        <v>4.692708390621767e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.470619037852123e-06</v>
+        <v>6.47061903785215e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.013415896480531e-06</v>
+        <v>5.013415896480517e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.709068477022115e-06</v>
+        <v>4.709068477022159e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.679481670186305e-06</v>
+        <v>4.679481670186284e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.918883170763409e-06</v>
+        <v>4.91888317076337e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.721414596513894e-06</v>
+        <v>4.72141459651391e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.396934165723361e-06</v>
+        <v>7.396934165723407e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.809625685881579e-06</v>
+        <v>4.809625685881586e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.117584700838649e-06</v>
+        <v>7.117584700838742e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.027616161442853e-06</v>
+        <v>5.027616161442937e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.779364805489477e-06</v>
+        <v>4.779364805489478e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.789905428445356e-06</v>
+        <v>5.789905428445306e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.329613423253043e-06</v>
+        <v>5.329613423253054e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.998691190693212e-06</v>
+        <v>5.99869119069321e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4977,79 +4977,79 @@
         <v>7.472818922690752e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589574394082224e-06</v>
+        <v>4.58957439408222e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.955727162066086e-06</v>
+        <v>4.955727162066049e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.768715358707499e-06</v>
+        <v>4.768715358707486e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.684149959888747e-06</v>
+        <v>4.684149959888721e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.406459307103145e-06</v>
+        <v>7.406459307103193e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.77403681801773e-06</v>
+        <v>4.774036818017667e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.848463206361597e-06</v>
+        <v>4.848463206361554e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.021431921828251e-06</v>
+        <v>7.021431921828343e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.493425232658823e-06</v>
+        <v>6.493425232658951e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.208164254335172e-06</v>
+        <v>8.208164254335155e-06</v>
       </c>
       <c r="M3" t="n">
         <v>1.189830532611668e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.656759961156653e-06</v>
+        <v>4.65675996115663e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.906605313015066e-06</v>
+        <v>7.906605313015086e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>6.935334557943863e-06</v>
+        <v>6.935334557943869e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.774206516331122e-06</v>
+        <v>4.77420651633107e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.562231619742139e-06</v>
+        <v>4.562231619742166e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>6.258308650045612e-06</v>
+        <v>6.258308650045614e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.864354666371373e-06</v>
+        <v>4.864354666371372e-06</v>
       </c>
       <c r="U3" t="n">
         <v>1.408801355396025e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.488137499628084e-06</v>
+        <v>5.488137499628221e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.102486119362469e-05</v>
+        <v>1.102486119362486e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>7.050502246552383e-06</v>
+        <v>7.050502246552398e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.275127893790866e-06</v>
+        <v>5.275127893790904e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.798839280146175e-06</v>
+        <v>7.798839280146233e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.202171023050701e-06</v>
+        <v>9.202171023050689e-06</v>
       </c>
       <c r="AB3" t="n">
         <v>1.392526212712498e-05</v>
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.945482799370729e-06</v>
+        <v>9.945482799370734e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.171830359021039e-06</v>
+        <v>5.171830359021037e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.937183684857872e-06</v>
+        <v>5.937183684857874e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.654533528906915e-06</v>
+        <v>5.654533528906916e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.506469805679699e-06</v>
+        <v>5.506469805679702e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>9.84675428358355e-06</v>
+        <v>9.846754283583561e-06</v>
       </c>
       <c r="H4" t="n">
         <v>5.648115957002743e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.767368285624993e-06</v>
+        <v>5.767368285624997e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.206868881627823e-06</v>
+        <v>9.206868881627827e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>8.374875126855969e-06</v>
+        <v>8.374875126855966e-06</v>
       </c>
       <c r="L4" t="n">
         <v>1.111751708783981e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.693989470690395e-05</v>
+        <v>1.693989470690397e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>5.465879894192705e-06</v>
+        <v>5.465879894192703e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>6.118572434829754e-06</v>
+        <v>6.118572434829759e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>9.088418705608981e-06</v>
+        <v>9.088418705608993e-06</v>
       </c>
       <c r="Q4" t="n">
         <v>5.650674596096666e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>5.316478002281974e-06</v>
+        <v>5.316478002281976e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.020628081431473e-06</v>
+        <v>8.020628081431471e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.790129695251503e-06</v>
+        <v>5.790129695251502e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.568513041288385e-05</v>
+        <v>1.568513041288386e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.679465207845615e-06</v>
+        <v>6.679465207845605e-06</v>
       </c>
       <c r="W4" t="n">
         <v>1.033660916543112e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>9.248817230802948e-06</v>
+        <v>9.248817230802949e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.401251821234045e-06</v>
+        <v>6.401251821234052e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.227440992891472e-06</v>
+        <v>8.227440992891477e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.266001522855336e-05</v>
+        <v>1.266001522855337e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.00621952175618e-05</v>
+        <v>2.006219521756181e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5150,79 +5150,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.492282711617946e-05</v>
+        <v>9.492282711617953e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.352047888102729e-05</v>
+        <v>1.352047888102726e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.778624123324339e-05</v>
+        <v>2.778624123324341e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.775969212560032e-05</v>
+        <v>1.775969212560033e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.995928145600868e-05</v>
+        <v>1.995928145600874e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>9.084376782035925e-05</v>
+        <v>9.084376782035946e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.285306068613565e-05</v>
+        <v>2.285306068613566e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.459435617963639e-05</v>
+        <v>2.459435617963642e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.396033643034412e-05</v>
+        <v>8.396033643034414e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.245403570075697e-05</v>
+        <v>7.245403570075695e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001141882510933549</v>
+        <v>0.000114188251093355</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002287534442026704</v>
+        <v>0.0002287534442026707</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001917999752871849</v>
+        <v>0.000191799975287185</v>
       </c>
       <c r="O5" t="n">
-        <v>2.948233306548235e-05</v>
+        <v>2.948233306548236e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>8.097140503845898e-05</v>
+        <v>8.097140503845915e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.209669753636666e-05</v>
+        <v>2.209669753636667e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53259325974657e-05</v>
+        <v>1.532593259746568e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>5.947969615338193e-05</v>
+        <v>5.947969615338191e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.586431434536845e-05</v>
+        <v>2.586431434536843e-05</v>
       </c>
       <c r="U5" t="n">
         <v>0.0002020626779486856</v>
       </c>
       <c r="V5" t="n">
-        <v>4.13799690413798e-05</v>
+        <v>4.137996904137931e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001101040188699919</v>
+        <v>0.0001101040188699918</v>
       </c>
       <c r="X5" t="n">
-        <v>9.169005656016807e-05</v>
+        <v>9.169005656016815e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.667242426452555e-05</v>
+        <v>3.667242426452552e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.466754400720495e-05</v>
+        <v>6.466754400720488e-05</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0001541304897869441</v>
@@ -5241,79 +5241,79 @@
         <v>1.048218251356778e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>7.849092766289214e-06</v>
+        <v>7.849092766289217e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>8.61444609212604e-06</v>
+        <v>6.473883399054905e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>8.331795936175094e-06</v>
+        <v>6.191233243103958e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>8.183732212947874e-06</v>
+        <v>8.183732212947886e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.03834539977806e-05</v>
+        <v>1.252401669085172e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>6.184815671199786e-06</v>
+        <v>6.184815671199781e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>8.44463069289317e-06</v>
+        <v>6.304067999822044e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.743568595824859e-06</v>
+        <v>9.743568595824868e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.105213753412415e-05</v>
+        <v>8.911574841053015e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3794779495108e-05</v>
+        <v>1.165421680203685e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.747659442110101e-05</v>
+        <v>1.961715711417216e-05</v>
       </c>
       <c r="N6" t="n">
         <v>6.020091165137454e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>8.79019279862277e-06</v>
+        <v>8.790192798622818e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.176014830898803e-05</v>
+        <v>9.579893184709846e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.327937003364847e-06</v>
+        <v>8.327937003364848e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>7.993740409550148e-06</v>
+        <v>5.853177716479012e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.069789048869964e-05</v>
+        <v>8.5573277956285e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.326829409448542e-06</v>
+        <v>8.467392102519683e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.840584496296176e-05</v>
+        <v>1.626528226989064e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>7.216164922042656e-06</v>
+        <v>9.356727615113793e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.095600674617015e-05</v>
+        <v>1.095600674617009e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>9.785516944999992e-06</v>
+        <v>9.78551694499999e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.040791939347788e-06</v>
+        <v>7.040791939347785e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.764140707088504e-06</v>
+        <v>1.090470340015966e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.31967149427504e-05</v>
+        <v>1.533727763582156e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>2.068588066092738e-05</v>
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.288090954951393e-05</v>
+        <v>1.288090954951394e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.107257109164248e-06</v>
+        <v>8.107257109164249e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.872610435001064e-06</v>
+        <v>8.872610435001071e-06</v>
       </c>
       <c r="E7" t="n">
         <v>8.589960279050124e-06</v>
@@ -5344,7 +5344,7 @@
         <v>1.278218103372676e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.583542707145947e-06</v>
+        <v>8.583542707145949e-06</v>
       </c>
       <c r="I7" t="n">
         <v>8.702795035768206e-06</v>
@@ -5356,7 +5356,7 @@
         <v>1.131030187699918e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.405294383798302e-05</v>
+        <v>1.405294383798303e-05</v>
       </c>
       <c r="M7" t="n">
         <v>1.987532145704718e-05</v>
@@ -5365,46 +5365,46 @@
         <v>8.401306644335908e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>9.052466448378838e-06</v>
+        <v>9.052466448378836e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.202231271915806e-05</v>
+        <v>1.202231271915809e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.586101346239872e-06</v>
+        <v>8.586101346239879e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>8.251904752425187e-06</v>
+        <v>8.25190475242518e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.095605483157468e-05</v>
+        <v>1.095605483157469e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>8.72555644539469e-06</v>
+        <v>8.725556445394701e-06</v>
       </c>
       <c r="U7" t="n">
         <v>1.866679556290241e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.614891957988804e-06</v>
+        <v>9.614891957988802e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.327203591557432e-05</v>
+        <v>1.327203591557433e-05</v>
       </c>
       <c r="X7" t="n">
         <v>1.218424398094615e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.380130714186996e-06</v>
+        <v>9.380130714187001e-06</v>
       </c>
       <c r="Z7" t="n">
         <v>1.116286774303468e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.559544197869657e-05</v>
+        <v>1.559544197869658e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.299762196770503e-05</v>
+        <v>2.299762196770502e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,52 +5414,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.980994672696785e-05</v>
+        <v>1.980994672696786e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.166363354254289e-05</v>
+        <v>2.166363354254288e-05</v>
       </c>
       <c r="D8" t="n">
         <v>2.242898686837973e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.214633671242878e-05</v>
+        <v>1.861747405284762e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.640339573406393e-05</v>
+        <v>1.640339573406394e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.63385574671054e-05</v>
+        <v>2.771277943496011e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.21399191405246e-05</v>
+        <v>2.213991914052458e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.225917146914685e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.569867206514969e-05</v>
+        <v>2.569867206514968e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.486667831037783e-05</v>
+        <v>2.48666783103778e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.760932027136167e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.343169789042581e-05</v>
+        <v>3.343169789042635e-05</v>
       </c>
       <c r="N8" t="n">
         <v>1.682038642479777e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.888485269229725e-05</v>
+        <v>1.888485269229724e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.150863910936044e-05</v>
+        <v>2.150863910936043e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.421271509816636e-05</v>
+        <v>1.421271509816635e-05</v>
       </c>
       <c r="R8" t="n">
         <v>2.180828118580382e-05</v>
@@ -5468,25 +5468,25 @@
         <v>2.451243126495334e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.228193287877335e-05</v>
+        <v>2.228193287877332e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.814540912502149e-05</v>
+        <v>2.898901701684458e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.317126839136748e-05</v>
+        <v>2.136360841367004e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.682971481147443e-05</v>
+        <v>2.682971481147444e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.841826654467824e-05</v>
+        <v>1.841826654467822e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.953164566017624e-05</v>
+        <v>2.953164566017619e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.471924417641332e-05</v>
+        <v>1.796879869130421e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>2.915181841207521e-05</v>
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.420048659071589e-05</v>
+        <v>2.420048659071591e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.352563469650713e-05</v>
+        <v>2.352563469650714e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.429098802234391e-05</v>
+        <v>2.429098802234396e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.400833786639299e-05</v>
+        <v>2.306235028767117e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.386027414316576e-05</v>
+        <v>1.44114221353324e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82005586210696e-05</v>
+        <v>2.820055715023685e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.400192029448881e-05</v>
+        <v>2.400192029448884e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.412117262311108e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.756067321911391e-05</v>
+        <v>2.756067321911389e-05</v>
       </c>
       <c r="K9" t="n">
         <v>2.672867946434204e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.947132142532589e-05</v>
+        <v>2.947132142532591e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.529369904439004e-05</v>
+        <v>3.529369904439006e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.381968423167878e-05</v>
+        <v>2.381968423167879e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.583071194814273e-05</v>
+        <v>2.583071194814277e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.909597313441958e-05</v>
+        <v>2.90959731344196e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.400447746274995e-05</v>
+        <v>2.400447746274996e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.367028233976806e-05</v>
+        <v>2.367028233976807e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.637443241891754e-05</v>
+        <v>2.637443241891755e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41439340327376e-05</v>
+        <v>2.414393403273761e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.408238689317966e-05</v>
+        <v>3.408238689317967e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.503326954533167e-05</v>
+        <v>2.976319266423594e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.869041350291718e-05</v>
+        <v>2.869041350291719e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.760262156828903e-05</v>
+        <v>2.760262156828904e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.479850830152988e-05</v>
+        <v>2.479850830152989e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.658124533037752e-05</v>
+        <v>2.411003249656928e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.101381956603944e-05</v>
+        <v>3.101381956603945e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.841599955504788e-05</v>
+        <v>3.841599955504791e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.211895170389875e-06</v>
+        <v>4.211895170389907e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.289512637492533e-06</v>
+        <v>4.289512637492529e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.198490328154581e-06</v>
+        <v>4.198490328154577e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.216973042837278e-06</v>
+        <v>4.216973042837258e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.220429940034714e-06</v>
+        <v>4.220429940034696e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.285831996102313e-06</v>
+        <v>4.2858319961023e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.201908346180465e-06</v>
+        <v>4.201908346180449e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.264400935585939e-06</v>
+        <v>4.26440093558596e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.281443961703797e-06</v>
+        <v>4.281443961703889e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.361382008081115e-06</v>
+        <v>4.361382008081133e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.273113076395254e-06</v>
+        <v>4.273113076395191e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.282899056472552e-06</v>
+        <v>4.282899056472555e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.197694588652192e-06</v>
+        <v>4.197694588652183e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.730199253183518e-06</v>
+        <v>5.730199253183512e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.189305035861007e-06</v>
+        <v>4.189305035860991e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.201315630132962e-06</v>
+        <v>4.201315630132945e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.212518902294871e-06</v>
+        <v>4.212518902294861e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.359906489940404e-06</v>
+        <v>4.359906489940381e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.196556850296557e-06</v>
+        <v>4.196556850296536e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.960533814192223e-06</v>
+        <v>5.960533814192277e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.261422667415853e-06</v>
+        <v>4.261422667415836e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.227716935017518e-06</v>
+        <v>6.227716935017444e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.199206341553947e-06</v>
+        <v>5.199206341553936e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.648013552484867e-06</v>
+        <v>4.648013552484942e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.97699899679403e-06</v>
+        <v>4.976998996794055e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.365651800053432e-06</v>
+        <v>4.36565180005341e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.271550666604341e-06</v>
+        <v>4.271550666604337e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.261765736359874e-06</v>
+        <v>4.261765736359868e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.346353726875074e-06</v>
+        <v>4.346353726875069e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.170430423773905e-06</v>
+        <v>4.170430423773891e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.29218614667532e-06</v>
+        <v>4.292186146675311e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.325751293678798e-06</v>
+        <v>4.325751293678808e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.789751318676061e-06</v>
+        <v>4.789751318676074e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193319492335154e-06</v>
+        <v>4.19331949233518e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.63986474967061e-06</v>
+        <v>4.639864749670597e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.759081692670723e-06</v>
+        <v>4.759081692670715e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.329712554493656e-06</v>
+        <v>5.329712554493665e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.702016772653988e-06</v>
+        <v>4.702016772653877e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.800727219529946e-06</v>
+        <v>4.800727219529943e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.161911454779935e-06</v>
+        <v>4.161911454779946e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.786776647222625e-06</v>
+        <v>6.78677664722263e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.101302888821542e-06</v>
+        <v>4.101302888821566e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.189984760482016e-06</v>
+        <v>4.189984760482014e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.268980682508435e-06</v>
+        <v>4.268980682508446e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.31160407812601e-06</v>
+        <v>5.311604078126004e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.15699386979607e-06</v>
+        <v>4.156993869796065e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.626089147944818e-06</v>
+        <v>7.626089147944829e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.616188787636688e-06</v>
+        <v>4.616188787636633e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.430799706305355e-06</v>
+        <v>8.430799706305358e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.129729635358904e-05</v>
+        <v>1.129729635358905e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.375561008647431e-06</v>
+        <v>7.375561008647443e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.687512782088592e-06</v>
+        <v>5.687512782088656e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.359630187172795e-06</v>
+        <v>5.359630187172789e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.69542769201898e-06</v>
+        <v>4.695427692018974e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.677936790621031e-06</v>
+        <v>4.677936790621035e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.585270229814227e-06</v>
+        <v>4.585270229814222e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.526522931041338e-06</v>
+        <v>4.526522931041345e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.73529369585121e-06</v>
+        <v>4.735293695851194e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.774340939947595e-06</v>
+        <v>4.7743409399476e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.513087249663314e-06</v>
+        <v>5.513087249663307e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.565131017009673e-06</v>
+        <v>4.565131017009668e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.271013562356164e-06</v>
+        <v>5.271013562356161e-06</v>
       </c>
       <c r="J4" t="n">
         <v>5.448232272830368e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.366459389686725e-06</v>
+        <v>6.366459389686711e-06</v>
       </c>
       <c r="L4" t="n">
         <v>5.369421200579955e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.528828049225979e-06</v>
+        <v>5.52882804922597e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.51753468730362e-06</v>
+        <v>4.517534687303623e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.713535727629249e-06</v>
+        <v>4.713535727629254e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.422770829142293e-06</v>
+        <v>4.422770829142294e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.558436016590391e-06</v>
+        <v>4.558436016590395e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.684982129418886e-06</v>
+        <v>4.684982129418878e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>6.349792733515253e-06</v>
+        <v>6.349792733515239e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.504683409191211e-06</v>
+        <v>4.504683409191204e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.647182456088509e-06</v>
+        <v>5.647182456088498e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.138649674705134e-06</v>
+        <v>5.138649674705156e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>6.412319120667842e-06</v>
+        <v>6.412319120667839e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.583007065449729e-05</v>
+        <v>1.58300706544973e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.592470091959075e-06</v>
+        <v>9.592470091959077e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.012907083283797e-06</v>
+        <v>5.012907083283785e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.414688654215133e-06</v>
+        <v>6.414688654215122e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.358254697396607e-06</v>
+        <v>5.358254697396609e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.566830070257944e-05</v>
+        <v>1.566830070257945e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.602849887051892e-05</v>
+        <v>1.602849887051891e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.523717109972124e-05</v>
+        <v>1.523717109972123e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.366636407907827e-05</v>
+        <v>1.36663640790783e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.896560258177869e-05</v>
+        <v>1.896560258177868e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.059207244579746e-05</v>
+        <v>3.059207244579743e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.513983337775537e-05</v>
+        <v>1.513983337775536e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.790050188859846e-05</v>
+        <v>2.790050188859847e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.003595248337461e-05</v>
+        <v>3.003595248337458e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.607768062297753e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.962703186852057e-05</v>
+        <v>2.962703186852058e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.364637010808658e-05</v>
+        <v>3.364637010808659e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.208631045778382e-05</v>
+        <v>3.208631045778381e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.70654964133642e-05</v>
+        <v>1.706549641336417e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.155122890193219e-05</v>
+        <v>1.155122890193218e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.548549773070411e-05</v>
+        <v>1.54854977307041e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.722494035872658e-05</v>
+        <v>1.72249403587266e-05</v>
       </c>
       <c r="S5" t="n">
         <v>4.185598852339225e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.503890149617252e-05</v>
+        <v>1.50389014961725e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.322758267536139e-05</v>
+        <v>3.322758267536137e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>2.595272496213135e-05</v>
+        <v>2.595272496213185e-05</v>
       </c>
       <c r="W5" t="n">
         <v>4.589636284184869e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002072332613102457</v>
+        <v>0.0002072332613102456</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0001034156566184019</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.164630555256647e-05</v>
+        <v>2.164630555256648e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.664251752958666e-05</v>
+        <v>4.664251752958661e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.996865031026092e-05</v>
+        <v>2.99686503102609e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.093438779165885e-06</v>
+        <v>5.093438779165886e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.692100794168443e-06</v>
+        <v>5.000772218359072e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.942024919586197e-06</v>
+        <v>4.942024919586181e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.842124260205425e-06</v>
+        <v>6.842124260205419e-06</v>
       </c>
       <c r="F6" t="n">
         <v>6.881171504301814e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.619917814017529e-06</v>
+        <v>5.928589238208162e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.671961581363894e-06</v>
+        <v>4.980633005554522e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.686515550901016e-06</v>
+        <v>5.686515550901018e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.555062837184591e-06</v>
+        <v>5.863734261375218e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>6.781961378231575e-06</v>
+        <v>6.781961378231582e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.476251764934171e-06</v>
+        <v>7.476251764934156e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>5.944330037770829e-06</v>
+        <v>7.63565861358019e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.936930701968407e-06</v>
+        <v>4.9369307019684e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>5.132931742294036e-06</v>
+        <v>5.132931742294043e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>6.524243110865132e-06</v>
+        <v>4.792521226801114e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.665266580944619e-06</v>
+        <v>4.973938005135254e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>6.791812693773104e-06</v>
+        <v>6.791812693773097e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>8.456623297869467e-06</v>
+        <v>6.765294722060109e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.611513973545437e-06</v>
+        <v>6.611513973545436e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>6.074308893426052e-06</v>
+        <v>6.074308893426057e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>5.554151663250017e-06</v>
+        <v>7.24548023905937e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.880660372410656e-06</v>
+        <v>6.880660372410648e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.624557264304214e-05</v>
+        <v>1.624557264304215e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.006110847486692e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.119737647638012e-06</v>
+        <v>7.119737647638011e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.830190642759981e-06</v>
+        <v>8.521519218569344e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.778616111259459e-06</v>
+        <v>5.778616111259443e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.173388345420238e-06</v>
+        <v>7.173388345420223e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.080721784613418e-06</v>
+        <v>7.080721784613416e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.021974485840545e-06</v>
+        <v>7.021974485840533e-06</v>
       </c>
       <c r="E7" t="n">
         <v>7.230745250650406e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.269792494746789e-06</v>
+        <v>7.269792494746795e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>8.00853880446251e-06</v>
+        <v>8.008538804462503e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.060582571808873e-06</v>
+        <v>7.060582571808859e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.766465117155362e-06</v>
+        <v>7.76646511715535e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.943683827629567e-06</v>
+        <v>7.94368382762956e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>8.861910944485926e-06</v>
+        <v>8.861910944485929e-06</v>
       </c>
       <c r="L7" t="n">
         <v>7.864872755379147e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>8.024279604025166e-06</v>
+        <v>8.024279604025179e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>7.012986242102818e-06</v>
+        <v>7.012986242102822e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>7.207560105617291e-06</v>
+        <v>7.207560105617281e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.916795207130331e-06</v>
+        <v>6.916795207130317e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.053887571389585e-06</v>
+        <v>7.053887571389586e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.180433684218082e-06</v>
+        <v>7.18043368421808e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>8.845244288314442e-06</v>
+        <v>8.84524428831444e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>7.000134963990412e-06</v>
+        <v>7.000134963990419e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>8.159913488938776e-06</v>
+        <v>8.159913488938747e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.634101229504361e-06</v>
+        <v>7.634101229504342e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.907770675467046e-06</v>
+        <v>8.907770675467031e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.832552220929649e-05</v>
+        <v>1.832552220929651e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.209954609555095e-05</v>
+        <v>1.209954609555096e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.508358638082992e-06</v>
+        <v>7.508358638082994e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.910140209014322e-06</v>
+        <v>8.910140209014329e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.853706252195815e-06</v>
+        <v>7.853706252195817e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.341220418463463e-05</v>
+        <v>1.341220418463465e-05</v>
       </c>
       <c r="C8" t="n">
         <v>1.916025697669329e-05</v>
@@ -6283,13 +6283,13 @@
         <v>1.910150967792041e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.931028044273027e-05</v>
+        <v>1.620026967770782e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.441852414725943e-05</v>
+        <v>1.441852414725944e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.008807399654238e-05</v>
+        <v>2.129918520313722e-05</v>
       </c>
       <c r="H8" t="n">
         <v>1.914011776388874e-05</v>
@@ -6298,7 +6298,7 @@
         <v>1.984600030923524e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.002321901970946e-05</v>
+        <v>2.002321901970945e-05</v>
       </c>
       <c r="K8" t="n">
         <v>2.094144613656581e-05</v>
@@ -6307,52 +6307,52 @@
         <v>1.994440794745904e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.010381479610507e-05</v>
+        <v>2.010381479610631e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.456498680475324e-05</v>
+        <v>1.456498680475323e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.600519367336525e-05</v>
+        <v>1.600519367336526e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.540944386211633e-05</v>
+        <v>1.540944386211631e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.214486874976972e-05</v>
+        <v>1.214486874976973e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.925996887629796e-05</v>
+        <v>1.925996887629798e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.092477948039434e-05</v>
+        <v>2.092477948039435e-05</v>
       </c>
       <c r="T8" t="n">
         <v>1.90796701560703e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.664487273217682e-05</v>
+        <v>1.738850502690389e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.971363642158422e-05</v>
+        <v>1.812333344968966e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.09884537366269e-05</v>
+        <v>2.098845373662691e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.395181692227517e-05</v>
+        <v>2.395181692227518e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.999576488487244e-05</v>
+        <v>2.999576488487245e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.958789383016287e-05</v>
+        <v>1.363868011666819e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>2.09896754010942e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.603436120167771e-05</v>
+        <v>2.60343612016777e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.598661576761663e-05</v>
+        <v>1.598661576761661e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.91481094336963e-05</v>
+        <v>1.914810943369627e-05</v>
       </c>
       <c r="D9" t="n">
         <v>1.908936213492341e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.929813289973329e-05</v>
+        <v>1.854708617849833e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.933718014382968e-05</v>
+        <v>1.183545236121039e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.007592645354541e-05</v>
+        <v>2.007592669490816e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.912797022089175e-05</v>
+        <v>1.912797022089173e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.983385276623825e-05</v>
+        <v>1.983385276623822e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.001107147671244e-05</v>
+        <v>2.001107147671242e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.092929859356882e-05</v>
+        <v>2.092929859356877e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.993226040446203e-05</v>
+        <v>1.993226040446202e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.009166725310806e-05</v>
+        <v>2.009166725310804e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.908037389118571e-05</v>
+        <v>1.908037389118569e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.035479969111287e-05</v>
+        <v>2.035479969111286e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.029857362267659e-05</v>
+        <v>2.029857362267657e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.912127546183525e-05</v>
+        <v>1.912127546183519e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.924782133330097e-05</v>
+        <v>1.924782133330095e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.091263193739733e-05</v>
+        <v>2.091263193739728e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.906752261307328e-05</v>
+        <v>1.906752261307326e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.022164610876329e-05</v>
+        <v>2.022164610876325e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.970148887858724e-05</v>
+        <v>2.345672015313036e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.097515832454993e-05</v>
+        <v>2.097515832454991e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.039290985837939e-05</v>
+        <v>3.039290985837937e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.416693374463386e-05</v>
+        <v>2.416693374463382e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.957574628716588e-05</v>
+        <v>1.761377713741415e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.09775278580972e-05</v>
+        <v>2.097752785809719e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.99210939012787e-05</v>
+        <v>1.992109390127867e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.216218655853979e-06</v>
+        <v>4.216218655853996e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.287332005552976e-06</v>
+        <v>4.287332005552973e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.257840556959057e-06</v>
+        <v>4.257840556959071e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.192111041559471e-06</v>
+        <v>4.192111041559494e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.211746259541674e-06</v>
+        <v>4.211746259541695e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.219786319587913e-06</v>
+        <v>4.219786319587942e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.194427085871382e-06</v>
+        <v>4.194427085871399e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.276918820554733e-06</v>
+        <v>4.276918820554761e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.254950911603526e-06</v>
+        <v>4.254950911603523e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.442727139144226e-06</v>
+        <v>4.442727139144251e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.237518137341514e-06</v>
+        <v>4.237518137341535e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.274000140136311e-06</v>
+        <v>4.274000140136304e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.188850084588793e-06</v>
+        <v>4.188850084588814e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.728591906008458e-06</v>
+        <v>5.72859190600848e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.1850796334683e-06</v>
+        <v>4.185079633468325e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.206371825096474e-06</v>
+        <v>4.206371825096488e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.213185711138885e-06</v>
+        <v>4.213185711138891e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.307898143158634e-06</v>
+        <v>4.307898143158666e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.206675232098093e-06</v>
+        <v>4.206675232098101e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.001124574309807e-06</v>
+        <v>6.00112457430981e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.298054344001896e-06</v>
+        <v>4.298054344001912e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.118829811974379e-06</v>
+        <v>6.118829811974348e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.271567950204506e-06</v>
+        <v>5.2715679502045e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.509206662696883e-06</v>
+        <v>4.509206662696901e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.960163655585583e-06</v>
+        <v>4.960163655585603e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.268635647118392e-06</v>
+        <v>4.2686356471184e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.402821191080135e-06</v>
+        <v>4.402821191080134e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.348238343962049e-06</v>
+        <v>4.348238343962035e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.370974796449373e-06</v>
+        <v>4.370974796449374e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.648512215915056e-06</v>
+        <v>4.648512215915032e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.172899337173322e-06</v>
+        <v>4.172899337173309e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.319057423653733e-06</v>
+        <v>4.319057423653731e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.375995366696565e-06</v>
+        <v>4.375995366696579e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19607351132743e-06</v>
+        <v>4.196073511327417e-06</v>
       </c>
       <c r="I3" t="n">
         <v>4.78493182750132e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.626297435387221e-06</v>
+        <v>4.626297435387198e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.965184354843434e-06</v>
+        <v>5.965184354843428e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.50405270918767e-06</v>
+        <v>4.504052709187681e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.790555050890998e-06</v>
+        <v>4.790555050891002e-06</v>
       </c>
       <c r="N3" t="n">
         <v>4.15398396153111e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.80386182703605e-06</v>
+        <v>6.803861827036049e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.127895491073207e-06</v>
+        <v>4.127895491073216e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.28018576674918e-06</v>
+        <v>4.280185766749181e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.329134069386594e-06</v>
+        <v>4.329134069386588e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>4.999744331227243e-06</v>
+        <v>4.999744331227262e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.283115187081146e-06</v>
+        <v>4.28311518708115e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.838778397780858e-06</v>
+        <v>7.838778397780845e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.930872558887081e-06</v>
+        <v>4.930872558887111e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.600619178834657e-06</v>
+        <v>7.600619178834669e-06</v>
       </c>
       <c r="X3" t="n">
         <v>1.186264519406407e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.441526303612197e-06</v>
+        <v>6.441526303612198e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.575453902723537e-06</v>
+        <v>5.575453902723543e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.722860171587207e-06</v>
+        <v>4.722860171587201e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.677556073432289e-06</v>
+        <v>5.677556073432292e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.786352640989925e-06</v>
+        <v>4.786352640989931e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.58982713746881e-06</v>
+        <v>4.589827137468813e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.256491160992258e-06</v>
+        <v>5.256491160992266e-06</v>
       </c>
       <c r="E4" t="n">
         <v>4.514046047483094e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.735834867238554e-06</v>
+        <v>4.735834867238557e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.826651044071284e-06</v>
+        <v>4.826651044071308e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.540206833419093e-06</v>
+        <v>4.540206833419095e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.471988924740427e-06</v>
+        <v>5.471988924740432e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.209084188088825e-06</v>
+        <v>5.209084188088834e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.34487015880371e-06</v>
+        <v>7.344870158803703e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.02694008263734e-06</v>
+        <v>5.026940082637345e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.485341951622776e-06</v>
+        <v>5.485341951622781e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.477212038384998e-06</v>
+        <v>4.477212038385009e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.699684596787203e-06</v>
+        <v>4.699684596787213e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.434623058485794e-06</v>
+        <v>4.434623058485792e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.675128157818003e-06</v>
+        <v>4.675128157818009e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.752094135209374e-06</v>
+        <v>4.752094135209376e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>5.821914624744013e-06</v>
+        <v>5.82191462474402e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.678555279475308e-06</v>
+        <v>4.678555279475314e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.927431385956281e-06</v>
+        <v>5.927431385956276e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.615558791231297e-06</v>
+        <v>5.615558791231307e-06</v>
       </c>
       <c r="W4" t="n">
         <v>5.013681861865733e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.670700840533988e-05</v>
+        <v>1.67070084053399e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.116287400042848e-06</v>
+        <v>8.116287400042865e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.781737864419292e-06</v>
+        <v>4.78173786441929e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.378426670328676e-06</v>
+        <v>5.378426670328678e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.875235892126842e-06</v>
+        <v>6.875235892126846e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.79298455006475e-05</v>
+        <v>1.792984550064748e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.618867051411528e-05</v>
+        <v>1.618867051411527e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.791178126132124e-05</v>
+        <v>2.791178126132122e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.141296412346427e-05</v>
+        <v>1.141296412346425e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.845566653518543e-05</v>
+        <v>1.845566653518541e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.983161888798265e-05</v>
+        <v>1.983161888798263e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.531897898096798e-05</v>
+        <v>1.531897898096795e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.18564468612306e-05</v>
+        <v>3.185644686123052e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.649510555983033e-05</v>
+        <v>2.649510555983035e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.335954990846225e-05</v>
+        <v>6.335954990846216e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.415371722329916e-05</v>
+        <v>2.415371722329912e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.275953949990806e-05</v>
+        <v>3.275953949990805e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.574942992035245e-05</v>
+        <v>3.574942992035241e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.705536932090176e-05</v>
+        <v>1.705536932090174e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.269246720040889e-05</v>
+        <v>1.269246720040886e-05</v>
       </c>
       <c r="Q5" t="n">
         <v>1.711557463161481e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.864125600904958e-05</v>
+        <v>1.86412560090496e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>3.478662198110318e-05</v>
+        <v>3.478662198110316e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.757210711274369e-05</v>
+        <v>1.75721071127437e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.717914882730345e-05</v>
+        <v>3.717914882730346e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>3.344205137198599e-05</v>
+        <v>3.344205137198601e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.265312139079165e-05</v>
+        <v>2.265312139079157e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002196073788470219</v>
+        <v>0.0002196073788470218</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.761204821667515e-05</v>
+        <v>7.761204821667538e-05</v>
       </c>
       <c r="Z5" t="n">
         <v>1.859426480933033e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.867068695267269e-05</v>
+        <v>2.867068695267265e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.890856207152984e-05</v>
+        <v>5.890856207152987e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.931580316698512e-06</v>
+        <v>6.931580316698507e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.735054813177391e-06</v>
+        <v>6.735054813177377e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.401718836700849e-06</v>
+        <v>7.401718836700841e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.65927372319168e-06</v>
+        <v>6.65927372319167e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.178377198219108e-06</v>
+        <v>6.881062542947121e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>5.269193375051837e-06</v>
+        <v>6.971878719779901e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.982749164399644e-06</v>
+        <v>4.982749164399637e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.617216600449039e-06</v>
+        <v>5.914531255720979e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.354311863797422e-06</v>
+        <v>5.651626519069377e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>7.787412489784258e-06</v>
+        <v>9.490097834512282e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.172167758345929e-06</v>
+        <v>7.172167758345915e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.630569627331376e-06</v>
+        <v>7.630569627331367e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.925693287711292e-06</v>
+        <v>4.925693287711287e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>5.148165846113488e-06</v>
+        <v>6.808923919806092e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>6.543946827343045e-06</v>
+        <v>6.543946827343037e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.820355833526599e-06</v>
+        <v>6.82035583352659e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>6.89732181091795e-06</v>
+        <v>5.19463646618992e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>6.264456955724566e-06</v>
+        <v>6.26445695572456e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.823782955183891e-06</v>
+        <v>6.823782955183879e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>8.052158621044673e-06</v>
+        <v>8.052158621044671e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>6.058101122211857e-06</v>
+        <v>6.058101122211847e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>7.122813438912169e-06</v>
+        <v>7.122813438912179e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.885223608104847e-05</v>
+        <v>1.714955073632044e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.584947718213344e-06</v>
+        <v>8.584947718213371e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.926965540127887e-06</v>
+        <v>5.224280195399844e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.523654346037263e-06</v>
+        <v>5.820969001309229e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.332161852917959e-06</v>
+        <v>7.332161852917958e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.283536630535813e-06</v>
+        <v>7.283536630535797e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.0870111270147e-06</v>
+        <v>7.087011127014677e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.753675150538158e-06</v>
+        <v>7.753675150538136e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.011230037028983e-06</v>
+        <v>7.011230037028969e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.233018856784447e-06</v>
+        <v>7.233018856784423e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.323835033617181e-06</v>
+        <v>7.323835033617206e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.037390822964985e-06</v>
+        <v>7.037390822964969e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.969172914286332e-06</v>
+        <v>7.969172914286309e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.706268177634727e-06</v>
+        <v>7.706268177634695e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>9.842054148349592e-06</v>
+        <v>9.84205414834957e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.52412407218324e-06</v>
+        <v>7.524124072183212e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>7.982525941168659e-06</v>
+        <v>7.982525941168654e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>6.974396027930908e-06</v>
+        <v>6.974396027930876e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>7.195438512310181e-06</v>
+        <v>7.195438512310171e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.930376974008756e-06</v>
+        <v>6.930376974008753e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.172312147363913e-06</v>
+        <v>7.172312147363884e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.249278124755263e-06</v>
+        <v>7.249278124755245e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>8.319098614289895e-06</v>
+        <v>8.31909861428989e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>7.175739269021199e-06</v>
+        <v>7.175739269021192e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>8.410438802700729e-06</v>
+        <v>8.410438802700716e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>8.112742780777194e-06</v>
+        <v>8.112742780777181e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.51086585141162e-06</v>
+        <v>7.510865851411598e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.920419239488568e-05</v>
+        <v>1.920419239488575e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.059297094896855e-05</v>
+        <v>1.059297094896856e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.278921853965177e-06</v>
+        <v>7.278921853965168e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.875610659874567e-06</v>
+        <v>7.87561065987455e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.37241988167274e-06</v>
+        <v>9.372419881672716e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.349356772545628e-05</v>
+        <v>1.349356772545627e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.91127748217464e-05</v>
+        <v>1.911277482174634e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977943884526981e-05</v>
+        <v>1.97794388452698e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.903699373176067e-05</v>
+        <v>1.594028767570849e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.434907312088599e-05</v>
+        <v>1.434907312088595e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.934959872834886e-05</v>
+        <v>2.05555287689112e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90631545176967e-05</v>
+        <v>1.906315451769664e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.999493660901803e-05</v>
+        <v>1.999493660901798e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.973203187236645e-05</v>
+        <v>1.973203187236635e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.186781784308127e-05</v>
+        <v>2.186781784308123e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.954988776691494e-05</v>
+        <v>1.954988776691488e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.000828963590041e-05</v>
+        <v>2.000828963590216e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.449199400700241e-05</v>
+        <v>1.449199400700237e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.595334964792695e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.538460793047484e-05</v>
+        <v>1.538460793047479e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.223941904876392e-05</v>
+        <v>1.223941904876391e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.927504181948694e-05</v>
+        <v>1.927504181948691e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.03448623090216e-05</v>
+        <v>2.034486230902156e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.920150296375287e-05</v>
+        <v>1.920150296375286e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.685682207269312e-05</v>
+        <v>1.759730628406693e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.01385064755089e-05</v>
+        <v>1.855560694299252e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.95377725044508e-05</v>
+        <v>1.953777250445075e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.480432274521946e-05</v>
+        <v>2.480432274521954e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.84114650398214e-05</v>
+        <v>2.841146503982136e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.93046855486969e-05</v>
+        <v>1.338092273003723e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.990137435460626e-05</v>
+        <v>1.990137435460624e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.747320258073184e-05</v>
+        <v>2.747320258073179e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7222,43 +7222,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.541819873713784e-05</v>
+        <v>1.541819873713783e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.828525799124605e-05</v>
+        <v>1.828525799124604e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.89519220147695e-05</v>
+        <v>1.895192201476948e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.82094769012603e-05</v>
+        <v>1.750241405202435e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.843126572101577e-05</v>
+        <v>1.136886669472918e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.852208189784852e-05</v>
+        <v>1.852208191955248e-05</v>
       </c>
       <c r="H9" t="n">
         <v>1.823563768719632e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.916741977851763e-05</v>
+        <v>1.916741977851765e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.890451504186608e-05</v>
+        <v>1.890451504186605e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.104030101258092e-05</v>
+        <v>2.104030101258091e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.872237093641455e-05</v>
+        <v>1.872237093641456e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.918077280539999e-05</v>
+        <v>1.91807728054e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.817264289216224e-05</v>
+        <v>1.817264289216221e-05</v>
       </c>
       <c r="O9" t="n">
         <v>1.94103834567381e-05</v>
@@ -7267,40 +7267,40 @@
         <v>1.936612528597617e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.837055903329925e-05</v>
+        <v>1.837055903329926e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.844752498898662e-05</v>
+        <v>1.844752498898658e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.951734547852124e-05</v>
+        <v>1.951734547852122e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.837398613325255e-05</v>
+        <v>1.837398613325252e-05</v>
       </c>
       <c r="U9" t="n">
         <v>1.96023617991133e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.931098964500854e-05</v>
+        <v>2.284630064550529e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.870911271564295e-05</v>
+        <v>1.870911271564294e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.040243925911719e-05</v>
+        <v>3.040243925911715e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.179121781319988e-05</v>
+        <v>2.179121781319991e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.847716871819652e-05</v>
+        <v>1.66300995425509e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.907385752410593e-05</v>
+        <v>1.907385752410591e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.057066674590405e-05</v>
+        <v>2.057066674590408e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.360162245141636e-06</v>
+        <v>8.360162245141753e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.990173056957235e-06</v>
+        <v>5.990173056957236e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.284368936296307e-06</v>
+        <v>6.28436893629632e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.233264355630862e-06</v>
+        <v>6.233264355630943e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.092210850903182e-06</v>
+        <v>6.092210850903268e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.064688980696511e-06</v>
+        <v>7.064688980696689e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.983801073170126e-06</v>
+        <v>5.983801073170238e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.034350258953313e-06</v>
+        <v>6.034350258953388e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.981813907495827e-06</v>
+        <v>6.981813907495913e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.014391794154908e-06</v>
+        <v>6.014391794154959e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.98920763625217e-06</v>
+        <v>7.989207636252272e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>9.100793040158566e-06</v>
+        <v>9.100793040158564e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>5.982486873252495e-06</v>
+        <v>5.982486873252627e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>8.531832298775261e-06</v>
+        <v>8.531832298775237e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>7.066142588688035e-06</v>
+        <v>7.066142588688116e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.056934007406162e-06</v>
+        <v>6.056934007406158e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.017482263185735e-06</v>
+        <v>6.017482263185819e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>6.760581232717668e-06</v>
+        <v>6.760581232717749e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>6.158551479837192e-06</v>
+        <v>6.158551479837197e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.055081271551441e-05</v>
+        <v>1.055081271551454e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>6.340742610987726e-06</v>
+        <v>6.340742610987802e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>8.950834596931913e-06</v>
+        <v>8.950834596931938e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.481810333233477e-06</v>
+        <v>7.481810333233616e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.787797974636956e-06</v>
+        <v>6.7877979746371e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.883761839360356e-06</v>
+        <v>7.883761839360344e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.080268907105276e-06</v>
+        <v>7.080268907105388e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.27531050568791e-06</v>
+        <v>9.275310505687905e-06</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.27393746253876e-05</v>
+        <v>2.273937462538753e-05</v>
       </c>
       <c r="C3" t="n">
         <v>5.746396369019208e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.01185562463874e-06</v>
+        <v>8.011855624638656e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.632182973259132e-06</v>
+        <v>7.632182973259139e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.637658035157223e-06</v>
+        <v>6.637658035157143e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.353383079391624e-05</v>
+        <v>1.353383079391635e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.862461403160963e-06</v>
+        <v>5.862461403160952e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.223061226343588e-06</v>
+        <v>6.223061226343558e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.296100933015366e-05</v>
+        <v>1.296100933015375e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.082728966472241e-06</v>
+        <v>6.08272896647232e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.014136873077308e-05</v>
+        <v>2.014136873077297e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.797117323059359e-05</v>
+        <v>2.797117323059362e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.850072768542329e-06</v>
+        <v>5.850072768542224e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.162298419171094e-05</v>
+        <v>1.162298419171075e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355649575421069e-05</v>
+        <v>1.355649575421062e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.382388242205148e-06</v>
+        <v>6.382388242205138e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>6.102499431625725e-06</v>
+        <v>6.102499431625669e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.136976543277873e-05</v>
+        <v>1.136976543277865e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>7.11144373872408e-06</v>
+        <v>7.111443738724058e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.712514388343025e-05</v>
+        <v>2.712514388343031e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>8.394186340498282e-06</v>
+        <v>8.394186340498354e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.471384896404347e-05</v>
+        <v>1.471384896404356e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.657184074366543e-05</v>
+        <v>1.657184074366534e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.159536010351122e-05</v>
+        <v>1.159536010351114e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.316723656047448e-05</v>
+        <v>1.31672365604745e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.368558617805924e-05</v>
+        <v>1.368558617805916e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.927813628193136e-05</v>
+        <v>2.927813628193133e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.463360999448315e-05</v>
+        <v>3.463360999448313e-05</v>
       </c>
       <c r="C4" t="n">
         <v>7.522466826568516e-06</v>
@@ -7654,73 +7654,73 @@
         <v>1.060931991109063e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>9.016055687373556e-06</v>
+        <v>9.016055687373576e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.000064352543093e-05</v>
+        <v>2.000064352543097e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.791517376917057e-06</v>
+        <v>7.791517376917073e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>8.362493684112459e-06</v>
+        <v>8.362493684112469e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.90454832241156e-05</v>
+        <v>1.904548322411561e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>8.13705364286705e-06</v>
+        <v>8.137053642867068e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.044350703952558e-05</v>
+        <v>3.044350703952556e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.27916941164806e-05</v>
+        <v>4.279169411648065e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>7.776672884285558e-06</v>
+        <v>7.776672884285559e-06</v>
       </c>
       <c r="O4" t="n">
         <v>1.102337836499584e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.001706269638802e-05</v>
+        <v>2.001706269638805e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.617587511924965e-06</v>
+        <v>8.61758751192498e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>8.171961912256245e-06</v>
+        <v>8.171961912256257e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.656560661553408e-05</v>
+        <v>1.656560661553417e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>9.765403609380298e-06</v>
+        <v>9.765403609380311e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.600890312327475e-05</v>
+        <v>3.600890312327473e-05</v>
       </c>
       <c r="V4" t="n">
         <v>1.169929303719325e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.593658631815108e-05</v>
+        <v>1.59365863181511e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.471222108763832e-05</v>
+        <v>2.471222108763837e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.676486794481845e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.642907700401772e-05</v>
+        <v>1.642907700401774e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.017662596133825e-05</v>
+        <v>2.017662596133829e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.459979566220425e-05</v>
+        <v>4.45997956622042e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7733,82 +7733,82 @@
         <v>0.0004887892929832424</v>
       </c>
       <c r="C5" t="n">
-        <v>2.213179893705465e-05</v>
+        <v>2.213179893705462e-05</v>
       </c>
       <c r="D5" t="n">
         <v>9.4130076354038e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.490840750545666e-05</v>
+        <v>7.490840750545677e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.155758633649521e-05</v>
+        <v>5.155758633649517e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002345309700741744</v>
+        <v>0.0002345309700741747</v>
       </c>
       <c r="H5" t="n">
         <v>2.758623099433031e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.828640719855251e-05</v>
+        <v>3.828640719855254e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002271909536635684</v>
+        <v>0.0002271909536635688</v>
       </c>
       <c r="K5" t="n">
-        <v>3.519856791794699e-05</v>
+        <v>3.519856791794686e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004371014621472703</v>
+        <v>0.0004371014621472702</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006756972575829626</v>
+        <v>0.0006756972575829619</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005152648325403528</v>
+        <v>0.000515264832540353</v>
       </c>
       <c r="O5" t="n">
-        <v>8.02235244611725e-05</v>
+        <v>8.022352446117239e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002416768045415894</v>
+        <v>0.0002416768045415889</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.207841119522846e-05</v>
+        <v>4.207841119522848e-05</v>
       </c>
       <c r="R5" t="n">
         <v>3.458704232834755e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001731225284447154</v>
+        <v>0.0001731225284447152</v>
       </c>
       <c r="T5" t="n">
-        <v>6.589821855983128e-05</v>
+        <v>6.589821855983107e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005436052270703555</v>
+        <v>0.0005436052270703559</v>
       </c>
       <c r="V5" t="n">
-        <v>9.491678633016615e-05</v>
+        <v>9.491678633016607e-05</v>
       </c>
       <c r="W5" t="n">
         <v>0.0001802458955557349</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003575390138339628</v>
+        <v>0.0003575390138339636</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001963692447449627</v>
+        <v>0.0001963692447449621</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001759748163526717</v>
+        <v>0.0001759748163526716</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002604163386090609</v>
+        <v>0.0002604163386090612</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007933451982472039</v>
+        <v>0.0007933451982472026</v>
       </c>
     </row>
     <row r="6">
@@ -7821,82 +7821,82 @@
         <v>3.835306045283225e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.336906520260544e-06</v>
+        <v>8.336906520260553e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.490602011732454e-05</v>
+        <v>1.490602011732455e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.432877036943971e-05</v>
+        <v>1.43287703694397e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.273550614572266e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.081508321912294e-05</v>
+        <v>2.081508321912297e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.151096783526613e-05</v>
+        <v>1.151096783526612e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.176933377804481e-06</v>
+        <v>9.176933377804489e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.276493368246467e-05</v>
+        <v>1.985992291780761e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.951493336559077e-06</v>
+        <v>8.951493336559085e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.125794673321757e-05</v>
+        <v>3.416295749787463e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.651114457482968e-05</v>
+        <v>4.651114457482967e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.638579795694763e-06</v>
+        <v>8.638579795694807e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>1.188528527640505e-05</v>
+        <v>1.188528527640509e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.37493607310017e-05</v>
+        <v>2.374936073100173e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.432027205616991e-06</v>
+        <v>1.233703797027405e-05</v>
       </c>
       <c r="R6" t="n">
         <v>1.189141237060532e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.028505707388315e-05</v>
+        <v>2.02850570738832e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.34848540677294e-05</v>
+        <v>1.057984330307233e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.983651787263794e-05</v>
+        <v>3.983651787263788e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.251373273088528e-05</v>
+        <v>1.541874349554234e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.686087769677492e-05</v>
+        <v>1.686087769677479e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.843167154598741e-05</v>
+        <v>2.55266607813304e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.778574816605496e-05</v>
+        <v>1.778574816605499e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>1.724351669770976e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38960764196873e-05</v>
+        <v>2.389607641968731e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.561759214165074e-05</v>
+        <v>4.561759214165073e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7909,43 +7909,43 @@
         <v>3.817200195154425e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.106085878362966e-05</v>
+        <v>1.106085878362967e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.472496161603662e-05</v>
+        <v>1.472496161603661e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.414771186815177e-05</v>
+        <v>1.414771186815176e-05</v>
       </c>
       <c r="F7" t="n">
         <v>1.255444764443471e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.353903548249208e-05</v>
+        <v>2.353903548249211e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.13299093339782e-05</v>
+        <v>1.132990933397821e-05</v>
       </c>
       <c r="I7" t="n">
         <v>1.190088564117361e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.258387518117675e-05</v>
+        <v>2.258387518117676e-05</v>
       </c>
       <c r="K7" t="n">
         <v>1.16754455999282e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.39818989965867e-05</v>
+        <v>3.398189899658671e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.633008607354176e-05</v>
+        <v>4.633008607354179e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.13150648413467e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.456023520760477e-05</v>
+        <v>1.456023520760478e-05</v>
       </c>
       <c r="P7" t="n">
         <v>2.355391953899693e-05</v>
@@ -7957,34 +7957,34 @@
         <v>1.171035386931739e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.010399857259523e-05</v>
+        <v>2.010399857259527e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.330379556644143e-05</v>
+        <v>1.330379556644144e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.965326814119707e-05</v>
+        <v>3.965326814119711e-05</v>
       </c>
       <c r="V7" t="n">
         <v>1.52376849942544e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.947497827521222e-05</v>
+        <v>1.947497827521224e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.825061304469949e-05</v>
+        <v>2.825061304469953e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.041142419289368e-05</v>
+        <v>2.04114241928937e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.996746896107891e-05</v>
+        <v>1.99674689610789e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.37150179183994e-05</v>
+        <v>2.371501791839939e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.813818761926539e-05</v>
+        <v>4.813818761926534e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.562978316667602e-05</v>
+        <v>4.562978316667598e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.599165900116572e-05</v>
+        <v>2.599165900116576e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.965576183357269e-05</v>
+        <v>2.965576183357272e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.907851208568782e-05</v>
+        <v>2.509934990712927e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11764378811715e-05</v>
+        <v>2.117643788117151e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.846983570002813e-05</v>
+        <v>4.001941487239579e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.626070955151427e-05</v>
+        <v>2.626070955151428e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.683168585870967e-05</v>
+        <v>2.68316858587097e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.751467539871281e-05</v>
+        <v>3.751467539871283e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.660624581746427e-05</v>
+        <v>2.66062458174643e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.891269921412277e-05</v>
+        <v>4.891269921412279e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.126088629107785e-05</v>
+        <v>6.126088629107831e-05</v>
       </c>
       <c r="N8" t="n">
         <v>2.045302512326792e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.529165331683852e-05</v>
+        <v>2.529165331683853e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.389511892504526e-05</v>
+        <v>3.389511892504529e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.814514188674958e-05</v>
+        <v>1.814514188674959e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.664115408685346e-05</v>
+        <v>2.664115408685349e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.503479879013125e-05</v>
+        <v>3.503479879013131e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82345957839775e-05</v>
+        <v>2.823459578397751e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.998727535064023e-05</v>
+        <v>5.093827028170983e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.016848521179045e-05</v>
+        <v>2.812543560767564e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.440724715542611e-05</v>
+        <v>3.440724715542612e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.492469250333594e-05</v>
+        <v>3.492469250333601e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>4.277160725734879e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.489826917861492e-05</v>
+        <v>2.728643501157704e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.864581813593544e-05</v>
+        <v>3.864581813593547e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.087518106876378e-05</v>
+        <v>7.087518106876376e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.207428157442649e-05</v>
+        <v>5.207428157442646e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.999805990148401e-05</v>
@@ -8091,13 +8091,13 @@
         <v>3.366216273389095e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.30849129860061e-05</v>
+        <v>3.192287007370234e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.149164876228906e-05</v>
+        <v>1.988478661106266e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.247623660034646e-05</v>
+        <v>4.247623196135631e-05</v>
       </c>
       <c r="H9" t="n">
         <v>3.026711045183254e-05</v>
@@ -8106,61 +8106,61 @@
         <v>3.083808675902793e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.15210762990311e-05</v>
+        <v>4.152107629903112e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.061264671778251e-05</v>
+        <v>3.061264671778252e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.291910011444102e-05</v>
+        <v>5.291910011444104e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>6.526728719139605e-05</v>
+        <v>6.526728719139614e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.025226595920104e-05</v>
+        <v>3.025226595920105e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.516753165435474e-05</v>
+        <v>3.516753165435476e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.452410021359823e-05</v>
+        <v>4.452410021359821e-05</v>
       </c>
       <c r="Q9" t="n">
         <v>3.109317594785026e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.064755498717173e-05</v>
+        <v>3.064755498717174e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.904119969044955e-05</v>
+        <v>3.90411996904496e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.224099668429579e-05</v>
+        <v>3.224099668429581e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>5.859266048920436e-05</v>
+        <v>5.859266048920434e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.417488611210872e-05</v>
+        <v>3.998506259457019e-05</v>
       </c>
       <c r="W9" t="n">
         <v>3.841217939306657e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.718781416255384e-05</v>
+        <v>4.718781416255388e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.934862531074805e-05</v>
+        <v>3.934862531074808e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.890467007893324e-05</v>
+        <v>3.586905829806234e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.265221903625375e-05</v>
+        <v>4.265221903625377e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.707538873711977e-05</v>
+        <v>6.707538873711971e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.866813734368717e-06</v>
+        <v>4.866813734368646e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.943170367605225e-06</v>
+        <v>4.943170367605198e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.993562958042335e-06</v>
+        <v>4.993562958042239e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.890001680513753e-06</v>
+        <v>4.890001680513675e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.86533135532259e-06</v>
+        <v>4.865331355322521e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.689201583390417e-06</v>
+        <v>5.689201583390326e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.85716644927265e-06</v>
+        <v>4.857166449272713e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.961184231298182e-06</v>
+        <v>4.961184231298188e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.284275850414037e-06</v>
+        <v>5.284275850414065e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.373084063445036e-06</v>
+        <v>5.373084063445074e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.535517864635812e-06</v>
+        <v>5.53551786463572e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.338549677198468e-06</v>
+        <v>5.338549677198478e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.856685375482648e-06</v>
+        <v>4.856685375482559e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.669126824390022e-06</v>
+        <v>6.669126824389986e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.33215718741696e-06</v>
+        <v>5.332157187417028e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.868331249089749e-06</v>
+        <v>4.868331249089718e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.871946178950571e-06</v>
+        <v>4.871946178950555e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.220210392449113e-06</v>
+        <v>5.220210392448989e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.862159576715187e-06</v>
+        <v>4.862159576715315e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.09905250250205e-06</v>
+        <v>7.099052502502228e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.920416166456155e-06</v>
+        <v>4.920416166456075e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.021367054246379e-06</v>
+        <v>7.021367054246635e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.674777718104104e-06</v>
+        <v>6.674777718104047e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.388945744536977e-06</v>
+        <v>6.388945744536909e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.720378628868219e-06</v>
+        <v>5.720378628868126e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.34413850237832e-06</v>
+        <v>5.344138502378533e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.052755950217989e-06</v>
+        <v>7.052755950217937e-06</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.739528166793082e-06</v>
+        <v>4.739528166793011e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.827791632535216e-06</v>
+        <v>4.827791632535236e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.647243098021262e-06</v>
+        <v>5.647243098021248e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.898586264262304e-06</v>
+        <v>4.898586264262277e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.731669935690477e-06</v>
+        <v>4.731669935690442e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.056968329760507e-05</v>
+        <v>1.056968329760496e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.671895659182139e-06</v>
+        <v>4.671895659182257e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.416335110550396e-06</v>
+        <v>5.416335110550511e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.70626933237464e-06</v>
+        <v>7.706269332374632e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.341901323260478e-06</v>
+        <v>8.34190132326066e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.490402251076023e-06</v>
+        <v>9.490402251075879e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>8.121313571812578e-06</v>
+        <v>8.121313571812551e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.66722083838504e-06</v>
+        <v>4.66722083838498e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.946306747155305e-06</v>
+        <v>7.946306747155373e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>8.045392568356606e-06</v>
+        <v>8.045392568356533e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.753118573597753e-06</v>
+        <v>4.753118573597797e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.777501426120692e-06</v>
+        <v>4.77750142612082e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.247221697262911e-06</v>
+        <v>7.247221697262939e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.707758304328805e-06</v>
+        <v>4.707758304328763e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.100228942839186e-05</v>
+        <v>1.100228942839208e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.123026506815933e-06</v>
+        <v>5.123026506815902e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.320525050006144e-06</v>
+        <v>9.320525050006404e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.764514253239088e-05</v>
+        <v>1.764514253239077e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.559973458674209e-05</v>
+        <v>1.559973458674214e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.716705087247013e-06</v>
+        <v>6.716705087246935e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.147158417033216e-06</v>
+        <v>8.147158417033335e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.024364944041628e-05</v>
+        <v>2.024364944041619e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.616578687331742e-06</v>
+        <v>5.616578687331707e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.532359289702704e-06</v>
+        <v>5.532359289702743e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>7.048269476248525e-06</v>
+        <v>7.048269476248537e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.878497206022063e-06</v>
+        <v>5.878497206022066e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.599834534077729e-06</v>
+        <v>5.599834534077784e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.490582775913312e-05</v>
+        <v>1.490582775913304e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.50760816420293e-06</v>
+        <v>5.507608164202837e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.682536862724316e-06</v>
+        <v>6.6825368627242e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.031362767635524e-05</v>
+        <v>1.03136276763552e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.133513495010764e-05</v>
+        <v>1.133513495010768e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.316989945779618e-05</v>
+        <v>1.316989945779624e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09754364842246e-05</v>
+        <v>1.097543648422459e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>5.50217421443823e-06</v>
+        <v>5.502174214438156e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>6.09395405352791e-06</v>
+        <v>6.093954053527968e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.087284705807799e-05</v>
+        <v>1.087284705807785e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.633719714197272e-06</v>
+        <v>5.633719714197307e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>5.674552009925483e-06</v>
+        <v>5.67455200992551e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.608356510843877e-06</v>
+        <v>9.608356510843789e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.564007835619186e-06</v>
+        <v>5.564007835619114e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.085732902315346e-05</v>
+        <v>1.085732902315339e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.102404101593408e-06</v>
+        <v>6.102404101593382e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>7.725738813867123e-06</v>
+        <v>7.725738813867056e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.603836358814635e-05</v>
+        <v>2.603836358814632e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.271775068601141e-05</v>
+        <v>2.27177506860114e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.792986176624168e-06</v>
+        <v>6.792986176624156e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.100818152224524e-05</v>
+        <v>1.100818152224514e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.001099953163946e-05</v>
+        <v>3.001099953163935e-05</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.564100676206686e-05</v>
+        <v>1.564100676206681e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.620292647034884e-05</v>
+        <v>1.620292647034875e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.256900805187456e-05</v>
+        <v>4.256900805187447e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6938469257336e-05</v>
+        <v>1.693846925733607e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.675524976249627e-05</v>
+        <v>1.675524976249626e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001595870867661929</v>
+        <v>0.0001595870867661916</v>
       </c>
       <c r="H5" t="n">
-        <v>1.434625267180034e-05</v>
+        <v>1.434625267180011e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.619401436406673e-05</v>
+        <v>3.619401436406677e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>9.243776963399e-05</v>
+        <v>9.243776963398965e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001111326889445805</v>
+        <v>0.0001111326889445807</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000137988146746519</v>
+        <v>0.0001379881467465189</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001096307502488248</v>
+        <v>0.0001096307502488247</v>
       </c>
       <c r="N5" t="n">
-        <v>9.767408908392955e-05</v>
+        <v>9.767408908392967e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.40130879359853e-05</v>
+        <v>2.401308793598531e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001006701645385768</v>
+        <v>0.0001006701645385771</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.737438538899007e-05</v>
+        <v>1.737438538898998e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73622050000362e-05</v>
+        <v>1.736220500003613e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.871961656708876e-05</v>
+        <v>7.87196165670888e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.54611236628057e-05</v>
+        <v>1.546112366280578e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001031212531641348</v>
+        <v>0.0001031212531641347</v>
       </c>
       <c r="V5" t="n">
-        <v>2.671459736976614e-05</v>
+        <v>2.671459736976617e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.297758018910617e-05</v>
+        <v>5.297758018910607e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003779146165266868</v>
+        <v>0.0003779146165266861</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003180073712644443</v>
+        <v>0.0003180073712644445</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479656046560669e-05</v>
+        <v>3.47965604656066e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001114873160773028</v>
+        <v>0.0001114873160773029</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004803672489006386</v>
+        <v>0.0004803672489006373</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.289008396036639e-06</v>
+        <v>6.017183942000301e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>8.204788998407598e-06</v>
+        <v>8.204788998407607e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.448874730917045e-06</v>
+        <v>7.448874730917129e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.279102460690583e-06</v>
+        <v>8.550926914726923e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.000439788746422e-06</v>
+        <v>8.272264242782647e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.757825746783798e-05</v>
+        <v>1.530643301380164e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.908213418871454e-06</v>
+        <v>8.180037872907704e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.083142117392796e-06</v>
+        <v>9.354966571429072e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.298605738506017e-05</v>
+        <v>1.071423293102378e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.173574020477642e-05</v>
+        <v>1.400756465881254e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.584232916650097e-05</v>
+        <v>1.357050471246483e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.137604173889311e-05</v>
+        <v>1.364786619292946e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.915525293119282e-06</v>
+        <v>5.915525293118956e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>8.774063672126112e-06</v>
+        <v>6.507305132208761e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.122995231441563e-05</v>
+        <v>1.122995231441553e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.034324968865809e-06</v>
+        <v>8.306149422902181e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>8.346981718630394e-06</v>
+        <v>8.346981718630375e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.000896176551238e-05</v>
+        <v>1.000896176551239e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.96461309028767e-06</v>
+        <v>5.964613090287716e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.362176800334819e-05</v>
+        <v>1.134994354931194e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>8.774833810298304e-06</v>
+        <v>8.774833810298249e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>8.185968326051516e-06</v>
+        <v>8.18596832605143e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.871079329685113e-05</v>
+        <v>2.64389688428149e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.325217871048864e-05</v>
+        <v>2.325217871048888e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.193591431292709e-06</v>
+        <v>7.193591431292759e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.368061123095008e-05</v>
+        <v>1.368061123095e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.054643285316819e-05</v>
+        <v>3.054643285316796e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.412877400902575e-06</v>
+        <v>8.412877400902638e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.328658003273656e-06</v>
+        <v>8.328658003273686e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.844568189819504e-06</v>
+        <v>9.844568189819467e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.674795919593137e-06</v>
+        <v>8.674795919593007e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.396133247648786e-06</v>
+        <v>8.39613324764872e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.770212647270401e-05</v>
+        <v>1.770212647270393e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.303906877773918e-06</v>
+        <v>8.303906877773774e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>9.478835576295097e-06</v>
+        <v>9.478835576295139e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.310992638992626e-05</v>
+        <v>1.310992638992612e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.41314336636786e-05</v>
+        <v>1.413143366367861e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.596619817136719e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.377173519779548e-05</v>
+        <v>1.377173519779552e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.298472928008928e-06</v>
+        <v>8.298472928009086e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>8.888825527406966e-06</v>
+        <v>8.888825527406976e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.366771853195692e-05</v>
+        <v>1.366771853195688e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.430018427767986e-06</v>
+        <v>8.430018427768247e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>8.470850723496563e-06</v>
+        <v>8.47085072349645e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.24046552244147e-05</v>
+        <v>1.240465522441474e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>8.360306549190118e-06</v>
+        <v>8.360306549190059e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.374707490593124e-05</v>
+        <v>1.374707490593122e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.898702815164267e-06</v>
+        <v>8.898702815164331e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0522037527438e-05</v>
+        <v>1.052203752743799e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.883466230171711e-05</v>
+        <v>2.883466230171728e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.560605867107222e-05</v>
+        <v>2.560605867107227e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.58928489019503e-06</v>
+        <v>9.589284890195081e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.380448023581631e-05</v>
+        <v>1.380448023581608e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.280729824521029e-05</v>
+        <v>3.28072982452103e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.49519252375282e-05</v>
+        <v>1.495192523752815e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.11734046769406e-05</v>
+        <v>2.117340467694061e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.268931486348634e-05</v>
+        <v>2.268931486348639e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.151954259325986e-05</v>
+        <v>1.816194396895349e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.591753526687613e-05</v>
+        <v>1.591753526687615e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.054687314637106e-05</v>
+        <v>3.185440087806841e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.114865355144061e-05</v>
+        <v>2.11486535514407e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.232358224996187e-05</v>
+        <v>2.232358224996206e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.595467306359309e-05</v>
+        <v>2.595467306359303e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.697618033734559e-05</v>
+        <v>2.697618033734554e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.881094484503405e-05</v>
+        <v>2.88109448450341e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.661648187146238e-05</v>
+        <v>2.661648187146288e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.625524808263455e-05</v>
+        <v>1.62552480826345e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.819028493689131e-05</v>
+        <v>1.819028493689127e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.263991318936384e-05</v>
+        <v>2.263991318936402e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.372985252228533e-05</v>
+        <v>1.372985252228527e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.131559739716328e-05</v>
+        <v>2.131559739716336e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.524940189808167e-05</v>
+        <v>2.524940189808163e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.120505322285688e-05</v>
+        <v>2.120505322285696e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.271226987658115e-05</v>
+        <v>2.351487665211369e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.174344948883127e-05</v>
+        <v>2.002245596697411e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.336802345196485e-05</v>
+        <v>2.336802345196484e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.471242622447735e-05</v>
+        <v>3.471242622447737e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.472421664897801e-05</v>
+        <v>4.472421664897785e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2434031563862e-05</v>
+        <v>1.601120113355341e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6649226909483e-05</v>
+        <v>2.664922690948302e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.223887462844082e-05</v>
+        <v>5.223887462844078e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.861837684718328e-05</v>
+        <v>1.861837684718316e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.229271108534665e-05</v>
+        <v>2.22927110853466e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.380862127189232e-05</v>
+        <v>2.380862127189239e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.263884900166588e-05</v>
+        <v>2.177139016904386e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.236018632972169e-05</v>
+        <v>1.369569436601884e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.166617955477699e-05</v>
+        <v>3.166617957513857e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.226795995984679e-05</v>
+        <v>2.226795995984671e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.344288865836797e-05</v>
+        <v>2.344288865836805e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.707397947199901e-05</v>
+        <v>2.707397947199908e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.80954867457516e-05</v>
+        <v>2.809548674575154e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.993025125344014e-05</v>
+        <v>2.993025125344011e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.773578827986849e-05</v>
+        <v>2.77357882798685e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.226252601008197e-05</v>
+        <v>2.226252601008199e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.409988562979772e-05</v>
+        <v>2.409988562979751e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.914967086163764e-05</v>
+        <v>2.91496708616376e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.239407153020292e-05</v>
+        <v>2.239407153020289e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.243490380556929e-05</v>
+        <v>2.243490380556938e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.636870830648754e-05</v>
+        <v>2.636870830648767e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.232435963126296e-05</v>
+        <v>2.2324359631263e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.770969009028723e-05</v>
+        <v>2.770969009028721e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.286275589723727e-05</v>
+        <v>2.720004448695025e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.44860906095109e-05</v>
+        <v>2.448609060951093e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.279871538379029e-05</v>
+        <v>4.279871538379022e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.957011175314528e-05</v>
+        <v>3.957011175314519e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.355333797226803e-05</v>
+        <v>2.128726436160094e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.776853331788894e-05</v>
+        <v>2.776853331788899e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.677135132728322e-05</v>
+        <v>4.677135132728324e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.228945968244608e-05</v>
+        <v>1.5450759852506e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.968721593784014e-06</v>
+        <v>8.260455542811656e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.275464753444258e-06</v>
+        <v>8.697079323604556e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.382736107896361e-06</v>
+        <v>1.011165605299445e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.229137500954746e-06</v>
+        <v>8.792883217704949e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.069687948445713e-06</v>
+        <v>9.223496239799205e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.236452748646518e-06</v>
+        <v>8.904851743746391e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.178939896203706e-06</v>
+        <v>8.795208261878586e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.239769411113023e-06</v>
+        <v>1.026440671044148e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>7.101519469518613e-06</v>
+        <v>8.63922359686962e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.187813394397832e-06</v>
+        <v>1.885441541505283e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.035464068071486e-05</v>
+        <v>1.201718680066612e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>6.966356627391098e-06</v>
+        <v>8.391274243411398e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.087868693706594e-05</v>
+        <v>1.242363790109857e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.168389778829793e-06</v>
+        <v>1.07260940391544e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.14981578614196e-06</v>
+        <v>9.459591843707242e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>7.123365068185098e-06</v>
+        <v>8.692041368341379e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.410926557125632e-06</v>
+        <v>1.130450569764157e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>7.351803991894183e-06</v>
+        <v>9.126208465300962e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.388281242662367e-05</v>
+        <v>1.72347381455998e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.750679398606803e-06</v>
+        <v>9.784576062413488e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.083736675503371e-05</v>
+        <v>1.214390480123658e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>7.851096569616658e-06</v>
+        <v>1.162965124587632e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.84551931599918e-06</v>
+        <v>9.341346238472501e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.838355037143129e-06</v>
+        <v>1.40476747985717e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.225711699844246e-06</v>
+        <v>1.069705865463796e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.079406225430906e-05</v>
+        <v>1.296663615000162e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.477443940874727e-05</v>
+        <v>5.870052261255723e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.951955000028341e-06</v>
+        <v>8.129589492961534e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.152325041578368e-06</v>
+        <v>1.071601060925326e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>9.901632858227305e-06</v>
+        <v>2.079236086481515e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.825019937680705e-06</v>
+        <v>1.140827756056043e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.479009203241284e-05</v>
+        <v>1.444413550964946e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.88066285153402e-06</v>
+        <v>1.221664930409212e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.463002322168894e-06</v>
+        <v>1.142148438048931e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.601690874430062e-05</v>
+        <v>2.187618118974901e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.906213351255472e-06</v>
+        <v>1.030028448245069e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.278818194247838e-05</v>
+        <v>8.318362165348561e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.112858632567574e-05</v>
+        <v>3.451307928553096e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>6.938235826392438e-06</v>
+        <v>8.524563290806748e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.810123270218436e-05</v>
+        <v>1.938414495318035e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.548686110002279e-05</v>
+        <v>2.513049571465069e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.250441154670912e-06</v>
+        <v>1.616343038387793e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.066477713766252e-06</v>
+        <v>1.068528267165708e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.722166392100421e-05</v>
+        <v>2.926297759771285e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>9.699668040361617e-06</v>
+        <v>1.378957904309158e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.258110698712409e-05</v>
+        <v>5.778980315094399e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.251450705131566e-05</v>
+        <v>1.842856402716719e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.990072412196339e-05</v>
+        <v>2.088664727596442e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.326782713115312e-05</v>
+        <v>3.169006004922145e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.321439050959037e-05</v>
+        <v>1.530628986896019e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.88297425649258e-05</v>
+        <v>3.444707593919706e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.307299674719661e-05</v>
+        <v>2.499054789723643e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.421088086187367e-05</v>
+        <v>4.121209925872973e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.976893981076721e-05</v>
+        <v>8.908926928848889e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.640523820340772e-06</v>
+        <v>8.934788464871529e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.313356053606796e-05</v>
+        <v>1.280334086800851e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.434523983186452e-05</v>
+        <v>2.878163576391287e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.261027290761035e-05</v>
+        <v>1.388548992384131e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.210467688432887e-05</v>
+        <v>1.874946210017277e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.269290199546918e-05</v>
+        <v>1.515022593354606e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.20432678699073e-05</v>
+        <v>1.391175236735554e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.400808884108893e-05</v>
+        <v>3.049049256975803e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.116876853534392e-05</v>
+        <v>1.214983381958831e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.473441815947494e-05</v>
+        <v>0.0001275351246263707</v>
       </c>
       <c r="M4" t="n">
-        <v>4.775856814932675e-05</v>
+        <v>5.032307024653583e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>9.642042055534175e-06</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9399786955956e-05</v>
+        <v>1.807512892650743e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.321955946360271e-05</v>
+        <v>3.57219954730279e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.171429764900723e-05</v>
+        <v>2.141627055565754e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.141552462175405e-05</v>
+        <v>1.274643484573715e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.595912394688513e-05</v>
+        <v>4.225542123814921e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.399584735214455e-05</v>
+        <v>1.76505519326278e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.953050761042464e-05</v>
+        <v>8.08685334518849e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.838630868702926e-05</v>
+        <v>2.498051097752018e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.317157162752395e-05</v>
+        <v>2.204635058003758e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.96355867034529e-05</v>
+        <v>4.592808977980285e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.949986825717707e-05</v>
+        <v>2.010248362070607e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.441845195210231e-05</v>
+        <v>4.361844020595081e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.516249695357418e-05</v>
+        <v>3.539402744797795e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.250676921350093e-05</v>
+        <v>6.07443623604209e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001158023498315678</v>
+        <v>0.001539134706216903</v>
       </c>
       <c r="C5" t="n">
-        <v>4.008014489637593e-05</v>
+        <v>4.928484352082555e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001143981230542671</v>
+        <v>0.0001317805406342758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001291148863952734</v>
+        <v>0.0004419268903646057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001058422771308287</v>
+        <v>0.0001586304820864977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002768441275402212</v>
+        <v>0.000234322821443771</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001095470240817365</v>
+        <v>0.0001895953726777679</v>
       </c>
       <c r="I5" t="n">
-        <v>9.219234625307733e-05</v>
+        <v>0.000157146207765156</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003232031903506423</v>
+        <v>0.0004728707262220475</v>
       </c>
       <c r="K5" t="n">
-        <v>7.206442694923501e-05</v>
+        <v>0.0001169520217328693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005418621159432192</v>
+        <v>0.002426895875653284</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000861967935710516</v>
+        <v>0.000941872907647426</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0009705962460628203</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002153466983960909</v>
+        <v>0.0002119011005815982</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002947363171777802</v>
+        <v>0.000553673346476967</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.277359003395087e-05</v>
+        <v>0.0003083942466006407</v>
       </c>
       <c r="R5" t="n">
-        <v>7.961971949346714e-05</v>
+        <v>0.0001337419550595696</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003521671956628983</v>
+        <v>0.000687815452870663</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001332521938777987</v>
+        <v>0.0002358430403797008</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001020557432418715</v>
+        <v>0.001460527881021266</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000204875636715467</v>
+        <v>0.0003499404145348518</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003125135317667296</v>
+        <v>0.0003128973440434376</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002496077966241416</v>
+        <v>0.000825074806498304</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002402372907231254</v>
+        <v>0.0002736425913577817</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003212442468040263</v>
+        <v>0.0007116724871154416</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005590013437763994</v>
+        <v>0.0005870561306643303</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009950781578811773</v>
+        <v>0.001203725295114694</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.45200483930405e-05</v>
+        <v>9.11777224453168e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.439163240261416e-05</v>
+        <v>1.496328570912386e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.446365148955376e-05</v>
+        <v>1.883183811226085e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.567533078535031e-05</v>
+        <v>3.481013300816517e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.736138148988373e-05</v>
+        <v>1.597394308066919e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.685578546660225e-05</v>
+        <v>2.477795934442507e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.744401057774256e-05</v>
+        <v>2.117872317779841e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.337335882339312e-05</v>
+        <v>1.600020552418345e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.875919742336232e-05</v>
+        <v>3.257894572658589e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.249885948882973e-05</v>
+        <v>1.817833106384063e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.606450911296075e-05</v>
+        <v>0.0001335636218706229</v>
       </c>
       <c r="M6" t="n">
-        <v>4.908865910281261e-05</v>
+        <v>5.635156749078816e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.107584058111049e-05</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.415490740346725e-05</v>
+        <v>2.023588429060391e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.797467716681907e-05</v>
+        <v>4.171847782338484e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.304438860249304e-05</v>
+        <v>2.744476779990984e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.274561557523984e-05</v>
+        <v>1.877493208998947e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.071023252915853e-05</v>
+        <v>4.434387439497712e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.532593830563036e-05</v>
+        <v>1.973900508945569e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>6.093331936491424e-05</v>
+        <v>8.293513503687221e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.313741726930264e-05</v>
+        <v>3.100900822177249e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.792669108557208e-05</v>
+        <v>2.804282887659755e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.438669528572628e-05</v>
+        <v>5.195658702405525e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.109299166255234e-05</v>
+        <v>2.236722566383489e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.574854290558816e-05</v>
+        <v>4.57068933627787e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.649258790705996e-05</v>
+        <v>4.142252469223027e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.408077941640338e-05</v>
+        <v>6.303838435258324e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.411805919695539e-05</v>
+        <v>9.393083885033212e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.398964320652899e-05</v>
+        <v>1.37763580267147e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.748267992225617e-05</v>
+        <v>1.764491042985169e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.869435921805274e-05</v>
+        <v>3.362320532575604e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.695939229379856e-05</v>
+        <v>1.872705948568445e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.645379627051708e-05</v>
+        <v>2.359103166201593e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.704202138165739e-05</v>
+        <v>1.999179549538923e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.639238725609554e-05</v>
+        <v>1.875332192919873e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.835720822727715e-05</v>
+        <v>3.533206213160119e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.551788792153215e-05</v>
+        <v>1.699140338143148e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.908353754566318e-05</v>
+        <v>0.000132376694188214</v>
       </c>
       <c r="M7" t="n">
-        <v>5.210768753551502e-05</v>
+        <v>5.516463980837903e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.399116144172239e-05</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.374725903895877e-05</v>
+        <v>2.291504185772133e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.756703154660548e-05</v>
+        <v>4.056190840424184e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.606341703519545e-05</v>
+        <v>2.625784011750066e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.576464400794226e-05</v>
+        <v>1.758800440758032e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.030824333307332e-05</v>
+        <v>4.709699079999242e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.834496673833278e-05</v>
+        <v>2.2492121494471e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>6.394916320572455e-05</v>
+        <v>8.568499689496591e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.273542807321748e-05</v>
+        <v>2.982208053936332e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.752069101371218e-05</v>
+        <v>2.688792014188073e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.398470608964111e-05</v>
+        <v>5.076965934164609e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.392170844436902e-05</v>
+        <v>2.492220161070869e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.876757133829058e-05</v>
+        <v>4.846000976779398e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.951161633976234e-05</v>
+        <v>4.023559700982108e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.685588859968911e-05</v>
+        <v>6.558593192226411e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.248431598584454e-05</v>
+        <v>0.0001028250551821385</v>
       </c>
       <c r="C8" t="n">
-        <v>3.103611530453693e-05</v>
+        <v>3.20144194995877e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.452915202026415e-05</v>
+        <v>3.588297190272467e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1118872714239e-05</v>
+        <v>4.688594488720089e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.667792518007922e-05</v>
+        <v>2.90769376866677e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.530016755923204e-05</v>
+        <v>4.376660029437745e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.408849347966538e-05</v>
+        <v>3.822985696826227e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.343885935410348e-05</v>
+        <v>3.69913834020717e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.540368032528511e-05</v>
+        <v>5.357012360447421e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25643600195401e-05</v>
+        <v>3.522946485430444e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.613000964367114e-05</v>
+        <v>0.0001506147556610867</v>
       </c>
       <c r="M8" t="n">
-        <v>6.915415963352336e-05</v>
+        <v>7.340270128125214e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.430901450686719e-05</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.591584234130478e-05</v>
+        <v>3.590216794065465e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.928235994169772e-05</v>
+        <v>5.306112681304455e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.272381339954166e-05</v>
+        <v>3.33157776162434e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.28111161059502e-05</v>
+        <v>3.582606588045333e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.735471543108131e-05</v>
+        <v>6.53350522728654e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.539143883634078e-05</v>
+        <v>4.073018296734399e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>7.676093129595725e-05</v>
+        <v>9.936446846645291e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.740815240929329e-05</v>
+        <v>4.550496238780428e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.456886902305675e-05</v>
+        <v>4.512781794812541e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.144066143509995e-05</v>
+        <v>5.868397881410253e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.959668297775116e-05</v>
+        <v>5.244851717812055e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.697258867137682e-05</v>
+        <v>5.718065937898444e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.655808843777031e-05</v>
+        <v>5.847365848269411e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.296957141612511e-05</v>
+        <v>9.358442096462719e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.264551033341176e-05</v>
+        <v>0.0001153277419747969</v>
       </c>
       <c r="C9" t="n">
-        <v>3.910532222397854e-05</v>
+        <v>4.269788256304753e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.259835893970577e-05</v>
+        <v>4.65664349661845e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.228949949246886e-05</v>
+        <v>6.080807941682292e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.688741239514896e-05</v>
+        <v>3.030227548501668e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.156947188056492e-05</v>
+        <v>5.25125581279096e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.215770039910693e-05</v>
+        <v>4.891332003172208e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.150806627354511e-05</v>
+        <v>4.767484646553154e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.347288724472672e-05</v>
+        <v>6.425358666793402e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.063356693898175e-05</v>
+        <v>4.591292791776429e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>6.419921656311274e-05</v>
+        <v>0.0001612982187245469</v>
       </c>
       <c r="M9" t="n">
-        <v>7.722336655296454e-05</v>
+        <v>8.408616434471188e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.910684045917195e-05</v>
+        <v>5.692976481231345e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>5.104791091622019e-05</v>
+        <v>5.433187527696479e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.534252001390658e-05</v>
+        <v>7.252106798482253e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.117909264524334e-05</v>
+        <v>5.517936658339435e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.088032302539187e-05</v>
+        <v>4.650952894391317e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>5.542392235052292e-05</v>
+        <v>7.601851533632528e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.34606457557824e-05</v>
+        <v>5.141364603080384e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>8.906802681506614e-05</v>
+        <v>0.0001146097759782203</v>
       </c>
       <c r="V9" t="n">
-        <v>5.545376589404962e-05</v>
+        <v>6.742684684371203e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>5.263637003116179e-05</v>
+        <v>5.58094446782136e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.910038510709071e-05</v>
+        <v>7.969118387797901e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.903738746181862e-05</v>
+        <v>5.384372614704154e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.991113343854184e-05</v>
+        <v>7.284485747442173e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.462729535721194e-05</v>
+        <v>6.915712154615396e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.197156761713863e-05</v>
+        <v>9.450745645859684e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.271323031437632e-06</v>
+        <v>4.401866047558408e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.344977211299945e-06</v>
+        <v>4.479184186631666e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.328958473075953e-06</v>
+        <v>4.4590784463747e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.283224311700266e-06</v>
+        <v>4.413237643069713e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.354687525821228e-06</v>
+        <v>4.484811388084536e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.484876223375566e-06</v>
+        <v>4.610618150289805e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.268670071379963e-06</v>
+        <v>4.399013038086913e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.35668736399498e-06</v>
+        <v>4.487862579982329e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.444330962014268e-06</v>
+        <v>4.583198558084343e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.834133211091193e-06</v>
+        <v>4.965337329781462e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.536234632023764e-06</v>
+        <v>4.759783327412081e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.455721862476973e-06</v>
+        <v>4.589574262298083e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.281710303743211e-06</v>
+        <v>4.412062186607558e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.870066142131161e-06</v>
+        <v>6.048625973995033e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.312176848183761e-06</v>
+        <v>4.442188686134294e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.341476083543752e-06</v>
+        <v>4.471873516134038e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.287309025475328e-06</v>
+        <v>4.418510438114024e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.642406886762274e-06</v>
+        <v>4.77242581285381e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.302561799827793e-06</v>
+        <v>4.433939091044571e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.341291793801287e-06</v>
+        <v>6.861202449010404e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.389192352580347e-06</v>
+        <v>4.523240934066826e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.26604463129303e-06</v>
+        <v>6.444106434108584e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.291928062880772e-06</v>
+        <v>6.422293111537044e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.514840916147759e-06</v>
+        <v>5.645729194441397e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.023369512384902e-06</v>
+        <v>5.192618228323531e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.476094917977904e-06</v>
+        <v>4.606733076987543e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.474450332637227e-06</v>
+        <v>4.610797978038759e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.245577169125799e-06</v>
+        <v>4.378943745152211e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.328874811851921e-06</v>
+        <v>4.464866620287292e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.659358153787601e-06</v>
+        <v>4.789793552687528e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.32580999938686e-06</v>
+        <v>4.45569651886084e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.843093356489327e-06</v>
+        <v>4.973530843629129e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.761972299064684e-06</v>
+        <v>5.861369487981711e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.22869278068697e-06</v>
+        <v>4.360699743132041e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.857496521021381e-06</v>
+        <v>4.995438566988343e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.477583933466285e-06</v>
+        <v>5.670080247654557e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.248114252763027e-06</v>
+        <v>8.386342759308511e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.129314584171927e-06</v>
+        <v>6.923081444998248e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>5.587216967512274e-06</v>
+        <v>5.745251048248333e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.319333084665143e-06</v>
+        <v>4.451323951150636e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.050610102775731e-06</v>
+        <v>7.26176630029803e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.535870483237765e-06</v>
+        <v>4.665476732085817e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.746464677372428e-06</v>
+        <v>4.87883855468794e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.361121692563102e-06</v>
+        <v>4.499244888348632e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>6.87978056894488e-06</v>
+        <v>7.009456499551382e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.469698988927398e-06</v>
+        <v>4.609060750254371e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>9.695617076764396e-06</v>
+        <v>1.229430001135117e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.083850918835875e-06</v>
+        <v>5.242149987809425e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.120133977175379e-06</v>
+        <v>8.334111483095437e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.86483764960527e-05</v>
+        <v>1.878053392007128e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.312809227963305e-05</v>
+        <v>1.326390840273539e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.575054314104626e-06</v>
+        <v>5.86430744334864e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.707207758081268e-06</v>
+        <v>5.841234095083981e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.69797330140231e-06</v>
+        <v>5.87358017653182e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.658950612102253e-06</v>
+        <v>4.469827098429037e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.578109791762729e-06</v>
+        <v>4.381547365752254e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.309969439020118e-06</v>
+        <v>5.116067462062754e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.793381047528206e-06</v>
+        <v>4.598274500921573e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.600590925727142e-06</v>
+        <v>5.406732876413419e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>7.071132154363084e-06</v>
+        <v>6.82777812949178e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.628984207828934e-06</v>
+        <v>4.437601043999284e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.623180017870599e-06</v>
+        <v>5.441197492516606e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>6.597746477363216e-06</v>
+        <v>6.50266278285582e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.101615049676317e-05</v>
+        <v>1.083449444073395e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.651249006079731e-06</v>
+        <v>8.512667424459674e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.781913343713011e-06</v>
+        <v>6.631884310960313e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>5.001735728902383e-06</v>
+        <v>4.809448122115711e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>5.120413265934016e-06</v>
+        <v>4.925289850473799e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.451361607639369e-06</v>
+        <v>5.260593661017415e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.83951976867865e-06</v>
+        <v>4.657833146552628e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.850513465001337e-06</v>
+        <v>8.655470113354386e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.011806871612561e-06</v>
+        <v>4.832106878933936e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>8.87581682420321e-06</v>
+        <v>1.245785848067782e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.890816217579371e-06</v>
+        <v>5.741375649705438e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>5.858157841121693e-06</v>
+        <v>5.673529329350794e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.748261396649044e-05</v>
+        <v>2.729148022843673e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.871081540613277e-05</v>
+        <v>1.851393344024364e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.83875391643612e-06</v>
+        <v>4.840913720819224e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.971943270296488e-06</v>
+        <v>6.783894439320717e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.943838758853882e-06</v>
+        <v>6.821333021907371e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.442457645966381e-05</v>
+        <v>1.451205819276193e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.459416715429793e-05</v>
+        <v>1.460304460634862e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.720025912272798e-05</v>
+        <v>2.724888174425884e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.436281319130815e-05</v>
+        <v>1.450011349217775e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.239514079897597e-05</v>
+        <v>3.243123882454707e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.307452026932167e-05</v>
+        <v>5.235635749681576e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.495689015276741e-05</v>
+        <v>1.503972276777812e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.286214927730993e-05</v>
+        <v>3.310880111508135e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.754247271229448e-05</v>
+        <v>4.914627604237795e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001194685181667533</v>
+        <v>0.000119762495691541</v>
       </c>
       <c r="L5" t="n">
-        <v>6.374670948077347e-05</v>
+        <v>8.066010983268886e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.393817720897775e-05</v>
+        <v>5.477790014077314e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.023808505306237e-05</v>
+        <v>2.030376700390108e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.19217270849289e-05</v>
+        <v>2.191900942969315e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.854418706487973e-05</v>
+        <v>2.86265978885583e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.837054001402636e-05</v>
+        <v>1.861941088190483e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.117946480413373e-05</v>
+        <v>8.118805785098443e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.127131570366005e-05</v>
+        <v>2.154667492740118e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>8.203293692164713e-05</v>
+        <v>0.0001413690673127232</v>
       </c>
       <c r="V5" t="n">
-        <v>3.633607082170737e-05</v>
+        <v>3.707894167193595e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.533992422160958e-05</v>
+        <v>3.550130358452603e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004085843718868731</v>
+        <v>0.000408667916713404</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002667222015475371</v>
+        <v>0.0002668710900339976</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.799528559469033e-05</v>
+        <v>2.099261384835339e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.541835997313039e-05</v>
+        <v>5.551485861526e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.89011850725058e-05</v>
+        <v>6.029175054798787e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1065147418428e-06</v>
+        <v>4.94758493099162e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.025673921503285e-06</v>
+        <v>6.648714888092974e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.514743021291163e-06</v>
+        <v>5.593825294625339e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.240945177268751e-06</v>
+        <v>6.865442023262291e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.048155055467698e-06</v>
+        <v>7.673900398754141e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.275905736634126e-06</v>
+        <v>7.305535962054382e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.833757790099973e-06</v>
+        <v>4.915358876561868e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.827953600141651e-06</v>
+        <v>5.918955325079191e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.802520059634254e-06</v>
+        <v>8.769830305196543e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.146371462650374e-05</v>
+        <v>1.131225227329651e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>9.856022588350769e-06</v>
+        <v>1.077983494680038e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>8.98668692598407e-06</v>
+        <v>7.109642143522895e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>7.211278300856154e-06</v>
+        <v>7.089442414254805e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>7.330334173296945e-06</v>
+        <v>5.365354890351046e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.656135189910415e-06</v>
+        <v>5.738351493580014e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>7.044293350949693e-06</v>
+        <v>5.135590979115221e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.105528704727238e-05</v>
+        <v>1.092263763569511e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.459371001353103e-06</v>
+        <v>5.309864711496533e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.107483216673389e-05</v>
+        <v>1.473092611056498e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>8.095589799850408e-06</v>
+        <v>6.219133482268045e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.357271533841575e-06</v>
+        <v>6.204753920709988e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.793017809623099e-05</v>
+        <v>2.955864775077748e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.920404540708967e-05</v>
+        <v>1.905468528218868e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.286318046176667e-06</v>
+        <v>5.318671553381821e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.419507400037043e-06</v>
+        <v>9.051061961661454e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.404566169111893e-06</v>
+        <v>7.311822592611961e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.196066655620269e-06</v>
+        <v>7.034764896024514e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.115225835280751e-06</v>
+        <v>6.946485163347728e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.847085482538123e-06</v>
+        <v>7.681005259658218e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.330497091046219e-06</v>
+        <v>7.163212298517041e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.137706969245173e-06</v>
+        <v>7.97167067400889e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.608248197881108e-06</v>
+        <v>9.392715927087248e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.166100251346953e-06</v>
+        <v>7.00253884159474e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.160296061388624e-06</v>
+        <v>8.006135290112061e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>9.134862520881229e-06</v>
+        <v>9.067600580451287e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.355326654028121e-05</v>
+        <v>1.33994322383294e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.018836504959774e-05</v>
+        <v>1.107760522205513e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>9.319029387231032e-06</v>
+        <v>9.19682210855578e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>7.537422588512296e-06</v>
+        <v>7.372958248571013e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>7.656100125543936e-06</v>
+        <v>7.488799976929096e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.98847765115739e-06</v>
+        <v>7.82553145861288e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.376635812196662e-06</v>
+        <v>7.222770944148084e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.138762950851936e-05</v>
+        <v>1.122040791094985e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>7.548922915130574e-06</v>
+        <v>7.397044676529405e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.141447491618778e-05</v>
+        <v>1.503250459586861e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.427932261097388e-06</v>
+        <v>8.306313447300912e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.395273884639713e-06</v>
+        <v>8.238467126946258e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>3.001973001000847e-05</v>
+        <v>2.985641802603219e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.124217320991044e-05</v>
+        <v>2.108477134538551e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.375869959954139e-06</v>
+        <v>7.405851518414682e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.509059313814514e-06</v>
+        <v>9.348832236916186e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.480954802371899e-06</v>
+        <v>9.386270819502841e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.35526565676509e-05</v>
+        <v>1.341878432520252e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.942052195536894e-05</v>
+        <v>1.932956822222484e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015238160262628e-05</v>
+        <v>2.006408831853534e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.646828263112165e-05</v>
+        <v>1.63519709358782e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.542103578454992e-05</v>
+        <v>1.529027410417638e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.314704730246064e-05</v>
+        <v>2.301974390985344e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.947139637143509e-05</v>
+        <v>1.938562190047185e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.046559218147679e-05</v>
+        <v>2.038921834898918e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.144015864096937e-05</v>
+        <v>2.145068363932843e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.585856266036935e-05</v>
+        <v>2.578251529720651e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.249366116968587e-05</v>
+        <v>2.346068828093223e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.162432550731987e-05</v>
+        <v>2.157990516743209e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65001148646786e-05</v>
+        <v>1.638512779824453e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.630816873802404e-05</v>
+        <v>1.61877163488812e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.317601102061471e-05</v>
+        <v>1.303059796260912e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.968193193228482e-05</v>
+        <v>1.960585400302521e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36929256286075e-05</v>
+        <v>2.360349096982695e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.985421903521874e-05</v>
+        <v>1.978012773540652e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.081575177125701e-05</v>
+        <v>2.448777423508799e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.911481901578696e-05</v>
+        <v>1.905423746291554e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.070173909637133e-05</v>
+        <v>2.062272917380337e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.575247412395047e-05</v>
+        <v>3.561131063205949e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.947370567478937e-05</v>
+        <v>3.943952833263075e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.362195960007472e-05</v>
+        <v>1.367843526075527e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.181435543390266e-05</v>
+        <v>2.173191529579328e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.800017197987438e-05</v>
+        <v>2.803587747319176e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.447916128752375e-05</v>
+        <v>1.544581393939291e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.724374551325694e-05</v>
+        <v>1.852923318494656e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.797560516051432e-05</v>
+        <v>1.926375328125703e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.680230433318779e-05</v>
+        <v>1.801394523873252e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.170674522652295e-05</v>
+        <v>1.224278673267824e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.973676795194386e-05</v>
+        <v>2.097546408606475e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.729461992932312e-05</v>
+        <v>1.858528686319358e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.828881573936479e-05</v>
+        <v>1.958888331171089e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.926338219885743e-05</v>
+        <v>2.065034860205013e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.368178621825739e-05</v>
+        <v>2.498218025992823e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.031688472757393e-05</v>
+        <v>2.266035324365398e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.94475490652072e-05</v>
+        <v>2.077957013015463e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.630355218413735e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.861034168622113e-05</v>
+        <v>2.00082310126365e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.893409905433482e-05</v>
+        <v>2.035266829032433e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.811699740522014e-05</v>
+        <v>1.940827961759041e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.750515549017284e-05</v>
+        <v>1.880551896574692e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151614918649555e-05</v>
+        <v>2.280315593254868e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.767744259310675e-05</v>
+        <v>1.897979269812822e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.153569430595704e-05</v>
+        <v>2.661144440741855e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.184001107912946e-05</v>
+        <v>2.354913386183999e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.85237935626159e-05</v>
+        <v>1.982121514854511e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.014824968798464e-05</v>
+        <v>4.1439166047631e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.137069288788661e-05</v>
+        <v>3.266751936698437e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.578885139042964e-05</v>
+        <v>1.707634714917018e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.963757899179069e-05</v>
+        <v>2.0931580258515e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.960947448034806e-05</v>
+        <v>2.096901884110167e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.121015144822271e-05</v>
+        <v>1.364490944465745e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.587388217380602e-06</v>
+        <v>7.506116183943391e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.460262558407124e-06</v>
+        <v>8.579792731974477e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.97787245409505e-06</v>
+        <v>9.119044746848664e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.923262331357504e-06</v>
+        <v>8.117685594423573e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73958606211981e-06</v>
+        <v>8.530126040192682e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.60703899334785e-06</v>
+        <v>7.647132486103402e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.776611283340867e-06</v>
+        <v>7.904014330001942e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.86071643853175e-06</v>
+        <v>9.416062225129337e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.81837285004696e-06</v>
+        <v>8.04505652903338e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>9.006671204798032e-06</v>
+        <v>1.833606125008905e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.885508191097283e-06</v>
+        <v>1.11359214031397e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>6.729598403223553e-06</v>
+        <v>7.873391584069865e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.047725754346055e-05</v>
+        <v>1.155013881611063e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.196881081550625e-06</v>
+        <v>1.073899501345032e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.852740459296484e-06</v>
+        <v>8.712399445613875e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.615898941715933e-06</v>
+        <v>7.669623994365992e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.189442743370948e-06</v>
+        <v>1.072453980538773e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>7.18906419845706e-06</v>
+        <v>8.725552650705776e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.271132345393601e-05</v>
+        <v>1.617126326617265e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.095879944670729e-06</v>
+        <v>8.46237624432364e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.930135415107289e-06</v>
+        <v>1.081411541635466e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>7.793841863446425e-06</v>
+        <v>1.127124018446691e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.406449467153199e-06</v>
+        <v>8.503997410502426e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.098046154111948e-06</v>
+        <v>1.238628228262276e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.957179988042525e-06</v>
+        <v>9.410688330332556e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.040668576763918e-05</v>
+        <v>1.215634477565373e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.913382333810874e-05</v>
+        <v>5.014093724670905e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.245688382512738e-06</v>
+        <v>6.960536291446442e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.253403572545331e-05</v>
+        <v>1.420207240743452e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>9.063609466409635e-06</v>
+        <v>1.8017399568888e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.691748459048445e-06</v>
+        <v>1.089591158337432e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.448234151278035e-05</v>
+        <v>1.380374001524111e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.428558027956757e-06</v>
+        <v>7.528697465866859e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.641289598320715e-06</v>
+        <v>9.36636483292247e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.536410011236532e-05</v>
+        <v>2.013475602207728e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.93555705745346e-06</v>
+        <v>1.036294979984593e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.35469201992719e-05</v>
+        <v>8.379482128160311e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.98171016161708e-05</v>
+        <v>3.249945156897675e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>7.301035184466264e-06</v>
+        <v>9.14082631588029e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.772750458794723e-05</v>
+        <v>1.846041267450953e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.773265110673871e-05</v>
+        <v>2.951513952454229e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.181837251654649e-06</v>
+        <v>1.5138336197225e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>6.490588296631805e-06</v>
+        <v>7.688227160719979e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.768528389783413e-05</v>
+        <v>2.942165348254083e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.059265148801418e-05</v>
+        <v>1.524514296079533e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>3.714487716509796e-05</v>
+        <v>5.580225021667888e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>9.89626425934622e-06</v>
+        <v>1.330890660088092e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.638268128953115e-05</v>
+        <v>1.716974433841963e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.491286588985325e-05</v>
+        <v>3.344064125760837e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.212924922827875e-05</v>
+        <v>1.363721874327406e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.659842086189355e-05</v>
+        <v>2.918293550795815e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.606260168973802e-05</v>
+        <v>2.011196539005801e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.348816430717332e-05</v>
+        <v>3.971134309484334e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.086226019423789e-05</v>
+        <v>7.553370883875115e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.543389807942084e-06</v>
+        <v>7.064614733230362e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.850554014965544e-05</v>
+        <v>1.832088550019088e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.305672201103935e-05</v>
+        <v>2.441198507637776e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.243987555282085e-05</v>
+        <v>1.310117280176763e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.166062761925027e-05</v>
+        <v>1.775987736870862e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.867987480079396e-06</v>
+        <v>7.78605897816701e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.07833845026579e-05</v>
+        <v>1.068765757648738e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.300935298303653e-05</v>
+        <v>2.774722903189747e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.125510060987351e-05</v>
+        <v>1.228079409716469e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.597293719376439e-05</v>
+        <v>0.0001285224265175506</v>
       </c>
       <c r="M4" t="n">
-        <v>4.573674409142977e-05</v>
+        <v>4.717115620798103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02523523947395e-05</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.906144512970825e-05</v>
+        <v>1.711393082697151e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.682598522982357e-05</v>
+        <v>4.271006855158363e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.164329856622785e-05</v>
+        <v>1.981873933285011e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.968064672674486e-06</v>
+        <v>8.040110910597913e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.674196577827951e-05</v>
+        <v>4.254679032679249e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.544222991661034e-05</v>
+        <v>1.996731083513637e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.133139514083143e-05</v>
+        <v>7.827865340915602e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.426267741892083e-05</v>
+        <v>1.686645640734767e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.807370322915143e-05</v>
+        <v>1.688145643741807e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.22734718541362e-05</v>
+        <v>4.872202260309128e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.778256105726454e-05</v>
+        <v>1.739893305498109e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.139855668318678e-05</v>
+        <v>3.638780221200389e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.411845111069872e-05</v>
+        <v>2.770623351450499e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.140011649344542e-05</v>
+        <v>5.838830997643387e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009327056673932265</v>
+        <v>0.001214901475220816</v>
       </c>
       <c r="C5" t="n">
-        <v>2.483179884803366e-05</v>
+        <v>2.663176829515914e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002226798421557117</v>
+        <v>0.0002505448779189134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001043131851150525</v>
+        <v>0.0003471719393478254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000102601789143184</v>
+        <v>0.000147357813193323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002571756160501707</v>
+        <v>0.0002155452544172926</v>
       </c>
       <c r="H5" t="n">
-        <v>3.156739401773554e-05</v>
+        <v>4.193646292885767e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>6.916595630731344e-05</v>
+        <v>9.918486077229393e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002926172355293326</v>
+        <v>0.0004092124286815845</v>
       </c>
       <c r="K5" t="n">
-        <v>7.597901291513547e-05</v>
+        <v>0.0001237238325579212</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005396534903402466</v>
+        <v>0.002312965666779955</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007723584521286206</v>
+        <v>0.0008329271147746611</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007721089146791041</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002016877652980339</v>
+        <v>0.0001951753354818429</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003473738273295609</v>
+        <v>0.0006575978462746063</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.387342523081862e-05</v>
+        <v>0.0002732173522362754</v>
       </c>
       <c r="R5" t="n">
-        <v>3.279024553501038e-05</v>
+        <v>4.618761497249733e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000348966709845574</v>
+        <v>0.0006598949844180296</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001615177968427873</v>
+        <v>0.0002832185126986505</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0008133030928966284</v>
+        <v>0.001337497563802536</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001240667789748078</v>
+        <v>0.0001946631610080075</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002041800864204672</v>
+        <v>0.0002114625731581013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002928435066672335</v>
+        <v>0.0008418144374286504</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001996634394841983</v>
+        <v>0.00022106570476243</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000252767592425758</v>
+        <v>0.0005488809441202316</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000318820564546674</v>
+        <v>0.0004167398782941611</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009199629683963473</v>
+        <v>0.001098946544373159</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.18663321631916e-05</v>
+        <v>7.708631644214064e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.268745755534521e-05</v>
+        <v>1.210063034903614e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.264960789705855e-05</v>
+        <v>1.987349310358045e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.406079397999308e-05</v>
+        <v>2.944800069218352e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.34439475217746e-05</v>
+        <v>1.465378040515723e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2664699588204e-05</v>
+        <v>2.279589298451438e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.30120552274825e-05</v>
+        <v>1.282207459397278e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.178745647161166e-05</v>
+        <v>1.572367319229316e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.715342073043961e-05</v>
+        <v>3.278324464770327e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.539916835727665e-05</v>
+        <v>1.383340170055427e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.697700916271825e-05</v>
+        <v>0.0001335584421333562</v>
       </c>
       <c r="M6" t="n">
-        <v>4.674081606038347e-05</v>
+        <v>5.22071718237867e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.133250577119792e-05</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.320973623126434e-05</v>
+        <v>1.872142300303982e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.097443010326137e-05</v>
+        <v>4.772155503494909e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.578736631363097e-05</v>
+        <v>2.13713469362397e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31121324200776e-05</v>
+        <v>1.307612652640369e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.088603352568265e-05</v>
+        <v>4.409939793018198e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.644630188556407e-05</v>
+        <v>2.151991843852592e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.245060258121797e-05</v>
+        <v>7.989707043415806e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.840674516632396e-05</v>
+        <v>1.841906401073725e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.222185561070134e-05</v>
+        <v>1.850620325923894e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.641753960153935e-05</v>
+        <v>5.375803821889702e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.903907075176442e-05</v>
+        <v>1.915571021462037e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.554262443058995e-05</v>
+        <v>3.794040981539348e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.51225230796525e-05</v>
+        <v>3.274224913031075e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.263345150029194e-05</v>
+        <v>6.014457324433118e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.477589288676423e-05</v>
+        <v>7.976667016665171e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.245702250046846e-05</v>
+        <v>1.129757606113093e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.241917284218184e-05</v>
+        <v>2.255384682809144e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.697035470356575e-05</v>
+        <v>2.864494640427833e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.635350824534723e-05</v>
+        <v>1.733413412966819e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.557426031177666e-05</v>
+        <v>2.199283869660917e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.27816201726058e-05</v>
+        <v>1.201902030606757e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.469701719518432e-05</v>
+        <v>1.492061890438793e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.692298567556291e-05</v>
+        <v>3.198019035979806e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.516873330239994e-05</v>
+        <v>1.651375542506522e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.988656988629085e-05</v>
+        <v>0.0001327553878454511</v>
       </c>
       <c r="M7" t="n">
-        <v>4.965037678395615e-05</v>
+        <v>5.140411753588151e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.416598508726589e-05</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.297353909871171e-05</v>
+        <v>2.134534935223283e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.073807919882706e-05</v>
+        <v>4.694148707684492e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.555693125875421e-05</v>
+        <v>2.405170066075066e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.288169736520088e-05</v>
+        <v>1.227307223849847e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.06555984708059e-05</v>
+        <v>4.677975165469299e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.935586260913672e-05</v>
+        <v>2.420027216303692e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>5.535619820362493e-05</v>
+        <v>8.257071680651965e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.817631011144725e-05</v>
+        <v>2.109941773524823e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.198733592167784e-05</v>
+        <v>2.111441776531858e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.618710454666264e-05</v>
+        <v>5.295498393099191e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.181132922122372e-05</v>
+        <v>2.169770380449416e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.531218937571319e-05</v>
+        <v>4.062076353990444e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.803208380322513e-05</v>
+        <v>3.193919484240554e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.531374918597173e-05</v>
+        <v>6.262127130433445e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.254010771146578e-05</v>
+        <v>8.793017408859732e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.819200275261803e-05</v>
+        <v>2.788931680751651e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.815415309433136e-05</v>
+        <v>3.914558757447705e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.846113748842342e-05</v>
+        <v>4.074889965910929e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.535947516738905e-05</v>
+        <v>2.681065884598075e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.296203070004088e-05</v>
+        <v>4.033222925339926e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.851660042475532e-05</v>
+        <v>2.861076105245315e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.043199744733387e-05</v>
+        <v>3.151235965077355e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.265796592771246e-05</v>
+        <v>4.857193110618362e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.09037135545495e-05</v>
+        <v>3.310549617145084e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.562155013844037e-05</v>
+        <v>0.0001493471285918364</v>
       </c>
       <c r="M8" t="n">
-        <v>6.538535703610578e-05</v>
+        <v>6.799585828226701e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.372228865322574e-05</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.422933539027025e-05</v>
+        <v>3.320074514477713e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.157766593613914e-05</v>
+        <v>5.835678552576964e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.175470875306345e-05</v>
+        <v>3.055886368161626e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.861667761735044e-05</v>
+        <v>2.886481298488406e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.639057872295546e-05</v>
+        <v>6.33714924010785e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.509084286128628e-05</v>
+        <v>4.079201290942249e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.72028389534912e-05</v>
+        <v>9.505145260234877e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.173068598032e-05</v>
+        <v>3.538317974599e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.772388265792583e-05</v>
+        <v>3.770781490168028e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.311541853072827e-05</v>
+        <v>6.023461160394027e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.546824332318171e-05</v>
+        <v>4.666260164594128e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.292834314039427e-05</v>
+        <v>4.862770863579423e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.37670640553747e-05</v>
+        <v>4.853093558879111e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.937486043190676e-05</v>
+        <v>8.801701017146601e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.959339636499613e-05</v>
+        <v>9.615880634240486e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.269445597597735e-05</v>
+        <v>3.363380128185881e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.265660631769072e-05</v>
+        <v>4.489007204881932e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.595688797708598e-05</v>
+        <v>4.960930091786147e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.40965280226449e-05</v>
+        <v>2.596761045016239e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.581169058123875e-05</v>
+        <v>4.432906495599791e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.301905364811472e-05</v>
+        <v>3.435524552679547e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.49344506706932e-05</v>
+        <v>3.72568441251158e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.716041915107178e-05</v>
+        <v>5.4316415580526e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.54061667779088e-05</v>
+        <v>3.884998064579315e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>6.012400336179974e-05</v>
+        <v>0.000155091613066179</v>
       </c>
       <c r="M9" t="n">
-        <v>6.988781025946508e-05</v>
+        <v>7.374034275660951e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.440341856277475e-05</v>
+        <v>8.876134756871438e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.500866473354421e-05</v>
+        <v>4.565298208487886e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.316383808638447e-05</v>
+        <v>7.167753136066266e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.57943615282163e-05</v>
+        <v>4.638792692013942e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.311913084070975e-05</v>
+        <v>3.460929745922637e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>5.089303194631484e-05</v>
+        <v>6.911597687542084e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.959329608464561e-05</v>
+        <v>4.65364973837648e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>7.55975967802995e-05</v>
+        <v>0.0001049136493793969</v>
       </c>
       <c r="V9" t="n">
-        <v>4.466821246863147e-05</v>
+        <v>5.02949836707131e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.222476939718678e-05</v>
+        <v>4.345064298604647e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.642453802217154e-05</v>
+        <v>7.529120915171977e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.204876269673263e-05</v>
+        <v>4.403392902522204e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.228188574875921e-05</v>
+        <v>5.937323204797552e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.826951727873402e-05</v>
+        <v>5.427542006313347e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.555118266148066e-05</v>
+        <v>8.495749652506232e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.062154625500508e-05</v>
+        <v>1.291797728592632e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.795556347628081e-06</v>
+        <v>7.896464213325457e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.06470017546036e-06</v>
+        <v>9.384184635885466e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.13516381878165e-06</v>
+        <v>9.187882020338689e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.386453941987961e-06</v>
+        <v>8.869504405484768e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.953563746098772e-06</v>
+        <v>8.940046641095685e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.766194582325719e-06</v>
+        <v>7.952092288189629e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.801625550925555e-06</v>
+        <v>9.581397712842936e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.119563614515835e-06</v>
+        <v>9.913630836835545e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.508322898954705e-06</v>
+        <v>1.060571958614869e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.276652197153162e-06</v>
+        <v>1.763814986626275e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.860725848468519e-06</v>
+        <v>1.123569618636443e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>7.028390602685117e-06</v>
+        <v>8.424638994852161e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.061195930220728e-05</v>
+        <v>1.196699615783571e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.473527662166052e-06</v>
+        <v>1.11797415391358e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.114158268486982e-06</v>
+        <v>9.139770264663518e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.809898932090035e-06</v>
+        <v>8.045511010969437e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.467612996490669e-06</v>
+        <v>1.103694247547979e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>7.542288874222833e-06</v>
+        <v>9.324161432421288e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.104502539482154e-05</v>
+        <v>1.70425276128072e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.654939260242001e-06</v>
+        <v>9.430234323498103e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.002992958542729e-05</v>
+        <v>1.176154932148978e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>9.476200734250443e-06</v>
+        <v>1.313203912818558e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.576252603148445e-06</v>
+        <v>9.924944854842971e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.482921142135531e-06</v>
+        <v>1.297889350868897e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.985577102394553e-06</v>
+        <v>9.977238128771475e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.052192585550223e-05</v>
+        <v>1.236394655471017e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.36752277699589e-05</v>
+        <v>4.252928113933592e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.474451652606715e-06</v>
+        <v>7.334755611013689e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.554587167959907e-05</v>
+        <v>1.745723742929842e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.880673565628648e-06</v>
+        <v>1.602161294835468e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.069370579617561e-05</v>
+        <v>1.377483651455417e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.469722008245827e-05</v>
+        <v>1.423502870725791e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.256109068542011e-06</v>
+        <v>7.211771307818342e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.367100410656698e-05</v>
+        <v>1.887982165692932e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.59026946526673e-05</v>
+        <v>2.119004733486741e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.864757365587056e-05</v>
+        <v>2.608363564361066e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.416301380524334e-05</v>
+        <v>7.630669831159268e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.835527653500691e-05</v>
+        <v>3.074530083495684e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.128542809861462e-06</v>
+        <v>1.058747550340642e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.755369525446587e-05</v>
+        <v>1.860379978234935e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.839239828258786e-05</v>
+        <v>3.015643765153794e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.73988084517764e-06</v>
+        <v>1.56900106706558e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>6.56875278628842e-06</v>
+        <v>7.880784567618127e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.835787536194602e-05</v>
+        <v>2.915409514375114e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.18112832056308e-05</v>
+        <v>1.703343765205918e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.423245848893626e-05</v>
+        <v>5.846773836414369e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.256240362483997e-05</v>
+        <v>1.76984162984041e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.569548914607585e-05</v>
+        <v>2.032235107914814e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.562913388976521e-05</v>
+        <v>4.42420564204122e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.917156024749986e-05</v>
+        <v>2.128878927834943e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.755466166753019e-05</v>
+        <v>3.02466513290377e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.496025023055835e-05</v>
+        <v>2.166844614540824e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.302381157151344e-05</v>
+        <v>3.872742543965345e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.209138558051581e-05</v>
+        <v>6.337101846032988e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.868773154857662e-06</v>
+        <v>7.677161625596517e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.321063290475014e-05</v>
+        <v>2.345520485318387e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.271109214821409e-05</v>
+        <v>2.12378765069193e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.554952968899762e-05</v>
+        <v>1.764165488620545e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.195529580982788e-05</v>
+        <v>1.843846188846229e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.543414888210031e-06</v>
+        <v>7.279062990932135e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.023908400032322e-05</v>
+        <v>2.568281727991705e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.381276687481845e-05</v>
+        <v>2.941934240589133e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.822155564315424e-05</v>
+        <v>3.72530040502474e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.690018851524554e-05</v>
+        <v>0.000116687539141895</v>
       </c>
       <c r="M4" t="n">
-        <v>4.337961942148289e-05</v>
+        <v>4.439797991536718e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.150503955429795e-05</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O4" t="n">
-        <v>1.88147524434839e-05</v>
+        <v>1.716698340082859e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.782852743702693e-05</v>
+        <v>4.373684607238141e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.247382479460581e-05</v>
+        <v>2.069443209406711e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>9.037075623792356e-06</v>
+        <v>8.334270439465838e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.776171856734268e-05</v>
+        <v>4.212386495757211e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.730975693620071e-05</v>
+        <v>2.277721515801891e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.100087387507083e-05</v>
+        <v>8.213790601952473e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.846823202942515e-05</v>
+        <v>2.387091441876718e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.688645581688494e-05</v>
+        <v>2.132400762640709e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>3.915418103862168e-05</v>
+        <v>6.578894544196114e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.89183742569907e-05</v>
+        <v>2.958895864503118e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.268304288465011e-05</v>
+        <v>3.786161941513921e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.231690139606074e-05</v>
+        <v>3.015401687341738e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.061092552103769e-05</v>
+        <v>5.682684708310243e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007390432015790096</v>
+        <v>0.0009461018276795289</v>
       </c>
       <c r="C5" t="n">
-        <v>2.61120676860602e-05</v>
+        <v>2.687482862502744e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002898987608279491</v>
+        <v>0.0003172421228735223</v>
       </c>
       <c r="E5" t="n">
-        <v>8.810576758410343e-05</v>
+        <v>0.0002600929211173594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001484457791058751</v>
+        <v>0.0002097027830454976</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002389525342959427</v>
+        <v>0.0002013713951886604</v>
       </c>
       <c r="H5" t="n">
-        <v>1.894733309056146e-05</v>
+        <v>1.841709381549289e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002387459566884802</v>
+        <v>0.0003644480061396054</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002828385508722687</v>
+        <v>0.0003992250233274895</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003451227587167158</v>
+        <v>0.0005137279059323078</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005151167190267102</v>
+        <v>0.001935375202271077</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006752081809133827</v>
+        <v>0.0007176664536588288</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003823754720323937</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00018014904747074</v>
+        <v>0.0001736035653988387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003346267320764228</v>
+        <v>0.0006159569277379084</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.863807157540764e-05</v>
+        <v>0.0002565826427052115</v>
       </c>
       <c r="R5" t="n">
-        <v>2.805352245044624e-05</v>
+        <v>3.826130516882004e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000337430432570028</v>
+        <v>0.0005961460261983438</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001823641382241793</v>
+        <v>0.0003076287951550497</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0004019417849974067</v>
+        <v>0.001291170883482108</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001773562821128626</v>
+        <v>0.0002810031144467811</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001663281826568339</v>
+        <v>0.0002671063488199223</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005767126112093341</v>
+        <v>0.001084741137917361</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003789919707540751</v>
+        <v>0.0004108260630158606</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002411899933351477</v>
+        <v>0.0004986040824008544</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002632523884866485</v>
+        <v>0.0004246090504142525</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0008437457036518711</v>
+        <v>0.0009898433456973317</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3153488844999e-05</v>
+        <v>6.843363320671932e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.930876419340834e-06</v>
+        <v>9.437959102405934e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.728853295104722e-05</v>
+        <v>2.851781959957328e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.377319541269729e-05</v>
+        <v>2.630049125330873e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.962742973529465e-05</v>
+        <v>1.940245236301486e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.301739907431104e-05</v>
+        <v>2.019925936527171e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.605518152693205e-06</v>
+        <v>9.039860467741568e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.130118726480645e-05</v>
+        <v>2.744361475672649e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.789066692111547e-05</v>
+        <v>3.448195715228078e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.229945568945127e-05</v>
+        <v>4.231561879663687e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.796229177972871e-05</v>
+        <v>0.0001217501538882845</v>
       </c>
       <c r="M6" t="n">
-        <v>4.745751946777996e-05</v>
+        <v>4.61587773921766e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.262807843950828e-05</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O6" t="n">
-        <v>1.993779132869417e-05</v>
+        <v>2.222485937652636e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.192289913275112e-05</v>
+        <v>4.879654524404244e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655172484090286e-05</v>
+        <v>2.575704684045653e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31149756700894e-05</v>
+        <v>1.009506791627526e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.882382183182583e-05</v>
+        <v>4.718647970396152e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.837186020068388e-05</v>
+        <v>2.453801263482836e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.213345578379401e-05</v>
+        <v>8.387308513960359e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.254613207572217e-05</v>
+        <v>2.893352916515661e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.806487207359312e-05</v>
+        <v>2.638165512401221e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.021628430310482e-05</v>
+        <v>6.754974291877061e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.018382645102395e-05</v>
+        <v>3.152117231394492e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.374514614913326e-05</v>
+        <v>4.292423416152858e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.639480144235778e-05</v>
+        <v>3.521663161980675e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.188414573604779e-05</v>
+        <v>5.878525111433373e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.574908876389575e-05</v>
+        <v>6.742623306130161e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.252647633823759e-05</v>
+        <v>1.173237622656833e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.68683360881301e-05</v>
+        <v>2.751041945415567e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.636879533159403e-05</v>
+        <v>2.529309110789109e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.920723287237756e-05</v>
+        <v>2.169686948717724e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.56129989932078e-05</v>
+        <v>2.249367648943411e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.220111807158996e-05</v>
+        <v>1.133427759190393e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.389678718370321e-05</v>
+        <v>2.973803188088886e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74704700581984e-05</v>
+        <v>3.34745570068631e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.187925882653416e-05</v>
+        <v>4.130821865121924e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>4.055789169862544e-05</v>
+        <v>0.000120742753742867</v>
       </c>
       <c r="M7" t="n">
-        <v>4.703732260486284e-05</v>
+        <v>4.845319451633899e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.516274273767792e-05</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O7" t="n">
-        <v>2.247101343919396e-05</v>
+        <v>2.12207452796876e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.148478843273707e-05</v>
+        <v>4.77906079512404e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.613152797798574e-05</v>
+        <v>2.47496466950389e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.269477880717229e-05</v>
+        <v>1.238948504043764e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.141942175072259e-05</v>
+        <v>4.617907955854393e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.096746011958063e-05</v>
+        <v>2.683242975899071e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.473189695136645e-05</v>
+        <v>8.616901482362794e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.212593521280511e-05</v>
+        <v>2.792612901973899e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.054415900026487e-05</v>
+        <v>2.537922222737886e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>4.281188422200158e-05</v>
+        <v>6.984416004293307e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.264655608461064e-05</v>
+        <v>3.361855488927229e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.634074606803004e-05</v>
+        <v>4.191683401611102e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.59746045794407e-05</v>
+        <v>3.420923147438919e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.426862870441756e-05</v>
+        <v>6.088206168407428e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.299449341544067e-05</v>
+        <v>7.506588133437598e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.721742590204967e-05</v>
+        <v>2.734361436893578e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.155928565194214e-05</v>
+        <v>4.312165759652314e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.709521185942784e-05</v>
+        <v>3.665969279214715e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.761256640336494e-05</v>
+        <v>3.057839829589998e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.184783079781479e-05</v>
+        <v>3.975787572124933e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.689206763540207e-05</v>
+        <v>2.694551573427142e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85877367475153e-05</v>
+        <v>4.534927002325632e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.216141962201044e-05</v>
+        <v>4.908579514923051e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.657020839034623e-05</v>
+        <v>5.691945679358663e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.524884126243749e-05</v>
+        <v>0.0001363539918852343</v>
       </c>
       <c r="M8" t="n">
-        <v>6.172827216867494e-05</v>
+        <v>6.406443265870587e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.408214938201743e-05</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29779323790581e-05</v>
+        <v>3.235225000400225e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.160292326432864e-05</v>
+        <v>5.850586007154922e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.191371311796231e-05</v>
+        <v>3.082269561626957e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.738572837098442e-05</v>
+        <v>2.800072318280511e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.611037131453467e-05</v>
+        <v>6.179031770091134e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.565840968339275e-05</v>
+        <v>4.244366790135822e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.578925372754707e-05</v>
+        <v>9.789021180703697e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.478556646233666e-05</v>
+        <v>4.136114610316567e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.52365718272083e-05</v>
+        <v>4.099202701513341e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.927646834783643e-05</v>
+        <v>7.664782101520598e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.474612028112888e-05</v>
+        <v>5.715969463830547e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.344784590027423e-05</v>
+        <v>4.940840591478699e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.066555414325279e-05</v>
+        <v>4.982046961675666e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.673707251561272e-05</v>
+        <v>8.48202920180037e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.871540418636196e-05</v>
+        <v>8.18595297393736e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.031564087258707e-05</v>
+        <v>3.151415214197051e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.465750062247954e-05</v>
+        <v>4.72921953695579e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.304486420472049e-05</v>
+        <v>4.384046103611114e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.587841690699792e-05</v>
+        <v>2.91489389776883e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.340216124176683e-05</v>
+        <v>4.227545397106338e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.999028260593942e-05</v>
+        <v>3.111605350730612e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.168595171805268e-05</v>
+        <v>4.951980779629104e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.525963459254788e-05</v>
+        <v>5.325633292226534e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.966842336088366e-05</v>
+        <v>6.108999456662145e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.834705623297492e-05</v>
+        <v>0.0001405245296582693</v>
       </c>
       <c r="M9" t="n">
-        <v>6.482648713921236e-05</v>
+        <v>6.823497043174122e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.295190727202737e-05</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O9" t="n">
-        <v>4.185990299863203e-05</v>
+        <v>4.277645501851206e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.122127758450087e-05</v>
+        <v>6.973180157830024e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.392069022654477e-05</v>
+        <v>4.453142417666814e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.048394334152176e-05</v>
+        <v>3.217126095583984e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.920858628507208e-05</v>
+        <v>6.596085547394612e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.875662465393008e-05</v>
+        <v>4.661420567439293e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>5.251822023704026e-05</v>
+        <v>0.0001059492781791682</v>
       </c>
       <c r="V9" t="n">
-        <v>4.54805529544771e-05</v>
+        <v>5.387992782204279e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.83333235346144e-05</v>
+        <v>4.516099814278109e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>6.060104875635103e-05</v>
+        <v>8.962593595833519e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.043572061896008e-05</v>
+        <v>5.34003308046745e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.122216054472874e-05</v>
+        <v>5.847395317866604e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.376376911379007e-05</v>
+        <v>5.399100738979139e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.205779323876703e-05</v>
+        <v>8.066383759947656e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.046298928647898e-05</v>
+        <v>1.283226936504508e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.221991753652202e-06</v>
+        <v>8.594550333543018e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.331765656039911e-06</v>
+        <v>9.885095614696939e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.429746831538261e-06</v>
+        <v>9.499589511773127e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.886052548831948e-06</v>
+        <v>9.673079757193272e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.284998576724714e-06</v>
+        <v>9.565657393399117e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.158861956036517e-06</v>
+        <v>8.610721306833858e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>8.33414651483725e-06</v>
+        <v>1.042306480285845e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.534690307561062e-06</v>
+        <v>1.060132320072687e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.138625890441605e-06</v>
+        <v>1.170451864896969e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.346372394787592e-06</v>
+        <v>1.655630602004336e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.929347689165091e-06</v>
+        <v>1.152871978751994e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>7.380850010033621e-06</v>
+        <v>9.00705128565478e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.055953035484369e-05</v>
+        <v>1.228915147167439e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>8.776423986253435e-06</v>
+        <v>1.157615077807971e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.625037326526697e-06</v>
+        <v>1.01668584127915e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>7.374697747369166e-06</v>
+        <v>8.975000245366141e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.804873237724188e-06</v>
+        <v>1.149726026968308e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>7.987015148410604e-06</v>
+        <v>1.001235689239288e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.132540912702256e-05</v>
+        <v>1.889057440498694e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>8.835708695231368e-06</v>
+        <v>1.132358983599318e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.067623099679071e-05</v>
+        <v>1.301448007201735e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.057790221227058e-05</v>
+        <v>1.44661952723592e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.006871719858707e-05</v>
+        <v>1.182246859080767e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.001355177021492e-05</v>
+        <v>1.3701103106792e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.441880187967673e-06</v>
+        <v>1.076845351318064e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.075609068273557e-05</v>
+        <v>1.278725210282569e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.015259208882605e-05</v>
+        <v>3.79065734534631e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.242806818218119e-06</v>
+        <v>8.455741757988827e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.50653649302909e-05</v>
+        <v>1.702958912347069e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.612978591038759e-06</v>
+        <v>1.424769870704374e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.189200728286976e-05</v>
+        <v>1.552817572270522e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.468548146534172e-05</v>
+        <v>1.471030783118629e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.69176477677295e-06</v>
+        <v>7.931688457728281e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.51004579390427e-05</v>
+        <v>2.089795108081442e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.648538983510462e-05</v>
+        <v>2.209702642984469e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.077360230847016e-05</v>
+        <v>2.993464803614659e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.226381473908655e-05</v>
+        <v>6.449183729966469e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.644558052364198e-05</v>
+        <v>2.88178227071949e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2770626610313e-06</v>
+        <v>1.076306822246217e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.556731781675961e-05</v>
+        <v>1.717404153862067e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.817104471843145e-05</v>
+        <v>2.897631391392813e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.001551497435035e-05</v>
+        <v>1.902548345849503e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.238620669666748e-06</v>
+        <v>1.054270875277552e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.839149052649009e-05</v>
+        <v>2.844920401343725e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.262010343518889e-05</v>
+        <v>1.796578050131755e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.319259016142386e-05</v>
+        <v>6.55785336372059e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.858234746489025e-05</v>
+        <v>2.716697067963721e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.711188957261426e-05</v>
+        <v>2.337308374468357e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.109227087534544e-05</v>
+        <v>4.971962443236551e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.747691971848294e-05</v>
+        <v>3.087326826589043e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.824309928754125e-05</v>
+        <v>3.060318621684737e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.585284505835085e-05</v>
+        <v>2.333952478448381e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.231248791633194e-05</v>
+        <v>3.774728478321177e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.638859136146267e-05</v>
+        <v>5.634739632510678e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.964307193267649e-06</v>
+        <v>9.756001200517333e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.231544004434541e-05</v>
+        <v>2.30577130480171e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.212672247243851e-05</v>
+        <v>1.870324427392365e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.728090546027165e-05</v>
+        <v>2.066289640540026e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.178718436956093e-05</v>
+        <v>1.944951138961631e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>9.066953190447966e-06</v>
+        <v>8.663068999558523e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.234233293971026e-05</v>
+        <v>2.913432250635473e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.459533163029218e-05</v>
+        <v>3.114025127618192e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.142929756595875e-05</v>
+        <v>4.360893319607482e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.377588990065919e-05</v>
+        <v>9.841210348481249e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.028221831111222e-05</v>
+        <v>4.168847350792728e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.157441037989493e-05</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O4" t="n">
-        <v>1.583588187640215e-05</v>
+        <v>1.524185422735398e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.733806043704335e-05</v>
+        <v>4.215895904223438e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.43326184513989e-05</v>
+        <v>2.6240353469786e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.150491774291874e-05</v>
+        <v>1.277776718687163e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.765940781970887e-05</v>
+        <v>4.126785445846769e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.842132446760243e-05</v>
+        <v>2.449518772267286e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>2.901349591084829e-05</v>
+        <v>9.307893224619377e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.792992855092705e-05</v>
+        <v>3.926011985203009e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.856580250383029e-05</v>
+        <v>2.548424863155933e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.768658572083542e-05</v>
+        <v>7.480334109127245e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.197197135087457e-05</v>
+        <v>4.5180359176052e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.330445072209269e-05</v>
+        <v>3.837310709894341e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35592343376567e-05</v>
+        <v>3.303564687610053e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.936671174331398e-05</v>
+        <v>5.557902680989331e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006179428569426784</v>
+        <v>0.0007844577704594451</v>
       </c>
       <c r="C5" t="n">
-        <v>3.759212685757273e-05</v>
+        <v>4.166853951805554e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002561298495483712</v>
+        <v>0.0002771094696214769</v>
       </c>
       <c r="E5" t="n">
-        <v>6.834237378307813e-05</v>
+        <v>0.0001842803226935625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001710859836099083</v>
+        <v>0.0002408445764852526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002228942925738237</v>
+        <v>0.0001928563919528359</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04984387477953e-05</v>
+        <v>2.115469735171166e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002659857246346879</v>
+        <v>0.0003995346209102987</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002820134414798807</v>
+        <v>0.000397224049879528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003912234158758626</v>
+        <v>0.0005990021147510425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000436621373185205</v>
+        <v>0.001531876627220592</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0005847446702435206</v>
+        <v>0.0006181006713594517</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003302240282170284</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001269316786558412</v>
+        <v>0.0001245663420029705</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003097918498241609</v>
+        <v>0.0005515053491208962</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001118857309218608</v>
+        <v>0.0003255948382965407</v>
       </c>
       <c r="R5" t="n">
-        <v>6.694750517828665e-05</v>
+        <v>9.97046839237455e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000324493596922473</v>
+        <v>0.0005543674040765465</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001951537672064549</v>
+        <v>0.0003170030852201916</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003476262491517078</v>
+        <v>0.001401778997993861</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003154349845386898</v>
+        <v>0.0004974773813827835</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001886754135937087</v>
+        <v>0.0003196482317821589</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0007028483513076091</v>
+        <v>0.001189465366430303</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006108290956789612</v>
+        <v>0.0006727330769835901</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002328180745721649</v>
+        <v>0.000462828552839638</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002789509428330174</v>
+        <v>0.0004563666446057872</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007995096723928157</v>
+        <v>0.0009279931704724873</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.085660861713667e-05</v>
+        <v>5.866328113393744e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.136487588202412e-05</v>
+        <v>1.207188600934796e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.371600873310189e-05</v>
+        <v>2.875175875023405e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.659473972811256e-05</v>
+        <v>2.439728997614059e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.868147414902813e-05</v>
+        <v>2.297878121423086e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.625520162523497e-05</v>
+        <v>2.176539619844702e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.046752187920445e-05</v>
+        <v>1.435711470177543e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.37429016284667e-05</v>
+        <v>3.145020731518539e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.906334888596626e-05</v>
+        <v>3.683429697839879e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.589731482163276e-05</v>
+        <v>4.930297889829175e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.824390715633329e-05</v>
+        <v>0.0001007279882936431</v>
       </c>
       <c r="M6" t="n">
-        <v>4.168278699986867e-05</v>
+        <v>4.400435831675788e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.306137171226067e-05</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O6" t="n">
-        <v>2.034435117048261e-05</v>
+        <v>1.770975492356126e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.869782291458505e-05</v>
+        <v>4.788563149997652e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.880063570707297e-05</v>
+        <v>3.193439917200293e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.597293499859281e-05</v>
+        <v>1.847181288908855e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.212742507538293e-05</v>
+        <v>4.358373926729832e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.288934172327653e-05</v>
+        <v>3.018923342488981e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.03772000033315e-05</v>
+        <v>9.85338508211473e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.933049723968348e-05</v>
+        <v>4.157600466086083e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.307414194959234e-05</v>
+        <v>2.799504166828755e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.90871544095919e-05</v>
+        <v>7.711922590010296e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.353456678474836e-05</v>
+        <v>4.758397088258987e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.777246797776678e-05</v>
+        <v>4.068899190777401e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.802725159333073e-05</v>
+        <v>3.872969257831743e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.097468479480461e-05</v>
+        <v>5.80986901733212e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.016551398091469e-05</v>
+        <v>6.062549390349611e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.374122981271971e-05</v>
+        <v>1.403409877890663e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.609236266379746e-05</v>
+        <v>2.733581062640641e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.590364509189056e-05</v>
+        <v>2.298134185231294e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.105782807972372e-05</v>
+        <v>2.494099398378952e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.556410698901298e-05</v>
+        <v>2.372760896800561e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.284387580990004e-05</v>
+        <v>1.294116657794785e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.611925555916231e-05</v>
+        <v>3.341242008474402e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.837225424974426e-05</v>
+        <v>3.54183488545712e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.520622018541075e-05</v>
+        <v>4.788703077446411e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.75528125201113e-05</v>
+        <v>0.0001026902010632018</v>
       </c>
       <c r="M7" t="n">
-        <v>4.40591409305643e-05</v>
+        <v>4.596657108631652e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.535133299934702e-05</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O7" t="n">
-        <v>1.961134366047678e-05</v>
+        <v>1.951847053343916e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.111352222111807e-05</v>
+        <v>4.643557534831951e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.810954107085098e-05</v>
+        <v>3.051845104817533e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.528184036237081e-05</v>
+        <v>1.705586476526093e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.143633043916092e-05</v>
+        <v>4.554595203685702e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.219824708705448e-05</v>
+        <v>2.877328530106216e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.277437831785958e-05</v>
+        <v>9.713981622913121e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>3.170685117037908e-05</v>
+        <v>4.353821743041946e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.234272512328236e-05</v>
+        <v>2.976234620994868e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.146350834028742e-05</v>
+        <v>7.908143866966167e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.571202937405339e-05</v>
+        <v>4.921932962717793e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.708137334154476e-05</v>
+        <v>4.265120467733261e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.733615695710871e-05</v>
+        <v>3.731374445448979e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.314363436276605e-05</v>
+        <v>5.98571243882826e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.742196723043299e-05</v>
+        <v>6.828310094957099e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.853923611661845e-05</v>
+        <v>2.98500105979385e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.089036896769626e-05</v>
+        <v>4.315172244543825e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.668599685621057e-05</v>
+        <v>3.44531970348382e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.94891671551423e-05</v>
+        <v>3.38695695652818e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.192590344740938e-05</v>
+        <v>4.123519842806716e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.764188211379881e-05</v>
+        <v>2.875707839697971e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.091726186306109e-05</v>
+        <v>4.922833190377588e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.317026055364301e-05</v>
+        <v>5.123426067360308e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.000422648930963e-05</v>
+        <v>6.370294259349595e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.235081882401002e-05</v>
+        <v>0.0001185061128822337</v>
       </c>
       <c r="M8" t="n">
-        <v>5.885714723446381e-05</v>
+        <v>6.17824829053467e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.430337401180059e-05</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O8" t="n">
-        <v>3.017136753014546e-05</v>
+        <v>3.074971671091978e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.127974872421515e-05</v>
+        <v>5.72408192274767e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.388390701760986e-05</v>
+        <v>3.657276500236281e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.007984666626958e-05</v>
+        <v>3.287177658429285e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.623433674305972e-05</v>
+        <v>6.136186385588891e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.699625339095328e-05</v>
+        <v>4.458919712009403e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.388789934597475e-05</v>
+        <v>0.0001089699852427954</v>
       </c>
       <c r="V8" t="n">
-        <v>4.446268616540838e-05</v>
+        <v>5.714433884157996e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.714221355859329e-05</v>
+        <v>4.5579861368874e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.792907260985865e-05</v>
+        <v>8.588347746662516e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.803797502010706e-05</v>
+        <v>7.317787402424729e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.419773837123226e-05</v>
+        <v>5.015726702384101e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.213416326100749e-05</v>
+        <v>5.31296562735217e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.581942344649987e-05</v>
+        <v>8.419506772829914e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.262724593755582e-05</v>
+        <v>7.476373238214797e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.092499815242699e-05</v>
+        <v>3.351551905358681e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.327613100350481e-05</v>
+        <v>4.681723090108667e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.199758489792756e-05</v>
+        <v>4.122957825572215e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.735601684029486e-05</v>
+        <v>3.210492075029546e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.274787299216225e-05</v>
+        <v>4.320903014337618e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.002764414960732e-05</v>
+        <v>3.242258685262807e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.330302389886958e-05</v>
+        <v>5.289384035942419e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.555602258945152e-05</v>
+        <v>5.489976912925143e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.238998852511812e-05</v>
+        <v>6.736845104914432e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.473658085981858e-05</v>
+        <v>0.0001221716213378821</v>
       </c>
       <c r="M9" t="n">
-        <v>6.124290927027155e-05</v>
+        <v>6.544799136099681e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.253510133905425e-05</v>
+        <v>0.0001017596901612095</v>
       </c>
       <c r="O9" t="n">
-        <v>3.836144639906147e-05</v>
+        <v>4.077209673052742e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.020395861919874e-05</v>
+        <v>6.807430358038416e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.529330707400031e-05</v>
+        <v>4.999987222354593e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.24656087020781e-05</v>
+        <v>3.653728503994109e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.862009877886824e-05</v>
+        <v>6.502737231153715e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.938201542676181e-05</v>
+        <v>4.825470557574233e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.993732227373439e-05</v>
+        <v>0.0001165993229719998</v>
       </c>
       <c r="V9" t="n">
-        <v>5.433973918989052e-05</v>
+        <v>6.91855499364239e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.95264934629897e-05</v>
+        <v>4.924376648462888e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>6.864727667999481e-05</v>
+        <v>9.856285894434195e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.289579771376063e-05</v>
+        <v>6.870074990185809e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.141817271430109e-05</v>
+        <v>5.891116182092667e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.451992529681603e-05</v>
+        <v>5.679516472916998e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.032740270247334e-05</v>
+        <v>7.933854466296283e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.089292761348188e-06</v>
+        <v>5.342672266325755e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.737834981561714e-06</v>
+        <v>4.841014118087615e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.734433454471914e-06</v>
+        <v>4.863891067061937e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.709410112759249e-06</v>
+        <v>4.945024120429982e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6963018619284e-06</v>
+        <v>4.827436686471111e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.080552212880991e-06</v>
+        <v>5.152182329091496e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.708841957775566e-06</v>
+        <v>4.852039683424231e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.719399502876174e-06</v>
+        <v>4.882291965204022e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.025365103298248e-06</v>
+        <v>5.254679676638074e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.950245067021829e-06</v>
+        <v>5.071607938049509e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.193054297939889e-06</v>
+        <v>7.107503568323868e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.711732322648366e-06</v>
+        <v>5.912010485993234e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.692708390621767e-06</v>
+        <v>4.813406691149939e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.47061903785215e-06</v>
+        <v>6.577029134085764e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.013415896480517e-06</v>
+        <v>5.404754790967134e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.709068477022159e-06</v>
+        <v>4.923636698486229e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.679481670186284e-06</v>
+        <v>4.801308307174994e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.91888317076337e-06</v>
+        <v>5.154484590237606e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.72141459651391e-06</v>
+        <v>4.885859814915883e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.396934165723407e-06</v>
+        <v>9.317624131368299e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.809625685881586e-06</v>
+        <v>4.973679109775076e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.117584700838742e-06</v>
+        <v>7.415306205538905e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.027616161442937e-06</v>
+        <v>5.348665749947383e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.779364805489478e-06</v>
+        <v>4.90711411188963e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.789905428445306e-06</v>
+        <v>6.202279233356805e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.329613423253054e-06</v>
+        <v>5.667787666901505e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.99869119069321e-06</v>
+        <v>6.277114641206161e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.472818922690752e-06</v>
+        <v>8.514745343227333e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58957439408222e-06</v>
+        <v>4.659500324625521e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.955727162066049e-06</v>
+        <v>5.118075891972374e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.768715358707486e-06</v>
+        <v>5.688251701647066e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.684149959888721e-06</v>
+        <v>4.858452518417886e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.406459307103193e-06</v>
+        <v>7.158587167940689e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.774036818017667e-06</v>
+        <v>5.035130239501127e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.848463206361554e-06</v>
+        <v>5.250205717936624e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.021431921828343e-06</v>
+        <v>7.893338116315135e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.493425232658951e-06</v>
+        <v>6.597736385528013e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.208164254335155e-06</v>
+        <v>2.102401010971838e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.189830532611668e-05</v>
+        <v>1.257070027240775e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.65675996115663e-06</v>
+        <v>4.756448653480906e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.906605313015086e-06</v>
+        <v>7.972363793266971e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>6.935334557943869e-06</v>
+        <v>8.959295385579452e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.77420651633107e-06</v>
+        <v>5.542965497566467e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.562231619742166e-06</v>
+        <v>4.670051766823387e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>6.258308650045614e-06</v>
+        <v>7.170014722167678e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.864354666371372e-06</v>
+        <v>5.276167770805326e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.408801355396025e-05</v>
+        <v>2.667298332954234e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.488137499628221e-06</v>
+        <v>5.895385131818823e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.102486119362486e-05</v>
+        <v>1.233090262936221e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>7.050502246552398e-06</v>
+        <v>8.58201095494473e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.275127893790904e-06</v>
+        <v>5.425109664219396e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.798839280146233e-06</v>
+        <v>9.449722033255171e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.202171023050689e-06</v>
+        <v>1.085416153110208e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.392526212712498e-05</v>
+        <v>1.515245082580957e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.945482799370734e-06</v>
+        <v>1.078986721911899e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>5.171830359021037e-06</v>
+        <v>4.513286485309024e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.937183684857874e-06</v>
+        <v>5.381813323200859e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.654533528906916e-06</v>
+        <v>6.29824848404141e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.506469805679702e-06</v>
+        <v>4.970044324583869e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>9.846754283583561e-06</v>
+        <v>8.638195748357423e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.648115957002743e-06</v>
+        <v>5.247946493107135e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.767368285624997e-06</v>
+        <v>5.589659932547066e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.206868881627827e-06</v>
+        <v>9.779448151907557e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>8.374875126855966e-06</v>
+        <v>7.728070935487044e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.111751708783981e-05</v>
+        <v>3.072444863769686e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.693989470690397e-05</v>
+        <v>1.71959905279557e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>5.465879894192703e-06</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>6.118572434829759e-06</v>
+        <v>5.442893733543648e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>9.088418705608993e-06</v>
+        <v>1.149111789431565e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.650674596096666e-06</v>
+        <v>6.056667714486609e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>5.316478002281976e-06</v>
+        <v>4.674912260785939e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.020628081431471e-06</v>
+        <v>8.664200847095286e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.790129695251502e-06</v>
+        <v>5.629960436334517e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.568513041288386e-05</v>
+        <v>3.47119849077786e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.679465207845605e-06</v>
+        <v>6.515041962435033e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.033660916543112e-05</v>
+        <v>1.156372591172359e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>9.248817230802949e-06</v>
+        <v>1.085756637376393e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.401251821234052e-06</v>
+        <v>5.845474557305529e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.227440992891477e-06</v>
+        <v>9.793591910182951e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.266001522855337e-05</v>
+        <v>1.446219522909541e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.006219521756181e-05</v>
+        <v>2.118616536874127e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.492282711617953e-05</v>
+        <v>0.0001200967188004427</v>
       </c>
       <c r="C5" t="n">
-        <v>1.352047888102726e-05</v>
+        <v>1.288692905181378e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.778624123324341e-05</v>
+        <v>2.919606537183455e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.775969212560033e-05</v>
+        <v>4.158817337872147e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.995928145600874e-05</v>
+        <v>2.171812778960297e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>9.084376782035946e-05</v>
+        <v>8.129180410437693e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.285306068613566e-05</v>
+        <v>2.757604799168212e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.459435617963642e-05</v>
+        <v>3.357187569696117e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.396033643034414e-05</v>
+        <v>0.0001049580892626009</v>
       </c>
       <c r="K5" t="n">
-        <v>7.245403570075695e-05</v>
+        <v>7.198765572111079e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000114188251093355</v>
+        <v>0.0004489528582168081</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002287534442026707</v>
+        <v>0.0002445830819400099</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000191799975287185</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.948233306548236e-05</v>
+        <v>2.855585694309703e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>8.097140503845915e-05</v>
+        <v>0.0001341700892868142</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.209669753636667e-05</v>
+        <v>4.111193960784344e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.532593259746568e-05</v>
+        <v>1.506931586330333e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>5.947969615338191e-05</v>
+        <v>7.900063231086383e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.586431434536843e-05</v>
+        <v>3.461091079120774e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0002020626779486856</v>
+        <v>0.0005531761649885738</v>
       </c>
       <c r="V5" t="n">
-        <v>4.137996904137931e-05</v>
+        <v>4.905910700910087e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001101040188699918</v>
+        <v>0.0001453074910904363</v>
       </c>
       <c r="X5" t="n">
-        <v>9.169005656016815e-05</v>
+        <v>0.0001349968366703529</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.667242426452552e-05</v>
+        <v>3.762024357947993e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.466754400720488e-05</v>
+        <v>0.0001012276595900456</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001541304897869441</v>
+        <v>0.0002001282064130853</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003120319903730472</v>
+        <v>0.0003471160011422982</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.048218251356778e-05</v>
+        <v>1.147938907238966e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>7.849092766289217e-06</v>
+        <v>5.202808338579708e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>6.473883399054905e-06</v>
+        <v>8.207760563467855e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.191233243103958e-06</v>
+        <v>9.124195724308406e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>8.183732212947886e-06</v>
+        <v>5.659566177854552e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.252401669085172e-05</v>
+        <v>9.327717601628107e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.184815671199781e-06</v>
+        <v>8.073893733374117e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.304067999822044e-06</v>
+        <v>8.415607172814049e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.743568595824868e-06</v>
+        <v>1.046897000517823e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.911574841053015e-06</v>
+        <v>1.055401817575406e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.165421680203685e-05</v>
+        <v>3.141397049096765e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.961715711417216e-05</v>
+        <v>2.002193776822266e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>6.020091165137454e-06</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>8.790192798622818e-06</v>
+        <v>8.266343532755279e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>9.579893184709846e-06</v>
+        <v>1.431496187728125e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.327937003364848e-06</v>
+        <v>8.882614954753571e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>5.853177716479012e-06</v>
+        <v>7.500859501052929e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>8.5573277956285e-06</v>
+        <v>9.35372270036595e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>8.467392102519683e-06</v>
+        <v>6.319482289605198e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.626528226989064e-05</v>
+        <v>3.542606970185647e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>9.356727615113793e-06</v>
+        <v>9.340989202702004e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.095600674617009e-05</v>
+        <v>1.438701151949674e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>9.78551694499999e-06</v>
+        <v>1.154708822703459e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.040791939347785e-06</v>
+        <v>6.642018557472727e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.090470340015966e-05</v>
+        <v>1.048311376345365e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.533727763582156e-05</v>
+        <v>1.728814246936239e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.068588066092738e-05</v>
+        <v>2.196500300922412e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.288090954951394e-05</v>
+        <v>1.370574691043735e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.107257109164249e-06</v>
+        <v>7.429166176627391e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.872610435001071e-06</v>
+        <v>8.29769301451923e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.589960279050124e-06</v>
+        <v>9.214128175359769e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.441896555822902e-06</v>
+        <v>7.885924015902245e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.278218103372676e-05</v>
+        <v>1.155407543967578e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.583542707145949e-06</v>
+        <v>8.163826184425499e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.702795035768206e-06</v>
+        <v>8.505539623865434e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.214229563177104e-05</v>
+        <v>1.269532784322593e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.131030187699918e-05</v>
+        <v>1.064395062680541e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.405294383798303e-05</v>
+        <v>3.364032832901534e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.987532145704718e-05</v>
+        <v>2.011187021927408e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.401306644335908e-06</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.052466448378836e-06</v>
+        <v>8.357240835993722e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.202231271915809e-05</v>
+        <v>1.440546499676572e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.586101346239879e-06</v>
+        <v>8.972547405804945e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>8.25190475242518e-06</v>
+        <v>7.590791952104306e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.095605483157469e-05</v>
+        <v>1.158008053841364e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>8.725556445394701e-06</v>
+        <v>8.545840127652891e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.866679556290241e-05</v>
+        <v>3.765443193927875e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.614891957988802e-06</v>
+        <v>9.430921653753424e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.327203591557433e-05</v>
+        <v>1.447960560304194e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.218424398094615e-05</v>
+        <v>1.377344606508229e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.380130714187001e-06</v>
+        <v>8.785917189431063e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.116286774303468e-05</v>
+        <v>1.270947160150132e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.559544197869658e-05</v>
+        <v>1.737807492041377e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.299762196770502e-05</v>
+        <v>2.410204506005963e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.980994672696786e-05</v>
+        <v>2.072689496143099e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.166363354254288e-05</v>
+        <v>2.110963005294724e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.242898686837973e-05</v>
+        <v>2.197815689083904e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.861747405284762e-05</v>
+        <v>1.93487028121907e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.640339573406394e-05</v>
+        <v>1.594451564345102e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.771277943496011e-05</v>
+        <v>2.661539183380287e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.213991914052458e-05</v>
+        <v>2.184429006074534e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.225917146914685e-05</v>
+        <v>2.21860035001853e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.569867206514968e-05</v>
+        <v>2.637579171954575e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.48666783103778e-05</v>
+        <v>2.432441450312528e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.760932027136167e-05</v>
+        <v>4.732079220533517e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.343169789042635e-05</v>
+        <v>3.379233409559376e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.682038642479777e-05</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.888485269229724e-05</v>
+        <v>1.829573891937227e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.150863910936043e-05</v>
+        <v>2.399623350556209e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.421271509816635e-05</v>
+        <v>1.468498790562565e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.180828118580382e-05</v>
+        <v>2.127125582842417e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.451243126495334e-05</v>
+        <v>2.526054441473348e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.228193287877332e-05</v>
+        <v>2.222630400397274e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.898901701684458e-05</v>
+        <v>4.808530932196997e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.136360841367004e-05</v>
+        <v>2.129431743479429e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.682971481147444e-05</v>
+        <v>2.81613782259461e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.841826654467822e-05</v>
+        <v>2.009622609267985e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.953164566017619e-05</v>
+        <v>2.90922764038427e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.796879869130421e-05</v>
+        <v>1.960691944214236e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.915181841207521e-05</v>
+        <v>3.105853879673362e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.347680842339697e-05</v>
+        <v>4.473872115903114e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.420048659071591e-05</v>
+        <v>2.516446451729202e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.352563469650714e-05</v>
+        <v>2.301360813720078e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.429098802234396e-05</v>
+        <v>2.388213497509262e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.306235028767117e-05</v>
+        <v>2.384636896614457e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44114221353324e-05</v>
+        <v>1.395944671130654e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.820055715023685e-05</v>
+        <v>2.713851633750312e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.400192029448884e-05</v>
+        <v>2.374826814499887e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.412117262311108e-05</v>
+        <v>2.408998158443882e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.756067321911389e-05</v>
+        <v>2.82797698037993e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.672867946434204e-05</v>
+        <v>2.622839258737878e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.947132142532591e-05</v>
+        <v>4.922477028958869e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.529369904439006e-05</v>
+        <v>3.569631217984748e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.381968423167879e-05</v>
+        <v>1.768108256292961e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.583071194814277e-05</v>
+        <v>2.531047361916605e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.90959731344196e-05</v>
+        <v>3.165605321868399e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.400447746274996e-05</v>
+        <v>2.455698830363225e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.367028233976807e-05</v>
+        <v>2.31752339126777e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.637443241891755e-05</v>
+        <v>2.716452249898706e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.414393403273761e-05</v>
+        <v>2.413028208822628e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.408238689317967e-05</v>
+        <v>5.323686950047758e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.976319266423594e-05</v>
+        <v>2.977635640562866e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.869041350291719e-05</v>
+        <v>3.006404756361531e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.760262156828904e-05</v>
+        <v>2.935788802565564e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.479850830152989e-05</v>
+        <v>2.437035915000447e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.411003249656928e-05</v>
+        <v>2.580646822850219e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.101381956603945e-05</v>
+        <v>3.296251688098714e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.841599955504791e-05</v>
+        <v>3.968648702063299e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.211895170389907e-06</v>
+        <v>4.187722180602664e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.289512637492529e-06</v>
+        <v>4.267366353192166e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.198490328154577e-06</v>
+        <v>4.173777879476656e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.216973042837258e-06</v>
+        <v>4.191718706819324e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.220429940034696e-06</v>
+        <v>4.196318130624663e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2858319961023e-06</v>
+        <v>4.26126784966959e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.201908346180449e-06</v>
+        <v>4.177474793162838e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.26440093558596e-06</v>
+        <v>4.241013431415563e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.281443961703889e-06</v>
+        <v>4.258809151087568e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.361382008081133e-06</v>
+        <v>4.33737006499299e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.273113076395191e-06</v>
+        <v>4.248843923270145e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.282899056472555e-06</v>
+        <v>4.258782026643936e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.197694588652183e-06</v>
+        <v>4.173262727970676e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.730199253183512e-06</v>
+        <v>5.655969345437351e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.189305035860991e-06</v>
+        <v>4.165191050259748e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.201315630132945e-06</v>
+        <v>4.176648609706937e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.212518902294861e-06</v>
+        <v>4.188201879267162e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.359906489940381e-06</v>
+        <v>4.335964023802279e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.196556850296536e-06</v>
+        <v>4.172823799834791e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.960533814192277e-06</v>
+        <v>5.906485871943276e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.261422667415836e-06</v>
+        <v>4.241380390159627e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.227716935017444e-06</v>
+        <v>6.181995984079725e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.199206341553936e-06</v>
+        <v>5.178359324161139e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.648013552484942e-06</v>
+        <v>4.624381549366087e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.976998996794055e-06</v>
+        <v>4.95991878972606e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.36565180005341e-06</v>
+        <v>4.341347788449358e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.271550666604337e-06</v>
+        <v>4.247049683873237e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.261765736359868e-06</v>
+        <v>4.238516852111023e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.346353726875069e-06</v>
+        <v>4.326484120090834e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.170430423773891e-06</v>
+        <v>4.143329996191095e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.292186146675311e-06</v>
+        <v>4.261198836989154e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.325751293678808e-06</v>
+        <v>4.302934790142319e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.789751318676074e-06</v>
+        <v>4.763722424837325e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19331949233518e-06</v>
+        <v>4.168201013090975e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.639864749670597e-06</v>
+        <v>4.62222538996037e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.759081692670715e-06</v>
+        <v>4.746738987684303e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.329712554493665e-06</v>
+        <v>5.307595223966986e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.702016772653877e-06</v>
+        <v>4.678068611195704e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.800727219529943e-06</v>
+        <v>4.778094696605708e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.161911454779946e-06</v>
+        <v>4.136816402512736e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.78677664722263e-06</v>
+        <v>6.680439676822656e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.101302888821566e-06</v>
+        <v>4.078472845203952e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.189984760482014e-06</v>
+        <v>4.163222450956976e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.268980682508446e-06</v>
+        <v>4.24469888468984e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.311604078126004e-06</v>
+        <v>5.28997606669728e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.156993869796065e-06</v>
+        <v>4.136871639595801e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.626089147944829e-06</v>
+        <v>7.553985556653005e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.616188787636633e-06</v>
+        <v>4.622216170450162e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.430799706305358e-06</v>
+        <v>8.431152348113277e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.129729635358905e-05</v>
+        <v>1.129773386759586e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.375561008647443e-06</v>
+        <v>7.356174843750545e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.687512782088656e-06</v>
+        <v>5.715594036411782e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.359630187172789e-06</v>
+        <v>5.335447492249693e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.695427692018974e-06</v>
+        <v>4.670412155387862e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.677936790621035e-06</v>
+        <v>4.356964261718099e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.585270229814222e-06</v>
+        <v>4.264255357133076e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.526522931041345e-06</v>
+        <v>4.199456965804419e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.735293695851194e-06</v>
+        <v>4.402106863828195e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7743409399476e-06</v>
+        <v>4.454059471548891e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.513087249663307e-06</v>
+        <v>5.187696426508298e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.565131017009668e-06</v>
+        <v>4.241215306554193e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.271013562356161e-06</v>
+        <v>4.958913454836332e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.448232272830368e-06</v>
+        <v>5.144638929736444e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.366459389686711e-06</v>
+        <v>6.047305957334821e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.369421200579955e-06</v>
+        <v>5.047362462538027e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.52882804922597e-06</v>
+        <v>5.208929967403521e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.517534687303623e-06</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.713535727629254e-06</v>
+        <v>4.391623491991357e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.422770829142294e-06</v>
+        <v>4.102464779662849e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.558436016590395e-06</v>
+        <v>4.231883184356595e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.684982129418878e-06</v>
+        <v>4.362382678805859e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>6.349792733515239e-06</v>
+        <v>6.031424075274811e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.504683409191204e-06</v>
+        <v>4.188680197351237e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.647182456088498e-06</v>
+        <v>5.33724124230623e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.138649674705156e-06</v>
+        <v>4.864378810018661e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>6.412319120667839e-06</v>
+        <v>6.213672525829964e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.58300706544973e-05</v>
+        <v>1.554666651381194e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.592470091959077e-06</v>
+        <v>9.287648444677137e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.012907083283785e-06</v>
+        <v>4.77425405869939e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.414688654215122e-06</v>
+        <v>6.092236173617648e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.358254697396609e-06</v>
+        <v>5.034648151088636e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.566830070257945e-05</v>
+        <v>1.535516831083239e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.602849887051891e-05</v>
+        <v>1.571130830020122e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.523717109972123e-05</v>
+        <v>1.481554157827881e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.36663640790783e-05</v>
+        <v>1.312642070407593e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.896560258177868e-05</v>
+        <v>1.866248163170958e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.059207244579743e-05</v>
+        <v>3.020685580958253e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.513983337775536e-05</v>
+        <v>1.476949365454585e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.790050188859847e-05</v>
+        <v>2.774609349864194e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.003595248337458e-05</v>
+        <v>2.999286939092824e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.607768062297753e-05</v>
+        <v>4.578747444468152e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.962703186852058e-05</v>
+        <v>2.928797464459855e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.364637010808659e-05</v>
+        <v>3.334013158971623e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.208631045778381e-05</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.706549641336417e-05</v>
+        <v>1.673390400091889e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.155122890193218e-05</v>
+        <v>1.124870524139306e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54854977307041e-05</v>
+        <v>1.508014421304898e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72249403587266e-05</v>
+        <v>1.688047254505178e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.185598852339225e-05</v>
+        <v>4.157627247714004e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.50389014961725e-05</v>
+        <v>1.48068114158783e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.322758267536137e-05</v>
+        <v>3.292083853210977e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>2.595272496213185e-05</v>
+        <v>2.635871479953999e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.589636284184869e-05</v>
+        <v>4.761976086515743e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002072332613102456</v>
+        <v>0.0002075580378958654</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001034156566184019</v>
+        <v>0.0001032114676308302</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.164630555256648e-05</v>
+        <v>2.260175982876231e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.664251752958661e-05</v>
+        <v>4.630388269815066e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.99686503102609e-05</v>
+        <v>2.960502097817783e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.093438779165886e-06</v>
+        <v>6.505868483188779e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.000772218359072e-06</v>
+        <v>4.720695079446861e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.942024919586181e-06</v>
+        <v>4.655896688118197e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.842124260205419e-06</v>
+        <v>4.858546586141977e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.881171504301814e-06</v>
+        <v>6.602963693019557e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>5.928589238208162e-06</v>
+        <v>7.336600647978966e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.980633005554522e-06</v>
+        <v>6.390119528024857e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.686515550901018e-06</v>
+        <v>7.107817676307006e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.863734261375218e-06</v>
+        <v>7.293543151207105e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>6.781961378231582e-06</v>
+        <v>8.196210178805489e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.476251764934156e-06</v>
+        <v>5.503802184851811e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.63565861358019e-06</v>
+        <v>7.357834188874189e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9369307019684e-06</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>5.132931742294043e-06</v>
+        <v>6.541503052186648e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>4.792521226801114e-06</v>
+        <v>4.512153552259994e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.973938005135254e-06</v>
+        <v>6.380787405827273e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>6.791812693773097e-06</v>
+        <v>4.818822401119634e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>6.765294722060109e-06</v>
+        <v>8.180328296745479e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.611513973545436e-06</v>
+        <v>4.645119919665022e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>6.074308893426057e-06</v>
+        <v>5.795265225077707e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>7.24548023905937e-06</v>
+        <v>5.320818532332448e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.880660372410648e-06</v>
+        <v>6.723910821086162e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.624557264304215e-05</v>
+        <v>1.76955707352826e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.006110847486692e-05</v>
+        <v>9.78740095372719e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.119737647638011e-06</v>
+        <v>5.230693781013181e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.521519218569344e-06</v>
+        <v>8.241140395088316e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.778616111259443e-06</v>
+        <v>5.495075823091799e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.173388345420223e-06</v>
+        <v>6.767801885297648e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.080721784613416e-06</v>
+        <v>6.67509298071261e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.021974485840533e-06</v>
+        <v>6.610294589383955e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.230745250650406e-06</v>
+        <v>6.812944487407739e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.269792494746795e-06</v>
+        <v>6.86489709512843e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>8.008538804462503e-06</v>
+        <v>7.598534050087825e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.060582571808859e-06</v>
+        <v>6.652052930133731e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.76646511715535e-06</v>
+        <v>7.369751078415868e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.94368382762956e-06</v>
+        <v>7.555476553315981e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>8.861910944485929e-06</v>
+        <v>8.458143580914356e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.864872755379147e-06</v>
+        <v>7.458200086117564e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>8.024279604025179e-06</v>
+        <v>7.619767590983065e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>7.012986242102822e-06</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>7.207560105617281e-06</v>
+        <v>6.801035732709447e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.916795207130317e-06</v>
+        <v>6.511877020380939e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.053887571389586e-06</v>
+        <v>6.642720807936138e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.18043368421808e-06</v>
+        <v>6.773220302385391e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>8.84524428831444e-06</v>
+        <v>8.442261698854349e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>7.000134963990419e-06</v>
+        <v>6.59951782093077e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>8.159913488938747e-06</v>
+        <v>7.753267476976555e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.634101229504342e-06</v>
+        <v>7.2752164335982e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.907770675467031e-06</v>
+        <v>8.624510149409496e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.832552220929651e-05</v>
+        <v>1.795750413739147e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.209954609555096e-05</v>
+        <v>1.170007032871436e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.508358638082994e-06</v>
+        <v>7.185091682278938e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.910140209014329e-06</v>
+        <v>8.503073797197186e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.853706252195817e-06</v>
+        <v>7.445485774668178e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.341220418463465e-05</v>
+        <v>1.302220221579926e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.916025697669329e-05</v>
+        <v>1.87146873082709e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.910150967792041e-05</v>
+        <v>1.864988891694225e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.620026967770782e-05</v>
+        <v>1.577209366406723e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.441852414725944e-05</v>
+        <v>1.402056303740413e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.129918520313722e-05</v>
+        <v>2.083772603997763e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.914011776388874e-05</v>
+        <v>1.869164725769203e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.984600030923524e-05</v>
+        <v>1.940934540597417e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.002321901970945e-05</v>
+        <v>1.959507088087426e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.094144613656581e-05</v>
+        <v>2.049773790847263e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.994440794745904e-05</v>
+        <v>1.949779441367586e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.010381479610631e-05</v>
+        <v>1.965936191854151e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.456498680475323e-05</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.600519367336526e-05</v>
+        <v>1.558993992032677e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.540944386211631e-05</v>
+        <v>1.499869566345169e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.214486874976973e-05</v>
+        <v>1.176019847739854e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.925996887629798e-05</v>
+        <v>1.881281462994367e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.092477948039435e-05</v>
+        <v>2.048185602641264e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.90796701560703e-05</v>
+        <v>1.863911214848907e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.738850502690389e-05</v>
+        <v>1.6969479398112e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.812333344968966e-05</v>
+        <v>1.773792930332926e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.098845373662691e-05</v>
+        <v>2.066524143346428e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.395181692227518e-05</v>
+        <v>2.360520633210303e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.999576488487245e-05</v>
+        <v>2.949841957503885e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.363868011666819e-05</v>
+        <v>1.333202906416804e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.09896754010942e-05</v>
+        <v>2.054266812475547e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.60343612016777e-05</v>
+        <v>2.552819898228068e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.598661576761661e-05</v>
+        <v>1.555024700045659e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.914810943369627e-05</v>
+        <v>1.867470769931229e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908936213492341e-05</v>
+        <v>1.860990930798361e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.854708617849833e-05</v>
+        <v>1.807004980156122e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.183545236121039e-05</v>
+        <v>1.144805745992334e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.007592669490816e-05</v>
+        <v>1.959814905136498e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.912797022089173e-05</v>
+        <v>1.86516676487334e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.983385276623822e-05</v>
+        <v>1.936936579701555e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.001107147671242e-05</v>
+        <v>1.955509127191566e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.092929859356877e-05</v>
+        <v>2.045775829951403e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.993226040446202e-05</v>
+        <v>1.945781480471725e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.009166725310804e-05</v>
+        <v>1.961938230958274e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.908037389118569e-05</v>
+        <v>1.324245718720612e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.035479969111286e-05</v>
+        <v>1.986824200460362e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.029857362267657e-05</v>
+        <v>1.981095608051837e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.912127546183519e-05</v>
+        <v>1.864233580921329e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.924782133330095e-05</v>
+        <v>1.877283502098507e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.091263193739728e-05</v>
+        <v>2.044187641745403e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.906752261307326e-05</v>
+        <v>1.859913253953044e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.022164610876325e-05</v>
+        <v>1.974927784494314e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.345672015313036e-05</v>
+        <v>2.298737614002959e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.097515832454991e-05</v>
+        <v>2.062412486800919e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.039290985837937e-05</v>
+        <v>2.995711885599116e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.416693374463382e-05</v>
+        <v>2.3699685047314e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.761377713741415e-05</v>
+        <v>1.724503932413573e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.097752785809719e-05</v>
+        <v>2.050268851579687e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.992109390127867e-05</v>
+        <v>1.944510049326785e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.216218655853996e-06</v>
+        <v>4.176953486215757e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.287332005552973e-06</v>
+        <v>4.248089932270889e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.257840556959071e-06</v>
+        <v>4.218582053603643e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.192111041559494e-06</v>
+        <v>4.151449535382429e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.211746259541695e-06</v>
+        <v>4.172683788800036e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.219786319587942e-06</v>
+        <v>4.180387868623147e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.194427085871399e-06</v>
+        <v>4.154965019673034e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.276918820554761e-06</v>
+        <v>4.237830663384624e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.254950911603523e-06</v>
+        <v>4.215603232742143e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.442727139144251e-06</v>
+        <v>4.403516680386076e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.237518137341535e-06</v>
+        <v>4.19790737267715e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.274000140136304e-06</v>
+        <v>4.234611084119593e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.188850084588814e-06</v>
+        <v>4.14938172871733e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.72859190600848e-06</v>
+        <v>5.62829006271511e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.185079633468325e-06</v>
+        <v>4.14599115542548e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.206371825096488e-06</v>
+        <v>4.166907921770532e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.213185711138891e-06</v>
+        <v>4.173689296805509e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.307898143158666e-06</v>
+        <v>4.269022615315155e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.206675232098101e-06</v>
+        <v>4.167641101986397e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.00112457430981e-06</v>
+        <v>5.896589827043561e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.298054344001912e-06</v>
+        <v>4.25912380086806e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.118829811974348e-06</v>
+        <v>6.000310552474328e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.2715679502045e-06</v>
+        <v>5.236436023907979e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.509206662696901e-06</v>
+        <v>4.470280499067154e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.960163655585603e-06</v>
+        <v>4.908150082145713e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.2686356471184e-06</v>
+        <v>4.229002960818657e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.402821191080134e-06</v>
+        <v>4.36380602479888e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.348238343962035e-06</v>
+        <v>4.309932705679274e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.370974796449374e-06</v>
+        <v>4.334379002713252e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.648512215915032e-06</v>
+        <v>4.610228839600309e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.172899337173309e-06</v>
+        <v>4.124632399177357e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.319057423653731e-06</v>
+        <v>4.282176638008484e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.375995366696579e-06</v>
+        <v>4.33673048488527e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.196073511327417e-06</v>
+        <v>4.15632449342938e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.78493182750132e-06</v>
+        <v>4.747868479131972e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.626297435387198e-06</v>
+        <v>4.587388242746115e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.965184354843428e-06</v>
+        <v>5.92724024409068e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.504052709187681e-06</v>
+        <v>4.463272838663827e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.790555050891002e-06</v>
+        <v>4.750811050084668e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.15398396153111e-06</v>
+        <v>4.114217994473952e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.803861827036049e-06</v>
+        <v>6.6647576996697e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.127895491073216e-06</v>
+        <v>4.090840699474317e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.280185766749181e-06</v>
+        <v>4.240450888007109e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.329134069386588e-06</v>
+        <v>4.289147745353739e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>4.999744331227262e-06</v>
+        <v>4.96419706862235e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.28311518708115e-06</v>
+        <v>4.246434933704414e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.838778397780845e-06</v>
+        <v>7.69471505632165e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.930872558887111e-06</v>
+        <v>4.89495155423976e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.600619178834669e-06</v>
+        <v>7.41650957310343e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.186264519406407e-05</v>
+        <v>1.185373734478213e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.441526303612198e-06</v>
+        <v>6.405634852714864e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.575453902723543e-06</v>
+        <v>5.516112702797997e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.722860171587201e-06</v>
+        <v>4.68192319288605e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.677556073432292e-06</v>
+        <v>5.641177040705683e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.786352640989931e-06</v>
+        <v>4.513079960110812e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.589827137468813e-06</v>
+        <v>4.319970419334649e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.256491160992266e-06</v>
+        <v>4.983293778844614e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.514046047483094e-06</v>
+        <v>4.225001103051547e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.735834867238557e-06</v>
+        <v>4.464851763642697e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.826651044071308e-06</v>
+        <v>4.551872889296279e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.540206833419095e-06</v>
+        <v>4.264710115316515e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.471988924740432e-06</v>
+        <v>5.200715681118556e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.209084188088834e-06</v>
+        <v>4.934878695637675e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.344870158803703e-06</v>
+        <v>7.07221546248322e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.026940082637345e-06</v>
+        <v>4.749763746956403e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.485341951622781e-06</v>
+        <v>5.209714499661382e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.477212038385009e-06</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.699684596787213e-06</v>
+        <v>4.426327193641351e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.434623058485792e-06</v>
+        <v>4.163346190459019e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.675128157818009e-06</v>
+        <v>4.399610688514185e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.752094135209376e-06</v>
+        <v>4.476209439121188e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>5.82191462474402e-06</v>
+        <v>5.553043127180793e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.678555279475314e-06</v>
+        <v>4.407892296332091e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.927431385956276e-06</v>
+        <v>5.647308073406183e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.615558791231307e-06</v>
+        <v>5.346066418698819e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>5.013681861865733e-06</v>
+        <v>4.709509966688388e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.67070084053399e-05</v>
+        <v>1.648042260939166e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.116287400042865e-06</v>
+        <v>7.835827947222319e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.78173786441929e-06</v>
+        <v>4.508494784081462e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.378426670328678e-06</v>
+        <v>5.101002719692013e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.875235892126846e-06</v>
+        <v>6.605094944145233e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.792984550064748e-05</v>
+        <v>1.755551524908915e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.618867051411527e-05</v>
+        <v>1.586120227656963e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.791178126132122e-05</v>
+        <v>2.75256636104714e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.141296412346425e-05</v>
+        <v>1.076196787375761e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.845566653518541e-05</v>
+        <v>1.811052383650909e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.983161888798263e-05</v>
+        <v>1.94265118738181e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.531897898096795e-05</v>
+        <v>1.48855587287478e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.185644686123052e-05</v>
+        <v>3.150656775373916e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.649510555983035e-05</v>
+        <v>2.609668234560272e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.335954990846216e-05</v>
+        <v>6.298114881416104e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.415371722329912e-05</v>
+        <v>2.370635234921346e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.275953949990805e-05</v>
+        <v>3.232538097439325e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.574942992035241e-05</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.705536932090174e-05</v>
+        <v>1.667687983698428e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.269246720040886e-05</v>
+        <v>1.234814509726401e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.711557463161481e-05</v>
+        <v>1.669590941128024e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.86412560090496e-05</v>
+        <v>1.820503568338201e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>3.478662198110316e-05</v>
+        <v>3.447846493175366e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75721071127437e-05</v>
+        <v>1.72317265203093e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.717914882730346e-05</v>
+        <v>3.685729089195128e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>3.344205137198601e-05</v>
+        <v>3.313270093007331e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.265312139079157e-05</v>
+        <v>2.174659471667419e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002196073788470218</v>
+        <v>0.0002200062482824921</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.761204821667538e-05</v>
+        <v>7.730268962541671e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.859426480933033e-05</v>
+        <v>1.821715973469865e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.867068695267265e-05</v>
+        <v>2.821860452370998e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.890856207152987e-05</v>
+        <v>5.857670179310273e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.931580316698507e-06</v>
+        <v>6.675180362372793e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.735054813177377e-06</v>
+        <v>6.48207082159663e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.401718836700841e-06</v>
+        <v>7.145394181106599e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.65927372319167e-06</v>
+        <v>4.681098932038811e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.881062542947121e-06</v>
+        <v>6.626952165904687e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.971878719779901e-06</v>
+        <v>6.713973291558259e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.982749164399637e-06</v>
+        <v>6.42681051757849e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.914531255720979e-06</v>
+        <v>7.362816083380525e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.651626519069377e-06</v>
+        <v>5.390976524624936e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>9.490097834512282e-06</v>
+        <v>7.52831329147048e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.172167758345915e-06</v>
+        <v>6.91186414921839e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.630569627331367e-06</v>
+        <v>7.371814901923366e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.925693287711287e-06</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.808923919806092e-06</v>
+        <v>4.888216830331795e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>6.543946827343037e-06</v>
+        <v>6.309856875737153e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.82035583352659e-06</v>
+        <v>6.561711090776176e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>5.19463646618992e-06</v>
+        <v>6.638309841383166e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>6.26445695572456e-06</v>
+        <v>7.715143529442771e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.823782955183879e-06</v>
+        <v>4.863990125319366e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>8.052158621044671e-06</v>
+        <v>7.799924035805806e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>6.058101122211847e-06</v>
+        <v>5.80216424768608e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>7.122813438912179e-06</v>
+        <v>6.85559447363824e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.714955073632044e-05</v>
+        <v>1.693652043837892e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.584947718213371e-06</v>
+        <v>8.328390367948423e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.224280195399844e-06</v>
+        <v>4.964592613068729e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.820969001309229e-06</v>
+        <v>7.263103121953996e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.332161852917958e-06</v>
+        <v>7.074640624550525e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.283536630535797e-06</v>
+        <v>6.910272022193058e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.087011127014677e-06</v>
+        <v>6.717162481416897e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.753675150538136e-06</v>
+        <v>7.380485840926874e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.011230037028969e-06</v>
+        <v>6.622193165133802e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.233018856784423e-06</v>
+        <v>6.862043825724948e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.323835033617206e-06</v>
+        <v>6.949064951378526e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.037390822964969e-06</v>
+        <v>6.661902177398774e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.969172914286309e-06</v>
+        <v>7.597907743200811e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.706268177634695e-06</v>
+        <v>7.33207075771992e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>9.84205414834957e-06</v>
+        <v>9.469407524565485e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.524124072183212e-06</v>
+        <v>7.146955809038659e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>7.982525941168654e-06</v>
+        <v>7.606906561743632e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>6.974396027930876e-06</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>7.195438512310171e-06</v>
+        <v>6.822093591484109e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.930376974008753e-06</v>
+        <v>6.559112588301775e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.172312147363884e-06</v>
+        <v>6.796802750596445e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.249278124755245e-06</v>
+        <v>6.873401501203446e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>8.31909861428989e-06</v>
+        <v>7.950235189263044e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>7.175739269021192e-06</v>
+        <v>6.805084358414355e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>8.410438802700716e-06</v>
+        <v>8.039418470731864e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>8.112742780777181e-06</v>
+        <v>7.743258480781074e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.510865851411598e-06</v>
+        <v>7.106702028770644e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.920419239488575e-05</v>
+        <v>1.887761467147392e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.059297094896856e-05</v>
+        <v>1.022353556944221e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.278921853965168e-06</v>
+        <v>6.905686846163714e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.87561065987455e-06</v>
+        <v>7.498194781774275e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.372419881672716e-06</v>
+        <v>9.002287006227482e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.349356772545627e-05</v>
+        <v>1.313715159593366e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.911277482174634e-05</v>
+        <v>1.870497429540061e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.97794388452698e-05</v>
+        <v>1.93682976549106e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.594028767570849e-05</v>
+        <v>1.554247849806021e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.434907312088595e-05</v>
+        <v>1.398640931307202e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.05555287689112e-05</v>
+        <v>2.013144359436102e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.906315451769664e-05</v>
+        <v>1.864971399138247e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.999493660901798e-05</v>
+        <v>1.958571955718452e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.973203187236635e-05</v>
+        <v>1.931988257170364e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.186781784308123e-05</v>
+        <v>2.145721933854919e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.954988776691488e-05</v>
+        <v>1.913476762302238e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.000828963590216e-05</v>
+        <v>1.959471837572821e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.449199400700237e-05</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.595334964792695e-05</v>
+        <v>1.557285416225008e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.538460793047479e-05</v>
+        <v>1.500905449098144e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.223941904876391e-05</v>
+        <v>1.189152765227985e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.927504181948691e-05</v>
+        <v>1.886121331518716e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.034486230902156e-05</v>
+        <v>1.993804700324678e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.920150296375286e-05</v>
+        <v>1.879289617239809e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.759730628406693e-05</v>
+        <v>1.721551027088291e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.855560694299252e-05</v>
+        <v>1.816150265483849e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.953777250445075e-05</v>
+        <v>1.90956460310413e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.480432274521954e-05</v>
+        <v>2.450034046013742e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.841146503982136e-05</v>
+        <v>2.794703827989329e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.338092273003723e-05</v>
+        <v>1.302555414588691e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.990137435460624e-05</v>
+        <v>1.948600659575801e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.747320258073179e-05</v>
+        <v>2.7007874266466e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.541819873713783e-05</v>
+        <v>1.498739571769719e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.828525799124604e-05</v>
+        <v>1.781344676819512e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.895192201476948e-05</v>
+        <v>1.847677012770509e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.750241405202435e-05</v>
+        <v>1.702166755202487e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.136886669472918e-05</v>
+        <v>1.099833885824567e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.852208191955248e-05</v>
+        <v>1.804534930270621e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.823563768719632e-05</v>
+        <v>1.775818646417697e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.916741977851765e-05</v>
+        <v>1.869419202997903e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.890451504186605e-05</v>
+        <v>1.842835504449813e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.104030101258091e-05</v>
+        <v>2.056569181134369e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.872237093641456e-05</v>
+        <v>1.824324009581688e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.91807728054e-05</v>
+        <v>1.870319084852186e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.817264289216221e-05</v>
+        <v>1.259984245270707e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.94103834567381e-05</v>
+        <v>1.892034949515822e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.936612528597617e-05</v>
+        <v>1.887497005614512e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.837055903329926e-05</v>
+        <v>1.789308710192412e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.844752498898658e-05</v>
+        <v>1.796968578798164e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.951734547852122e-05</v>
+        <v>1.904651947604126e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.837398613325252e-05</v>
+        <v>1.790136864519256e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96023617991133e-05</v>
+        <v>1.913129998240427e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.284630064550529e-05</v>
+        <v>2.232358940731163e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.870911271564294e-05</v>
+        <v>1.820298631554885e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.040243925911715e-05</v>
+        <v>2.997389895825212e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.179121781319991e-05</v>
+        <v>2.131981985622042e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.66300995425509e-05</v>
+        <v>1.618168579627096e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.907385752410591e-05</v>
+        <v>1.859447906855249e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.057066674590408e-05</v>
+        <v>2.009857129300568e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.360162245141753e-06</v>
+        <v>9.774876717879592e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.990173056957236e-06</v>
+        <v>6.567722317479866e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.28436893629632e-06</v>
+        <v>6.976920182026115e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.233264355630943e-06</v>
+        <v>7.668196240085048e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.092210850903268e-06</v>
+        <v>6.814848004375829e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.064688980696689e-06</v>
+        <v>7.510687004475472e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.983801073170238e-06</v>
+        <v>6.65870554005382e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.034350258953388e-06</v>
+        <v>6.752958883539057e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.981813907495913e-06</v>
+        <v>8.029928643850574e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.014391794154959e-06</v>
+        <v>6.705872282315929e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.989207636252272e-06</v>
+        <v>1.585395873903368e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.100793040158564e-06</v>
+        <v>9.992177245785315e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>5.982486873252627e-06</v>
+        <v>6.651510285473542e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>8.531832298775237e-06</v>
+        <v>9.227092356841262e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>7.066142588688116e-06</v>
+        <v>8.743560276186406e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.056934007406158e-06</v>
+        <v>7.056409156313427e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.017482263185819e-06</v>
+        <v>6.719954681040469e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>6.760581232717749e-06</v>
+        <v>8.198948893543535e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>6.158551479837197e-06</v>
+        <v>6.990391781329183e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.055081271551454e-05</v>
+        <v>1.432672174473773e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>6.340742610987802e-06</v>
+        <v>7.227442560828058e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>8.950834596931938e-06</v>
+        <v>9.656107191088842e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.481810333233616e-06</v>
+        <v>1.003795644222678e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.7877979746371e-06</v>
+        <v>7.51079483057045e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.883761839360344e-06</v>
+        <v>1.001572663920341e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.080268907105388e-06</v>
+        <v>8.128041783629957e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.275310505687905e-06</v>
+        <v>1.056925623284504e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.273937462538753e-05</v>
+        <v>2.876043537737691e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.746396369019208e-06</v>
+        <v>6.205723116607907e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.011855624638656e-06</v>
+        <v>8.906207900074606e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.632182973259139e-06</v>
+        <v>1.382160294348697e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.637658035157143e-06</v>
+        <v>7.746899135378851e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.353383079391635e-05</v>
+        <v>1.267437133516355e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.862461403160952e-06</v>
+        <v>6.631055581704784e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.223061226343558e-06</v>
+        <v>7.303903824653557e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.296100933015375e-05</v>
+        <v>1.638516083182592e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.08272896647232e-06</v>
+        <v>6.966665200318699e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.014136873077297e-05</v>
+        <v>7.2109215769392e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.797117323059362e-05</v>
+        <v>3.032270535677566e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.850072768542224e-06</v>
+        <v>6.575557823116113e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.162298419171075e-05</v>
+        <v>1.216173028407016e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355649575421062e-05</v>
+        <v>2.145418101861406e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.382388242205138e-06</v>
+        <v>9.466078701993048e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>6.102499431625669e-06</v>
+        <v>7.068578865584829e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.136976543277865e-05</v>
+        <v>1.755000426982842e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>7.111443738724058e-06</v>
+        <v>9.002678061030393e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.712514388343031e-05</v>
+        <v>4.977752330878219e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>8.394186340498354e-06</v>
+        <v>1.066250222182227e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.471384896404356e-05</v>
+        <v>1.60512456462314e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.657184074366534e-05</v>
+        <v>3.079128724845625e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.159536010351114e-05</v>
+        <v>1.270538475084391e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.31672365604745e-05</v>
+        <v>2.139291179498299e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.368558617805916e-05</v>
+        <v>1.711418479263389e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.927813628193133e-05</v>
+        <v>3.44919396853247e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.463360999448313e-05</v>
+        <v>4.202366844277819e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.522466826568516e-06</v>
+        <v>6.240504956032182e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.118656965897548e-05</v>
+        <v>1.041946224671571e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.060931991109063e-05</v>
+        <v>1.82277433251892e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>9.016055687373576e-06</v>
+        <v>8.588782443270502e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.000064352543097e-05</v>
+        <v>1.644860405115081e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.791517376917073e-06</v>
+        <v>6.82508147967113e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>8.362493684112469e-06</v>
+        <v>7.889716353017068e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.904548322411561e-05</v>
+        <v>2.229478801394315e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>8.137053642867068e-06</v>
+        <v>7.357851531295045e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.044350703952556e-05</v>
+        <v>0.0001106896963876064</v>
       </c>
       <c r="M4" t="n">
-        <v>4.279169411648065e-05</v>
+        <v>4.434756975431208e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>7.776672884285559e-06</v>
+        <v>3.164163856150573e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.102337836499584e-05</v>
+        <v>9.516834129598395e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.001706269638805e-05</v>
+        <v>3.037447480485111e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.61758751192498e-06</v>
+        <v>1.131732677802573e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.171961912256257e-06</v>
+        <v>7.516918703112165e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.656560661553417e-05</v>
+        <v>2.422283870428613e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>9.765403609380311e-06</v>
+        <v>1.057163015808582e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.600890312327473e-05</v>
+        <v>6.969199068256952e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.169929303719325e-05</v>
+        <v>1.312642271273385e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59365863181511e-05</v>
+        <v>1.604047434887462e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.471222108763837e-05</v>
+        <v>4.499527495193201e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.676486794481845e-05</v>
+        <v>1.639044973061028e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.642907700401774e-05</v>
+        <v>2.592669681734307e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.017662596133829e-05</v>
+        <v>2.34219102789302e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.45997956622042e-05</v>
+        <v>5.063160151144431e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0004887892929832424</v>
+        <v>0.0006393437480258263</v>
       </c>
       <c r="C5" t="n">
-        <v>2.213179893705462e-05</v>
+        <v>2.32535980470028e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>9.4130076354038e-05</v>
+        <v>0.0001056917915191497</v>
       </c>
       <c r="E5" t="n">
-        <v>7.490840750545677e-05</v>
+        <v>0.0002431654275644647</v>
       </c>
       <c r="F5" t="n">
-        <v>5.155758633649517e-05</v>
+        <v>6.963617447057306e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002345309700741747</v>
+        <v>0.0001966894480945729</v>
       </c>
       <c r="H5" t="n">
-        <v>2.758623099433031e-05</v>
+        <v>3.548353176259644e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.828640719855254e-05</v>
+        <v>5.570110232191902e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002271909536635688</v>
+        <v>0.0003103119873684819</v>
       </c>
       <c r="K5" t="n">
-        <v>3.519856791794686e-05</v>
+        <v>4.498883607669794e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004371014621472702</v>
+        <v>0.00191657901001156</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006756972575829619</v>
+        <v>0.0007290814803613015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000515264832540353</v>
+        <v>3.164163856150574e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>8.022352446117239e-05</v>
+        <v>7.729098077171693e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002416768045415889</v>
+        <v>0.0004492823640934867</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.207841119522848e-05</v>
+        <v>0.0001185274352152627</v>
       </c>
       <c r="R5" t="n">
-        <v>3.458704232834755e-05</v>
+        <v>4.877890441701098e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001731225284447152</v>
+        <v>0.000323369651085799</v>
       </c>
       <c r="T5" t="n">
-        <v>6.589821855983107e-05</v>
+        <v>0.0001087484299258596</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005436052270703559</v>
+        <v>0.001182905946838664</v>
       </c>
       <c r="V5" t="n">
-        <v>9.491678633016607e-05</v>
+        <v>0.0001414459068422775</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001802458955557349</v>
+        <v>0.0002077148878180285</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003575390138339636</v>
+        <v>0.0007807546834457138</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001963692447449621</v>
+        <v>0.0002135326652087876</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001759748163526716</v>
+        <v>0.0003647041308878649</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002604163386090612</v>
+        <v>0.0003472944125229095</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007933451982472026</v>
+        <v>0.0009468471373161114</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.835306045283225e-05</v>
+        <v>4.326105909854098e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.336906520260553e-06</v>
+        <v>7.477895611794986e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.490602011732455e-05</v>
+        <v>1.165685290247852e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.43287703694397e-05</v>
+        <v>2.253488049431736e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.273550614572266e-05</v>
+        <v>9.82617309903331e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.081508321912297e-05</v>
+        <v>2.075574122027896e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.151096783526612e-05</v>
+        <v>8.06247213543392e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>9.176933377804489e-06</v>
+        <v>9.127107008779888e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.985992291780761e-05</v>
+        <v>2.353217866970596e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.951493336559085e-06</v>
+        <v>1.166498870042318e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.416295749787463e-05</v>
+        <v>0.0001149968335567346</v>
       </c>
       <c r="M6" t="n">
-        <v>4.651114457482967e-05</v>
+        <v>4.558496041007494e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.638579795694807e-06</v>
+        <v>3.164163856150574e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.188528527640509e-05</v>
+        <v>1.381906238525804e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.374936073100173e-05</v>
+        <v>3.467753407357241e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.233703797027405e-05</v>
+        <v>1.255471743378854e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.189141237060532e-05</v>
+        <v>1.18240558722403e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02850570738832e-05</v>
+        <v>2.546022936004894e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.057984330307233e-05</v>
+        <v>1.180902081384862e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.983651787263788e-05</v>
+        <v>7.405850011758336e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.541874349554234e-05</v>
+        <v>1.436381336849667e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.686087769677479e-05</v>
+        <v>1.736093070148761e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.55266607813304e-05</v>
+        <v>4.930241212106015e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.778574816605499e-05</v>
+        <v>1.780448233051651e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.724351669770976e-05</v>
+        <v>3.023383398647124e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.389607641968731e-05</v>
+        <v>2.772904744805835e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.561759214165073e-05</v>
+        <v>5.206302500444e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.817200195154425e-05</v>
+        <v>4.575179571364245e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.106085878362967e-05</v>
+        <v>9.968632226896451e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.472496161603661e-05</v>
+        <v>1.414758951757998e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.414771186815176e-05</v>
+        <v>2.195587059605348e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.255444764443471e-05</v>
+        <v>1.231690971413478e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.353903548249211e-05</v>
+        <v>2.01767313220151e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.132990933397821e-05</v>
+        <v>1.05532087505354e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.190088564117361e-05</v>
+        <v>1.161784362388134e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.258387518117676e-05</v>
+        <v>2.602291528480744e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.16754455999282e-05</v>
+        <v>1.108597880215932e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.398189899658671e-05</v>
+        <v>0.0001144178236584707</v>
       </c>
       <c r="M7" t="n">
-        <v>4.633008607354179e-05</v>
+        <v>4.807569702517636e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.13150648413467e-05</v>
+        <v>3.164163856150574e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.456023520760478e-05</v>
+        <v>1.32434226329164e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.355391953899693e-05</v>
+        <v>3.410106330816914e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.215597946898612e-05</v>
+        <v>1.504545404889e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.171035386931739e-05</v>
+        <v>1.124504597397644e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.010399857259527e-05</v>
+        <v>2.795096597515041e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.330379556644144e-05</v>
+        <v>1.429975742895009e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.965326814119711e-05</v>
+        <v>7.347638372247393e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52376849942544e-05</v>
+        <v>1.685454998359812e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.947497827521224e-05</v>
+        <v>1.976860161973887e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.825061304469953e-05</v>
+        <v>4.872340222279626e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.04114241928937e-05</v>
+        <v>2.017794926736035e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.99674689610789e-05</v>
+        <v>2.965482408820732e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.371501791839939e-05</v>
+        <v>2.715003754979446e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.813818761926534e-05</v>
+        <v>5.435972878230862e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.562978316667598e-05</v>
+        <v>5.349604396880218e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.599165900116576e-05</v>
+        <v>2.547674244200959e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.965576183357272e-05</v>
+        <v>2.965569973269306e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.509934990712927e-05</v>
+        <v>3.332995333710122e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.117643788117151e-05</v>
+        <v>2.127067692449948e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.001941487239579e-05</v>
+        <v>3.729472889138842e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.626070955151428e-05</v>
+        <v>2.60613189656485e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68316858587097e-05</v>
+        <v>2.712595383899448e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.751467539871283e-05</v>
+        <v>4.153102549992055e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.66062458174643e-05</v>
+        <v>2.659408901727242e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.891269921412279e-05</v>
+        <v>0.0001299259338735837</v>
       </c>
       <c r="M8" t="n">
-        <v>6.126088629107831e-05</v>
+        <v>6.358380724029076e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.045302512326792e-05</v>
+        <v>3.164163856150574e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.529165331683853e-05</v>
+        <v>2.438865859672333e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.389511892504529e-05</v>
+        <v>4.484089359862949e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.814514188674959e-05</v>
+        <v>2.126392622743499e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.664115408685349e-05</v>
+        <v>2.675315618908955e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.503479879013131e-05</v>
+        <v>4.345907619026352e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.823459578397751e-05</v>
+        <v>2.980786764406322e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>5.093827028170983e-05</v>
+        <v>8.519694808319072e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.812543560767564e-05</v>
+        <v>3.023933960401459e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.440724715542612e-05</v>
+        <v>3.527823765621971e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.492469250333601e-05</v>
+        <v>5.565344777701652e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.277160725734879e-05</v>
+        <v>4.340341228339959e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.728643501157704e-05</v>
+        <v>3.725485462150396e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.864581813593547e-05</v>
+        <v>4.265814776490753e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.087518106876376e-05</v>
+        <v>7.797784201817089e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.207428157442646e-05</v>
+        <v>6.053232641534724e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.999805990148401e-05</v>
+        <v>3.007433339292715e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.366216273389095e-05</v>
+        <v>3.425329068361063e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.192287007370234e-05</v>
+        <v>4.083254237361036e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.988478661106266e-05</v>
+        <v>2.01466425801912e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.247623196135631e-05</v>
+        <v>4.028243019180526e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.026711045183254e-05</v>
+        <v>3.065890991656603e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.083808675902793e-05</v>
+        <v>3.1723544789912e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.152107629903112e-05</v>
+        <v>4.612861645083805e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.061264671778252e-05</v>
+        <v>3.119167996818997e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.291910011444104e-05</v>
+        <v>0.0001345235248245014</v>
       </c>
       <c r="M9" t="n">
-        <v>6.526728719139614e-05</v>
+        <v>6.818139819120698e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.025226595920105e-05</v>
+        <v>3.164163856150574e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.516753165435476e-05</v>
+        <v>3.511541402846625e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.452410021359821e-05</v>
+        <v>5.635685836803609e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.109317594785026e-05</v>
+        <v>3.515115291868018e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.064755498717174e-05</v>
+        <v>3.135074714000711e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.90411996904496e-05</v>
+        <v>4.805666714118106e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.224099668429581e-05</v>
+        <v>3.440545859498075e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>5.859266048920434e-05</v>
+        <v>9.358519138535015e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.998506259457019e-05</v>
+        <v>4.310537029013135e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.841217939306657e-05</v>
+        <v>3.987430278576953e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.718781416255388e-05</v>
+        <v>6.882910338882696e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.934862531074808e-05</v>
+        <v>4.028365043339099e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.586905829806234e-05</v>
+        <v>4.654992008507235e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.265221903625377e-05</v>
+        <v>4.725573871582506e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.707538873711971e-05</v>
+        <v>7.446542994833925e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.866813734368646e-06</v>
+        <v>4.8427043777599e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.943170367605198e-06</v>
+        <v>4.912277669005253e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.993562958042239e-06</v>
+        <v>4.975177078623361e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.890001680513675e-06</v>
+        <v>4.896081145393992e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.865331355322521e-06</v>
+        <v>4.841090943647841e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.689201583390326e-06</v>
+        <v>5.514962461396123e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.857166449272713e-06</v>
+        <v>4.832669447824778e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.961184231298188e-06</v>
+        <v>4.953390821139653e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.284275850414065e-06</v>
+        <v>5.303025755709788e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.373084063445074e-06</v>
+        <v>5.351570426548553e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.53551786463572e-06</v>
+        <v>7.664962346427346e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.338549677198478e-06</v>
+        <v>5.330353347106848e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.856685375482559e-06</v>
+        <v>4.83266916233749e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.669126824389986e-06</v>
+        <v>6.609502258958867e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.332157187417028e-06</v>
+        <v>5.727625306807665e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.868331249089718e-06</v>
+        <v>4.843936342453093e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.871946178950555e-06</v>
+        <v>4.848095301510261e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.220210392448989e-06</v>
+        <v>5.217143561626468e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.862159576715315e-06</v>
+        <v>4.839255636223673e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.099052502502228e-06</v>
+        <v>7.445169664897805e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.920416166456075e-06</v>
+        <v>4.91577377015367e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.021367054246635e-06</v>
+        <v>7.069682701980483e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.674777718104047e-06</v>
+        <v>7.001563227512745e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.388945744536909e-06</v>
+        <v>6.43021904273321e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.720378628868126e-06</v>
+        <v>5.835090745467739e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.344138502378533e-06</v>
+        <v>5.385942272671291e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.052755950217937e-06</v>
+        <v>7.369001833408573e-06</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.739528166793011e-06</v>
+        <v>4.728304248351136e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.827791632535236e-06</v>
+        <v>4.805446031592782e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.647243098021248e-06</v>
+        <v>5.676914678983788e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.898586264262277e-06</v>
+        <v>5.102718149573087e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.731669935690442e-06</v>
+        <v>4.719519855453087e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.056968329760496e-05</v>
+        <v>9.494906147111789e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.671895659182257e-06</v>
+        <v>4.65789411308473e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.416335110550511e-06</v>
+        <v>5.521928876435357e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.706269332374632e-06</v>
+        <v>8.000440538345772e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.34190132326066e-06</v>
+        <v>8.349143107256611e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.490402251075879e-06</v>
+        <v>2.476615402910027e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>8.121313571812551e-06</v>
+        <v>8.225096466743236e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.66722083838498e-06</v>
+        <v>4.656661659756163e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.946306747155373e-06</v>
+        <v>7.860323839317739e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>8.045392568356533e-06</v>
+        <v>1.101486399676352e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.753118573597797e-06</v>
+        <v>4.739875977959255e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.77750142612082e-06</v>
+        <v>4.768133223097955e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.247221697262939e-06</v>
+        <v>7.385192083445136e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.707758304328763e-06</v>
+        <v>4.705160927884415e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.100228942839208e-05</v>
+        <v>1.358974932024384e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.123026506815902e-06</v>
+        <v>5.249878544331299e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.320525050006404e-06</v>
+        <v>9.839940073264115e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.764514253239077e-05</v>
+        <v>2.013833614601477e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.559973458674214e-05</v>
+        <v>1.605497032687415e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.716705087246935e-06</v>
+        <v>7.407457149169126e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.147158417033335e-06</v>
+        <v>8.606484295876289e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.024364944041619e-05</v>
+        <v>2.264389043041272e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.616578687331707e-06</v>
+        <v>4.70196877269091e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.532359289702743e-06</v>
+        <v>4.617163515822678e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>7.048269476248537e-06</v>
+        <v>6.19830886939693e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.878497206022066e-06</v>
+        <v>5.304883917644217e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.599834534077784e-06</v>
+        <v>4.68374429217884e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.490582775913304e-05</v>
+        <v>1.229543308135938e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.507608164202837e-06</v>
+        <v>4.588619622777962e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6825368627242e-06</v>
+        <v>5.952223068944876e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03136276763552e-05</v>
+        <v>9.883627842257318e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.133513495010768e-05</v>
+        <v>1.044984488370655e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.316989945779624e-05</v>
+        <v>3.658067083159868e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.097543648422459e-05</v>
+        <v>1.024367512358103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>5.502174214438156e-06</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>6.093954053527968e-06</v>
+        <v>5.145830895481372e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.087284705807785e-05</v>
+        <v>1.469755775002497e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.633719714197307e-06</v>
+        <v>4.715884380632391e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>5.67455200992551e-06</v>
+        <v>4.762861736398816e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.608356510843789e-06</v>
+        <v>8.93143160499854e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.564007835619114e-06</v>
+        <v>4.663013650539874e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.085732902315339e-05</v>
+        <v>1.409141419452726e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.102404101593382e-06</v>
+        <v>5.411075919610817e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>7.725738813867056e-06</v>
+        <v>7.657188341099242e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.603836358814632e-05</v>
+        <v>2.9087272604786e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.27177506860114e-05</v>
+        <v>2.257238000741873e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.792986176624156e-06</v>
+        <v>6.860354856580958e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.100818152224514e-05</v>
+        <v>1.083809069749334e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.001099953163935e-05</v>
+        <v>3.289073558694874e-05</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.564100676206681e-05</v>
+        <v>1.479768747098296e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.620292647034875e-05</v>
+        <v>1.535822563757624e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.256900805187447e-05</v>
+        <v>4.289334927380764e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.693846925733607e-05</v>
+        <v>2.207269492028349e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.675524976249626e-05</v>
+        <v>1.589050820187161e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001595870867661916</v>
+        <v>0.0001328607383191244</v>
       </c>
       <c r="H5" t="n">
-        <v>1.434625267180011e-05</v>
+        <v>1.341979634738144e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.619401436406677e-05</v>
+        <v>3.880199907033424e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>9.243776963398965e-05</v>
+        <v>9.990154211598167e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001111326889445807</v>
+        <v>0.0001107768053639508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001379881467465189</v>
+        <v>0.0005243431562669769</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001096307502488247</v>
+        <v>0.0001118910769942771</v>
       </c>
       <c r="N5" t="n">
-        <v>9.767408908392967e-05</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.401308793598531e-05</v>
+        <v>2.265125542979488e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001006701645385771</v>
+        <v>0.0001764721305317583</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.737438538898998e-05</v>
+        <v>1.648402491012816e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.736220500003613e-05</v>
+        <v>1.657619205182618e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.87196165670888e-05</v>
+        <v>8.156853107612256e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.546112366280578e-05</v>
+        <v>1.487076150636256e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001031212531641347</v>
+        <v>0.0001685803628689422</v>
       </c>
       <c r="V5" t="n">
-        <v>2.671459736976617e-05</v>
+        <v>2.931771719671501e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.297758018910607e-05</v>
+        <v>6.71733708485559e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003779146165266861</v>
+        <v>0.0004472055152002935</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003180073712644445</v>
+        <v>0.0003301330461131223</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.47965604656066e-05</v>
+        <v>4.917811307977234e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001114873160773029</v>
+        <v>0.0001238765772122177</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004803672489006373</v>
+        <v>0.0005515902484519695</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.017183942000301e-06</v>
+        <v>7.418013698302502e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>8.204788998407607e-06</v>
+        <v>7.333208441434303e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.448874730917129e-06</v>
+        <v>8.914353795008555e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>8.550926914726923e-06</v>
+        <v>5.7921780821812e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>8.272264242782647e-06</v>
+        <v>5.171038456715819e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.530643301380164e-05</v>
+        <v>1.278272724589638e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.180037872907704e-06</v>
+        <v>5.075913787314942e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>9.354966571429072e-06</v>
+        <v>8.668267994556504e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.071423293102378e-05</v>
+        <v>1.259967276786893e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.400756465881254e-05</v>
+        <v>1.093713904824353e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.357050471246483e-05</v>
+        <v>3.929671575721027e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.364786619292946e-05</v>
+        <v>1.073096928811801e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.915525293118956e-06</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.507305132208761e-06</v>
+        <v>7.86369317156664e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.122995231441553e-05</v>
+        <v>1.514327623623388e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.306149422902181e-06</v>
+        <v>5.203178545169364e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>8.346981718630375e-06</v>
+        <v>7.478906662010436e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.000896176551239e-05</v>
+        <v>9.418725769535513e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>5.964613090287716e-06</v>
+        <v>5.150307815076861e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.134994354931194e-05</v>
+        <v>1.686875631911105e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>8.774833810298249e-06</v>
+        <v>5.898370084147788e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>8.18596832605143e-06</v>
+        <v>8.208359855521095e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.64389688428149e-05</v>
+        <v>3.180331753039764e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.325217871048888e-05</v>
+        <v>2.316985515821057e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.193591431292759e-06</v>
+        <v>9.576399782192569e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.368061123095e-05</v>
+        <v>1.132538486203032e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.054643285316796e-05</v>
+        <v>3.353121117165604e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.412877400902638e-06</v>
+        <v>7.436236419353763e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.328658003273686e-06</v>
+        <v>7.351431162485519e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.844568189819467e-06</v>
+        <v>8.932576516059774e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.674795919593007e-06</v>
+        <v>8.039151564307061e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.39613324764872e-06</v>
+        <v>7.418011938841704e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.770212647270393e-05</v>
+        <v>1.502970072802223e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.303906877773774e-06</v>
+        <v>7.32288726944082e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>9.478835576295139e-06</v>
+        <v>8.686490715607717e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.310992638992612e-05</v>
+        <v>1.261789548892016e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.413143366367861e-05</v>
+        <v>1.31841125303694e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.596619817136719e-05</v>
+        <v>3.931493847826146e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.377173519779552e-05</v>
+        <v>1.297794277024387e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.298472928009086e-06</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.888825527406976e-06</v>
+        <v>7.878671846599363e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.366771853195688e-05</v>
+        <v>1.743039870114296e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.430018427768247e-06</v>
+        <v>7.450152027295239e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>8.47085072349645e-06</v>
+        <v>7.497129383061656e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.240465522441474e-05</v>
+        <v>1.166569925166138e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>8.360306549190059e-06</v>
+        <v>7.397281297202725e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.374707490593122e-05</v>
+        <v>1.688668969173692e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.898702815164331e-06</v>
+        <v>8.145343566273667e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.052203752743799e-05</v>
+        <v>1.039145598776209e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.883466230171728e-05</v>
+        <v>3.182154025144887e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.560605867107227e-05</v>
+        <v>2.536794485305376e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.589284890195081e-06</v>
+        <v>9.594622503243819e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.380448023581608e-05</v>
+        <v>1.357235834415619e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.28072982452103e-05</v>
+        <v>3.562500323361159e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.495192523752815e-05</v>
+        <v>1.401690282601425e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.117340467694061e-05</v>
+        <v>2.020029200033555e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.268931486348639e-05</v>
+        <v>2.178143735390984e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.816194396895349e-05</v>
+        <v>1.7550383767714e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.591753526687615e-05</v>
+        <v>1.497518977996503e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.185440087806841e-05</v>
+        <v>2.917831251467611e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.11486535514407e-05</v>
+        <v>2.017174810729084e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.232358224996206e-05</v>
+        <v>2.153535155345776e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.595467306359303e-05</v>
+        <v>2.546675632677019e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.697618033734554e-05</v>
+        <v>2.603297336821944e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.88109448450341e-05</v>
+        <v>5.216379931611155e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.661648187146288e-05</v>
+        <v>2.582680360809342e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.62552480826345e-05</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.819028493689127e-05</v>
+        <v>1.720532777486738e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.263991318936402e-05</v>
+        <v>2.642974824539574e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.372985252228527e-05</v>
+        <v>1.279897516367656e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.131559739716336e-05</v>
+        <v>2.03459902209117e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.524940189808163e-05</v>
+        <v>2.451456008951143e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.120505322285696e-05</v>
+        <v>2.024614213505276e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.351487665211369e-05</v>
+        <v>2.667729925294559e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.002245596697411e-05</v>
+        <v>1.928198452935018e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.336802345196484e-05</v>
+        <v>2.324154870549235e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.471242622447737e-05</v>
+        <v>3.774485586257935e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.472421664897785e-05</v>
+        <v>4.445063658700174e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.601120113355341e-05</v>
+        <v>1.605885398026001e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.664922690948302e-05</v>
+        <v>2.642121918200621e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.223887462844078e-05</v>
+        <v>5.502151729277528e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.861837684718316e-05</v>
+        <v>1.742607596413953e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.22927110853466e-05</v>
+        <v>2.101234878927653e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.380862127189239e-05</v>
+        <v>2.259349414285074e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.177139016904386e-05</v>
+        <v>2.085279932891734e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.369569436601884e-05</v>
+        <v>1.261609267962171e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.166617957513857e-05</v>
+        <v>2.869061833543722e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.226795995984671e-05</v>
+        <v>2.098380489623181e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.344288865836805e-05</v>
+        <v>2.234740834239878e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.707397947199908e-05</v>
+        <v>2.627881311571113e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.809548674575154e-05</v>
+        <v>2.684503015716039e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.993025125344011e-05</v>
+        <v>5.297585610505244e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.77357882798685e-05</v>
+        <v>2.66388603970349e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.226252601008199e-05</v>
+        <v>1.278210748576922e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.409988562979751e-05</v>
+        <v>2.27576066126684e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.91496708616376e-05</v>
+        <v>3.257392101974363e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.239407153020289e-05</v>
+        <v>2.111106963471013e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.243490380556938e-05</v>
+        <v>2.115804700985268e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.636870830648767e-05</v>
+        <v>2.532661687845241e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2324359631263e-05</v>
+        <v>2.105819892399369e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.770969009028721e-05</v>
+        <v>3.054789666695328e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.720004448695025e-05</v>
+        <v>2.604260469808854e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.448609060951093e-05</v>
+        <v>2.405237361455307e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.279871538379022e-05</v>
+        <v>4.548245787823986e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.957011175314519e-05</v>
+        <v>3.902886247984476e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.128726436160094e-05</v>
+        <v>2.104220648389221e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.776853331788899e-05</v>
+        <v>2.72332759709472e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.677135132728324e-05</v>
+        <v>4.928592086040257e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -798,7 +798,7 @@
         <v>5.032307024653583e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>9.349131809939894e-06</v>
       </c>
       <c r="O4" t="n">
         <v>1.807512892650743e-05</v>
@@ -974,7 +974,7 @@
         <v>5.635156749078816e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>1.150986169158423e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.023588429060391e-05</v>
@@ -1062,7 +1062,7 @@
         <v>5.516463980837903e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>1.419070137178306e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.291504185772133e-05</v>
@@ -1150,7 +1150,7 @@
         <v>7.340270128125214e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>2.51857196691206e-05</v>
       </c>
       <c r="O8" t="n">
         <v>3.590216794065465e-05</v>
@@ -1238,7 +1238,7 @@
         <v>8.408616434471188e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>4.31122259081159e-05</v>
       </c>
       <c r="O9" t="n">
         <v>5.433187527696479e-05</v>
@@ -1658,7 +1658,7 @@
         <v>6.631884310960313e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>4.584997179444851e-06</v>
       </c>
       <c r="O4" t="n">
         <v>4.809448122115711e-06</v>
@@ -1834,7 +1834,7 @@
         <v>7.109642143522895e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>5.080277963255798e-06</v>
       </c>
       <c r="O6" t="n">
         <v>7.089442414254805e-06</v>
@@ -1922,7 +1922,7 @@
         <v>9.19682210855578e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>7.149934977040307e-06</v>
       </c>
       <c r="O7" t="n">
         <v>7.372958248571013e-06</v>
@@ -2010,7 +2010,7 @@
         <v>2.157990516743209e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>1.488274010144952e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.638512779824453e-05</v>
@@ -2098,7 +2098,7 @@
         <v>2.077957013015463e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>1.873268299863915e-05</v>
       </c>
       <c r="O9" t="n">
         <v>2.00082310126365e-05</v>
@@ -2518,7 +2518,7 @@
         <v>4.717115620798103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>1.034175957402554e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.711393082697151e-05</v>
@@ -2694,7 +2694,7 @@
         <v>5.22071718237867e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>1.19504593067281e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.872142300303982e-05</v>
@@ -2782,7 +2782,7 @@
         <v>5.140411753588151e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>1.45747209019261e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.134534935223283e-05</v>
@@ -2870,7 +2870,7 @@
         <v>6.799585828226701e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>2.46331680960622e-05</v>
       </c>
       <c r="O8" t="n">
         <v>3.320074514477713e-05</v>
@@ -2958,7 +2958,7 @@
         <v>7.374034275660951e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>3.691094612265401e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.565298208487886e-05</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.291797728592632e-05</v>
+        <v>1.29179772859264e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.896464213325457e-06</v>
+        <v>7.896464213325474e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.384184635885466e-06</v>
+        <v>9.384184635885479e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.187882020338689e-06</v>
+        <v>9.187882020338787e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.869504405484768e-06</v>
+        <v>8.869504405484727e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.940046641095685e-06</v>
+        <v>8.940046641095824e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.952092288189629e-06</v>
+        <v>7.952092288189573e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.581397712842936e-06</v>
+        <v>9.58139771284307e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.913630836835545e-06</v>
+        <v>9.913630836835551e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.060571958614869e-05</v>
+        <v>1.060571958614882e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.763814986626275e-05</v>
+        <v>1.763814986626281e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.123569618636443e-05</v>
+        <v>1.123569618636444e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>8.424638994852161e-06</v>
+        <v>8.424638994852236e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.196699615783571e-05</v>
+        <v>1.196699615783563e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.11797415391358e-05</v>
+        <v>1.117974153913583e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.139770264663518e-06</v>
+        <v>9.139770264663591e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>8.045511010969437e-06</v>
+        <v>8.045511010969676e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.103694247547979e-05</v>
+        <v>1.103694247548005e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.324161432421288e-06</v>
+        <v>9.324161432421351e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.70425276128072e-05</v>
+        <v>1.704252761280717e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>9.430234323498103e-06</v>
+        <v>9.430234323498186e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.176154932148978e-05</v>
+        <v>1.176154932148976e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.313203912818558e-05</v>
+        <v>1.313203912818569e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.924944854842971e-06</v>
+        <v>9.924944854843027e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.297889350868897e-05</v>
+        <v>1.297889350868903e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.977238128771475e-06</v>
+        <v>9.977238128771594e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.236394655471017e-05</v>
+        <v>1.236394655471016e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.252928113933592e-05</v>
+        <v>4.252928113933593e-05</v>
       </c>
       <c r="C3" t="n">
         <v>7.334755611013689e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.745723742929842e-05</v>
+        <v>1.745723742929836e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.602161294835468e-05</v>
+        <v>1.60216129483546e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.377483651455417e-05</v>
+        <v>1.377483651455409e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.423502870725791e-05</v>
+        <v>1.423502870725786e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.211771307818342e-06</v>
+        <v>7.211771307818322e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.887982165692932e-05</v>
+        <v>1.887982165692926e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.119004733486741e-05</v>
+        <v>2.119004733486735e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.608363564361066e-05</v>
+        <v>2.608363564361059e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.630669831159268e-05</v>
+        <v>7.630669831159247e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.074530083495684e-05</v>
+        <v>3.074530083495681e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.058747550340642e-05</v>
+        <v>1.058747550340635e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.860379978234935e-05</v>
+        <v>1.860379978234942e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.015643765153794e-05</v>
+        <v>3.015643765153795e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56900106706558e-05</v>
+        <v>1.569001067065574e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>7.880784567618127e-06</v>
+        <v>7.880784567618171e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.915409514375114e-05</v>
+        <v>2.915409514375109e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.703343765205918e-05</v>
+        <v>1.703343765205909e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>5.846773836414369e-05</v>
+        <v>5.846773836414389e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76984162984041e-05</v>
+        <v>1.769841629840393e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.032235107914814e-05</v>
+        <v>2.032235107914813e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.42420564204122e-05</v>
+        <v>4.424205642041216e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.128878927834943e-05</v>
+        <v>2.128878927834945e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.02466513290377e-05</v>
+        <v>3.02466513290376e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.166844614540824e-05</v>
+        <v>2.166844614540813e-05</v>
       </c>
       <c r="AB3" t="n">
         <v>3.872742543965345e-05</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.337101846032988e-05</v>
+        <v>6.337101846032994e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.677161625596517e-06</v>
+        <v>7.677161625596505e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.345520485318387e-05</v>
+        <v>2.345520485318385e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.12378765069193e-05</v>
+        <v>2.123787650691929e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.764165488620545e-05</v>
+        <v>1.764165488620542e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.843846188846229e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.279062990932135e-06</v>
+        <v>7.279062990932133e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.568281727991705e-05</v>
+        <v>2.568281727991702e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.941934240589133e-05</v>
+        <v>2.941934240589129e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.72530040502474e-05</v>
+        <v>3.725300405024738e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000116687539141895</v>
+        <v>0.0001166875391418948</v>
       </c>
       <c r="M4" t="n">
-        <v>4.439797991536718e-05</v>
+        <v>4.439797991536719e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001144360936757271</v>
+        <v>1.261669542491004e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.716698340082859e-05</v>
+        <v>1.716698340082856e-05</v>
       </c>
       <c r="P4" t="n">
         <v>4.373684607238141e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.069443209406711e-05</v>
+        <v>2.069443209406706e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.334270439465838e-06</v>
+        <v>8.334270439465805e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>4.212386495757211e-05</v>
+        <v>4.212386495757207e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.277721515801891e-05</v>
+        <v>2.27772151580189e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>8.213790601952473e-05</v>
+        <v>8.213790601952486e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.387091441876718e-05</v>
+        <v>2.387091441876717e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.132400762640709e-05</v>
+        <v>2.132400762640706e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>6.578894544196114e-05</v>
+        <v>6.578894544196106e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.958895864503118e-05</v>
+        <v>2.95889586450312e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.786161941513921e-05</v>
+        <v>3.786161941513908e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.015401687341738e-05</v>
+        <v>3.015401687341731e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.682684708310243e-05</v>
+        <v>5.68268470831023e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3433,82 +3433,82 @@
         <v>0.0009461018276795289</v>
       </c>
       <c r="C5" t="n">
-        <v>2.687482862502744e-05</v>
+        <v>2.687482862502742e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003172421228735223</v>
+        <v>0.000317242122873522</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002600929211173594</v>
+        <v>0.0002600929211173588</v>
       </c>
       <c r="F5" t="n">
         <v>0.0002097027830454976</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002013713951886604</v>
+        <v>0.0002013713951886608</v>
       </c>
       <c r="H5" t="n">
-        <v>1.841709381549289e-05</v>
+        <v>1.841709381549306e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003644480061396054</v>
+        <v>0.000364448006139605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003992250233274895</v>
+        <v>0.0003992250233274888</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005137279059323078</v>
+        <v>0.0005137279059323074</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001935375202271077</v>
+        <v>0.001935375202271074</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007176664536588288</v>
+        <v>0.0007176664536588257</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001144360936757271</v>
+        <v>0.0001144360936757272</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001736035653988387</v>
+        <v>0.0001736035653988391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006159569277379084</v>
+        <v>0.0006159569277379093</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002565826427052115</v>
+        <v>0.0002565826427052108</v>
       </c>
       <c r="R5" t="n">
         <v>3.826130516882004e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005961460261983438</v>
+        <v>0.0005961460261983425</v>
       </c>
       <c r="T5" t="n">
         <v>0.0003076287951550497</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001291170883482108</v>
+        <v>0.001291170883482113</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002810031144467811</v>
+        <v>0.0002810031144467816</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002671063488199223</v>
+        <v>0.0002671063488199217</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001084741137917361</v>
+        <v>0.001084741137917362</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0004108260630158606</v>
+        <v>0.0004108260630158605</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0004986040824008544</v>
+        <v>0.0004986040824008529</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004246090504142525</v>
+        <v>0.0004246090504142526</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009898433456973317</v>
+        <v>0.0009898433456973282</v>
       </c>
     </row>
     <row r="6">
@@ -3518,64 +3518,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.843363320671932e-05</v>
+        <v>6.843363320671937e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.437959102405934e-06</v>
+        <v>9.437959102405937e-06</v>
       </c>
       <c r="D6" t="n">
         <v>2.851781959957328e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.630049125330873e-05</v>
+        <v>2.630049125330869e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.940245236301486e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.019925936527171e-05</v>
+        <v>2.019925936527174e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.039860467741568e-06</v>
+        <v>9.039860467741567e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.744361475672649e-05</v>
+        <v>2.744361475672648e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.448195715228078e-05</v>
+        <v>3.448195715228072e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.231561879663687e-05</v>
+        <v>4.231561879663679e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001217501538882845</v>
+        <v>0.0001217501538882843</v>
       </c>
       <c r="M6" t="n">
-        <v>4.61587773921766e-05</v>
+        <v>4.615877739217652e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001144360936757271</v>
+        <v>1.446657443391948e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.222485937652636e-05</v>
+        <v>2.222485937652632e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.879654524404244e-05</v>
+        <v>4.879654524404243e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.575704684045653e-05</v>
+        <v>2.575704684045647e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.009506791627526e-05</v>
+        <v>1.009506791627525e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.718647970396152e-05</v>
+        <v>4.718647970396145e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.453801263482836e-05</v>
+        <v>2.453801263482832e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.387308513960359e-05</v>
+        <v>8.387308513960378e-05</v>
       </c>
       <c r="V6" t="n">
         <v>2.893352916515661e-05</v>
@@ -3584,19 +3584,19 @@
         <v>2.638165512401221e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>6.754974291877061e-05</v>
+        <v>6.754974291877054e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.152117231394492e-05</v>
+        <v>3.152117231394526e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.292423416152858e-05</v>
+        <v>4.292423416152851e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.521663161980675e-05</v>
+        <v>3.521663161980671e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.878525111433373e-05</v>
+        <v>5.878525111433371e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.742623306130161e-05</v>
+        <v>6.742623306130166e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.173237622656833e-05</v>
+        <v>1.173237622656832e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.751041945415567e-05</v>
+        <v>2.751041945415565e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.529309110789109e-05</v>
+        <v>2.529309110789107e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.169686948717724e-05</v>
+        <v>2.169686948717723e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.249367648943411e-05</v>
+        <v>2.249367648943408e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.133427759190393e-05</v>
+        <v>1.133427759190394e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.973803188088886e-05</v>
+        <v>2.973803188088881e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.34745570068631e-05</v>
+        <v>3.347455700686306e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.130821865121924e-05</v>
+        <v>4.130821865121917e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000120742753742867</v>
+        <v>0.0001207427537428669</v>
       </c>
       <c r="M7" t="n">
-        <v>4.845319451633899e-05</v>
+        <v>4.845319451633896e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001144360936757271</v>
+        <v>1.667191002588186e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.12207452796876e-05</v>
+        <v>2.122074527968759e-05</v>
       </c>
       <c r="P7" t="n">
         <v>4.77906079512404e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.47496466950389e-05</v>
+        <v>2.474964669503884e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.238948504043764e-05</v>
+        <v>1.238948504043763e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.617907955854393e-05</v>
+        <v>4.617907955854385e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.683242975899071e-05</v>
+        <v>2.683242975899067e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>8.616901482362794e-05</v>
+        <v>8.616901482362817e-05</v>
       </c>
       <c r="V7" t="n">
         <v>2.792612901973899e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.537922222737886e-05</v>
+        <v>2.537922222737882e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>6.984416004293307e-05</v>
+        <v>6.984416004293296e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.361855488927229e-05</v>
+        <v>3.361855488927231e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.191683401611102e-05</v>
+        <v>4.19168340161109e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.420923147438919e-05</v>
+        <v>3.420923147438914e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.088206168407428e-05</v>
+        <v>6.088206168407421e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.506588133437598e-05</v>
+        <v>7.506588133437611e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.734361436893578e-05</v>
+        <v>2.734361436893579e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.312165759652314e-05</v>
+        <v>4.312165759652316e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.665969279214715e-05</v>
+        <v>3.665969279214713e-05</v>
       </c>
       <c r="F8" t="n">
         <v>3.057839829589998e-05</v>
@@ -3712,10 +3712,10 @@
         <v>3.975787572124933e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.694551573427142e-05</v>
+        <v>2.694551573427143e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.534927002325632e-05</v>
+        <v>4.534927002325629e-05</v>
       </c>
       <c r="J8" t="n">
         <v>4.908579514923051e-05</v>
@@ -3724,55 +3724,55 @@
         <v>5.691945679358663e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001363539918852343</v>
+        <v>0.0001363539918852342</v>
       </c>
       <c r="M8" t="n">
-        <v>6.406443265870587e-05</v>
+        <v>6.406443265870583e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001144360936757271</v>
+        <v>2.610383240150503e-05</v>
       </c>
       <c r="O8" t="n">
         <v>3.235225000400225e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.850586007154922e-05</v>
+        <v>5.850586007154917e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.082269561626957e-05</v>
+        <v>3.082269561626954e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.800072318280511e-05</v>
+        <v>2.800072318280509e-05</v>
       </c>
       <c r="S8" t="n">
         <v>6.179031770091134e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.244366790135822e-05</v>
+        <v>4.244366790135816e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>9.789021180703697e-05</v>
+        <v>9.789021180703698e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>4.136114610316567e-05</v>
+        <v>4.136114610316574e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.099202701513341e-05</v>
+        <v>4.099202701513338e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>7.664782101520598e-05</v>
+        <v>7.664782101520599e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.715969463830547e-05</v>
+        <v>5.715969463830545e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.940840591478699e-05</v>
+        <v>4.94084059147869e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.982046961675666e-05</v>
+        <v>4.982046961675663e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.48202920180037e-05</v>
+        <v>8.482029201800361e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.18595297393736e-05</v>
+        <v>8.185952973937364e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.151415214197051e-05</v>
+        <v>3.15141521419705e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.72921953695579e-05</v>
+        <v>4.729219536955793e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.384046103611114e-05</v>
+        <v>4.384046103611109e-05</v>
       </c>
       <c r="F9" t="n">
         <v>2.91489389776883e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.227545397106338e-05</v>
+        <v>4.227545397106334e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.111605350730612e-05</v>
+        <v>3.111605350730608e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.951980779629104e-05</v>
+        <v>4.951980779629102e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.325633292226534e-05</v>
+        <v>5.325633292226528e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.108999456662145e-05</v>
+        <v>6.108999456662143e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001405245296582693</v>
+        <v>0.0001405245296582691</v>
       </c>
       <c r="M9" t="n">
-        <v>6.823497043174122e-05</v>
+        <v>6.823497043174115e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001144360936757271</v>
+        <v>3.645368594128405e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.277645501851206e-05</v>
+        <v>4.277645501851215e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>6.973180157830024e-05</v>
+        <v>6.973180157830026e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.453142417666814e-05</v>
+        <v>4.453142417666815e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.217126095583984e-05</v>
+        <v>3.217126095583982e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>6.596085547394612e-05</v>
+        <v>6.596085547394609e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.661420567439293e-05</v>
+        <v>4.661420567439291e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001059492781791682</v>
+        <v>0.0001059492781791685</v>
       </c>
       <c r="V9" t="n">
-        <v>5.387992782204279e-05</v>
+        <v>5.387992782204283e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.516099814278109e-05</v>
+        <v>4.51609981427811e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>8.962593595833519e-05</v>
+        <v>8.962593595833508e-05</v>
       </c>
       <c r="Y9" t="n">
         <v>5.34003308046745e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.847395317866604e-05</v>
+        <v>5.847395317866591e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.399100738979139e-05</v>
+        <v>5.399100738979135e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.066383759947656e-05</v>
+        <v>8.066383759947654e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,82 +4026,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.283226936504508e-05</v>
+        <v>1.283226936504506e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.594550333543018e-06</v>
+        <v>8.59455033354302e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.885095614696939e-06</v>
+        <v>9.885095614696954e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.499589511773127e-06</v>
+        <v>9.499589511773137e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.673079757193272e-06</v>
+        <v>9.673079757193275e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.565657393399117e-06</v>
+        <v>9.565657393399119e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.610721306833858e-06</v>
+        <v>8.610721306833876e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.042306480285845e-05</v>
+        <v>1.042306480285846e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.060132320072687e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.170451864896969e-05</v>
+        <v>1.17045186489697e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655630602004336e-05</v>
+        <v>1.655630602004339e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.152871978751994e-05</v>
+        <v>1.152871978751993e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.00705128565478e-06</v>
+        <v>9.007051285654782e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.228915147167439e-05</v>
+        <v>1.228915147167438e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.157615077807971e-05</v>
+        <v>1.157615077807973e-05</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01668584127915e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>8.975000245366141e-06</v>
+        <v>8.975000245366135e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.149726026968308e-05</v>
+        <v>1.14972602696831e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.001235689239288e-05</v>
+        <v>1.001235689239289e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.889057440498694e-05</v>
+        <v>1.889057440498693e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.132358983599318e-05</v>
+        <v>1.132358983599319e-05</v>
       </c>
       <c r="W2" t="n">
         <v>1.301448007201735e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.44661952723592e-05</v>
+        <v>1.446619527235921e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.182246859080767e-05</v>
+        <v>1.182246859080765e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>1.3701103106792e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.076845351318064e-05</v>
+        <v>1.076845351318066e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.278725210282569e-05</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.79065734534631e-05</v>
+        <v>3.790657345346311e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.455741757988827e-06</v>
+        <v>8.455741757988817e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.702958912347069e-05</v>
+        <v>1.702958912347062e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.424769870704374e-05</v>
+        <v>1.424769870704373e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.552817572270522e-05</v>
+        <v>1.55281757227052e-05</v>
       </c>
       <c r="G3" t="n">
         <v>1.471030783118629e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.931688457728281e-06</v>
+        <v>7.931688457728288e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.089795108081442e-05</v>
+        <v>2.089795108081439e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.209702642984469e-05</v>
+        <v>2.209702642984468e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.993464803614659e-05</v>
+        <v>2.99346480361466e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>6.449183729966469e-05</v>
+        <v>6.449183729966475e-05</v>
       </c>
       <c r="M3" t="n">
         <v>2.88178227071949e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.076306822246217e-05</v>
+        <v>1.076306822246214e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.717404153862067e-05</v>
+        <v>1.717404153862064e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.897631391392813e-05</v>
+        <v>2.897631391392814e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.902548345849503e-05</v>
+        <v>1.902548345849504e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.054270875277552e-05</v>
+        <v>1.054270875277553e-05</v>
       </c>
       <c r="S3" t="n">
         <v>2.844920401343725e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.796578050131755e-05</v>
+        <v>1.796578050131757e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.55785336372059e-05</v>
+        <v>6.557853363720597e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.716697067963721e-05</v>
+        <v>2.716697067963727e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.337308374468357e-05</v>
+        <v>2.337308374468359e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.971962443236551e-05</v>
+        <v>4.971962443236553e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.087326826589043e-05</v>
+        <v>3.087326826589031e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.060318621684737e-05</v>
+        <v>3.060318621684733e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.333952478448381e-05</v>
+        <v>2.333952478448378e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.774728478321177e-05</v>
+        <v>3.774728478321172e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.634739632510678e-05</v>
+        <v>5.63473963251069e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.756001200517333e-06</v>
+        <v>9.756001200517366e-06</v>
       </c>
       <c r="D4" t="n">
         <v>2.30577130480171e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.870324427392365e-05</v>
+        <v>1.870324427392369e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.066289640540026e-05</v>
+        <v>2.066289640540029e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.944951138961631e-05</v>
+        <v>1.944951138961628e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.663068999558523e-06</v>
+        <v>8.663068999558589e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.913432250635473e-05</v>
+        <v>2.913432250635477e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.114025127618192e-05</v>
+        <v>3.11402512761819e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.360893319607482e-05</v>
+        <v>4.360893319607491e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>9.841210348481249e-05</v>
+        <v>9.841210348481268e-05</v>
       </c>
       <c r="M4" t="n">
         <v>4.168847350792728e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001017596901612095</v>
+        <v>1.313979843113876e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.524185422735398e-05</v>
+        <v>1.524185422735397e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.215895904223438e-05</v>
+        <v>4.21589590422344e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>2.6240353469786e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.277776718687163e-05</v>
+        <v>1.277776718687164e-05</v>
       </c>
       <c r="S4" t="n">
         <v>4.126785445846769e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.449518772267286e-05</v>
+        <v>2.449518772267287e-05</v>
       </c>
       <c r="U4" t="n">
         <v>9.307893224619377e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>3.926011985203009e-05</v>
+        <v>3.926011985203007e-05</v>
       </c>
       <c r="W4" t="n">
         <v>2.548424863155933e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>7.480334109127245e-05</v>
+        <v>7.480334109127253e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5180359176052e-05</v>
+        <v>4.518035917605202e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.837310709894341e-05</v>
+        <v>3.837310709894348e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.303564687610053e-05</v>
+        <v>3.303564687610052e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.557902680989331e-05</v>
+        <v>5.557902680989337e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007844577704594451</v>
+        <v>0.0007844577704594457</v>
       </c>
       <c r="C5" t="n">
         <v>4.166853951805554e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002771094696214769</v>
+        <v>0.0002771094696214759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001842803226935625</v>
+        <v>0.0001842803226935629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002408445764852526</v>
+        <v>0.0002408445764852524</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001928563919528359</v>
+        <v>0.0001928563919528349</v>
       </c>
       <c r="H5" t="n">
-        <v>2.115469735171166e-05</v>
+        <v>2.115469735171191e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003995346209102987</v>
+        <v>0.0003995346209102988</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000397224049879528</v>
+        <v>0.0003972240498795275</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005990021147510425</v>
+        <v>0.0005990021147510442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001531876627220592</v>
+        <v>0.001531876627220593</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006181006713594517</v>
+        <v>0.0006181006713594519</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001017596901612095</v>
+        <v>0.0001017596901612093</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001245663420029705</v>
+        <v>0.0001245663420029698</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005515053491208962</v>
+        <v>0.0005515053491208955</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0003255948382965407</v>
       </c>
       <c r="R5" t="n">
-        <v>9.97046839237455e-05</v>
+        <v>9.970468392374535e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005543674040765465</v>
+        <v>0.0005543674040765469</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003170030852201916</v>
+        <v>0.0003170030852201919</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001401778997993861</v>
+        <v>0.001401778997993863</v>
       </c>
       <c r="V5" t="n">
         <v>0.0004974773813827835</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003196482317821589</v>
+        <v>0.0003196482317821587</v>
       </c>
       <c r="X5" t="n">
         <v>0.001189465366430303</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006727330769835901</v>
+        <v>0.0006727330769835898</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000462828552839638</v>
+        <v>0.0004628285528396379</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004563666446057872</v>
+        <v>0.0004563666446057867</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009279931704724873</v>
+        <v>0.000927993170472486</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.866328113393744e-05</v>
+        <v>5.866328113393758e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.207188600934796e-05</v>
+        <v>1.2071886009348e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.875175875023405e-05</v>
+        <v>2.875175875023407e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.439728997614059e-05</v>
+        <v>2.439728997614062e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.297878121423086e-05</v>
+        <v>2.297878121423089e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.176539619844702e-05</v>
+        <v>2.176539619844693e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.435711470177543e-05</v>
+        <v>1.435711470177552e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.145020731518539e-05</v>
+        <v>3.145020731518542e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.683429697839879e-05</v>
+        <v>3.683429697839878e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.930297889829175e-05</v>
+        <v>4.93029788982918e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001007279882936431</v>
+        <v>0.0001007279882936432</v>
       </c>
       <c r="M6" t="n">
-        <v>4.400435831675788e-05</v>
+        <v>4.400435831675793e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001017596901612095</v>
+        <v>1.560879076430086e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.770975492356126e-05</v>
+        <v>1.770975492356155e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.788563149997652e-05</v>
+        <v>4.788563149997653e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.193439917200293e-05</v>
+        <v>3.193439917200297e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.847181288908855e-05</v>
+        <v>1.847181288908863e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.358373926729832e-05</v>
+        <v>4.35837392672983e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.018923342488981e-05</v>
+        <v>3.01892334248898e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>9.85338508211473e-05</v>
+        <v>9.853385082114741e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.157600466086083e-05</v>
+        <v>4.157600466086075e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.799504166828755e-05</v>
+        <v>2.79950416682876e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>7.711922590010296e-05</v>
+        <v>7.711922590010304e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>4.758397088258987e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.068899190777401e-05</v>
+        <v>4.068899190777404e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.872969257831743e-05</v>
+        <v>3.872969257831746e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.80986901733212e-05</v>
+        <v>5.809869017332131e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.062549390349611e-05</v>
+        <v>6.062549390349619e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.403409877890663e-05</v>
+        <v>1.403409877890664e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.733581062640641e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.298134185231294e-05</v>
+        <v>2.298134185231297e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.494099398378952e-05</v>
+        <v>2.494099398378958e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.372760896800561e-05</v>
+        <v>2.372760896800557e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.294116657794785e-05</v>
+        <v>1.294116657794786e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.341242008474402e-05</v>
+        <v>3.341242008474404e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.54183488545712e-05</v>
+        <v>3.541834885457117e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.788703077446411e-05</v>
+        <v>4.788703077446414e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001026902010632018</v>
+        <v>0.0001026902010632019</v>
       </c>
       <c r="M7" t="n">
         <v>4.596657108631652e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001017596901612095</v>
+        <v>1.741789600952805e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.951847053343916e-05</v>
+        <v>1.951847053343914e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.643557534831951e-05</v>
+        <v>4.643557534831952e-05</v>
       </c>
       <c r="Q7" t="n">
         <v>3.051845104817533e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.705586476526093e-05</v>
+        <v>1.70558647652609e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.554595203685702e-05</v>
+        <v>4.554595203685697e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.877328530106216e-05</v>
+        <v>2.877328530106215e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>9.713981622913121e-05</v>
+        <v>9.713981622913119e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>4.353821743041946e-05</v>
+        <v>4.353821743041939e-05</v>
       </c>
       <c r="W7" t="n">
         <v>2.976234620994868e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.908143866966167e-05</v>
+        <v>7.908143866966172e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.921932962717793e-05</v>
+        <v>4.921932962717784e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.265120467733261e-05</v>
+        <v>4.265120467733269e-05</v>
       </c>
       <c r="AA7" t="n">
         <v>3.731374445448979e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.98571243882826e-05</v>
+        <v>5.985712438828263e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,34 +4554,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.828310094957099e-05</v>
+        <v>6.828310094957105e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.98500105979385e-05</v>
+        <v>2.985001059793849e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.315172244543825e-05</v>
+        <v>4.315172244543824e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.44531970348382e-05</v>
+        <v>3.445319703483819e-05</v>
       </c>
       <c r="F8" t="n">
         <v>3.38695695652818e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.123519842806716e-05</v>
+        <v>4.123519842806708e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.875707839697971e-05</v>
+        <v>2.875707839697969e-05</v>
       </c>
       <c r="I8" t="n">
         <v>4.922833190377588e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.123426067360308e-05</v>
+        <v>5.123426067360303e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.370294259349595e-05</v>
+        <v>6.370294259349594e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001185061128822337</v>
@@ -4590,49 +4590,49 @@
         <v>6.17824829053467e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001017596901612095</v>
+        <v>2.690975677466885e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.074971671091978e-05</v>
+        <v>3.074971671091975e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.72408192274767e-05</v>
+        <v>5.724081922747666e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.657276500236281e-05</v>
+        <v>3.657276500236284e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.287177658429285e-05</v>
+        <v>3.287177658429283e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.136186385588891e-05</v>
+        <v>6.136186385588888e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.458919712009403e-05</v>
+        <v>4.458919712009402e-05</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001089699852427954</v>
       </c>
       <c r="V8" t="n">
-        <v>5.714433884157996e-05</v>
+        <v>5.714433884157998e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.5579861368874e-05</v>
+        <v>4.557986136887399e-05</v>
       </c>
       <c r="X8" t="n">
         <v>8.588347746662516e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.317787402424729e-05</v>
+        <v>7.317787402424706e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.015726702384101e-05</v>
+        <v>5.015726702384109e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.31296562735217e-05</v>
+        <v>5.312965627352164e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.419506772829914e-05</v>
+        <v>8.419506772829915e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4642,76 +4642,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.476373238214797e-05</v>
+        <v>7.4763732382148e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.351551905358681e-05</v>
+        <v>3.351551905358679e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.681723090108667e-05</v>
+        <v>4.681723090108663e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.122957825572215e-05</v>
+        <v>4.122957825572209e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210492075029546e-05</v>
+        <v>3.210492075029547e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.320903014337618e-05</v>
+        <v>4.320903014337616e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.242258685262807e-05</v>
+        <v>3.242258685262806e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.289384035942419e-05</v>
+        <v>5.289384035942415e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.489976912925143e-05</v>
+        <v>5.489976912925135e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.736845104914432e-05</v>
+        <v>6.736845104914429e-05</v>
       </c>
       <c r="L9" t="n">
         <v>0.0001221716213378821</v>
       </c>
       <c r="M9" t="n">
-        <v>6.544799136099681e-05</v>
+        <v>6.54479913609967e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001017596901612095</v>
+        <v>3.689931628420826e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.077209673052742e-05</v>
+        <v>4.077209673052731e-05</v>
       </c>
       <c r="P9" t="n">
         <v>6.807430358038416e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.999987222354593e-05</v>
+        <v>4.99998722235459e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.653728503994109e-05</v>
+        <v>3.653728503994104e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>6.502737231153715e-05</v>
+        <v>6.502737231153723e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.825470557574233e-05</v>
+        <v>4.825470557574237e-05</v>
       </c>
       <c r="U9" t="n">
         <v>0.0001165993229719998</v>
       </c>
       <c r="V9" t="n">
-        <v>6.91855499364239e-05</v>
+        <v>6.918554993642383e-05</v>
       </c>
       <c r="W9" t="n">
         <v>4.924376648462888e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>9.856285894434195e-05</v>
+        <v>9.856285894434196e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.870074990185809e-05</v>
+        <v>6.87007499018582e-05</v>
       </c>
       <c r="Z9" t="n">
         <v>5.891116182092667e-05</v>
@@ -4720,7 +4720,7 @@
         <v>5.679516472916998e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.933854466296283e-05</v>
+        <v>7.933854466296281e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>1.71959905279557e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>4.811569073314567e-06</v>
       </c>
       <c r="O4" t="n">
         <v>5.442893733543648e-06</v>
@@ -5274,7 +5274,7 @@
         <v>2.002193776822266e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>5.537442718826799e-06</v>
       </c>
       <c r="O6" t="n">
         <v>8.266343532755279e-06</v>
@@ -5362,7 +5362,7 @@
         <v>2.011187021927408e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>7.727448764632921e-06</v>
       </c>
       <c r="O7" t="n">
         <v>8.357240835993722e-06</v>
@@ -5450,7 +5450,7 @@
         <v>3.379233409559376e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>1.624582879712439e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.829573891937227e-05</v>
@@ -5538,7 +5538,7 @@
         <v>3.569631217984748e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>2.331189072520629e-05</v>
       </c>
       <c r="O9" t="n">
         <v>2.531047361916605e-05</v>
@@ -5767,7 +5767,7 @@
         <v>4.177474793162838e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.241013431415563e-06</v>
+        <v>4.241013431415562e-06</v>
       </c>
       <c r="J2" t="n">
         <v>4.258809151087568e-06</v>
@@ -5800,7 +5800,7 @@
         <v>4.335964023802279e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.172823799834791e-06</v>
+        <v>4.172823799834792e-06</v>
       </c>
       <c r="U2" t="n">
         <v>5.906485871943276e-06</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.238516852111023e-06</v>
+        <v>4.238516852111024e-06</v>
       </c>
       <c r="C3" t="n">
         <v>4.326484120090834e-06</v>
@@ -5870,10 +5870,10 @@
         <v>4.778094696605708e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.136816402512736e-06</v>
+        <v>4.136816402512735e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.680439676822656e-06</v>
+        <v>6.680439676822657e-06</v>
       </c>
       <c r="P3" t="n">
         <v>4.078472845203952e-06</v>
@@ -5897,7 +5897,7 @@
         <v>4.622216170450162e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.431152348113277e-06</v>
+        <v>8.431152348113279e-06</v>
       </c>
       <c r="X3" t="n">
         <v>1.129773386759586e-05</v>
@@ -5958,7 +5958,7 @@
         <v>5.208929967403521e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>4.193638092562967e-06</v>
       </c>
       <c r="O4" t="n">
         <v>4.391623491991357e-06</v>
@@ -6025,7 +6025,7 @@
         <v>1.866248163170958e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.020685580958253e-05</v>
+        <v>3.020685580958252e-05</v>
       </c>
       <c r="H5" t="n">
         <v>1.476949365454585e-05</v>
@@ -6125,7 +6125,7 @@
         <v>7.293543151207105e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>8.196210178805489e-06</v>
+        <v>8.196210178805488e-06</v>
       </c>
       <c r="L6" t="n">
         <v>5.503802184851811e-06</v>
@@ -6134,7 +6134,7 @@
         <v>7.357834188874189e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>4.654966513482192e-06</v>
       </c>
       <c r="O6" t="n">
         <v>6.541503052186648e-06</v>
@@ -6192,7 +6192,7 @@
         <v>6.67509298071261e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>6.610294589383955e-06</v>
+        <v>6.610294589383954e-06</v>
       </c>
       <c r="E7" t="n">
         <v>6.812944487407739e-06</v>
@@ -6222,7 +6222,7 @@
         <v>7.619767590983065e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>6.604475716142512e-06</v>
       </c>
       <c r="O7" t="n">
         <v>6.801035732709447e-06</v>
@@ -6231,7 +6231,7 @@
         <v>6.511877020380939e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.642720807936138e-06</v>
+        <v>6.642720807936137e-06</v>
       </c>
       <c r="R7" t="n">
         <v>6.773220302385391e-06</v>
@@ -6310,7 +6310,7 @@
         <v>1.965936191854151e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>1.415957685414792e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.558993992032677e-05</v>
@@ -6398,7 +6398,7 @@
         <v>1.961938230958274e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>1.860409043474218e-05</v>
       </c>
       <c r="O9" t="n">
         <v>1.986824200460362e-05</v>
@@ -6818,7 +6818,7 @@
         <v>5.209714499661382e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>4.201644275531104e-06</v>
       </c>
       <c r="O4" t="n">
         <v>4.426327193641351e-06</v>
@@ -6994,7 +6994,7 @@
         <v>7.371814901923366e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>4.664468464671543e-06</v>
       </c>
       <c r="O6" t="n">
         <v>4.888216830331795e-06</v>
@@ -7082,7 +7082,7 @@
         <v>7.606906561743632e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>6.598836337613353e-06</v>
       </c>
       <c r="O7" t="n">
         <v>6.822093591484109e-06</v>
@@ -7170,7 +7170,7 @@
         <v>1.959471837572821e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>1.412096188245745e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.557285416225008e-05</v>
@@ -7258,7 +7258,7 @@
         <v>1.870319084852186e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>1.769512062439156e-05</v>
       </c>
       <c r="O9" t="n">
         <v>1.892034949515822e-05</v>
@@ -7678,7 +7678,7 @@
         <v>4.434756975431208e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.164163856150573e-05</v>
+        <v>6.743807769206146e-06</v>
       </c>
       <c r="O4" t="n">
         <v>9.516834129598395e-06</v>
@@ -7766,7 +7766,7 @@
         <v>0.0007290814803613015</v>
       </c>
       <c r="N5" t="n">
-        <v>3.164163856150574e-05</v>
+        <v>3.164163856150573e-05</v>
       </c>
       <c r="O5" t="n">
         <v>7.729098077171693e-05</v>
@@ -7854,7 +7854,7 @@
         <v>4.558496041007494e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.164163856150574e-05</v>
+        <v>8.030883112780499e-06</v>
       </c>
       <c r="O6" t="n">
         <v>1.381906238525804e-05</v>
@@ -7942,7 +7942,7 @@
         <v>4.807569702517636e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.164163856150574e-05</v>
+        <v>1.047193504007043e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.32434226329164e-05</v>
@@ -8030,7 +8030,7 @@
         <v>6.358380724029076e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.164163856150574e-05</v>
+        <v>1.996175337042856e-05</v>
       </c>
       <c r="O8" t="n">
         <v>2.438865859672333e-05</v>
@@ -8118,7 +8118,7 @@
         <v>6.818139819120698e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.164163856150574e-05</v>
+        <v>3.057763620610109e-05</v>
       </c>
       <c r="O9" t="n">
         <v>3.511541402846625e-05</v>
@@ -8538,7 +8538,7 @@
         <v>1.024367512358103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>4.588616398067766e-06</v>
       </c>
       <c r="O4" t="n">
         <v>5.145830895481372e-06</v>
@@ -8714,7 +8714,7 @@
         <v>1.073096928811801e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>5.092852108166613e-06</v>
       </c>
       <c r="O6" t="n">
         <v>7.86369317156664e-06</v>
@@ -8802,7 +8802,7 @@
         <v>1.297794277024387e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>7.322884044730609e-06</v>
       </c>
       <c r="O7" t="n">
         <v>7.878671846599363e-06</v>
@@ -8890,7 +8890,7 @@
         <v>2.582680360809342e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>1.531284555235314e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.720532777486738e-05</v>
@@ -8978,7 +8978,7 @@
         <v>2.66388603970349e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>2.098380167152159e-05</v>
       </c>
       <c r="O9" t="n">
         <v>2.27576066126684e-05</v>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -589,76 +589,76 @@
         <v>1.5450759852506e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.260455542811656e-06</v>
+        <v>8.260455542811661e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.697079323604556e-06</v>
+        <v>8.697079323604559e-06</v>
       </c>
       <c r="E2" t="n">
         <v>1.011165605299445e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.792883217704949e-06</v>
+        <v>8.792883217704966e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.223496239799205e-06</v>
+        <v>9.223496239799217e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.904851743746391e-06</v>
+        <v>8.904851743746396e-06</v>
       </c>
       <c r="I2" t="n">
         <v>8.795208261878586e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.026440671044148e-05</v>
+        <v>1.026440671044149e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.63922359686962e-06</v>
+        <v>8.639223596869628e-06</v>
       </c>
       <c r="L2" t="n">
         <v>1.885441541505283e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.201718680066612e-05</v>
+        <v>1.201718680066611e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>8.391274243411398e-06</v>
+        <v>8.391274243411403e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.242363790109857e-05</v>
+        <v>1.242363790109856e-05</v>
       </c>
       <c r="P2" t="n">
         <v>1.07260940391544e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.459591843707242e-06</v>
+        <v>9.459591843707229e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>8.692041368341379e-06</v>
+        <v>8.692041368341384e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.130450569764157e-05</v>
+        <v>1.130450569764156e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.126208465300962e-06</v>
+        <v>9.126208465300974e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72347381455998e-05</v>
+        <v>1.723473814559983e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>9.784576062413488e-06</v>
+        <v>9.784576062413491e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.214390480123658e-05</v>
+        <v>1.214390480123657e-05</v>
       </c>
       <c r="X2" t="n">
         <v>1.162965124587632e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.341346238472501e-06</v>
+        <v>9.3413462384725e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.40476747985717e-05</v>
+        <v>1.404767479857169e-05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.069705865463796e-05</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.870052261255723e-05</v>
+        <v>6.052227348168016e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.129589492961534e-06</v>
+        <v>8.17768340162749e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.071601060925326e-05</v>
+        <v>1.085112207652999e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.079236086481515e-05</v>
+        <v>2.128115288176138e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.140827756056043e-05</v>
+        <v>1.156846142115706e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.444413550964946e-05</v>
+        <v>1.470904588622341e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.221664930409212e-05</v>
+        <v>1.240574557688768e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.142148438048931e-05</v>
+        <v>1.158180023810431e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.187618118974901e-05</v>
+        <v>2.240401020308715e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.030028448245069e-05</v>
+        <v>1.042054461201138e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.318362165348561e-05</v>
+        <v>8.587320824232251e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.451307928553096e-05</v>
+        <v>3.549538819112192e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.524563290806748e-06</v>
+        <v>8.5818094952693e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.938414495318035e-05</v>
+        <v>1.963372244503006e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.513049571465069e-05</v>
+        <v>2.576970372348895e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.616343038387793e-05</v>
+        <v>1.649135442080141e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.068528267165708e-05</v>
+        <v>1.081961374379937e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.926297759771285e-05</v>
+        <v>3.005046083957884e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.378957904309158e-05</v>
+        <v>1.4033813157853e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>5.778980315094399e-05</v>
+        <v>5.943776920573677e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.842856402716719e-05</v>
+        <v>1.88342812776758e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.088664727596442e-05</v>
+        <v>2.122703107855816e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.169006004922145e-05</v>
+        <v>3.256902646058997e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.530628986896019e-05</v>
+        <v>1.560328133847666e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.444707593919706e-05</v>
+        <v>3.52632178910765e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.499054789723643e-05</v>
+        <v>2.562926041456431e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.121209925872973e-05</v>
+        <v>4.24252709368376e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.908926928848889e-05</v>
+        <v>8.908926928848879e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.934788464871529e-06</v>
+        <v>8.934788464871526e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.280334086800851e-05</v>
+        <v>1.280334086800847e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.878163576391287e-05</v>
+        <v>2.878163576391288e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.388548992384131e-05</v>
+        <v>1.38854899238413e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.874946210017277e-05</v>
+        <v>1.874946210017278e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.515022593354606e-05</v>
+        <v>1.515022593354605e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.391175236735554e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.049049256975803e-05</v>
+        <v>3.049049256975801e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.214983381958831e-05</v>
+        <v>1.21498338195883e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001275351246263707</v>
+        <v>0.0001275351246263709</v>
       </c>
       <c r="M4" t="n">
-        <v>5.032307024653583e-05</v>
+        <v>5.032307024653571e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>9.349131809939894e-06</v>
+        <v>9.34913180993989e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.807512892650743e-05</v>
+        <v>1.807512892650736e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.57219954730279e-05</v>
+        <v>3.572199547302781e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.141627055565754e-05</v>
+        <v>2.141627055565751e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.274643484573715e-05</v>
+        <v>1.274643484573714e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.225542123814921e-05</v>
+        <v>4.225542123814919e-05</v>
       </c>
       <c r="T4" t="n">
         <v>1.76505519326278e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>8.08685334518849e-05</v>
+        <v>8.086853345188488e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.498051097752018e-05</v>
+        <v>2.498051097752022e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.204635058003758e-05</v>
+        <v>2.204635058003754e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.592808977980285e-05</v>
+        <v>4.592808977980289e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.010248362070607e-05</v>
+        <v>2.010248362070603e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.361844020595081e-05</v>
+        <v>4.361844020595082e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.539402744797795e-05</v>
+        <v>3.539402744797793e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>6.07443623604209e-05</v>
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001539134706216903</v>
+        <v>0.001539134706216896</v>
       </c>
       <c r="C5" t="n">
-        <v>4.928484352082555e-05</v>
+        <v>4.928484352082549e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001317805406342758</v>
+        <v>0.0001317805406342744</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004419268903646057</v>
+        <v>0.0004419268903646055</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001586304820864977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000234322821443771</v>
+        <v>0.0002343228214437713</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001895953726777679</v>
+        <v>0.0001895953726777676</v>
       </c>
       <c r="I5" t="n">
         <v>0.000157146207765156</v>
@@ -877,58 +877,58 @@
         <v>0.0004728707262220475</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001169520217328693</v>
+        <v>0.0001169520217328691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002426895875653284</v>
+        <v>0.002426895875653287</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000941872907647426</v>
+        <v>0.0009418729076474238</v>
       </c>
       <c r="N5" t="n">
-        <v>5.692976481231345e-05</v>
+        <v>5.692976481231315e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002119011005815982</v>
+        <v>0.0002119011005815973</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000553673346476967</v>
+        <v>0.0005536733464769667</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0003083942466006407</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001337419550595696</v>
+        <v>0.0001337419550595694</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000687815452870663</v>
+        <v>0.0006878154528706629</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0002358430403797008</v>
+        <v>0.0002358430403797004</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001460527881021266</v>
+        <v>0.001460527881021265</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003499404145348518</v>
+        <v>0.0003499404145348522</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003128973440434376</v>
+        <v>0.000312897344043437</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000825074806498304</v>
+        <v>0.0008250748064983041</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002736425913577817</v>
+        <v>0.000273642591357781</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0007116724871154416</v>
+        <v>0.0007116724871154406</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005870561306643303</v>
+        <v>0.0005870561306643302</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001203725295114694</v>
+        <v>0.001203725295114695</v>
       </c>
     </row>
     <row r="6">
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.11777224453168e-05</v>
+        <v>9.117772244531673e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.496328570912386e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.883183811226085e-05</v>
+        <v>1.883183811226083e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.481013300816517e-05</v>
+        <v>3.481013300816521e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.597394308066919e-05</v>
+        <v>1.597394308066917e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.477795934442507e-05</v>
+        <v>2.477795934442513e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.117872317779841e-05</v>
+        <v>2.11787231777984e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.600020552418345e-05</v>
+        <v>1.600020552418341e-05</v>
       </c>
       <c r="J6" t="n">
         <v>3.257894572658589e-05</v>
@@ -968,55 +968,55 @@
         <v>1.817833106384063e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001335636218706229</v>
+        <v>0.0001335636218706232</v>
       </c>
       <c r="M6" t="n">
-        <v>5.635156749078816e-05</v>
+        <v>5.635156749078801e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.150986169158423e-05</v>
+        <v>1.150986169158378e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.023588429060391e-05</v>
+        <v>2.02358842906035e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.171847782338484e-05</v>
+        <v>4.17184778233848e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.744476779990984e-05</v>
+        <v>2.744476779990982e-05</v>
       </c>
       <c r="R6" t="n">
         <v>1.877493208998947e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.434387439497712e-05</v>
+        <v>4.434387439497706e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.973900508945569e-05</v>
+        <v>1.973900508945567e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.293513503687221e-05</v>
+        <v>8.293513503687227e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>3.100900822177249e-05</v>
+        <v>3.100900822177253e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.804282887659755e-05</v>
+        <v>2.804282887659753e-05</v>
       </c>
       <c r="X6" t="n">
         <v>5.195658702405525e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.236722566383489e-05</v>
+        <v>2.236722566383454e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.57068933627787e-05</v>
+        <v>4.570689336277868e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.142252469223027e-05</v>
+        <v>4.142252469223022e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.303838435258324e-05</v>
+        <v>6.303838435258325e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.393083885033212e-05</v>
+        <v>9.393083885033201e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.37763580267147e-05</v>
+        <v>1.377635802671468e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.764491042985169e-05</v>
+        <v>1.764491042985164e-05</v>
       </c>
       <c r="E7" t="n">
         <v>3.362320532575604e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.872705948568445e-05</v>
+        <v>1.872705948568444e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.359103166201593e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.999179549538923e-05</v>
+        <v>1.999179549538921e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.875332192919873e-05</v>
+        <v>1.87533219291987e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.533206213160119e-05</v>
+        <v>3.533206213160117e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.699140338143148e-05</v>
+        <v>1.699140338143145e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000132376694188214</v>
+        <v>0.0001323766941882141</v>
       </c>
       <c r="M7" t="n">
-        <v>5.516463980837903e-05</v>
+        <v>5.516463980837886e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.419070137178306e-05</v>
+        <v>1.419070137178305e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.291504185772133e-05</v>
+        <v>2.291504185772126e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.056190840424184e-05</v>
+        <v>4.056190840424175e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.625784011750066e-05</v>
+        <v>2.625784011750068e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.758800440758032e-05</v>
+        <v>1.758800440758029e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.709699079999242e-05</v>
+        <v>4.709699079999235e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2492121494471e-05</v>
+        <v>2.249212149447098e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>8.568499689496591e-05</v>
+        <v>8.568499689496609e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.982208053936332e-05</v>
+        <v>2.982208053936334e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.688792014188073e-05</v>
+        <v>2.68879201418807e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.076965934164609e-05</v>
+        <v>5.076965934164605e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.492220161070869e-05</v>
+        <v>2.492220161070863e-05</v>
       </c>
       <c r="Z7" t="n">
         <v>4.846000976779398e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.023559700982108e-05</v>
+        <v>4.023559700982105e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.558593192226411e-05</v>
+        <v>6.558593192226405e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001028250551821385</v>
+        <v>0.0001028250551821384</v>
       </c>
       <c r="C8" t="n">
-        <v>3.20144194995877e-05</v>
+        <v>3.201441949958775e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.588297190272467e-05</v>
+        <v>3.588297190272472e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.688594488720089e-05</v>
+        <v>4.688594488720093e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.90769376866677e-05</v>
+        <v>2.907693768666774e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.376660029437745e-05</v>
+        <v>4.376660029437754e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.822985696826227e-05</v>
+        <v>3.822985696826234e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.69913834020717e-05</v>
+        <v>3.699138340207177e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.357012360447421e-05</v>
+        <v>5.357012360447427e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.522946485430444e-05</v>
+        <v>3.522946485430452e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001506147556610867</v>
+        <v>0.0001506147556610871</v>
       </c>
       <c r="M8" t="n">
-        <v>7.340270128125214e-05</v>
+        <v>7.340270128125217e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.51857196691206e-05</v>
+        <v>2.518571966912063e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.590216794065465e-05</v>
+        <v>3.590216794065462e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.306112681304455e-05</v>
+        <v>5.306112681304451e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.33157776162434e-05</v>
+        <v>3.331577761624343e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.582606588045333e-05</v>
+        <v>3.582606588045338e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.53350522728654e-05</v>
+        <v>6.533505227286537e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.073018296734399e-05</v>
+        <v>4.073018296734403e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>9.936446846645291e-05</v>
+        <v>9.936446846645303e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>4.550496238780428e-05</v>
+        <v>4.550496238780437e-05</v>
       </c>
       <c r="W8" t="n">
         <v>4.512781794812541e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.868397881410253e-05</v>
+        <v>5.86839788141025e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.244851717812055e-05</v>
+        <v>5.244851717812062e-05</v>
       </c>
       <c r="Z8" t="n">
         <v>5.718065937898444e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.847365848269411e-05</v>
+        <v>5.847365848269413e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.358442096462719e-05</v>
+        <v>9.358442096462712e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1208,19 +1208,19 @@
         <v>4.269788256304753e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.65664349661845e-05</v>
+        <v>4.656643496618448e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>6.080807941682292e-05</v>
+        <v>6.080807941682294e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.030227548501668e-05</v>
+        <v>3.030227548501669e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.25125581279096e-05</v>
+        <v>5.251255812790959e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.891332003172208e-05</v>
+        <v>4.891332003172209e-05</v>
       </c>
       <c r="I9" t="n">
         <v>4.767484646553154e-05</v>
@@ -1229,40 +1229,40 @@
         <v>6.425358666793402e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.591292791776429e-05</v>
+        <v>4.591292791776428e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001612982187245469</v>
+        <v>0.000161298218724547</v>
       </c>
       <c r="M9" t="n">
-        <v>8.408616434471188e-05</v>
+        <v>8.408616434471174e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.31122259081159e-05</v>
+        <v>4.311222590811591e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>5.433187527696479e-05</v>
+        <v>5.433187527696475e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>7.252106798482253e-05</v>
+        <v>7.25210679848225e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.517936658339435e-05</v>
+        <v>5.517936658339434e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.650952894391317e-05</v>
+        <v>4.650952894391319e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>7.601851533632528e-05</v>
+        <v>7.601851533632527e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.141364603080384e-05</v>
+        <v>5.141364603080383e-05</v>
       </c>
       <c r="U9" t="n">
         <v>0.0001146097759782203</v>
       </c>
       <c r="V9" t="n">
-        <v>6.742684684371203e-05</v>
+        <v>6.742684684371209e-05</v>
       </c>
       <c r="W9" t="n">
         <v>5.58094446782136e-05</v>
@@ -1271,7 +1271,7 @@
         <v>7.969118387797901e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.384372614704154e-05</v>
+        <v>5.384372614704152e-05</v>
       </c>
       <c r="Z9" t="n">
         <v>7.284485747442173e-05</v>
@@ -1280,7 +1280,7 @@
         <v>6.915712154615396e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.450745645859684e-05</v>
+        <v>9.450745645859689e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.401866047558408e-06</v>
+        <v>4.401866047558478e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.479184186631666e-06</v>
+        <v>4.479184186631668e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4590784463747e-06</v>
+        <v>4.459078446374691e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.413237643069713e-06</v>
+        <v>4.413237643069767e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.484811388084536e-06</v>
+        <v>4.484811388084534e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.610618150289805e-06</v>
+        <v>4.610618150289855e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.399013038086913e-06</v>
+        <v>4.399013038086901e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.487862579982329e-06</v>
+        <v>4.487862579982323e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.583198558084343e-06</v>
+        <v>4.583198558084329e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.965337329781462e-06</v>
+        <v>4.965337329781396e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.759783327412081e-06</v>
+        <v>4.759783327412072e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.589574262298083e-06</v>
+        <v>4.589574262298089e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.412062186607558e-06</v>
+        <v>4.412062186607549e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.048625973995033e-06</v>
+        <v>6.048625973995039e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.442188686134294e-06</v>
+        <v>4.442188686134279e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.471873516134038e-06</v>
+        <v>4.471873516134023e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.418510438114024e-06</v>
+        <v>4.418510438114013e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.77242581285381e-06</v>
+        <v>4.772425812853855e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.433939091044571e-06</v>
+        <v>4.433939091044625e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.861202449010404e-06</v>
+        <v>6.861202449010443e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.523240934066826e-06</v>
+        <v>4.523240934066809e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.444106434108584e-06</v>
+        <v>6.444106434108625e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.422293111537044e-06</v>
+        <v>6.422293111537122e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.645729194441397e-06</v>
+        <v>5.645729194441394e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.192618228323531e-06</v>
+        <v>5.192618228323598e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.606733076987543e-06</v>
+        <v>4.60673307698753e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.610797978038759e-06</v>
+        <v>4.610797978038777e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.378943745152211e-06</v>
+        <v>4.393604542691851e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.464866620287292e-06</v>
+        <v>4.477664565013767e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.789793552687528e-06</v>
+        <v>4.81911196924865e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.45569651886084e-06</v>
+        <v>4.472231429415605e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.973530843629129e-06</v>
+        <v>5.00952830966367e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.861369487981711e-06</v>
+        <v>5.928257583590302e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.360699743132041e-06</v>
+        <v>4.374817415818423e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.995438566988343e-06</v>
+        <v>5.032123068909418e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.670080247654557e-06</v>
+        <v>5.730478047431597e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.386342759308511e-06</v>
+        <v>8.544005438712751e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.923081444998248e-06</v>
+        <v>7.027848471120961e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>5.745251048248333e-06</v>
+        <v>5.80886436733861e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.451323951150636e-06</v>
+        <v>4.468656909121846e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.26176630029803e-06</v>
+        <v>7.283927484669471e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.665476732085817e-06</v>
+        <v>4.690183071692091e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.87883855468794e-06</v>
+        <v>4.91133938302809e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.499244888348632e-06</v>
+        <v>4.518311431125613e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.009456499551382e-06</v>
+        <v>7.117079720020269e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.609060750254371e-06</v>
+        <v>4.632005828553611e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.229430001135117e-05</v>
+        <v>1.248689155286459e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.242149987809425e-06</v>
+        <v>5.287229258000561e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.334111483095437e-06</v>
+        <v>8.375695506284239e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.878053392007128e-05</v>
+        <v>1.930788708549817e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.326390840273539e-05</v>
+        <v>1.359264204277313e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.86430744334864e-06</v>
+        <v>5.88720059505693e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.841234095083981e-06</v>
+        <v>5.907641620917784e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.87358017653182e-06</v>
+        <v>5.941249249323561e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.469827098429037e-06</v>
+        <v>4.469827098429058e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.381547365752254e-06</v>
+        <v>4.381547365752263e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.116067462062754e-06</v>
+        <v>5.116067462062763e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.598274500921573e-06</v>
+        <v>4.598274500921584e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.406732876413419e-06</v>
+        <v>5.406732876413436e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>6.82777812949178e-06</v>
+        <v>6.827778129491784e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.437601043999284e-06</v>
+        <v>4.437601043999292e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.441197492516606e-06</v>
+        <v>5.441197492516614e-06</v>
       </c>
       <c r="J4" t="n">
         <v>6.50266278285582e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.083449444073395e-05</v>
+        <v>1.083449444073396e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.512667424459674e-06</v>
+        <v>8.512667424459689e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>6.631884310960313e-06</v>
+        <v>6.631884310960329e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.584997179444851e-06</v>
+        <v>4.584997179444874e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.809448122115711e-06</v>
+        <v>4.809448122115725e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.925289850473799e-06</v>
+        <v>4.925289850473818e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.260593661017415e-06</v>
+        <v>5.260593661017433e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.657833146552628e-06</v>
+        <v>4.657833146552638e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.655470113354386e-06</v>
+        <v>8.655470113354403e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.832106878933936e-06</v>
+        <v>4.832106878933946e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.245785848067782e-05</v>
+        <v>1.245785848067783e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.741375649705438e-06</v>
+        <v>5.741375649705455e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>5.673529329350794e-06</v>
+        <v>5.673529329350816e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.729148022843673e-05</v>
+        <v>2.729148022843675e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.851393344024364e-05</v>
+        <v>1.851393344024363e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.840913720819224e-06</v>
+        <v>4.840913720819241e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.783894439320717e-06</v>
+        <v>6.78389443932075e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.821333021907371e-06</v>
+        <v>6.82133302190739e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1713,82 +1713,82 @@
         <v>1.451205819276193e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.460304460634862e-05</v>
+        <v>1.460304460634866e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.724888174425884e-05</v>
+        <v>2.724888174425885e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.450011349217775e-05</v>
+        <v>1.450011349217778e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.243123882454707e-05</v>
+        <v>3.243123882454708e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.235635749681576e-05</v>
+        <v>5.235635749681646e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.503972276777812e-05</v>
+        <v>1.503972276777813e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.310880111508135e-05</v>
+        <v>3.310880111508132e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.914627604237795e-05</v>
+        <v>4.914627604237815e-05</v>
       </c>
       <c r="K5" t="n">
         <v>0.000119762495691541</v>
       </c>
       <c r="L5" t="n">
-        <v>8.066010983268886e-05</v>
+        <v>8.066010983268893e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.477790014077314e-05</v>
+        <v>5.477790014077312e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.634684747698624e-05</v>
+        <v>1.634684747698625e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.030376700390108e-05</v>
+        <v>2.030376700390112e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.191900942969315e-05</v>
+        <v>2.191900942969316e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86265978885583e-05</v>
+        <v>2.862659788855829e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.861941088190483e-05</v>
+        <v>1.861941088190485e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.118805785098443e-05</v>
+        <v>8.118805785098447e-05</v>
       </c>
       <c r="T5" t="n">
         <v>2.154667492740118e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001413690673127232</v>
+        <v>0.0001413690673127234</v>
       </c>
       <c r="V5" t="n">
-        <v>3.707894167193595e-05</v>
+        <v>3.707894167193592e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.550130358452603e-05</v>
+        <v>3.550130358452592e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000408667916713404</v>
+        <v>0.0004086679167134038</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002668710900339976</v>
+        <v>0.0002668710900339981</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.099261384835339e-05</v>
+        <v>2.099261384835342e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.551485861526e-05</v>
+        <v>5.551485861526022e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.029175054798787e-05</v>
+        <v>6.0291750547988e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.94758493099162e-06</v>
+        <v>4.947584930991637e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.648714888092974e-06</v>
+        <v>6.648714888092983e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.593825294625339e-06</v>
+        <v>5.593825294625335e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.865442023262291e-06</v>
+        <v>6.865442023262302e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.673900398754141e-06</v>
+        <v>7.673900398754151e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.305535962054382e-06</v>
+        <v>7.305535962054359e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.915358876561868e-06</v>
+        <v>4.915358876561862e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.918955325079191e-06</v>
+        <v>5.918955325079192e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.769830305196543e-06</v>
+        <v>8.769830305196546e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.131225227329651e-05</v>
+        <v>1.131225227329652e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.077983494680038e-05</v>
+        <v>1.07798349468004e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>7.109642143522895e-06</v>
+        <v>7.109642143522894e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>5.080277963255798e-06</v>
+        <v>5.080277963255791e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>7.089442414254805e-06</v>
+        <v>7.089442414254836e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>5.365354890351046e-06</v>
+        <v>5.365354890351054e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.738351493580014e-06</v>
+        <v>5.738351493580012e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>5.135590979115221e-06</v>
+        <v>5.135590979115219e-06</v>
       </c>
       <c r="S6" t="n">
         <v>1.092263763569511e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.309864711496533e-06</v>
+        <v>5.309864711496524e-06</v>
       </c>
       <c r="U6" t="n">
         <v>1.473092611056498e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>6.219133482268045e-06</v>
+        <v>6.219133482268035e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.204753920709988e-06</v>
+        <v>6.204753920709942e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.955864775077748e-05</v>
+        <v>2.955864775077747e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.905468528218868e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.318671553381821e-06</v>
+        <v>5.318671553381809e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.051061961661454e-06</v>
+        <v>9.051061961661461e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.311822592611961e-06</v>
+        <v>7.311822592611973e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1886,70 +1886,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.034764896024514e-06</v>
+        <v>7.034764896024517e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.946485163347728e-06</v>
+        <v>6.946485163347725e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.681005259658218e-06</v>
+        <v>7.681005259658228e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.163212298517041e-06</v>
+        <v>7.163212298517049e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.97167067400889e-06</v>
+        <v>7.971670674008904e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.392715927087248e-06</v>
+        <v>9.392715927087251e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.00253884159474e-06</v>
+        <v>7.002538841594754e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.006135290112061e-06</v>
+        <v>8.006135290112071e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>9.067600580451287e-06</v>
+        <v>9.067600580451293e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.33994322383294e-05</v>
+        <v>1.339943223832941e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.107760522205513e-05</v>
+        <v>1.107760522205514e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>9.19682210855578e-06</v>
+        <v>9.196822108555785e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>7.149934977040307e-06</v>
+        <v>7.149934977040326e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>7.372958248571013e-06</v>
+        <v>7.372958248571008e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>7.488799976929096e-06</v>
+        <v>7.488799976929103e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.82553145861288e-06</v>
+        <v>7.825531458612896e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.222770944148084e-06</v>
+        <v>7.222770944148095e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.122040791094985e-05</v>
+        <v>1.122040791094986e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>7.397044676529405e-06</v>
+        <v>7.397044676529409e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.503250459586861e-05</v>
+        <v>1.503250459586862e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.306313447300912e-06</v>
+        <v>8.306313447300919e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.238467126946258e-06</v>
+        <v>8.238467126946267e-06</v>
       </c>
       <c r="X7" t="n">
         <v>2.985641802603219e-05</v>
@@ -1958,13 +1958,13 @@
         <v>2.108477134538551e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.405851518414682e-06</v>
+        <v>7.405851518414698e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.348832236916186e-06</v>
+        <v>9.34883223691621e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.386270819502841e-06</v>
+        <v>9.38627081950285e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.341878432520252e-05</v>
+        <v>1.341878432520253e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.932956822222484e-05</v>
+        <v>1.932956822222487e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.006408831853534e-05</v>
+        <v>2.006408831853536e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.63519709358782e-05</v>
+        <v>1.635197093587823e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.529027410417638e-05</v>
+        <v>1.529027410417641e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.301974390985344e-05</v>
+        <v>2.301974390985347e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.938562190047185e-05</v>
+        <v>1.938562190047188e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.038921834898918e-05</v>
+        <v>2.038921834898922e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.145068363932843e-05</v>
+        <v>2.145068363932846e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.578251529720651e-05</v>
+        <v>2.578251529720657e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.346068828093223e-05</v>
+        <v>2.346068828093229e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.157990516743209e-05</v>
+        <v>2.157990516743213e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.488274010144952e-05</v>
+        <v>1.488274010144954e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.638512779824453e-05</v>
+        <v>1.638512779824455e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61877163488812e-05</v>
+        <v>1.618771634888122e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.303059796260912e-05</v>
+        <v>1.303059796260913e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.960585400302521e-05</v>
+        <v>1.960585400302525e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.360349096982695e-05</v>
+        <v>2.360349096982701e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.978012773540652e-05</v>
+        <v>1.978012773540653e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.448777423508799e-05</v>
+        <v>2.448777423508803e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.905423746291554e-05</v>
+        <v>1.905423746291558e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.062272917380337e-05</v>
+        <v>2.062272917380339e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.561131063205949e-05</v>
+        <v>3.561131063205953e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.943952833263075e-05</v>
+        <v>3.943952833263081e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.367843526075527e-05</v>
+        <v>1.36784352607553e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.173191529579328e-05</v>
+        <v>2.173191529579333e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.803587747319176e-05</v>
+        <v>2.803587747319181e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.544581393939291e-05</v>
+        <v>1.544581393939293e-05</v>
       </c>
       <c r="C9" t="n">
         <v>1.852923318494656e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.926375328125703e-05</v>
+        <v>1.926375328125704e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.801394523873252e-05</v>
+        <v>1.801394523873253e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.224278673267824e-05</v>
+        <v>1.224278673267825e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.097546408606475e-05</v>
+        <v>2.097546408606474e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.858528686319358e-05</v>
+        <v>1.858528686319361e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.958888331171089e-05</v>
+        <v>1.95888833117109e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.065034860205013e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.498218025992823e-05</v>
+        <v>2.498218025992825e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.266035324365398e-05</v>
+        <v>2.266035324365399e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.077957013015463e-05</v>
+        <v>2.077957013015466e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.873268299863915e-05</v>
+        <v>1.873268299863918e-05</v>
       </c>
       <c r="O9" t="n">
         <v>2.00082310126365e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.035266829032433e-05</v>
+        <v>2.035266829032435e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.940827961759041e-05</v>
+        <v>1.94082796175904e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.880551896574692e-05</v>
+        <v>1.880551896574694e-05</v>
       </c>
       <c r="S9" t="n">
         <v>2.280315593254868e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.897979269812822e-05</v>
+        <v>1.897979269812824e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.661144440741855e-05</v>
+        <v>2.661144440741859e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.354913386183999e-05</v>
+        <v>2.354913386184e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.982121514854511e-05</v>
+        <v>1.982121514854512e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1439166047631e-05</v>
+        <v>4.143916604763102e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.266751936698437e-05</v>
+        <v>3.266751936698438e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.707634714917018e-05</v>
+        <v>1.707634714917019e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.0931580258515e-05</v>
+        <v>2.093158025851503e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.096901884110167e-05</v>
+        <v>2.09690188411017e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.364490944465745e-05</v>
+        <v>1.364490944465747e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.506116183943391e-06</v>
+        <v>7.50611618394317e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.579792731974477e-06</v>
+        <v>8.579792731974436e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.119044746848664e-06</v>
+        <v>9.11904474684862e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.117685594423573e-06</v>
+        <v>8.117685594423535e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.530126040192682e-06</v>
+        <v>8.530126040192646e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.647132486103402e-06</v>
+        <v>7.647132486103365e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.904014330001942e-06</v>
+        <v>7.904014330001906e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.416062225129337e-06</v>
+        <v>9.416062225129295e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.04505652903338e-06</v>
+        <v>8.045056529033404e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.833606125008905e-05</v>
+        <v>1.833606125008913e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11359214031397e-05</v>
+        <v>1.113592140313973e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>7.873391584069865e-06</v>
+        <v>7.873391584069829e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.155013881611063e-05</v>
+        <v>1.155013881611067e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.073899501345032e-05</v>
+        <v>1.073899501345031e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.712399445613875e-06</v>
+        <v>8.712399445613893e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>7.669623994365992e-06</v>
+        <v>7.669623994365956e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.072453980538773e-05</v>
+        <v>1.072453980538774e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>8.725552650705776e-06</v>
+        <v>8.725552650705732e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.617126326617265e-05</v>
+        <v>1.617126326617269e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>8.46237624432364e-06</v>
+        <v>8.46237624432363e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.081411541635466e-05</v>
+        <v>1.081411541635467e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.127124018446691e-05</v>
+        <v>1.127124018446688e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.503997410502426e-06</v>
+        <v>8.503997410502385e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.238628228262276e-05</v>
+        <v>1.23862822826228e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.410688330332556e-06</v>
+        <v>9.410688330332519e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.215634477565373e-05</v>
+        <v>1.215634477565387e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.014093724670905e-05</v>
+        <v>5.16807862005381e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.960536291446442e-06</v>
+        <v>6.985061270697874e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.420207240743452e-05</v>
+        <v>1.447967533276557e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8017399568888e-05</v>
+        <v>1.842712610055522e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.089591158337432e-05</v>
+        <v>1.105691957318322e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.380374001524111e-05</v>
+        <v>1.406489681651327e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.528697465866859e-06</v>
+        <v>7.569691829527702e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>9.36636483292247e-06</v>
+        <v>9.472547315493767e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.013475602207728e-05</v>
+        <v>2.062034832797333e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.036294979984593e-05</v>
+        <v>1.050457162663686e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.379482128160311e-05</v>
+        <v>8.652467224381506e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.249945156897675e-05</v>
+        <v>3.342915302097959e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>9.14082631588029e-06</v>
+        <v>9.238662144238928e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.846041267450953e-05</v>
+        <v>1.870686913667596e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.951513952454229e-05</v>
+        <v>3.032683963995612e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5138336197225e-05</v>
+        <v>1.544883683952588e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>7.688227160719979e-06</v>
+        <v>7.734859548072761e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.942165348254083e-05</v>
+        <v>3.023381754054033e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.524514296079533e-05</v>
+        <v>1.555995545124007e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>5.580225021667888e-05</v>
+        <v>5.741278830536732e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.330890660088092e-05</v>
+        <v>1.355337898394678e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.716974433841963e-05</v>
+        <v>1.74131921803903e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.344064125760837e-05</v>
+        <v>3.440078945494311e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.363721874327406e-05</v>
+        <v>1.389408457534258e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.918293550795815e-05</v>
+        <v>2.985702227399176e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.011196539005801e-05</v>
+        <v>2.059732654646465e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.971134309484334e-05</v>
+        <v>4.088998843529246e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.553370883875115e-05</v>
+        <v>7.55337088387512e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.064614733230362e-06</v>
+        <v>7.064614733230357e-06</v>
       </c>
       <c r="D4" t="n">
         <v>1.832088550019088e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.441198507637776e-05</v>
+        <v>2.441198507637778e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.310117280176763e-05</v>
+        <v>1.310117280176762e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.775987736870862e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.78605897816701e-06</v>
+        <v>7.786058978167002e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.068765757648738e-05</v>
+        <v>1.068765757648739e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.774722903189747e-05</v>
+        <v>2.774722903189756e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.228079409716469e-05</v>
+        <v>1.228079409716467e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001285224265175506</v>
+        <v>0.0001285224265175511</v>
       </c>
       <c r="M4" t="n">
-        <v>4.717115620798103e-05</v>
+        <v>4.717115620798105e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.034175957402554e-05</v>
+        <v>1.034175957402552e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.711393082697151e-05</v>
+        <v>1.71139308269715e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.271006855158363e-05</v>
+        <v>4.27100685515836e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.981873933285011e-05</v>
+        <v>1.981873933285016e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.040110910597913e-06</v>
+        <v>8.04011091059791e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>4.254679032679249e-05</v>
+        <v>4.254679032679242e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.996731083513637e-05</v>
+        <v>1.996731083513639e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>7.827865340915602e-05</v>
+        <v>7.8278653409156e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.686645640734767e-05</v>
+        <v>1.686645640734768e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.688145643741807e-05</v>
+        <v>1.688145643741806e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.872202260309128e-05</v>
+        <v>4.872202260309146e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.739893305498109e-05</v>
+        <v>1.739893305498108e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.638780221200389e-05</v>
+        <v>3.638780221200388e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.770623351450499e-05</v>
+        <v>2.770623351450502e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.838830997643387e-05</v>
+        <v>5.838830997643386e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001214901475220816</v>
+        <v>0.001214901475220824</v>
       </c>
       <c r="C5" t="n">
-        <v>2.663176829515914e-05</v>
+        <v>2.66317682951591e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002505448779189134</v>
+        <v>0.000250544877918913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003471719393478254</v>
+        <v>0.0003471719393478278</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000147357813193323</v>
+        <v>0.0001473578131933229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002155452544172926</v>
+        <v>0.0002155452544172921</v>
       </c>
       <c r="H5" t="n">
-        <v>4.193646292885767e-05</v>
+        <v>4.193646292885765e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.918486077229393e-05</v>
+        <v>9.918486077229444e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004092124286815845</v>
+        <v>0.0004092124286815857</v>
       </c>
       <c r="K5" t="n">
         <v>0.0001237238325579212</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002312965666779955</v>
+        <v>0.00231296566677997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008329271147746611</v>
+        <v>0.0008329271147746615</v>
       </c>
       <c r="N5" t="n">
-        <v>8.876134756871438e-05</v>
+        <v>8.876134756871445e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0.0001951753354818429</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006575978462746063</v>
+        <v>0.0006575978462746061</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002732173522362754</v>
+        <v>0.0002732173522362763</v>
       </c>
       <c r="R5" t="n">
-        <v>4.618761497249733e-05</v>
+        <v>4.618761497249727e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006598949844180296</v>
+        <v>0.0006598949844180278</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0002832185126986505</v>
+        <v>0.0002832185126986503</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001337497563802536</v>
+        <v>0.001337497563802534</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001946631610080075</v>
+        <v>0.0001946631610080076</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002114625731581013</v>
+        <v>0.0002114625731581017</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0008418144374286504</v>
+        <v>0.0008418144374286541</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00022106570476243</v>
+        <v>0.0002210657047624298</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0005488809441202316</v>
+        <v>0.0005488809441202349</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004167398782941611</v>
+        <v>0.0004167398782941617</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001098946544373159</v>
+        <v>0.001098946544373156</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.708631644214064e-05</v>
+        <v>7.708631644214083e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.210063034903614e-05</v>
+        <v>1.210063034903613e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.987349310358045e-05</v>
+        <v>1.987349310358044e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.944800069218352e-05</v>
+        <v>2.944800069218363e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.465378040515723e-05</v>
+        <v>1.465378040515722e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.279589298451438e-05</v>
+        <v>2.279589298451433e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.282207459397278e-05</v>
+        <v>1.282207459397276e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.572367319229316e-05</v>
+        <v>1.572367319229311e-05</v>
       </c>
       <c r="J6" t="n">
         <v>3.278324464770327e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.383340170055427e-05</v>
+        <v>1.383340170055428e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001335584421333562</v>
+        <v>0.0001335584421333563</v>
       </c>
       <c r="M6" t="n">
-        <v>5.22071718237867e-05</v>
+        <v>5.220717182378665e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.19504593067281e-05</v>
+        <v>1.195045930672802e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.872142300303982e-05</v>
+        <v>1.87214230030393e-05</v>
       </c>
       <c r="P6" t="n">
         <v>4.772155503494909e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.13713469362397e-05</v>
+        <v>2.137134693623978e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.307612652640369e-05</v>
+        <v>1.307612652640372e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.409939793018198e-05</v>
+        <v>4.409939793018195e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.151991843852592e-05</v>
+        <v>2.151991843852595e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>7.989707043415806e-05</v>
+        <v>7.989707043415808e-05</v>
       </c>
       <c r="V6" t="n">
         <v>1.841906401073725e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.850620325923894e-05</v>
+        <v>1.850620325923897e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>5.375803821889702e-05</v>
+        <v>5.375803821889714e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.915571021462037e-05</v>
+        <v>1.915571021462003e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.794040981539348e-05</v>
+        <v>3.79404098153935e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>3.274224913031075e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.014457324433118e-05</v>
+        <v>6.014457324433123e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.976667016665171e-05</v>
+        <v>7.976667016665173e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.129757606113093e-05</v>
@@ -2755,76 +2755,76 @@
         <v>2.255384682809144e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.864494640427833e-05</v>
+        <v>2.864494640427842e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.733413412966819e-05</v>
+        <v>1.733413412966818e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.199283869660917e-05</v>
+        <v>2.199283869660918e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.201902030606757e-05</v>
+        <v>1.201902030606756e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.492061890438793e-05</v>
+        <v>1.492061890438794e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.198019035979806e-05</v>
+        <v>3.19801903597981e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.651375542506522e-05</v>
+        <v>1.651375542506523e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001327553878454511</v>
+        <v>0.000132755387845451</v>
       </c>
       <c r="M7" t="n">
         <v>5.140411753588151e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.45747209019261e-05</v>
+        <v>1.457472090192608e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.134534935223283e-05</v>
+        <v>2.134534935223281e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.694148707684492e-05</v>
+        <v>4.694148707684489e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.405170066075066e-05</v>
+        <v>2.405170066075068e-05</v>
       </c>
       <c r="R7" t="n">
         <v>1.227307223849847e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.677975165469299e-05</v>
+        <v>4.6779751654693e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.420027216303692e-05</v>
+        <v>2.42002721630369e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>8.257071680651965e-05</v>
+        <v>8.257071680651969e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.109941773524823e-05</v>
+        <v>2.109941773524824e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.111441776531858e-05</v>
+        <v>2.111441776531861e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>5.295498393099191e-05</v>
+        <v>5.295498393099202e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.169770380449416e-05</v>
+        <v>2.169770380449417e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.062076353990444e-05</v>
+        <v>4.062076353990447e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.193919484240554e-05</v>
+        <v>3.193919484240556e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.262127130433445e-05</v>
+        <v>6.262127130433448e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.793017408859732e-05</v>
+        <v>8.79301740885974e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.788931680751651e-05</v>
+        <v>2.788931680751654e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.914558757447705e-05</v>
+        <v>3.914558757447706e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.074889965910929e-05</v>
+        <v>4.074889965910937e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.681065884598075e-05</v>
+        <v>2.681065884598077e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.033222925339926e-05</v>
+        <v>4.033222925339931e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.861076105245315e-05</v>
+        <v>2.861076105245317e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.151235965077355e-05</v>
+        <v>3.151235965077356e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.857193110618362e-05</v>
+        <v>4.857193110618372e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.310549617145084e-05</v>
+        <v>3.310549617145087e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001493471285918364</v>
+        <v>0.0001493471285918368</v>
       </c>
       <c r="M8" t="n">
-        <v>6.799585828226701e-05</v>
+        <v>6.799585828226708e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.46331680960622e-05</v>
+        <v>2.463316809606222e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.320074514477713e-05</v>
+        <v>3.320074514477717e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.835678552576964e-05</v>
+        <v>5.835678552576963e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.055886368161626e-05</v>
+        <v>3.055886368161633e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.886481298488406e-05</v>
+        <v>2.88648129848841e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.33714924010785e-05</v>
+        <v>6.337149240107853e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.079201290942249e-05</v>
+        <v>4.079201290942251e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>9.505145260234877e-05</v>
+        <v>9.505145260234881e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.538317974599e-05</v>
+        <v>3.538317974599002e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.770781490168028e-05</v>
+        <v>3.770781490168035e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>6.023461160394027e-05</v>
+        <v>6.023461160394046e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.666260164594128e-05</v>
+        <v>4.666260164594131e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.862770863579423e-05</v>
+        <v>4.862770863579428e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.853093558879111e-05</v>
+        <v>4.853093558879118e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.801701017146601e-05</v>
+        <v>8.801701017146612e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.615880634240486e-05</v>
+        <v>9.615880634240499e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.363380128185881e-05</v>
+        <v>3.363380128185884e-05</v>
       </c>
       <c r="D9" t="n">
         <v>4.489007204881932e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.960930091786147e-05</v>
+        <v>4.960930091786156e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.596761045016239e-05</v>
+        <v>2.596761045016241e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.432906495599791e-05</v>
+        <v>4.432906495599793e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.435524552679547e-05</v>
+        <v>3.435524552679549e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.72568441251158e-05</v>
+        <v>3.725684412511584e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.4316415580526e-05</v>
+        <v>5.431641558052605e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.884998064579315e-05</v>
+        <v>3.884998064579317e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000155091613066179</v>
+        <v>0.0001550916130661791</v>
       </c>
       <c r="M9" t="n">
         <v>7.374034275660951e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.691094612265401e-05</v>
+        <v>3.691094612265406e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.565298208487886e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>7.167753136066266e-05</v>
+        <v>7.167753136066268e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.638792692013942e-05</v>
+        <v>4.63879269201395e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.460929745922637e-05</v>
+        <v>3.46092974592264e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>6.911597687542084e-05</v>
+        <v>6.911597687542096e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.65364973837648e-05</v>
+        <v>4.653649738376483e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001049136493793969</v>
+        <v>0.000104913649379397</v>
       </c>
       <c r="V9" t="n">
-        <v>5.02949836707131e-05</v>
+        <v>5.029498367071315e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.345064298604647e-05</v>
+        <v>4.345064298604651e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>7.529120915171977e-05</v>
+        <v>7.529120915171993e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.403392902522204e-05</v>
+        <v>4.403392902522206e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.937323204797552e-05</v>
+        <v>5.937323204797555e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.427542006313347e-05</v>
+        <v>5.427542006313353e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.495749652506232e-05</v>
+        <v>8.495749652506239e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.29179772859264e-05</v>
+        <v>1.291797728592627e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.896464213325474e-06</v>
+        <v>7.896464213325473e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.384184635885479e-06</v>
+        <v>9.384184635885366e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.187882020338787e-06</v>
+        <v>9.187882020338685e-06</v>
       </c>
       <c r="F2" t="n">
         <v>8.869504405484727e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.940046641095824e-06</v>
+        <v>8.940046641095675e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.952092288189573e-06</v>
+        <v>7.952092288189578e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.58139771284307e-06</v>
+        <v>9.581397712842902e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.913630836835551e-06</v>
+        <v>9.913630836835507e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.060571958614882e-05</v>
+        <v>1.060571958614863e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.763814986626281e-05</v>
+        <v>1.763814986626274e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.123569618636444e-05</v>
+        <v>1.123569618636445e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>8.424638994852236e-06</v>
+        <v>8.424638994852088e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.196699615783563e-05</v>
+        <v>1.196699615783569e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.117974153913583e-05</v>
+        <v>1.117974153913574e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.139770264663591e-06</v>
+        <v>9.139770264663459e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>8.045511010969676e-06</v>
+        <v>8.045511010969385e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.103694247548005e-05</v>
+        <v>1.103694247547974e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.324161432421351e-06</v>
+        <v>9.324161432421231e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.704252761280717e-05</v>
+        <v>1.704252761280714e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>9.430234323498186e-06</v>
+        <v>9.430234323498064e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.176154932148976e-05</v>
+        <v>1.176154932148973e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.313203912818569e-05</v>
+        <v>1.313203912818556e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.924944854843027e-06</v>
+        <v>9.924944854842912e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.297889350868903e-05</v>
+        <v>1.297889350868896e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.977238128771594e-06</v>
+        <v>9.977238128771443e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.236394655471016e-05</v>
+        <v>1.236394655471015e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.252928113933593e-05</v>
+        <v>4.378773171631678e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.334755611013689e-06</v>
+        <v>7.360667610031578e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.745723742929836e-05</v>
+        <v>1.783788376847955e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.60216129483546e-05</v>
+        <v>1.634835521695389e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.377483651455409e-05</v>
+        <v>1.402597175731636e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.423502870725786e-05</v>
+        <v>1.449903186130225e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.211771307818322e-06</v>
+        <v>7.228814711096668e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.887982165692926e-05</v>
+        <v>1.931134065036806e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.119004733486735e-05</v>
+        <v>2.170098657231958e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.608363564361059e-05</v>
+        <v>2.677351029903877e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.630669831159247e-05</v>
+        <v>7.876066834434621e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.074530083495681e-05</v>
+        <v>3.159998446803077e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.058747550340635e-05</v>
+        <v>1.072391314127284e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.860379978234942e-05</v>
+        <v>1.883926861748337e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.015643765153795e-05</v>
+        <v>3.097867192640467e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.569001067065574e-05</v>
+        <v>1.600779882310656e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>7.880784567618171e-06</v>
+        <v>7.921619048763837e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.915409514375109e-05</v>
+        <v>2.994465224019095e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.703343765205909e-05</v>
+        <v>1.739906880944555e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>5.846773836414389e-05</v>
+        <v>6.014987492512044e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.769841629840393e-05</v>
+        <v>1.808547072120191e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.032235107914813e-05</v>
+        <v>2.065264019793694e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.424205642041216e-05</v>
+        <v>4.557315477930175e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.128878927834945e-05</v>
+        <v>2.180373440660004e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.02466513290376e-05</v>
+        <v>3.094120751473547e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.166844614540813e-05</v>
+        <v>2.219617444757633e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.872742543965345e-05</v>
+        <v>3.985857200268819e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,40 +3342,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.337101846032994e-05</v>
+        <v>6.337101846032985e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.677161625596505e-06</v>
+        <v>7.677161625596498e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.345520485318385e-05</v>
+        <v>2.345520485318387e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.123787650691929e-05</v>
+        <v>2.123787650691925e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.764165488620542e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.843846188846229e-05</v>
+        <v>1.84384618884623e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.279062990932133e-06</v>
+        <v>7.279062990932128e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.568281727991702e-05</v>
+        <v>2.568281727991704e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.941934240589129e-05</v>
+        <v>2.941934240589122e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.725300405024738e-05</v>
+        <v>3.725300405024734e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001166875391418948</v>
+        <v>0.0001166875391418949</v>
       </c>
       <c r="M4" t="n">
-        <v>4.439797991536719e-05</v>
+        <v>4.439797991536715e-05</v>
       </c>
       <c r="N4" t="n">
         <v>1.261669542491004e-05</v>
@@ -3384,25 +3384,25 @@
         <v>1.716698340082856e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.373684607238141e-05</v>
+        <v>4.373684607238138e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>2.069443209406706e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.334270439465805e-06</v>
+        <v>8.334270439465825e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>4.212386495757207e-05</v>
+        <v>4.212386495757212e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.27772151580189e-05</v>
+        <v>2.277721515801887e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>8.213790601952486e-05</v>
+        <v>8.21379060195248e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.387091441876717e-05</v>
+        <v>2.387091441876714e-05</v>
       </c>
       <c r="W4" t="n">
         <v>2.132400762640706e-05</v>
@@ -3411,16 +3411,16 @@
         <v>6.578894544196106e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.95889586450312e-05</v>
+        <v>2.958895864503118e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.786161941513908e-05</v>
+        <v>3.786161941513919e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.015401687341731e-05</v>
+        <v>3.015401687341734e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.68268470831023e-05</v>
+        <v>5.682684708310239e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009461018276795289</v>
+        <v>0.0009461018276795287</v>
       </c>
       <c r="C5" t="n">
-        <v>2.687482862502742e-05</v>
+        <v>2.687482862502743e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000317242122873522</v>
+        <v>0.0003172421228735226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002600929211173588</v>
+        <v>0.0002600929211173585</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002097027830454976</v>
+        <v>0.0002097027830454973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002013713951886608</v>
+        <v>0.0002013713951886595</v>
       </c>
       <c r="H5" t="n">
-        <v>1.841709381549306e-05</v>
+        <v>1.841709381549291e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000364448006139605</v>
+        <v>0.0003644480061396056</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003992250233274888</v>
+        <v>0.0003992250233274889</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005137279059323074</v>
+        <v>0.0005137279059323076</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001935375202271074</v>
+        <v>0.001935375202271073</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007176664536588257</v>
+        <v>0.0007176664536588272</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001144360936757272</v>
+        <v>0.0001144360936757271</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001736035653988391</v>
+        <v>0.0001736035653988385</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006159569277379093</v>
+        <v>0.000615956927737909</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002565826427052108</v>
+        <v>0.0002565826427052105</v>
       </c>
       <c r="R5" t="n">
-        <v>3.826130516882004e-05</v>
+        <v>3.826130516881999e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005961460261983425</v>
+        <v>0.000596146026198342</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003076287951550497</v>
+        <v>0.0003076287951550499</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001291170883482113</v>
+        <v>0.00129117088348211</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002810031144467816</v>
+        <v>0.0002810031144467811</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002671063488199217</v>
+        <v>0.000267106348819922</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001084741137917362</v>
+        <v>0.001084741137917361</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0004108260630158605</v>
+        <v>0.0004108260630158611</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0004986040824008529</v>
+        <v>0.0004986040824008539</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004246090504142526</v>
+        <v>0.0004246090504142524</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009898433456973282</v>
+        <v>0.0009898433456973295</v>
       </c>
     </row>
     <row r="6">
@@ -3518,79 +3518,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.843363320671937e-05</v>
+        <v>6.843363320671929e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.437959102405937e-06</v>
+        <v>9.437959102405942e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.851781959957328e-05</v>
+        <v>2.851781959957325e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.630049125330869e-05</v>
+        <v>2.630049125330867e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.940245236301486e-05</v>
+        <v>1.940245236301485e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.019925936527174e-05</v>
+        <v>2.019925936527168e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.039860467741567e-06</v>
+        <v>9.039860467741558e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.744361475672648e-05</v>
+        <v>2.744361475672647e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.448195715228072e-05</v>
+        <v>3.448195715228068e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.231561879663679e-05</v>
+        <v>4.231561879663677e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001217501538882843</v>
+        <v>0.0001217501538882844</v>
       </c>
       <c r="M6" t="n">
-        <v>4.615877739217652e-05</v>
+        <v>4.615877739217655e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.446657443391948e-05</v>
+        <v>1.446657443391932e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.222485937652632e-05</v>
+        <v>2.222485937652629e-05</v>
       </c>
       <c r="P6" t="n">
         <v>4.879654524404243e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.575704684045647e-05</v>
+        <v>2.575704684045644e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.009506791627525e-05</v>
+        <v>1.009506791627526e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.718647970396145e-05</v>
+        <v>4.71864797039615e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.453801263482832e-05</v>
+        <v>2.453801263482834e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.387308513960378e-05</v>
+        <v>8.387308513960363e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.893352916515661e-05</v>
+        <v>2.893352916515659e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.638165512401221e-05</v>
+        <v>2.638165512401216e-05</v>
       </c>
       <c r="X6" t="n">
         <v>6.754974291877054e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.152117231394526e-05</v>
+        <v>3.152117231394492e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.292423416152851e-05</v>
+        <v>4.292423416152852e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>3.521663161980671e-05</v>
@@ -3606,46 +3606,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.742623306130166e-05</v>
+        <v>6.742623306130165e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.173237622656832e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.751041945415565e-05</v>
+        <v>2.751041945415567e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.529309110789107e-05</v>
+        <v>2.529309110789103e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.169686948717723e-05</v>
+        <v>2.169686948717724e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.249367648943408e-05</v>
+        <v>2.249367648943411e-05</v>
       </c>
       <c r="H7" t="n">
         <v>1.133427759190394e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.973803188088881e-05</v>
+        <v>2.97380318808888e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.347455700686306e-05</v>
+        <v>3.347455700686313e-05</v>
       </c>
       <c r="K7" t="n">
         <v>4.130821865121917e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001207427537428669</v>
+        <v>0.0001207427537428668</v>
       </c>
       <c r="M7" t="n">
         <v>4.845319451633896e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.667191002588186e-05</v>
+        <v>1.667191002588187e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.122074527968759e-05</v>
+        <v>2.12207452796876e-05</v>
       </c>
       <c r="P7" t="n">
         <v>4.77906079512404e-05</v>
@@ -3654,37 +3654,37 @@
         <v>2.474964669503884e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.238948504043763e-05</v>
+        <v>1.238948504043765e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.617907955854385e-05</v>
+        <v>4.617907955854388e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.683242975899067e-05</v>
+        <v>2.683242975899066e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>8.616901482362817e-05</v>
+        <v>8.616901482362797e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.792612901973899e-05</v>
+        <v>2.792612901973896e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.537922222737882e-05</v>
+        <v>2.537922222737885e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>6.984416004293296e-05</v>
+        <v>6.984416004293294e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.361855488927231e-05</v>
+        <v>3.36185548892723e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.19168340161109e-05</v>
+        <v>4.191683401611103e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.420923147438914e-05</v>
+        <v>3.420923147438917e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.088206168407421e-05</v>
+        <v>6.088206168407428e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.506588133437611e-05</v>
+        <v>7.506588133437602e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.734361436893579e-05</v>
+        <v>2.734361436893577e-05</v>
       </c>
       <c r="D8" t="n">
         <v>4.312165759652316e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.665969279214713e-05</v>
+        <v>3.665969279214711e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>3.057839829589998e-05</v>
+        <v>3.057839829589996e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.975787572124933e-05</v>
+        <v>3.975787572124922e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.694551573427143e-05</v>
+        <v>2.694551573427142e-05</v>
       </c>
       <c r="I8" t="n">
         <v>4.534927002325629e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.908579514923051e-05</v>
+        <v>4.908579514923047e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.691945679358663e-05</v>
+        <v>5.691945679358659e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001363539918852342</v>
+        <v>0.0001363539918852341</v>
       </c>
       <c r="M8" t="n">
-        <v>6.406443265870583e-05</v>
+        <v>6.406443265870587e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.610383240150503e-05</v>
+        <v>2.610383240150502e-05</v>
       </c>
       <c r="O8" t="n">
         <v>3.235225000400225e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.850586007154917e-05</v>
+        <v>5.850586007154922e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.082269561626954e-05</v>
+        <v>3.082269561626953e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.800072318280509e-05</v>
+        <v>2.800072318280508e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.179031770091134e-05</v>
+        <v>6.179031770091133e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.244366790135816e-05</v>
+        <v>4.244366790135815e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>9.789021180703698e-05</v>
+        <v>9.789021180703696e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>4.136114610316574e-05</v>
+        <v>4.136114610316566e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.099202701513338e-05</v>
+        <v>4.099202701513334e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>7.664782101520599e-05</v>
+        <v>7.664782101520591e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.715969463830545e-05</v>
+        <v>5.715969463830548e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.94084059147869e-05</v>
+        <v>4.940840591478696e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>4.982046961675663e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.482029201800361e-05</v>
+        <v>8.482029201800364e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.185952973937364e-05</v>
+        <v>8.185952973937359e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.15141521419705e-05</v>
+        <v>3.151415214197047e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.729219536955793e-05</v>
+        <v>4.729219536955789e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.384046103611109e-05</v>
+        <v>4.38404610361111e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.91489389776883e-05</v>
+        <v>2.914893897768828e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.227545397106334e-05</v>
+        <v>4.227545397106319e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.111605350730608e-05</v>
+        <v>3.111605350730605e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.951980779629102e-05</v>
+        <v>4.951980779629101e-05</v>
       </c>
       <c r="J9" t="n">
         <v>5.325633292226528e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.108999456662143e-05</v>
+        <v>6.108999456662137e-05</v>
       </c>
       <c r="L9" t="n">
         <v>0.0001405245296582691</v>
       </c>
       <c r="M9" t="n">
-        <v>6.823497043174115e-05</v>
+        <v>6.823497043174119e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.645368594128405e-05</v>
+        <v>3.645368594128399e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.277645501851215e-05</v>
+        <v>4.277645501851211e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>6.973180157830026e-05</v>
+        <v>6.973180157830025e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.453142417666815e-05</v>
+        <v>4.453142417666813e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.217126095583982e-05</v>
+        <v>3.217126095583984e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>6.596085547394609e-05</v>
+        <v>6.596085547394608e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.661420567439291e-05</v>
+        <v>4.661420567439292e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001059492781791685</v>
+        <v>0.0001059492781791682</v>
       </c>
       <c r="V9" t="n">
-        <v>5.387992782204283e-05</v>
+        <v>5.38799278220428e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.51609981427811e-05</v>
+        <v>4.516099814278109e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>8.962593595833508e-05</v>
+        <v>8.962593595833507e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.34003308046745e-05</v>
+        <v>5.340033080467448e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.847395317866591e-05</v>
+        <v>5.8473953178666e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.399100738979135e-05</v>
+        <v>5.399100738979136e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.066383759947654e-05</v>
+        <v>8.066383759947651e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.283226936504506e-05</v>
+        <v>1.283226936504507e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.59455033354302e-06</v>
+        <v>8.594550333543003e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.885095614696954e-06</v>
+        <v>9.885095614696913e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.499589511773137e-06</v>
+        <v>9.499589511773115e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.673079757193275e-06</v>
+        <v>9.673079757193248e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.565657393399119e-06</v>
+        <v>9.565657393399094e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.610721306833876e-06</v>
+        <v>8.610721306833844e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.042306480285846e-05</v>
+        <v>1.042306480285844e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.060132320072687e-05</v>
+        <v>1.060132320072685e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.17045186489697e-05</v>
+        <v>1.170451864896968e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655630602004339e-05</v>
+        <v>1.655630602004337e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.152871978751993e-05</v>
+        <v>1.152871978751992e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.007051285654782e-06</v>
+        <v>9.007051285654763e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.228915147167438e-05</v>
+        <v>1.228915147167435e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.157615077807973e-05</v>
+        <v>1.157615077807969e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01668584127915e-05</v>
+        <v>1.016685841279148e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>8.975000245366135e-06</v>
+        <v>8.975000245366124e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14972602696831e-05</v>
+        <v>1.149726026968306e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.001235689239289e-05</v>
+        <v>1.001235689239286e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.889057440498693e-05</v>
+        <v>1.889057440498691e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.132358983599319e-05</v>
+        <v>1.132358983599316e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.301448007201735e-05</v>
+        <v>1.301448007201731e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.446619527235921e-05</v>
+        <v>1.446619527235919e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.182246859080765e-05</v>
+        <v>1.182246859080764e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.3701103106792e-05</v>
+        <v>1.370110310679198e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.076845351318066e-05</v>
+        <v>1.076845351318063e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.278725210282569e-05</v>
+        <v>1.278725210282567e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.790657345346311e-05</v>
+        <v>3.898252773598521e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.455741757988817e-06</v>
+        <v>8.500890651253209e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.702958912347062e-05</v>
+        <v>1.737382099121301e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.424769870704373e-05</v>
+        <v>1.449075271866439e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55281757227052e-05</v>
+        <v>1.581994415206995e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.471030783118629e-05</v>
+        <v>1.496965991640515e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.931688457728288e-06</v>
+        <v>7.95238054489174e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.089795108081439e-05</v>
+        <v>2.137967734942629e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.209702642984468e-05</v>
+        <v>2.261920429965125e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.99346480361466e-05</v>
+        <v>3.073977425038483e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>6.449183729966475e-05</v>
+        <v>6.651151350854848e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88178227071949e-05</v>
+        <v>2.958377078368604e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.076306822246214e-05</v>
+        <v>1.088386152905131e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.717404153862064e-05</v>
+        <v>1.733994779012346e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.897631391392814e-05</v>
+        <v>2.973672003537709e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.902548345849504e-05</v>
+        <v>1.944023052695619e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.054270875277553e-05</v>
+        <v>1.065624067997395e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.844920401343725e-05</v>
+        <v>2.919363797398533e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.796578050131757e-05</v>
+        <v>1.834256188495393e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.557853363720597e-05</v>
+        <v>6.747220650054527e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.716697067963727e-05</v>
+        <v>2.786686777386482e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.337308374468359e-05</v>
+        <v>2.3768939146886e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.971962443236553e-05</v>
+        <v>5.12257347941408e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.087326826589031e-05</v>
+        <v>3.170457793489491e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.060318621684733e-05</v>
+        <v>3.128201762070007e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.333952478448378e-05</v>
+        <v>2.390431942527638e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.774728478321172e-05</v>
+        <v>3.882288712715061e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.63473963251069e-05</v>
+        <v>5.634739632510694e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.756001200517366e-06</v>
+        <v>9.756001200517339e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.30577130480171e-05</v>
+        <v>2.305771304801705e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.870324427392369e-05</v>
+        <v>1.870324427392367e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.066289640540029e-05</v>
+        <v>2.066289640540026e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.944951138961628e-05</v>
+        <v>1.944951138961626e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.663068999558589e-06</v>
+        <v>8.663068999558576e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.913432250635477e-05</v>
+        <v>2.913432250635473e-05</v>
       </c>
       <c r="J4" t="n">
         <v>3.11402512761819e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.360893319607491e-05</v>
+        <v>4.360893319607487e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>9.841210348481268e-05</v>
+        <v>9.841210348481266e-05</v>
       </c>
       <c r="M4" t="n">
         <v>4.168847350792728e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.313979843113876e-05</v>
+        <v>1.313979843113877e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.524185422735397e-05</v>
+        <v>1.524185422735395e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.21589590422344e-05</v>
+        <v>4.215895904223435e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6240353469786e-05</v>
+        <v>2.624035346978599e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.277776718687164e-05</v>
+        <v>1.277776718687165e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.126785445846769e-05</v>
+        <v>4.126785445846767e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.449518772267287e-05</v>
+        <v>2.449518772267288e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>9.307893224619377e-05</v>
+        <v>9.307893224619375e-05</v>
       </c>
       <c r="V4" t="n">
         <v>3.926011985203007e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.548424863155933e-05</v>
+        <v>2.548424863155934e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>7.480334109127253e-05</v>
+        <v>7.480334109127256e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.518035917605202e-05</v>
+        <v>4.518035917605196e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.837310709894348e-05</v>
+        <v>3.837310709894351e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.303564687610052e-05</v>
+        <v>3.303564687610049e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.557902680989337e-05</v>
+        <v>5.557902680989329e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,67 +4290,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007844577704594457</v>
+        <v>0.0007844577704594478</v>
       </c>
       <c r="C5" t="n">
-        <v>4.166853951805554e-05</v>
+        <v>4.166853951805552e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002771094696214759</v>
+        <v>0.0002771094696214758</v>
       </c>
       <c r="E5" t="n">
         <v>0.0001842803226935629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002408445764852524</v>
+        <v>0.0002408445764852528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001928563919528349</v>
+        <v>0.0001928563919528348</v>
       </c>
       <c r="H5" t="n">
-        <v>2.115469735171191e-05</v>
+        <v>2.115469735171197e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003995346209102988</v>
+        <v>0.0003995346209102984</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003972240498795275</v>
+        <v>0.0003972240498795276</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005990021147510442</v>
+        <v>0.0005990021147510426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001531876627220593</v>
+        <v>0.001531876627220595</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006181006713594519</v>
+        <v>0.0006181006713594521</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001017596901612093</v>
+        <v>0.0001017596901612094</v>
       </c>
       <c r="O5" t="n">
         <v>0.0001245663420029698</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005515053491208955</v>
+        <v>0.0005515053491208974</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003255948382965407</v>
+        <v>0.0003255948382965409</v>
       </c>
       <c r="R5" t="n">
-        <v>9.970468392374535e-05</v>
+        <v>9.970468392374536e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005543674040765469</v>
+        <v>0.000554367404076547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003170030852201919</v>
+        <v>0.0003170030852201916</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001401778997993863</v>
+        <v>0.001401778997993861</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0004974773813827835</v>
+        <v>0.0004974773813827836</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003196482317821587</v>
@@ -4359,16 +4359,16 @@
         <v>0.001189465366430303</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006727330769835898</v>
+        <v>0.00067273307698359</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0004628285528396379</v>
+        <v>0.0004628285528396381</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004563666446057867</v>
+        <v>0.0004563666446057878</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000927993170472486</v>
+        <v>0.0009279931704724867</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.866328113393758e-05</v>
+        <v>5.866328113393755e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2071886009348e-05</v>
+        <v>1.207188600934796e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.875175875023407e-05</v>
+        <v>2.875175875023401e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.439728997614062e-05</v>
+        <v>2.43972899761406e-05</v>
       </c>
       <c r="F6" t="n">
         <v>2.297878121423089e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.176539619844693e-05</v>
+        <v>2.176539619844688e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.435711470177552e-05</v>
+        <v>1.435711470177551e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.145020731518542e-05</v>
+        <v>3.145020731518536e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.683429697839878e-05</v>
+        <v>3.683429697839875e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.93029788982918e-05</v>
+        <v>4.930297889829176e-05</v>
       </c>
       <c r="L6" t="n">
         <v>0.0001007279882936432</v>
       </c>
       <c r="M6" t="n">
-        <v>4.400435831675793e-05</v>
+        <v>4.400435831675788e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.560879076430086e-05</v>
+        <v>1.560879076430134e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.770975492356155e-05</v>
+        <v>1.770975492356192e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.788563149997653e-05</v>
+        <v>4.78856314999765e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.193439917200297e-05</v>
+        <v>3.193439917200295e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.847181288908863e-05</v>
+        <v>1.847181288908855e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.35837392672983e-05</v>
+        <v>4.358373926729828e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.01892334248898e-05</v>
+        <v>3.018923342488982e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>9.853385082114741e-05</v>
+        <v>9.853385082114738e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.157600466086075e-05</v>
+        <v>4.157600466086077e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79950416682876e-05</v>
+        <v>2.799504166828754e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>7.711922590010304e-05</v>
+        <v>7.711922590010313e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.758397088258987e-05</v>
+        <v>4.758397088259029e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>4.068899190777404e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.872969257831746e-05</v>
+        <v>3.872969257831748e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.809869017332131e-05</v>
+        <v>5.809869017332115e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.062549390349619e-05</v>
+        <v>6.062549390349618e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.403409877890664e-05</v>
+        <v>1.403409877890661e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.733581062640641e-05</v>
+        <v>2.733581062640636e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.298134185231297e-05</v>
+        <v>2.298134185231296e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.494099398378958e-05</v>
+        <v>2.494099398378953e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.372760896800557e-05</v>
+        <v>2.372760896800555e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.294116657794786e-05</v>
+        <v>1.294116657794785e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.341242008474404e-05</v>
+        <v>3.341242008474403e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.541834885457117e-05</v>
+        <v>3.541834885457118e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.788703077446414e-05</v>
+        <v>4.78870307744641e-05</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001026902010632019</v>
       </c>
       <c r="M7" t="n">
-        <v>4.596657108631652e-05</v>
+        <v>4.596657108631656e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.741789600952805e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.951847053343914e-05</v>
+        <v>1.951847053343908e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.643557534831952e-05</v>
+        <v>4.643557534831948e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.051845104817533e-05</v>
+        <v>3.051845104817531e-05</v>
       </c>
       <c r="R7" t="n">
         <v>1.70558647652609e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.554595203685697e-05</v>
+        <v>4.554595203685698e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.877328530106215e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>9.713981622913119e-05</v>
+        <v>9.713981622913115e-05</v>
       </c>
       <c r="V7" t="n">
         <v>4.353821743041939e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.976234620994868e-05</v>
+        <v>2.976234620994865e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.908143866966172e-05</v>
+        <v>7.908143866966179e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.921932962717784e-05</v>
+        <v>4.92193296271779e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.265120467733269e-05</v>
+        <v>4.265120467733265e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.731374445448979e-05</v>
+        <v>3.731374445448981e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.985712438828263e-05</v>
+        <v>5.985712438828265e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4557,58 +4557,58 @@
         <v>6.828310094957105e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.985001059793849e-05</v>
+        <v>2.985001059793844e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.315172244543824e-05</v>
+        <v>4.315172244543813e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.445319703483819e-05</v>
+        <v>3.445319703483818e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>3.38695695652818e-05</v>
+        <v>3.386956956528177e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.123519842806708e-05</v>
+        <v>4.123519842806705e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.875707839697969e-05</v>
+        <v>2.875707839697968e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.922833190377588e-05</v>
+        <v>4.922833190377584e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.123426067360303e-05</v>
+        <v>5.123426067360298e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.370294259349594e-05</v>
+        <v>6.370294259349593e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001185061128822337</v>
       </c>
       <c r="M8" t="n">
-        <v>6.17824829053467e-05</v>
+        <v>6.178248290534665e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.690975677466885e-05</v>
+        <v>2.690975677466883e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.074971671091975e-05</v>
+        <v>3.074971671091972e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.724081922747666e-05</v>
+        <v>5.724081922747672e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.657276500236284e-05</v>
+        <v>3.657276500236278e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.287177658429283e-05</v>
+        <v>3.287177658429279e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.136186385588888e-05</v>
+        <v>6.136186385588881e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>4.458919712009402e-05</v>
+        <v>4.458919712009399e-05</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001089699852427954</v>
@@ -4617,22 +4617,22 @@
         <v>5.714433884157998e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.557986136887399e-05</v>
+        <v>4.557986136887397e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>8.588347746662516e-05</v>
+        <v>8.58834774666252e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.317787402424706e-05</v>
+        <v>7.317787402424711e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.015726702384109e-05</v>
+        <v>5.015726702384103e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.312965627352164e-05</v>
+        <v>5.31296562735216e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.419506772829915e-05</v>
+        <v>8.419506772829909e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4642,31 +4642,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.4763732382148e-05</v>
+        <v>7.476373238214812e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.351551905358679e-05</v>
+        <v>3.351551905358677e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.681723090108663e-05</v>
+        <v>4.681723090108652e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.122957825572209e-05</v>
+        <v>4.122957825572203e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210492075029547e-05</v>
+        <v>3.210492075029546e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.320903014337616e-05</v>
+        <v>4.320903014337612e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.242258685262806e-05</v>
+        <v>3.242258685262805e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.289384035942415e-05</v>
+        <v>5.289384035942413e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.489976912925135e-05</v>
+        <v>5.489976912925131e-05</v>
       </c>
       <c r="K9" t="n">
         <v>6.736845104914429e-05</v>
@@ -4675,52 +4675,52 @@
         <v>0.0001221716213378821</v>
       </c>
       <c r="M9" t="n">
-        <v>6.54479913609967e-05</v>
+        <v>6.544799136099668e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.689931628420826e-05</v>
+        <v>3.689931628420822e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.077209673052731e-05</v>
+        <v>4.077209673052726e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>6.807430358038416e-05</v>
+        <v>6.807430358038411e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.99998722235459e-05</v>
+        <v>4.999987222354585e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.653728503994104e-05</v>
+        <v>3.653728503994107e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>6.502737231153723e-05</v>
+        <v>6.50273723115371e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.825470557574237e-05</v>
+        <v>4.82547055757423e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001165993229719998</v>
+        <v>0.0001165993229719997</v>
       </c>
       <c r="V9" t="n">
-        <v>6.918554993642383e-05</v>
+        <v>6.918554993642379e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.924376648462888e-05</v>
+        <v>4.924376648462883e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>9.856285894434196e-05</v>
+        <v>9.8562858944342e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.87007499018582e-05</v>
+        <v>6.870074990185803e-05</v>
       </c>
       <c r="Z9" t="n">
         <v>5.891116182092667e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.679516472916998e-05</v>
+        <v>5.679516472916996e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.933854466296281e-05</v>
+        <v>7.933854466296275e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.342672266325755e-06</v>
+        <v>5.342672266325753e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.841014118087615e-06</v>
+        <v>4.841014118087604e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.863891067061937e-06</v>
+        <v>4.863891067061922e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.945024120429982e-06</v>
+        <v>4.94502412042998e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.827436686471111e-06</v>
+        <v>4.827436686471099e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.152182329091496e-06</v>
+        <v>5.152182329091489e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.852039683424231e-06</v>
+        <v>4.852039683424229e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.882291965204022e-06</v>
+        <v>4.882291965204017e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.254679676638074e-06</v>
+        <v>5.254679676638068e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.071607938049509e-06</v>
+        <v>5.071607938049501e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.107503568323868e-06</v>
+        <v>7.107503568323871e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.912010485993234e-06</v>
+        <v>5.912010485993233e-06</v>
       </c>
       <c r="N2" t="n">
         <v>4.813406691149939e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.577029134085764e-06</v>
+        <v>6.577029134085747e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.404754790967134e-06</v>
+        <v>5.404754790967135e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.923636698486229e-06</v>
+        <v>4.923636698486228e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.801308307174994e-06</v>
+        <v>4.80130830717499e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.154484590237606e-06</v>
+        <v>5.154484590237609e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.885859814915883e-06</v>
+        <v>4.885859814915878e-06</v>
       </c>
       <c r="U2" t="n">
         <v>9.317624131368299e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.973679109775076e-06</v>
+        <v>4.973679109775067e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.415306205538905e-06</v>
+        <v>7.415306205538916e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.348665749947383e-06</v>
+        <v>5.348665749947384e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.90711411188963e-06</v>
+        <v>4.907114111889643e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.202279233356805e-06</v>
+        <v>6.202279233356798e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.667787666901505e-06</v>
+        <v>5.667787666901502e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.277114641206161e-06</v>
+        <v>6.27711464120615e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.514745343227333e-06</v>
+        <v>8.663507411657477e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.659500324625521e-06</v>
+        <v>4.66938624702788e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.118075891972374e-06</v>
+        <v>5.147492173470186e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.688251701647066e-06</v>
+        <v>5.736816941048923e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.858452518417886e-06</v>
+        <v>4.878681648937558e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.158587167940689e-06</v>
+        <v>7.259774632162229e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.035130239501127e-06</v>
+        <v>5.061676458425437e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.250205717936624e-06</v>
+        <v>5.284347582160908e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.893338116315135e-06</v>
+        <v>8.020902698441556e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.597736385528013e-06</v>
+        <v>6.679792048176149e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.102401010971838e-05</v>
+        <v>2.161771636075002e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.257070027240775e-05</v>
+        <v>1.286681808914827e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.756448653480906e-06</v>
+        <v>4.772999922278471e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.972363793266971e-06</v>
+        <v>8.002743011058549e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>8.959295385579452e-06</v>
+        <v>9.123267037404705e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.542965497566467e-06</v>
+        <v>5.587454783571875e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.670051766823387e-06</v>
+        <v>4.683606083295751e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.170014722167678e-06</v>
+        <v>7.272021560523517e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.276167770805326e-06</v>
+        <v>5.311181269369878e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.667298332954234e-05</v>
+        <v>2.735538354121068e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.895385131818823e-06</v>
+        <v>5.951977509514758e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.233090262936221e-05</v>
+        <v>1.249807369341866e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>8.58201095494473e-06</v>
+        <v>8.734389260363236e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.425109664219396e-06</v>
+        <v>5.465297488609161e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.449722033255171e-06</v>
+        <v>9.576565387993738e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.085416153110208e-05</v>
+        <v>1.108618762473678e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.515245082580957e-05</v>
+        <v>1.553725864505996e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.078986721911899e-05</v>
+        <v>1.078986721911898e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.513286485309024e-06</v>
+        <v>4.513286485309034e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.381813323200859e-06</v>
+        <v>5.38181332320086e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>6.29824848404141e-06</v>
+        <v>6.298248484041418e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.970044324583869e-06</v>
+        <v>4.970044324583871e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>8.638195748357423e-06</v>
+        <v>8.63819574835744e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.247946493107135e-06</v>
+        <v>5.247946493107132e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.589659932547066e-06</v>
+        <v>5.589659932547078e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.779448151907557e-06</v>
+        <v>9.779448151907563e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.728070935487044e-06</v>
+        <v>7.72807093548704e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.072444863769686e-05</v>
+        <v>3.072444863769696e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.71959905279557e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.811569073314567e-06</v>
+        <v>4.811569073314564e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>5.442893733543648e-06</v>
+        <v>5.442893733543637e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.149111789431565e-05</v>
+        <v>1.149111789431564e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.056667714486609e-06</v>
+        <v>6.05666771448659e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.674912260785939e-06</v>
+        <v>4.674912260785948e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.664200847095286e-06</v>
+        <v>8.6642008470953e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>5.629960436334517e-06</v>
+        <v>5.629960436334533e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.47119849077786e-05</v>
+        <v>3.471198490777856e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.515041962435033e-06</v>
+        <v>6.515041962435064e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.156372591172359e-05</v>
+        <v>1.156372591172357e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.085756637376393e-05</v>
+        <v>1.085756637376392e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.845474557305529e-06</v>
+        <v>5.845474557305535e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.793591910182951e-06</v>
+        <v>9.793591910182941e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.446219522909541e-05</v>
+        <v>1.44621952290954e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.118616536874127e-05</v>
+        <v>2.118616536874126e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5153,25 +5153,25 @@
         <v>0.0001200967188004427</v>
       </c>
       <c r="C5" t="n">
-        <v>1.288692905181378e-05</v>
+        <v>1.288692905181379e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.919606537183455e-05</v>
+        <v>2.919606537183449e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.158817337872147e-05</v>
+        <v>4.158817337872148e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.171812778960297e-05</v>
+        <v>2.171812778960294e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.129180410437693e-05</v>
+        <v>8.129180410437742e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.757604799168212e-05</v>
+        <v>2.757604799168211e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.357187569696117e-05</v>
+        <v>3.357187569696114e-05</v>
       </c>
       <c r="J5" t="n">
         <v>0.0001049580892626009</v>
@@ -5180,55 +5180,55 @@
         <v>7.198765572111079e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004489528582168081</v>
+        <v>0.0004489528582168085</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002445830819400099</v>
+        <v>0.0002445830819400097</v>
       </c>
       <c r="N5" t="n">
-        <v>1.768108256292961e-05</v>
+        <v>1.768108256292965e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.855585694309703e-05</v>
+        <v>2.855585694309702e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001341700892868142</v>
+        <v>0.0001341700892868144</v>
       </c>
       <c r="Q5" t="n">
         <v>4.111193960784344e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.506931586330333e-05</v>
+        <v>1.506931586330341e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.900063231086383e-05</v>
+        <v>7.900063231086381e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.461091079120774e-05</v>
+        <v>3.461091079120785e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005531761649885738</v>
+        <v>0.0005531761649885717</v>
       </c>
       <c r="V5" t="n">
-        <v>4.905910700910087e-05</v>
+        <v>4.905910700910076e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001453074910904363</v>
+        <v>0.0001453074910904365</v>
       </c>
       <c r="X5" t="n">
         <v>0.0001349968366703529</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.762024357947993e-05</v>
+        <v>3.762024357947995e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001012276595900456</v>
+        <v>0.0001012276595900455</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002001282064130853</v>
+        <v>0.0002001282064130852</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003471160011422982</v>
+        <v>0.0003471160011422981</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.147938907238966e-05</v>
+        <v>1.147938907238967e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>5.202808338579708e-06</v>
+        <v>5.202808338579697e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>8.207760563467855e-06</v>
+        <v>8.207760563467865e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>9.124195724308406e-06</v>
+        <v>9.124195724308411e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.659566177854552e-06</v>
+        <v>5.659566177854567e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.327717601628107e-06</v>
+        <v>9.327717601628126e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>8.073893733374117e-06</v>
+        <v>8.073893733374139e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>8.415607172814049e-06</v>
+        <v>8.415607172814081e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.046897000517823e-05</v>
+        <v>1.046897000517824e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.055401817575406e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.141397049096765e-05</v>
+        <v>3.141397049096764e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.002193776822266e-05</v>
+        <v>2.002193776822271e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.537442718826799e-06</v>
+        <v>5.537442718826809e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>8.266343532755279e-06</v>
+        <v>8.266343532755314e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.431496187728125e-05</v>
+        <v>1.431496187728124e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.882614954753571e-06</v>
+        <v>8.882614954753599e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>7.500859501052929e-06</v>
+        <v>7.500859501052951e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>9.35372270036595e-06</v>
+        <v>9.353722700365967e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.319482289605198e-06</v>
+        <v>6.319482289605191e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>3.542606970185647e-05</v>
+        <v>3.54260697018564e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>9.340989202702004e-06</v>
+        <v>9.340989202702056e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.438701151949674e-05</v>
+        <v>1.438701151949675e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.154708822703459e-05</v>
+        <v>1.154708822703458e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.642018557472727e-06</v>
+        <v>6.642018557472734e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.048311376345365e-05</v>
+        <v>1.048311376345364e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.728814246936239e-05</v>
+        <v>1.728814246936241e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.196500300922412e-05</v>
+        <v>2.196500300922409e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.370574691043735e-05</v>
+        <v>1.370574691043736e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>7.429166176627391e-06</v>
+        <v>7.429166176627384e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.29769301451923e-06</v>
+        <v>8.29769301451922e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>9.214128175359769e-06</v>
+        <v>9.214128175359749e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.885924015902245e-06</v>
+        <v>7.88592401590224e-06</v>
       </c>
       <c r="G7" t="n">
         <v>1.155407543967578e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.163826184425499e-06</v>
+        <v>8.163826184425484e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.505539623865434e-06</v>
+        <v>8.505539623865429e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.269532784322593e-05</v>
+        <v>1.269532784322592e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.064395062680541e-05</v>
+        <v>1.06439506268054e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.364032832901534e-05</v>
+        <v>3.364032832901538e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.011187021927408e-05</v>
+        <v>2.011187021927406e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>7.727448764632921e-06</v>
+        <v>7.727448764632902e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>8.357240835993722e-06</v>
+        <v>8.357240835993726e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.440546499676572e-05</v>
+        <v>1.440546499676571e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.972547405804945e-06</v>
+        <v>8.972547405804928e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.590791952104306e-06</v>
+        <v>7.590791952104318e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.158008053841364e-05</v>
+        <v>1.158008053841362e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>8.545840127652891e-06</v>
+        <v>8.545840127652884e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>3.765443193927875e-05</v>
+        <v>3.765443193927872e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.430921653753424e-06</v>
+        <v>9.430921653753409e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.447960560304194e-05</v>
+        <v>1.447960560304191e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.377344606508229e-05</v>
+        <v>1.377344606508227e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.785917189431063e-06</v>
+        <v>8.785917189431065e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.270947160150132e-05</v>
+        <v>1.270947160150129e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.737807492041377e-05</v>
+        <v>1.737807492041376e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.410204506005963e-05</v>
+        <v>2.41020450600596e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.072689496143099e-05</v>
+        <v>2.072689496143103e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.110963005294724e-05</v>
+        <v>2.110963005294723e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.197815689083904e-05</v>
+        <v>2.197815689083912e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93487028121907e-05</v>
+        <v>1.934870281219068e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.594451564345102e-05</v>
+        <v>1.594451564345104e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.661539183380287e-05</v>
+        <v>2.661539183380293e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.184429006074534e-05</v>
+        <v>2.184429006074537e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.21860035001853e-05</v>
+        <v>2.218600350018528e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.637579171954575e-05</v>
+        <v>2.637579171954576e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.432441450312528e-05</v>
+        <v>2.432441450312521e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.732079220533517e-05</v>
+        <v>4.732079220533521e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.379233409559376e-05</v>
+        <v>3.379233409559374e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.624582879712439e-05</v>
+        <v>1.624582879712441e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.829573891937227e-05</v>
+        <v>1.829573891937228e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.399623350556209e-05</v>
+        <v>2.399623350556211e-05</v>
       </c>
       <c r="Q8" t="n">
         <v>1.468498790562565e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.127125582842417e-05</v>
+        <v>2.127125582842413e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.526054441473348e-05</v>
+        <v>2.526054441473353e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.222630400397274e-05</v>
+        <v>2.222630400397282e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>4.808530932196997e-05</v>
+        <v>4.808530932196994e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.129431743479429e-05</v>
+        <v>2.129431743479436e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.81613782259461e-05</v>
+        <v>2.816137822594609e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.009622609267985e-05</v>
+        <v>2.009622609267986e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.90922764038427e-05</v>
+        <v>2.909227640384291e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.960691944214236e-05</v>
+        <v>1.96069194421423e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.105853879673362e-05</v>
+        <v>3.10585387967337e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.473872115903114e-05</v>
+        <v>4.473872115903107e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.516446451729202e-05</v>
+        <v>2.516446451729203e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.301360813720078e-05</v>
+        <v>2.301360813720073e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.388213497509262e-05</v>
+        <v>2.38821349750926e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.384636896614457e-05</v>
+        <v>2.384636896614454e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.395944671130654e-05</v>
+        <v>1.395944671130655e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.713851633750312e-05</v>
+        <v>2.713851633750309e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374826814499887e-05</v>
+        <v>2.374826814499885e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.408998158443882e-05</v>
+        <v>2.408998158443881e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82797698037993e-05</v>
+        <v>2.827976980379929e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.622839258737878e-05</v>
+        <v>2.62283925873788e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.922477028958869e-05</v>
+        <v>4.922477028958871e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.569631217984748e-05</v>
+        <v>3.569631217984746e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.331189072520629e-05</v>
+        <v>2.331189072520631e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.531047361916605e-05</v>
+        <v>2.531047361916601e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>3.165605321868399e-05</v>
+        <v>3.165605321868396e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.455698830363225e-05</v>
+        <v>2.455698830363226e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.31752339126777e-05</v>
+        <v>2.317523391267771e-05</v>
       </c>
       <c r="S9" t="n">
         <v>2.716452249898706e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.413028208822628e-05</v>
+        <v>2.413028208822623e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>5.323686950047758e-05</v>
+        <v>5.323686950047748e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.977635640562866e-05</v>
+        <v>2.97763564056287e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.006404756361531e-05</v>
+        <v>3.006404756361529e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.935788802565564e-05</v>
+        <v>2.935788802565562e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.437035915000447e-05</v>
+        <v>2.437035915000441e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.580646822850219e-05</v>
+        <v>2.580646822850217e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.296251688098714e-05</v>
+        <v>3.296251688098708e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.968648702063299e-05</v>
+        <v>3.968648702063298e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.187722180602664e-06</v>
+        <v>4.187722180602686e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.267366353192166e-06</v>
+        <v>4.267366353192169e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.173777879476656e-06</v>
+        <v>4.173777879476719e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.191718706819324e-06</v>
+        <v>4.191718706819343e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.196318130624663e-06</v>
+        <v>4.196318130624673e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.26126784966959e-06</v>
+        <v>4.26126784966964e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.177474793162838e-06</v>
+        <v>4.177474793162871e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.241013431415562e-06</v>
+        <v>4.241013431415449e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.258809151087568e-06</v>
+        <v>4.258809151087471e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33737006499299e-06</v>
+        <v>4.337370064993039e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.248843923270145e-06</v>
+        <v>4.248843923269921e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.258782026643936e-06</v>
+        <v>4.258782026643938e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.173262727970676e-06</v>
+        <v>4.173262727970629e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.655969345437351e-06</v>
+        <v>5.655969345437331e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.165191050259748e-06</v>
+        <v>4.165191050259761e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.176648609706937e-06</v>
+        <v>4.176648609706966e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.188201879267162e-06</v>
+        <v>4.188201879267137e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.335964023802279e-06</v>
+        <v>4.335964023802343e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.172823799834792e-06</v>
+        <v>4.172823799834659e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.906485871943276e-06</v>
+        <v>5.906485871943088e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.241380390159627e-06</v>
+        <v>4.241380390159625e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.181995984079725e-06</v>
+        <v>6.181995984079682e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.178359324161139e-06</v>
+        <v>5.178359324161158e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.624381549366087e-06</v>
+        <v>4.6243815493661e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.95991878972606e-06</v>
+        <v>4.959918789725996e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.341347788449358e-06</v>
+        <v>4.341347788449406e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.247049683873237e-06</v>
+        <v>4.247049683873239e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.238516852111024e-06</v>
+        <v>4.254380404302685e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.326484120090834e-06</v>
+        <v>4.340410769347967e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.143329996191095e-06</v>
+        <v>4.15580920862027e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.261198836989154e-06</v>
+        <v>4.277097949863907e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.302934790142319e-06</v>
+        <v>4.321198468948728e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.763722424837325e-06</v>
+        <v>4.797990201643454e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.168201013090975e-06</v>
+        <v>4.181670557694132e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.62222538996037e-06</v>
+        <v>4.65182275716797e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.746738987684303e-06</v>
+        <v>4.780552587288366e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.307595223966986e-06</v>
+        <v>5.361548640866521e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.678068611195704e-06</v>
+        <v>4.709373980766973e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.778094696605708e-06</v>
+        <v>4.813380051782338e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.136816402512735e-06</v>
+        <v>4.149137445942809e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.680439676822657e-06</v>
+        <v>6.697058667520978e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.078472845203952e-06</v>
+        <v>4.088694365220271e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.163222450956976e-06</v>
+        <v>4.176411866293775e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.24469888468984e-06</v>
+        <v>4.260881635359973e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.28997606669728e-06</v>
+        <v>5.343049868105352e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.136871639595801e-06</v>
+        <v>4.149112644341447e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.553985556653005e-06</v>
+        <v>7.591751400840631e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.622216170450162e-06</v>
+        <v>4.651539618457174e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>8.431152348113279e-06</v>
+        <v>8.488523161110835e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.129773386759586e-05</v>
+        <v>1.156506347891271e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.356174843750545e-06</v>
+        <v>7.482362447380745e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.715594036411782e-06</v>
+        <v>5.740715739373161e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.335447492249693e-06</v>
+        <v>5.390148562165986e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.670412155387862e-06</v>
+        <v>4.701673273797576e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.356964261718099e-06</v>
+        <v>4.356964261718101e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.264255357133076e-06</v>
+        <v>4.264255357133078e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.199456965804419e-06</v>
+        <v>4.19945696580441e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.402106863828195e-06</v>
+        <v>4.402106863828198e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.454059471548891e-06</v>
+        <v>4.454059471548894e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.187696426508298e-06</v>
+        <v>5.187696426508304e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.241215306554193e-06</v>
+        <v>4.241215306554194e-06</v>
       </c>
       <c r="I4" t="n">
         <v>4.958913454836332e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.144638929736444e-06</v>
+        <v>5.144638929736443e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.047305957334821e-06</v>
+        <v>6.047305957334809e-06</v>
       </c>
       <c r="L4" t="n">
         <v>5.047362462538027e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.208929967403521e-06</v>
+        <v>5.208929967403527e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.193638092562967e-06</v>
+        <v>4.19363809256296e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.391623491991357e-06</v>
+        <v>4.39162349199136e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.102464779662849e-06</v>
+        <v>4.102464779662853e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.231883184356595e-06</v>
+        <v>4.231883184356602e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.362382678805859e-06</v>
+        <v>4.362382678805849e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>6.031424075274811e-06</v>
+        <v>6.031424075274816e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.188680197351237e-06</v>
+        <v>4.188680197351239e-06</v>
       </c>
       <c r="U4" t="n">
         <v>5.33724124230623e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>4.864378810018661e-06</v>
+        <v>4.86437881001866e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>6.213672525829964e-06</v>
+        <v>6.213672525829967e-06</v>
       </c>
       <c r="X4" t="n">
         <v>1.554666651381194e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.287648444677137e-06</v>
+        <v>9.287648444677129e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.77425405869939e-06</v>
+        <v>4.774254058699397e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.092236173617648e-06</v>
+        <v>6.092236173617653e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.034648151088636e-06</v>
+        <v>5.034648151088638e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6010,82 +6010,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.535516831083239e-05</v>
+        <v>1.535516831083242e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.571130830020122e-05</v>
+        <v>1.571130830020126e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.481554157827881e-05</v>
+        <v>1.481554157827878e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.312642070407593e-05</v>
+        <v>1.312642070407592e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.866248163170958e-05</v>
+        <v>1.866248163170961e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.020685580958252e-05</v>
+        <v>3.020685580958279e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.476949365454585e-05</v>
+        <v>1.476949365454588e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.774609349864194e-05</v>
+        <v>2.774609349864197e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.999286939092824e-05</v>
+        <v>2.999286939092833e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.578747444468152e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.928797464459855e-05</v>
+        <v>2.928797464459854e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.334013158971623e-05</v>
+        <v>3.334013158971622e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.324245718720612e-05</v>
+        <v>1.324245718720615e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.673390400091889e-05</v>
+        <v>1.673390400091891e-05</v>
       </c>
       <c r="P5" t="n">
         <v>1.124870524139306e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.508014421304898e-05</v>
+        <v>1.508014421304899e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.688047254505178e-05</v>
+        <v>1.68804725450518e-05</v>
       </c>
       <c r="S5" t="n">
         <v>4.157627247714004e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48068114158783e-05</v>
+        <v>1.480681141587831e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.292083853210977e-05</v>
+        <v>3.292083853210975e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>2.635871479953999e-05</v>
+        <v>2.635871479954004e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.761976086515743e-05</v>
+        <v>4.761976086515737e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002075580378958654</v>
+        <v>0.0002075580378958656</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001032114676308302</v>
+        <v>0.0001032114676308304</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.260175982876231e-05</v>
+        <v>2.260175982876229e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.630388269815066e-05</v>
+        <v>4.630388269815061e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>2.960502097817783e-05</v>
@@ -6101,82 +6101,82 @@
         <v>6.505868483188779e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.720695079446861e-06</v>
+        <v>4.72069507944686e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.655896688118197e-06</v>
+        <v>4.655896688118199e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.858546586141977e-06</v>
+        <v>4.858546586141983e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.602963693019557e-06</v>
+        <v>6.60296369301956e-06</v>
       </c>
       <c r="G6" t="n">
         <v>7.336600647978966e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.390119528024857e-06</v>
+        <v>6.390119528024864e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.107817676307006e-06</v>
+        <v>7.10781767630701e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.293543151207105e-06</v>
+        <v>7.293543151207107e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>8.196210178805488e-06</v>
+        <v>8.196210178805491e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.503802184851811e-06</v>
+        <v>5.503802184851813e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.357834188874189e-06</v>
+        <v>7.357834188874194e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.654966513482192e-06</v>
+        <v>4.654966513482191e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>6.541503052186648e-06</v>
+        <v>6.541503052186625e-06</v>
       </c>
       <c r="P6" t="n">
         <v>4.512153552259994e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.380787405827273e-06</v>
+        <v>6.380787405827274e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>4.818822401119634e-06</v>
+        <v>4.818822401119633e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>8.180328296745479e-06</v>
+        <v>8.180328296745483e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>4.645119919665022e-06</v>
+        <v>4.645119919665024e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>5.795265225077707e-06</v>
+        <v>5.795265225077708e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>5.320818532332448e-06</v>
+        <v>5.320818532332443e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.723910821086162e-06</v>
+        <v>6.72391082108616e-06</v>
       </c>
       <c r="X6" t="n">
         <v>1.76955707352826e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.78740095372719e-06</v>
+        <v>9.787400953727195e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.230693781013181e-06</v>
+        <v>5.230693781013185e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.241140395088316e-06</v>
+        <v>8.241140395088314e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.495075823091799e-06</v>
+        <v>5.495075823091797e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.767801885297648e-06</v>
+        <v>6.767801885297652e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.67509298071261e-06</v>
+        <v>6.675092980712626e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>6.610294589383954e-06</v>
+        <v>6.610294589383963e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.812944487407739e-06</v>
+        <v>6.812944487407743e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.86489709512843e-06</v>
+        <v>6.864897095128445e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.598534050087825e-06</v>
+        <v>7.598534050087835e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.652052930133731e-06</v>
+        <v>6.65205293013374e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.369751078415868e-06</v>
+        <v>7.369751078415883e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.555476553315981e-06</v>
+        <v>7.555476553315986e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>8.458143580914356e-06</v>
+        <v>8.458143580914359e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.458200086117564e-06</v>
+        <v>7.458200086117568e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>7.619767590983065e-06</v>
+        <v>7.619767590983072e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>6.604475716142512e-06</v>
+        <v>6.60447571614252e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>6.801035732709447e-06</v>
+        <v>6.801035732709458e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.511877020380939e-06</v>
+        <v>6.51187702038094e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.642720807936137e-06</v>
+        <v>6.642720807936147e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>6.773220302385391e-06</v>
+        <v>6.773220302385402e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>8.442261698854349e-06</v>
+        <v>8.442261698854357e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>6.59951782093077e-06</v>
+        <v>6.599517820930786e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>7.753267476976555e-06</v>
+        <v>7.753267476976557e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.2752164335982e-06</v>
+        <v>7.275216433598207e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.624510149409496e-06</v>
+        <v>8.624510149409511e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.795750413739147e-05</v>
+        <v>1.795750413739149e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.170007032871436e-05</v>
+        <v>1.170007032871438e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.185091682278938e-06</v>
+        <v>7.185091682278947e-06</v>
       </c>
       <c r="AA7" t="n">
         <v>8.503073797197186e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.445485774668178e-06</v>
+        <v>7.445485774668184e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6274,19 +6274,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.302220221579926e-05</v>
+        <v>1.302220221579928e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.87146873082709e-05</v>
+        <v>1.871468730827091e-05</v>
       </c>
       <c r="D8" t="n">
         <v>1.864988891694225e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.577209366406723e-05</v>
+        <v>1.577209366406722e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.402056303740413e-05</v>
+        <v>1.402056303740414e-05</v>
       </c>
       <c r="G8" t="n">
         <v>2.083772603997763e-05</v>
@@ -6295,16 +6295,16 @@
         <v>1.869164725769203e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.940934540597417e-05</v>
+        <v>1.940934540597416e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.959507088087426e-05</v>
+        <v>1.959507088087428e-05</v>
       </c>
       <c r="K8" t="n">
         <v>2.049773790847263e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.949779441367586e-05</v>
+        <v>1.949779441367585e-05</v>
       </c>
       <c r="M8" t="n">
         <v>1.965936191854151e-05</v>
@@ -6316,43 +6316,43 @@
         <v>1.558993992032677e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.499869566345169e-05</v>
+        <v>1.49986956634517e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.176019847739854e-05</v>
+        <v>1.176019847739855e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.881281462994367e-05</v>
+        <v>1.881281462994368e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.048185602641264e-05</v>
+        <v>2.048185602641266e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.863911214848907e-05</v>
+        <v>1.863911214848905e-05</v>
       </c>
       <c r="U8" t="n">
         <v>1.6969479398112e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.773792930332926e-05</v>
+        <v>1.773792930332925e-05</v>
       </c>
       <c r="W8" t="n">
         <v>2.066524143346428e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.360520633210303e-05</v>
+        <v>2.360520633210304e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>2.949841957503885e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.333202906416804e-05</v>
+        <v>1.333202906416805e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.054266812475547e-05</v>
+        <v>2.054266812475548e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.552819898228068e-05</v>
+        <v>2.552819898228067e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.555024700045659e-05</v>
+        <v>1.55502470004566e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.867470769931229e-05</v>
+        <v>1.867470769931228e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.860990930798361e-05</v>
+        <v>1.86099093079836e-05</v>
       </c>
       <c r="E9" t="n">
         <v>1.807004980156122e-05</v>
@@ -6377,10 +6377,10 @@
         <v>1.144805745992334e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.959814905136498e-05</v>
+        <v>1.9598149051365e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.86516676487334e-05</v>
+        <v>1.865166764873342e-05</v>
       </c>
       <c r="I9" t="n">
         <v>1.936936579701555e-05</v>
@@ -6392,52 +6392,52 @@
         <v>2.045775829951403e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.945781480471725e-05</v>
+        <v>1.945781480471726e-05</v>
       </c>
       <c r="M9" t="n">
         <v>1.961938230958274e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.860409043474218e-05</v>
+        <v>1.860409043474219e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.986824200460362e-05</v>
+        <v>1.986824200460363e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.981095608051837e-05</v>
+        <v>1.981095608051838e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.864233580921329e-05</v>
+        <v>1.86423358092133e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.877283502098507e-05</v>
+        <v>1.877283502098508e-05</v>
       </c>
       <c r="S9" t="n">
         <v>2.044187641745403e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.859913253953044e-05</v>
+        <v>1.859913253953047e-05</v>
       </c>
       <c r="U9" t="n">
         <v>1.974927784494314e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.298737614002959e-05</v>
+        <v>2.29873761400296e-05</v>
       </c>
       <c r="W9" t="n">
         <v>2.062412486800919e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.995711885599116e-05</v>
+        <v>2.995711885599114e-05</v>
       </c>
       <c r="Y9" t="n">
         <v>2.3699685047314e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.724503932413573e-05</v>
+        <v>1.724503932413575e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.050268851579687e-05</v>
+        <v>2.050268851579689e-05</v>
       </c>
       <c r="AB9" t="n">
         <v>1.944510049326785e-05</v>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.176953486215757e-06</v>
+        <v>4.176953486215747e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.248089932270889e-06</v>
+        <v>4.248089932270892e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.218582053603643e-06</v>
+        <v>4.218582053603674e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.151449535382429e-06</v>
+        <v>4.151449535382432e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.172683788800036e-06</v>
+        <v>4.172683788800051e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.180387868623147e-06</v>
+        <v>4.180387868623134e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.154965019673034e-06</v>
+        <v>4.154965019673031e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.237830663384624e-06</v>
+        <v>4.237830663384636e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.215603232742143e-06</v>
+        <v>4.215603232742149e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.403516680386076e-06</v>
+        <v>4.403516680386069e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.19790737267715e-06</v>
+        <v>4.197907372677149e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.234611084119593e-06</v>
+        <v>4.234611084119599e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.14938172871733e-06</v>
+        <v>4.14938172871732e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.62829006271511e-06</v>
+        <v>5.628290062715103e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.14599115542548e-06</v>
+        <v>4.145991155425488e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.166907921770532e-06</v>
+        <v>4.166907921770531e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.173689296805509e-06</v>
+        <v>4.173689296805532e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.269022615315155e-06</v>
+        <v>4.269022615315172e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.167641101986397e-06</v>
+        <v>4.167641101986405e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.896589827043561e-06</v>
+        <v>5.896589827043562e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.25912380086806e-06</v>
+        <v>4.259123800868057e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.000310552474328e-06</v>
+        <v>6.000310552474321e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.236436023907979e-06</v>
+        <v>5.236436023907998e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.470280499067154e-06</v>
+        <v>4.470280499067146e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.908150082145713e-06</v>
+        <v>4.908150082145736e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.229002960818657e-06</v>
+        <v>4.22900296081866e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.36380602479888e-06</v>
+        <v>4.363806024798883e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.309932705679274e-06</v>
+        <v>4.328769351981306e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.334379002713252e-06</v>
+        <v>4.34906497419158e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.610228839600309e-06</v>
+        <v>4.639837326635525e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.124632399177357e-06</v>
+        <v>4.136100628616517e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.282176638008484e-06</v>
+        <v>4.30018842168191e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.33673048488527e-06</v>
+        <v>4.356433464198762e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.15632449342938e-06</v>
+        <v>4.169828888590749e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.747868479131972e-06</v>
+        <v>4.782418362973281e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.587388242746115e-06</v>
+        <v>4.616081992257665e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.92724024409068e-06</v>
+        <v>6.00371090205385e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.463272838663827e-06</v>
+        <v>4.487462627825526e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.750811050084668e-06</v>
+        <v>4.785619107449357e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.114217994473952e-06</v>
+        <v>4.126228465899328e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.6647576996697e-06</v>
+        <v>6.681662167843356e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.090840699474317e-06</v>
+        <v>4.101925885461099e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.240450888007109e-06</v>
+        <v>4.256910566452034e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.289147745353739e-06</v>
+        <v>4.307404515284396e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>4.96419706862235e-06</v>
+        <v>5.006164503682392e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.246434933704414e-06</v>
+        <v>4.263114335199451e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.69471505632165e-06</v>
+        <v>7.738648486556581e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>4.89495155423976e-06</v>
+        <v>4.934394101782773e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.41650957310343e-06</v>
+        <v>7.439831578918701e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.185373734478213e-05</v>
+        <v>1.214154708252172e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.405634852714864e-06</v>
+        <v>6.498640714054237e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.516112702797997e-06</v>
+        <v>5.534861994968842e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.68192319288605e-06</v>
+        <v>4.714001512479002e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.641177040705683e-06</v>
+        <v>5.707259511336184e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.513079960110812e-06</v>
+        <v>4.513079960110818e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.319970419334649e-06</v>
+        <v>4.319970419334656e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.983293778844614e-06</v>
+        <v>4.983293778844626e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.225001103051547e-06</v>
+        <v>4.225001103051545e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.464851763642697e-06</v>
+        <v>4.464851763642712e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.551872889296279e-06</v>
+        <v>4.551872889296283e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.264710115316515e-06</v>
+        <v>4.264710115316517e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.200715681118556e-06</v>
+        <v>5.200715681118563e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.934878695637675e-06</v>
+        <v>4.934878695637684e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.07221546248322e-06</v>
+        <v>7.072215462483222e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.749763746956403e-06</v>
+        <v>4.749763746956415e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.209714499661382e-06</v>
+        <v>5.20971449966139e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.201644275531104e-06</v>
+        <v>4.201644275531117e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>4.426327193641351e-06</v>
+        <v>4.426327193641348e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.163346190459019e-06</v>
+        <v>4.16334619045902e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.399610688514185e-06</v>
+        <v>4.399610688514195e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.476209439121188e-06</v>
+        <v>4.476209439121194e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>5.553043127180793e-06</v>
+        <v>5.553043127180801e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.407892296332091e-06</v>
+        <v>4.407892296332102e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.647308073406183e-06</v>
+        <v>5.647308073406189e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.346066418698819e-06</v>
+        <v>5.346066418698828e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>4.709509966688388e-06</v>
+        <v>4.70950996668839e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.648042260939166e-05</v>
+        <v>1.648042260939164e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.835827947222319e-06</v>
+        <v>7.835827947222326e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.508494784081462e-06</v>
+        <v>4.508494784081467e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.101002719692013e-06</v>
+        <v>5.101002719692046e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.605094944145233e-06</v>
+        <v>6.605094944145236e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.755551524908915e-05</v>
+        <v>1.755551524908916e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.586120227656963e-05</v>
+        <v>1.586120227656965e-05</v>
       </c>
       <c r="D5" t="n">
         <v>2.75256636104714e-05</v>
@@ -6882,73 +6882,73 @@
         <v>1.076196787375761e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.811052383650909e-05</v>
+        <v>1.811052383650912e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94265118738181e-05</v>
+        <v>1.94265118738182e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.48855587287478e-05</v>
+        <v>1.488555872874784e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.150656775373916e-05</v>
+        <v>3.150656775373918e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.609668234560272e-05</v>
+        <v>2.609668234560275e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.298114881416104e-05</v>
+        <v>6.29811488141612e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.370635234921346e-05</v>
+        <v>2.370635234921347e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.232538097439325e-05</v>
+        <v>3.232538097439329e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.259984245270707e-05</v>
+        <v>1.259984245270708e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.667687983698428e-05</v>
+        <v>1.667687983698431e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.234814509726401e-05</v>
+        <v>1.234814509726406e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.669590941128024e-05</v>
+        <v>1.669590941128023e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.820503568338201e-05</v>
+        <v>1.820503568338205e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>3.447846493175366e-05</v>
+        <v>3.447846493175364e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72317265203093e-05</v>
+        <v>1.723172652030936e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>3.685729089195128e-05</v>
+        <v>3.685729089195135e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>3.313270093007331e-05</v>
+        <v>3.31327009300733e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.174659471667419e-05</v>
+        <v>2.174659471667421e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002200062482824921</v>
+        <v>0.000220006248282492</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.730268962541671e-05</v>
+        <v>7.730268962541656e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.821715973469865e-05</v>
+        <v>1.821715973469869e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.821860452370998e-05</v>
+        <v>2.821860452371049e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.857670179310273e-05</v>
+        <v>5.85767017931026e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.675180362372793e-06</v>
+        <v>6.675180362372817e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.48207082159663e-06</v>
+        <v>6.482070821596648e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.145394181106599e-06</v>
+        <v>7.145394181106623e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.681098932038811e-06</v>
+        <v>4.681098932038827e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.626952165904687e-06</v>
+        <v>6.626952165904695e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.713973291558259e-06</v>
+        <v>6.713973291558277e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.42681051757849e-06</v>
+        <v>6.426810517578501e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.362816083380525e-06</v>
+        <v>7.362816083380547e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.390976524624936e-06</v>
+        <v>5.390976524624946e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>7.52831329147048e-06</v>
+        <v>7.528313291470483e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.91186414921839e-06</v>
+        <v>6.911864149218403e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>7.371814901923366e-06</v>
+        <v>7.371814901923379e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.664468464671543e-06</v>
+        <v>4.66446846467155e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>4.888216830331795e-06</v>
+        <v>4.888216830331799e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>6.309856875737153e-06</v>
+        <v>6.309856875737198e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.561711090776176e-06</v>
+        <v>6.561711090776184e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>6.638309841383166e-06</v>
+        <v>6.638309841383193e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>7.715143529442771e-06</v>
+        <v>7.715143529442786e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>4.863990125319366e-06</v>
+        <v>4.863990125319376e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>7.799924035805806e-06</v>
+        <v>7.799924035805818e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>5.80216424768608e-06</v>
+        <v>5.802164247686105e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>6.85559447363824e-06</v>
+        <v>6.855594473638274e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.693652043837892e-05</v>
+        <v>1.69365204383789e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.328390367948423e-06</v>
+        <v>8.32839036794832e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.964592613068729e-06</v>
+        <v>4.964592613068739e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.263103121953996e-06</v>
+        <v>7.263103121954043e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.074640624550525e-06</v>
+        <v>7.074640624550526e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.910272022193058e-06</v>
+        <v>6.910272022193067e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.717162481416897e-06</v>
+        <v>6.717162481416899e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.380485840926874e-06</v>
+        <v>7.380485840926878e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.622193165133802e-06</v>
+        <v>6.622193165133821e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.862043825724948e-06</v>
+        <v>6.862043825724952e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.949064951378526e-06</v>
+        <v>6.949064951378538e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.661902177398774e-06</v>
+        <v>6.661902177398779e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.597907743200811e-06</v>
+        <v>7.597907743200806e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.33207075771992e-06</v>
+        <v>7.332070757719933e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>9.469407524565485e-06</v>
+        <v>9.469407524565492e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.146955809038659e-06</v>
+        <v>7.146955809038662e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>7.606906561743632e-06</v>
+        <v>7.606906561743635e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>6.598836337613353e-06</v>
+        <v>6.598836337613357e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>6.822093591484109e-06</v>
+        <v>6.822093591484121e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.559112588301775e-06</v>
+        <v>6.559112588301781e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.796802750596445e-06</v>
+        <v>6.796802750596457e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>6.873401501203446e-06</v>
+        <v>6.873401501203441e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>7.950235189263044e-06</v>
+        <v>7.950235189263042e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>6.805084358414355e-06</v>
+        <v>6.805084358414366e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>8.039418470731864e-06</v>
+        <v>8.039418470731883e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.743258480781074e-06</v>
+        <v>7.743258480781089e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.106702028770644e-06</v>
+        <v>7.106702028770652e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.887761467147392e-05</v>
+        <v>1.887761467147391e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.022353556944221e-05</v>
+        <v>1.022353556944222e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.905686846163714e-06</v>
+        <v>6.905686846163711e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.498194781774275e-06</v>
+        <v>7.498194781774307e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.002287006227482e-06</v>
+        <v>9.002287006227493e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.313715159593366e-05</v>
+        <v>1.313715159593367e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.870497429540061e-05</v>
+        <v>1.870497429540063e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.93682976549106e-05</v>
+        <v>1.936829765491062e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.554247849806021e-05</v>
+        <v>1.554247849806023e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.398640931307202e-05</v>
+        <v>1.398640931307203e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.013144359436102e-05</v>
+        <v>2.013144359436106e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.864971399138247e-05</v>
+        <v>1.86497139913825e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.958571955718452e-05</v>
+        <v>1.958571955718457e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.931988257170364e-05</v>
+        <v>1.931988257170367e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.145721933854919e-05</v>
+        <v>2.14572193385492e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.913476762302238e-05</v>
+        <v>1.91347676230224e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.959471837572821e-05</v>
+        <v>1.959471837572824e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.412096188245745e-05</v>
+        <v>1.412096188245746e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.557285416225008e-05</v>
+        <v>1.55728541622501e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.500905449098144e-05</v>
+        <v>1.500905449098146e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.189152765227985e-05</v>
+        <v>1.189152765227986e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.886121331518716e-05</v>
+        <v>1.886121331518719e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.993804700324678e-05</v>
+        <v>1.99380470032468e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.879289617239809e-05</v>
+        <v>1.879289617239812e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.721551027088291e-05</v>
+        <v>1.721551027088292e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.816150265483849e-05</v>
+        <v>1.816150265483852e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.90956460310413e-05</v>
+        <v>1.909564603104133e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.450034046013742e-05</v>
+        <v>2.450034046013744e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.794703827989329e-05</v>
+        <v>2.794703827989331e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.302555414588691e-05</v>
+        <v>1.302555414588693e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.948600659575801e-05</v>
+        <v>1.948600659575804e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7007874266466e-05</v>
+        <v>2.700787426646602e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.498739571769719e-05</v>
+        <v>1.49873957176972e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.781344676819512e-05</v>
+        <v>1.781344676819515e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.847677012770509e-05</v>
+        <v>1.84767701277051e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.702166755202487e-05</v>
+        <v>1.70216675520249e-05</v>
       </c>
       <c r="F9" t="n">
         <v>1.099833885824567e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.804534930270621e-05</v>
+        <v>1.804534930270623e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.775818646417697e-05</v>
+        <v>1.775818646417699e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.869419202997903e-05</v>
+        <v>1.869419202997904e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.842835504449813e-05</v>
+        <v>1.842835504449816e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.056569181134369e-05</v>
+        <v>2.056569181134373e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.824324009581688e-05</v>
+        <v>1.82432400958169e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.870319084852186e-05</v>
+        <v>1.870319084852187e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.769512062439156e-05</v>
+        <v>1.76951206243916e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.892034949515822e-05</v>
+        <v>1.892034949515823e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.887497005614512e-05</v>
+        <v>1.887497005614514e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.789308710192412e-05</v>
+        <v>1.789308710192415e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.796968578798164e-05</v>
+        <v>1.796968578798168e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.904651947604126e-05</v>
+        <v>1.904651947604129e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.790136864519256e-05</v>
+        <v>1.79013686451926e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.913129998240427e-05</v>
+        <v>1.91312999824043e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.232358940731163e-05</v>
+        <v>2.232358940731167e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.820298631554885e-05</v>
+        <v>1.820298631554887e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.997389895825212e-05</v>
+        <v>2.997389895825213e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.131981985622042e-05</v>
+        <v>2.131981985622044e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.618168579627096e-05</v>
+        <v>1.618168579627097e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.859447906855249e-05</v>
+        <v>1.859447906855253e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.009857129300568e-05</v>
+        <v>2.009857129300571e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,82 +7466,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.774876717879592e-06</v>
+        <v>9.774876717879684e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.567722317479866e-06</v>
+        <v>6.567722317479865e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.976920182026115e-06</v>
+        <v>6.976920182026088e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.668196240085048e-06</v>
+        <v>7.668196240085009e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.814848004375829e-06</v>
+        <v>6.814848004375856e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.510687004475472e-06</v>
+        <v>7.510687004475391e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.65870554005382e-06</v>
+        <v>6.658705540053818e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.752958883539057e-06</v>
+        <v>6.752958883538992e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.029928643850574e-06</v>
+        <v>8.029928643850654e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.705872282315929e-06</v>
+        <v>6.705872282315976e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.585395873903368e-05</v>
+        <v>1.585395873903353e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.992177245785315e-06</v>
+        <v>9.99217724578532e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>6.651510285473542e-06</v>
+        <v>6.651510285473583e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>9.227092356841262e-06</v>
+        <v>9.227092356841233e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>8.743560276186406e-06</v>
+        <v>8.743560276186515e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.056409156313427e-06</v>
+        <v>7.056409156313395e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.719954681040469e-06</v>
+        <v>6.719954681040526e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.198948893543535e-06</v>
+        <v>8.198948893543531e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>6.990391781329183e-06</v>
+        <v>6.990391781329197e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.432672174473773e-05</v>
+        <v>1.43267217447376e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.227442560828058e-06</v>
+        <v>7.227442560827962e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.656107191088842e-06</v>
+        <v>9.656107191088883e-06</v>
       </c>
       <c r="X2" t="n">
         <v>1.003795644222678e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.51079483057045e-06</v>
+        <v>7.510794830570444e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.001572663920341e-05</v>
+        <v>1.001572663920343e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.128041783629957e-06</v>
+        <v>8.128041783629947e-06</v>
       </c>
       <c r="AB2" t="n">
         <v>1.056925623284504e-05</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.876043537737691e-05</v>
+        <v>2.957327179018455e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.205723116607907e-06</v>
+        <v>6.226699424485735e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.906207900074606e-06</v>
+        <v>9.02115006316174e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.382160294348697e-05</v>
+        <v>1.410841742533146e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.746899135378851e-06</v>
+        <v>7.821014830920309e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.267437133516355e-05</v>
+        <v>1.292123302112087e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.631055581704784e-06</v>
+        <v>6.665378441663907e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.303903824653557e-06</v>
+        <v>7.362070247029664e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.638516083182592e-05</v>
+        <v>1.676419391808626e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.966665200318699e-06</v>
+        <v>7.012721809202459e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2109215769392e-05</v>
+        <v>7.445667698836411e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.032270535677566e-05</v>
+        <v>3.120372011990216e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>6.575557823116113e-06</v>
+        <v>6.607757219555058e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.216173028407016e-05</v>
+        <v>1.225492802154154e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.145418101861406e-05</v>
+        <v>2.200807772226313e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.466078701993048e-06</v>
+        <v>9.60087814725683e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.068578865584829e-06</v>
+        <v>7.118438360702221e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.755000426982842e-05</v>
+        <v>1.797009319006309e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>9.002678061030393e-06</v>
+        <v>9.121112254584772e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>4.977752330878219e-05</v>
+        <v>5.121165970916197e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.066250222182227e-05</v>
+        <v>1.083869661376287e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.60512456462314e-05</v>
+        <v>1.629078836350291e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.079128724845625e-05</v>
+        <v>3.168269329753243e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.270538475084391e-05</v>
+        <v>1.295445258741595e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.139291179498299e-05</v>
+        <v>2.18499380963726e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.711418479263389e-05</v>
+        <v>1.751874703061909e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.44919396853247e-05</v>
+        <v>3.551114132358646e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.202366844277819e-05</v>
+        <v>4.202366844277794e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.240504956032182e-06</v>
+        <v>6.240504956032196e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.041946224671571e-05</v>
+        <v>1.041946224671572e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.82277433251892e-05</v>
+        <v>1.822774332518917e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>8.588782443270502e-06</v>
+        <v>8.588782443270514e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.644860405115081e-05</v>
+        <v>1.644860405115087e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.82508147967113e-06</v>
+        <v>6.825081479671109e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>7.889716353017068e-06</v>
+        <v>7.889716353017073e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>2.229478801394315e-05</v>
+        <v>2.229478801394312e-05</v>
       </c>
       <c r="K4" t="n">
         <v>7.357851531295045e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001106896963876064</v>
+        <v>0.0001106896963876056</v>
       </c>
       <c r="M4" t="n">
         <v>4.434756975431208e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>6.743807769206146e-06</v>
+        <v>6.743807769206148e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.516834129598395e-06</v>
+        <v>9.516834129598404e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>3.037447480485111e-05</v>
+        <v>3.037447480485108e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.131732677802573e-05</v>
+        <v>1.131732677802569e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>7.516918703112165e-06</v>
+        <v>7.516918703112182e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.422283870428613e-05</v>
+        <v>2.422283870428611e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.057163015808582e-05</v>
+        <v>1.057163015808581e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>6.969199068256952e-05</v>
+        <v>6.96919906825696e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.312642271273385e-05</v>
+        <v>1.312642271273387e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.604047434887462e-05</v>
+        <v>1.604047434887461e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.499527495193201e-05</v>
+        <v>4.49952749519319e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.639044973061028e-05</v>
+        <v>1.639044973061027e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.592669681734307e-05</v>
+        <v>2.592669681734296e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.34219102789302e-05</v>
+        <v>2.342191027893016e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.063160151144431e-05</v>
+        <v>5.063160151144439e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006393437480258263</v>
+        <v>0.0006393437480258243</v>
       </c>
       <c r="C5" t="n">
-        <v>2.32535980470028e-05</v>
+        <v>2.325359804700284e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001056917915191497</v>
+        <v>0.0001056917915191498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002431654275644647</v>
+        <v>0.0002431654275644639</v>
       </c>
       <c r="F5" t="n">
-        <v>6.963617447057306e-05</v>
+        <v>6.96361744705731e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001966894480945729</v>
+        <v>0.0001966894480945736</v>
       </c>
       <c r="H5" t="n">
-        <v>3.548353176259644e-05</v>
+        <v>3.548353176259641e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.570110232191902e-05</v>
+        <v>5.570110232191895e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003103119873684819</v>
+        <v>0.0003103119873684818</v>
       </c>
       <c r="K5" t="n">
-        <v>4.498883607669794e-05</v>
+        <v>4.498883607669787e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00191657901001156</v>
+        <v>0.001916579010011552</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007290814803613015</v>
+        <v>0.0007290814803613014</v>
       </c>
       <c r="N5" t="n">
-        <v>3.164163856150573e-05</v>
+        <v>3.164163856150564e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.729098077171693e-05</v>
+        <v>7.729098077171691e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004492823640934867</v>
+        <v>0.0004492823640934863</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001185274352152627</v>
+        <v>0.0001185274352152617</v>
       </c>
       <c r="R5" t="n">
-        <v>4.877890441701098e-05</v>
+        <v>4.877890441701114e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000323369651085799</v>
+        <v>0.0003233696510857977</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001087484299258596</v>
+        <v>0.0001087484299258592</v>
       </c>
       <c r="U5" t="n">
         <v>0.001182905946838664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001414459068422775</v>
+        <v>0.0001414459068422779</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002077148878180285</v>
+        <v>0.0002077148878180276</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0007807546834457138</v>
+        <v>0.0007807546834457136</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0002135326652087876</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003647041308878649</v>
+        <v>0.0003647041308878621</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003472944125229095</v>
+        <v>0.000347294412522909</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009468471373161114</v>
+        <v>0.0009468471373161098</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.326105909854098e-05</v>
+        <v>4.326105909854086e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>7.477895611794986e-06</v>
+        <v>7.477895611795007e-06</v>
       </c>
       <c r="D6" t="n">
         <v>1.165685290247852e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.253488049431736e-05</v>
+        <v>2.25348804943173e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>9.82617309903331e-06</v>
+        <v>9.826173099033334e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.075574122027896e-05</v>
+        <v>2.075574122027901e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.06247213543392e-06</v>
+        <v>8.062472135433919e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>9.127107008779888e-06</v>
+        <v>9.127107008779895e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.353217866970596e-05</v>
+        <v>2.353217866970594e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.166498870042318e-05</v>
+        <v>1.166498870042315e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001149968335567346</v>
+        <v>0.0001149968335567335</v>
       </c>
       <c r="M6" t="n">
-        <v>4.558496041007494e-05</v>
+        <v>4.558496041007492e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.030883112780499e-06</v>
+        <v>8.030883112780392e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>1.381906238525804e-05</v>
+        <v>1.381906238525803e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.467753407357241e-05</v>
+        <v>3.467753407357238e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.255471743378854e-05</v>
+        <v>1.255471743378847e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18240558722403e-05</v>
+        <v>1.182405587224032e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.546022936004894e-05</v>
+        <v>2.546022936004891e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.180902081384862e-05</v>
+        <v>1.180902081384863e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>7.405850011758336e-05</v>
+        <v>7.405850011758343e-05</v>
       </c>
       <c r="V6" t="n">
         <v>1.436381336849667e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.736093070148761e-05</v>
+        <v>1.736093070148757e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.930241212106015e-05</v>
+        <v>4.930241212106001e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.780448233051651e-05</v>
+        <v>1.780448233051653e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.023383398647124e-05</v>
+        <v>3.023383398647114e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.772904744805835e-05</v>
+        <v>2.77290474480583e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.206302500444e-05</v>
+        <v>5.206302500443999e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7906,64 +7906,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.575179571364245e-05</v>
+        <v>4.575179571364222e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.968632226896451e-06</v>
+        <v>9.968632226896458e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.414758951757998e-05</v>
+        <v>1.414758951757999e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.195587059605348e-05</v>
+        <v>2.195587059605343e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.231690971413478e-05</v>
+        <v>1.231690971413477e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.01767313220151e-05</v>
+        <v>2.017673132201512e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.05532087505354e-05</v>
+        <v>1.055320875053538e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.161784362388134e-05</v>
+        <v>1.161784362388135e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.602291528480744e-05</v>
+        <v>2.60229152848074e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.108597880215932e-05</v>
+        <v>1.10859788021593e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001144178236584707</v>
+        <v>0.0001144178236584696</v>
       </c>
       <c r="M7" t="n">
-        <v>4.807569702517636e-05</v>
+        <v>4.807569702517634e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.047193504007043e-05</v>
+        <v>1.047193504007042e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32434226329164e-05</v>
+        <v>1.324342263291639e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.410106330816914e-05</v>
+        <v>3.410106330816906e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.504545404889e-05</v>
+        <v>1.504545404888993e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.124504597397644e-05</v>
+        <v>1.124504597397645e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.795096597515041e-05</v>
+        <v>2.795096597515038e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.429975742895009e-05</v>
+        <v>1.429975742895008e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>7.347638372247393e-05</v>
+        <v>7.347638372247399e-05</v>
       </c>
       <c r="V7" t="n">
         <v>1.685454998359812e-05</v>
@@ -7972,19 +7972,19 @@
         <v>1.976860161973887e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>4.872340222279626e-05</v>
+        <v>4.872340222279615e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.017794926736035e-05</v>
+        <v>2.017794926736033e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.965482408820732e-05</v>
+        <v>2.965482408820728e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.715003754979446e-05</v>
+        <v>2.715003754979445e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.435972878230862e-05</v>
+        <v>5.435972878230867e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.349604396880218e-05</v>
+        <v>5.349604396880197e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.547674244200959e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.965569973269306e-05</v>
+        <v>2.96556997326931e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.332995333710122e-05</v>
+        <v>3.332995333710118e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.127067692449948e-05</v>
+        <v>2.127067692449949e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.729472889138842e-05</v>
+        <v>3.72947288913885e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.60613189656485e-05</v>
+        <v>2.606131896564848e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.712595383899448e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.153102549992055e-05</v>
+        <v>4.153102549992054e-05</v>
       </c>
       <c r="K8" t="n">
         <v>2.659408901727242e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001299259338735837</v>
+        <v>0.000129925933873583</v>
       </c>
       <c r="M8" t="n">
-        <v>6.358380724029076e-05</v>
+        <v>6.358380724029078e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.996175337042856e-05</v>
+        <v>1.996175337042855e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.438865859672333e-05</v>
+        <v>2.438865859672332e-05</v>
       </c>
       <c r="P8" t="n">
         <v>4.484089359862949e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.126392622743499e-05</v>
+        <v>2.126392622743498e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.675315618908955e-05</v>
+        <v>2.675315618908958e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>4.345907619026352e-05</v>
+        <v>4.345907619026351e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.980786764406322e-05</v>
+        <v>2.980786764406323e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>8.519694808319072e-05</v>
+        <v>8.519694808319079e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>3.023933960401459e-05</v>
+        <v>3.02393396040146e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.527823765621971e-05</v>
+        <v>3.527823765621973e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.565344777701652e-05</v>
+        <v>5.565344777701644e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.340341228339959e-05</v>
+        <v>4.340341228339962e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.725485462150396e-05</v>
+        <v>3.725485462150385e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.265814776490753e-05</v>
+        <v>4.265814776490751e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.797784201817089e-05</v>
+        <v>7.797784201817093e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8082,22 +8082,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.053232641534724e-05</v>
+        <v>6.053232641534696e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.007433339292715e-05</v>
+        <v>3.007433339292712e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.425329068361063e-05</v>
+        <v>3.425329068361066e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.083254237361036e-05</v>
+        <v>4.083254237361028e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.01466425801912e-05</v>
+        <v>2.014664258019119e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.028243019180526e-05</v>
+        <v>4.02824301918053e-05</v>
       </c>
       <c r="H9" t="n">
         <v>3.065890991656603e-05</v>
@@ -8106,61 +8106,61 @@
         <v>3.1723544789912e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.612861645083805e-05</v>
+        <v>4.6128616450838e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.119167996818997e-05</v>
+        <v>3.119167996818995e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001345235248245014</v>
+        <v>0.0001345235248245002</v>
       </c>
       <c r="M9" t="n">
-        <v>6.818139819120698e-05</v>
+        <v>6.818139819120694e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.057763620610109e-05</v>
+        <v>3.057763620610108e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.511541402846625e-05</v>
+        <v>3.511541402846623e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.635685836803609e-05</v>
+        <v>5.6356858368036e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.515115291868018e-05</v>
+        <v>3.515115291868015e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.135074714000711e-05</v>
+        <v>3.135074714000709e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.805666714118106e-05</v>
+        <v>4.805666714118098e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.440545859498075e-05</v>
+        <v>3.440545859498072e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>9.358519138535015e-05</v>
+        <v>9.358519138535021e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.310537029013135e-05</v>
+        <v>4.310537029013136e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.987430278576953e-05</v>
+        <v>3.987430278576949e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>6.882910338882696e-05</v>
+        <v>6.882910338882678e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.028365043339099e-05</v>
+        <v>4.028365043339097e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.654992008507235e-05</v>
+        <v>4.654992008507224e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.725573871582506e-05</v>
+        <v>4.725573871582504e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.446542994833925e-05</v>
+        <v>7.446542994833927e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.8427043777599e-06</v>
+        <v>4.842704377759936e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.912277669005253e-06</v>
+        <v>4.912277669005241e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.975177078623361e-06</v>
+        <v>4.975177078623395e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.896081145393992e-06</v>
+        <v>4.896081145394003e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.841090943647841e-06</v>
+        <v>4.841090943647868e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.514962461396123e-06</v>
+        <v>5.514962461396201e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.832669447824778e-06</v>
+        <v>4.832669447824821e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.953390821139653e-06</v>
+        <v>4.953390821139675e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.303025755709788e-06</v>
+        <v>5.303025755709881e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.351570426548553e-06</v>
+        <v>5.351570426548593e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.664962346427346e-06</v>
+        <v>7.664962346427364e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.330353347106848e-06</v>
+        <v>5.330353347106858e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.83266916233749e-06</v>
+        <v>4.832669162337377e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.609502258958867e-06</v>
+        <v>6.609502258958914e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.727625306807665e-06</v>
+        <v>5.727625306807731e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.843936342453093e-06</v>
+        <v>4.843936342453143e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.848095301510261e-06</v>
+        <v>4.848095301510329e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.217143561626468e-06</v>
+        <v>5.217143561626502e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.839255636223673e-06</v>
+        <v>4.839255636223717e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.445169664897805e-06</v>
+        <v>7.445169664898009e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.91577377015367e-06</v>
+        <v>4.915773770153701e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.069682701980483e-06</v>
+        <v>7.069682701980601e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.001563227512745e-06</v>
+        <v>7.001563227512788e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.43021904273321e-06</v>
+        <v>6.430219042733225e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.835090745467739e-06</v>
+        <v>5.835090745467784e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.385942272671291e-06</v>
+        <v>5.385942272671331e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.369001833408573e-06</v>
+        <v>7.36900183340857e-06</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.728304248351136e-06</v>
+        <v>4.743201301031038e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.805446031592782e-06</v>
+        <v>4.818563998936208e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.676914678983788e-06</v>
+        <v>5.725587060963224e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.102718149573087e-06</v>
+        <v>5.130046499618268e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.719519855453087e-06</v>
+        <v>4.734183735657508e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.494906147111789e-06</v>
+        <v>9.677984147402724e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.65789411308473e-06</v>
+        <v>4.670420846123081e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.521928876435357e-06</v>
+        <v>5.565138083404488e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.000440538345772e-06</v>
+        <v>8.131142568539313e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.349143107256611e-06</v>
+        <v>8.493200938193569e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.476615402910027e-05</v>
+        <v>2.549120242042571e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>8.225096466743236e-06</v>
+        <v>8.365222728262741e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.656661659756163e-06</v>
+        <v>4.669119508689496e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.860323839317739e-06</v>
+        <v>7.885025731019644e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.101486399676352e-05</v>
+        <v>1.125056118746341e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.739875977959255e-06</v>
+        <v>4.755198032520023e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.768133223097955e-06</v>
+        <v>4.784574835636768e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.385192083445136e-06</v>
+        <v>7.494025751987769e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.705160927884415e-06</v>
+        <v>4.719322647203532e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.358974932024384e-05</v>
+        <v>1.381499726644309e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.249878544331299e-06</v>
+        <v>5.283095433537304e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.839940073264115e-06</v>
+        <v>9.920843704603203e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.013833614601477e-05</v>
+        <v>2.070105077816506e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.605497032687415e-05</v>
+        <v>1.647069338072279e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.407457149169126e-06</v>
+        <v>7.470193045293133e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.606484295876289e-06</v>
+        <v>8.758479327085838e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.264389043041272e-05</v>
+        <v>2.329279462722254e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8502,37 +8502,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.70196877269091e-06</v>
+        <v>4.701968772690909e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.617163515822678e-06</v>
+        <v>4.617163515822675e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>6.19830886939693e-06</v>
+        <v>6.198308869396925e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.304883917644217e-06</v>
+        <v>5.304883917644214e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.68374429217884e-06</v>
+        <v>4.683744292178842e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.229543308135938e-05</v>
+        <v>1.229543308135934e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.588619622777962e-06</v>
+        <v>4.588619622777961e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.952223068944876e-06</v>
+        <v>5.952223068944872e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.883627842257318e-06</v>
+        <v>9.883627842257288e-06</v>
       </c>
       <c r="K4" t="n">
         <v>1.044984488370655e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.658067083159868e-05</v>
+        <v>3.658067083159873e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.024367512358103e-05</v>
@@ -8541,7 +8541,7 @@
         <v>4.588616398067766e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>5.145830895481372e-06</v>
+        <v>5.145830895481375e-06</v>
       </c>
       <c r="P4" t="n">
         <v>1.469755775002497e-05</v>
@@ -8550,31 +8550,31 @@
         <v>4.715884380632391e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.762861736398816e-06</v>
+        <v>4.762861736398814e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>8.93143160499854e-06</v>
+        <v>8.931431604998533e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>4.663013650539874e-06</v>
+        <v>4.663013650539886e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.409141419452726e-05</v>
+        <v>1.409141419452727e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.411075919610817e-06</v>
+        <v>5.411075919610818e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>7.657188341099242e-06</v>
+        <v>7.657188341099235e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9087272604786e-05</v>
+        <v>2.908727260478606e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.257238000741873e-05</v>
+        <v>2.257238000741871e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.860354856580958e-06</v>
+        <v>6.860354856580954e-06</v>
       </c>
       <c r="AA4" t="n">
         <v>1.083809069749334e-05</v>
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.479768747098296e-05</v>
+        <v>1.479768747098292e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.535822563757624e-05</v>
+        <v>1.535822563757623e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.289334927380764e-05</v>
+        <v>4.289334927380761e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.207269492028349e-05</v>
+        <v>2.20726949202835e-05</v>
       </c>
       <c r="F5" t="n">
         <v>1.589050820187161e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001328607383191244</v>
+        <v>0.0001328607383191234</v>
       </c>
       <c r="H5" t="n">
-        <v>1.341979634738144e-05</v>
+        <v>1.341979634738142e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.880199907033424e-05</v>
+        <v>3.880199907033418e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>9.990154211598167e-05</v>
+        <v>9.990154211598121e-05</v>
       </c>
       <c r="K5" t="n">
         <v>0.0001107768053639508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005243431562669769</v>
+        <v>0.0005243431562669781</v>
       </c>
       <c r="M5" t="n">
         <v>0.0001118910769942771</v>
       </c>
       <c r="N5" t="n">
-        <v>1.278210748576922e-05</v>
+        <v>1.278210748576918e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.265125542979488e-05</v>
+        <v>2.265125542979491e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001764721305317583</v>
+        <v>0.0001764721305317581</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.648402491012816e-05</v>
+        <v>1.648402491012815e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.657619205182618e-05</v>
+        <v>1.657619205182617e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.156853107612256e-05</v>
+        <v>8.156853107612259e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.487076150636256e-05</v>
+        <v>1.487076150636277e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001685803628689422</v>
+        <v>0.0001685803628689428</v>
       </c>
       <c r="V5" t="n">
-        <v>2.931771719671501e-05</v>
+        <v>2.931771719671496e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>6.71733708485559e-05</v>
+        <v>6.717337084855575e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004472055152002935</v>
+        <v>0.0004472055152002938</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003301330461131223</v>
+        <v>0.0003301330461131217</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.917811307977234e-05</v>
+        <v>4.917811307977239e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001238765772122177</v>
+        <v>0.0001238765772122175</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005515902484519695</v>
+        <v>0.0005515902484519707</v>
       </c>
     </row>
     <row r="6">
@@ -8678,43 +8678,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.418013698302502e-06</v>
+        <v>7.418013698302514e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>7.333208441434303e-06</v>
+        <v>7.333208441434281e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>8.914353795008555e-06</v>
+        <v>8.914353795008535e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7921780821812e-06</v>
+        <v>5.792178082181193e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.171038456715819e-06</v>
+        <v>5.171038456715825e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.278272724589638e-05</v>
+        <v>1.278272724589633e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.075913787314942e-06</v>
+        <v>5.075913787314949e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>8.668267994556504e-06</v>
+        <v>8.668267994556472e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.259967276786893e-05</v>
+        <v>1.25996727678689e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.093713904824353e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.929671575721027e-05</v>
+        <v>3.929671575721031e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.073096928811801e-05</v>
+        <v>1.073096928811802e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.092852108166613e-06</v>
+        <v>5.092852108166606e-06</v>
       </c>
       <c r="O6" t="n">
         <v>7.86369317156664e-06</v>
@@ -8723,40 +8723,40 @@
         <v>1.514327623623388e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.203178545169364e-06</v>
+        <v>5.203178545169363e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>7.478906662010436e-06</v>
+        <v>7.478906662010417e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>9.418725769535513e-06</v>
+        <v>9.41872576953552e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>5.150307815076861e-06</v>
+        <v>5.150307815076854e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.686875631911105e-05</v>
+        <v>1.686875631911106e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.898370084147788e-06</v>
+        <v>5.898370084147782e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>8.208359855521095e-06</v>
+        <v>8.208359855520917e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>3.180331753039764e-05</v>
+        <v>3.180331753039765e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.316985515821057e-05</v>
+        <v>2.316985515821055e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>9.576399782192569e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.132538486203032e-05</v>
+        <v>1.132538486203031e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.353121117165604e-05</v>
+        <v>3.353121117165603e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.436236419353763e-06</v>
+        <v>7.436236419353753e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.351431162485519e-06</v>
+        <v>7.351431162485524e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.932576516059774e-06</v>
+        <v>8.932576516059771e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.039151564307061e-06</v>
+        <v>8.03915156430706e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.418011938841704e-06</v>
+        <v>7.418011938841691e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.502970072802223e-05</v>
+        <v>1.502970072802216e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>7.32288726944082e-06</v>
+        <v>7.322887269440814e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.686490715607717e-06</v>
+        <v>8.686490715607713e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.261789548892016e-05</v>
+        <v>1.261789548892013e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.31841125303694e-05</v>
+        <v>1.318411253036939e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.931493847826146e-05</v>
+        <v>3.931493847826154e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.297794277024387e-05</v>
+        <v>1.297794277024386e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>7.322884044730609e-06</v>
+        <v>7.322884044730608e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>7.878671846599363e-06</v>
+        <v>7.878671846599367e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.743039870114296e-05</v>
+        <v>1.743039870114295e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.450152027295239e-06</v>
+        <v>7.45015202729523e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>7.497129383061656e-06</v>
+        <v>7.497129383061657e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.166569925166138e-05</v>
+        <v>1.166569925166137e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>7.397281297202725e-06</v>
+        <v>7.397281297202727e-06</v>
       </c>
       <c r="U7" t="n">
         <v>1.688668969173692e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.145343566273667e-06</v>
+        <v>8.145343566273656e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.039145598776209e-05</v>
+        <v>1.039145598776208e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>3.182154025144887e-05</v>
+        <v>3.182154025144886e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.536794485305376e-05</v>
+        <v>2.536794485305372e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.594622503243819e-06</v>
+        <v>9.5946225032438e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.357235834415619e-05</v>
+        <v>1.357235834415617e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.562500323361159e-05</v>
+        <v>3.562500323361158e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.401690282601425e-05</v>
+        <v>1.401690282601424e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.020029200033555e-05</v>
+        <v>2.020029200033549e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.178143735390984e-05</v>
+        <v>2.178143735390979e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7550383767714e-05</v>
+        <v>1.755038376771397e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.497518977996503e-05</v>
+        <v>1.4975189779965e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.917831251467611e-05</v>
+        <v>2.917831251467591e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.017174810729084e-05</v>
+        <v>2.017174810729079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.153535155345776e-05</v>
+        <v>2.15353515534577e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.546675632677019e-05</v>
+        <v>2.546675632677015e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.603297336821944e-05</v>
+        <v>2.60329733682194e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.216379931611155e-05</v>
+        <v>5.216379931611153e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.582680360809342e-05</v>
+        <v>2.582680360809339e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.531284555235314e-05</v>
+        <v>1.531284555235312e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.720532777486738e-05</v>
+        <v>1.720532777486735e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.642974824539574e-05</v>
+        <v>2.642974824539572e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.279897516367656e-05</v>
+        <v>1.279897516367655e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.03459902209117e-05</v>
+        <v>2.034599022091163e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.451456008951143e-05</v>
+        <v>2.451456008951137e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.024614213505276e-05</v>
+        <v>2.024614213505271e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.667729925294559e-05</v>
+        <v>2.667729925294556e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.928198452935018e-05</v>
+        <v>1.928198452935017e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.324154870549235e-05</v>
+        <v>2.324154870549231e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>3.774485586257935e-05</v>
+        <v>3.77448558625794e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.445063658700174e-05</v>
+        <v>4.445063658700171e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.605885398026001e-05</v>
+        <v>1.605885398025999e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.642121918200621e-05</v>
+        <v>2.642121918200618e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.502151729277528e-05</v>
+        <v>5.502151729277522e-05</v>
       </c>
     </row>
     <row r="9">
@@ -8948,79 +8948,79 @@
         <v>2.101234878927653e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.259349414285074e-05</v>
+        <v>2.259349414285076e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.085279932891734e-05</v>
+        <v>2.085279932891736e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.261609267962171e-05</v>
+        <v>1.261609267962172e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.869061833543722e-05</v>
+        <v>2.869061833543708e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.098380489623181e-05</v>
+        <v>2.098380489623183e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.234740834239878e-05</v>
+        <v>2.234740834239874e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.627881311571113e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.684503015716039e-05</v>
+        <v>2.684503015716038e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.297585610505244e-05</v>
+        <v>5.297585610505257e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.66388603970349e-05</v>
+        <v>2.663886039703488e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.098380167152159e-05</v>
+        <v>2.098380167152161e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.27576066126684e-05</v>
+        <v>2.275760661266846e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>3.257392101974363e-05</v>
+        <v>3.257392101974368e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.111106963471013e-05</v>
+        <v>2.111106963471014e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.115804700985268e-05</v>
+        <v>2.115804700985267e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>2.532661687845241e-05</v>
+        <v>2.532661687845242e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.105819892399369e-05</v>
+        <v>2.105819892399372e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.054789666695328e-05</v>
+        <v>3.054789666695329e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>2.604260469808854e-05</v>
+        <v>2.604260469808858e-05</v>
       </c>
       <c r="W9" t="n">
         <v>2.405237361455307e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.548245787823986e-05</v>
+        <v>4.548245787823989e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.902886247984476e-05</v>
+        <v>3.902886247984472e-05</v>
       </c>
       <c r="Z9" t="n">
         <v>2.104220648389221e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.72332759709472e-05</v>
+        <v>2.723327597094716e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.928592086040257e-05</v>
+        <v>4.928592086040261e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.545075985250601e-05</v>
+        <v>1.545075985250606e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.260455542811652e-06</v>
+        <v>8.260455542811642e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.697079323604561e-06</v>
+        <v>8.697079323604531e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.011165605299446e-05</v>
+        <v>1.011165605299444e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.792883217704961e-06</v>
+        <v>8.792883217704996e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.22349623979922e-06</v>
+        <v>9.223496239799284e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.904851743746393e-06</v>
+        <v>8.904851743746437e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>8.795208261878593e-06</v>
+        <v>8.79520826187862e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02644067104415e-05</v>
+        <v>1.026440671044154e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.639223596869627e-06</v>
+        <v>8.639223596869603e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.885441541505285e-05</v>
+        <v>1.885441541505286e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.201718680066611e-05</v>
+        <v>1.20171868006661e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>8.391274243411408e-06</v>
+        <v>8.391274243411354e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.242363790109857e-05</v>
+        <v>1.242363790109855e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.072609403915441e-05</v>
+        <v>1.072609403915445e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.459591843707232e-06</v>
+        <v>9.459591843707244e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>8.692041368341389e-06</v>
+        <v>8.692041368341564e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.130450569764156e-05</v>
+        <v>1.130450569764145e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.126208465300979e-06</v>
+        <v>9.126208465300918e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.723473814559983e-05</v>
+        <v>1.723473814559985e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>9.7845760624135e-06</v>
+        <v>9.784576062413567e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.214390480123657e-05</v>
+        <v>1.214390480123653e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.162965124587634e-05</v>
+        <v>1.162965124587639e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.341346238472511e-06</v>
+        <v>9.341346238472591e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.404767479857169e-05</v>
+        <v>1.40476747985716e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.069705865463796e-05</v>
+        <v>1.069705865463806e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.296663615000162e-05</v>
+        <v>1.296663615000161e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001750660171674797</v>
+        <v>6.430856389596688e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.163404180009461e-05</v>
+        <v>9.097466421401017e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.972780752851879e-05</v>
+        <v>1.198991352238044e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>5.168268953635215e-05</v>
+        <v>2.251059138567302e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.20229868937904e-05</v>
+        <v>1.282227161395541e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.170728065941043e-05</v>
+        <v>1.597344424401384e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.467747268333024e-05</v>
+        <v>1.378912434304046e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.204182983715231e-05</v>
+        <v>1.281430510804168e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.589224684405192e-05</v>
+        <v>2.431970183919486e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.836431974392614e-05</v>
+        <v>1.150550300335831e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000254896231768728</v>
+        <v>9.299487758037787e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>9.755745053797883e-05</v>
+        <v>3.92616019366471e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.257106516119055e-05</v>
+        <v>9.475767640599356e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>3.354763565947237e-05</v>
+        <v>1.864202307292147e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>6.621160589037394e-05</v>
+        <v>2.769211825886738e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.746234823817879e-05</v>
+        <v>1.812805698589278e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.965035272990648e-05</v>
+        <v>1.199029101749618e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>7.980530286131328e-05</v>
+        <v>3.235362481101732e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.975901536390824e-05</v>
+        <v>1.550522886037286e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001615094520180485</v>
+        <v>6.212551152160093e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.465819572293607e-05</v>
+        <v>2.030568742213008e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.125921505047572e-05</v>
+        <v>2.109499097911753e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>8.811862006347395e-05</v>
+        <v>3.578078470114532e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.462772248601817e-05</v>
+        <v>1.708004786457389e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.509801316398523e-05</v>
+        <v>3.589204927732371e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.608176140179328e-05</v>
+        <v>2.798399836662235e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001189537273250633</v>
+        <v>4.732966405964865e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001539134706216901</v>
+        <v>0.001539134706216902</v>
       </c>
       <c r="C4" t="n">
-        <v>4.928484352082545e-05</v>
+        <v>4.928484352082541e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001317805406342751</v>
+        <v>0.000131780540634275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004419268903646056</v>
+        <v>0.0004419268903646065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001586304820864976</v>
+        <v>0.0001586304820864974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002343228214437712</v>
+        <v>0.0002343228214437709</v>
       </c>
       <c r="H4" t="n">
         <v>0.0001895953726777676</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001571462077651561</v>
+        <v>0.000157146207765156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004728707262220472</v>
+        <v>0.0004728707262220477</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001169520217328696</v>
+        <v>0.0001169520217328693</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00242689587565329</v>
+        <v>0.002426895875653287</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0009418729076474258</v>
+        <v>0.0009418729076474265</v>
       </c>
       <c r="N4" t="n">
-        <v>5.692976481231337e-05</v>
+        <v>5.692976481231339e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002119011005815976</v>
+        <v>0.0002119011005815974</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005536733464769664</v>
+        <v>0.0005536733464769666</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003083942466006406</v>
+        <v>0.0003083942466006411</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001337419550595695</v>
+        <v>0.0001337419550595696</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0006878154528706622</v>
+        <v>0.0006878154528706631</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002358430403797008</v>
+        <v>0.0002358430403797005</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001460527881021265</v>
+        <v>0.001460527881021264</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003499404145348517</v>
+        <v>0.0003499404145348511</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003128973440434369</v>
+        <v>0.0003128973440434372</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008250748064983048</v>
+        <v>0.0008250748064983037</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002736425913577803</v>
+        <v>0.0002736425913577807</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007116724871154414</v>
+        <v>0.0007116724871154423</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005870561306643307</v>
+        <v>0.0005870561306643299</v>
       </c>
       <c r="AB4" t="n">
         <v>0.001203725295114695</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001028250551821385</v>
+        <v>0.0001028250551821386</v>
       </c>
       <c r="C5" t="n">
-        <v>3.201441949958769e-05</v>
+        <v>3.201441949958777e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.588297190272467e-05</v>
+        <v>3.58829719027247e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.688594488720089e-05</v>
+        <v>4.688594488720094e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.907693768666769e-05</v>
+        <v>2.907693768666777e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.376660029437743e-05</v>
+        <v>4.376660029437745e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.822985696826227e-05</v>
+        <v>3.822985696826231e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.699138340207169e-05</v>
+        <v>3.699138340207176e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.357012360447421e-05</v>
+        <v>5.357012360447416e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.522946485430444e-05</v>
+        <v>3.522946485430432e-05</v>
       </c>
       <c r="L5" t="n">
         <v>0.000150614755661087</v>
       </c>
       <c r="M5" t="n">
-        <v>7.340270128125202e-05</v>
+        <v>7.340270128125201e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.692976481231337e-05</v>
+        <v>2.518571966912064e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.590216794065467e-05</v>
+        <v>3.590216794065466e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>5.306112681304448e-05</v>
+        <v>5.306112681304468e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.331577761624339e-05</v>
+        <v>3.331577761624349e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.582606588045333e-05</v>
+        <v>3.582606588045331e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>6.533505227286535e-05</v>
+        <v>6.533505227286538e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.073018296734399e-05</v>
+        <v>4.073018296734392e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>9.93644684664528e-05</v>
+        <v>9.9364468466453e-05</v>
       </c>
       <c r="V5" t="n">
         <v>4.550496238780428e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.512781794812539e-05</v>
+        <v>4.512781794812545e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.868397881410257e-05</v>
+        <v>5.868397881410252e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.244851717812048e-05</v>
+        <v>5.244851717812052e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.718065937898442e-05</v>
+        <v>5.718065937898455e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.847365848269412e-05</v>
+        <v>5.847365848269409e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.358442096462708e-05</v>
+        <v>9.358442096462716e-05</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000115327741974797</v>
+        <v>0.0001153277419747968</v>
       </c>
       <c r="C6" t="n">
-        <v>4.269788256304755e-05</v>
+        <v>4.269788256304757e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.656643496618452e-05</v>
+        <v>4.656643496618462e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>6.080807941682298e-05</v>
+        <v>6.080807941682287e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.03022754850167e-05</v>
+        <v>3.030227548501664e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>5.251255812790964e-05</v>
+        <v>5.251255812790967e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.891332003172212e-05</v>
+        <v>4.891332003172209e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.767484646553159e-05</v>
+        <v>4.767484646553153e-05</v>
       </c>
       <c r="J6" t="n">
         <v>6.425358666793406e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.591292791776432e-05</v>
+        <v>4.591292791776425e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001612982187245471</v>
+        <v>0.0001612982187245469</v>
       </c>
       <c r="M6" t="n">
-        <v>8.408616434471188e-05</v>
+        <v>8.40861643447118e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.692976481231337e-05</v>
+        <v>4.311222590811593e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>5.43318752769648e-05</v>
+        <v>5.43318752769647e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>7.252106798482253e-05</v>
+        <v>7.252106798482252e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.51793665833944e-05</v>
+        <v>5.517936658339437e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.650952894391321e-05</v>
+        <v>4.650952894391327e-05</v>
       </c>
       <c r="S6" t="n">
         <v>7.601851533632525e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.141364603080385e-05</v>
+        <v>5.141364603080389e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001146097759782202</v>
+        <v>0.0001146097759782203</v>
       </c>
       <c r="V6" t="n">
-        <v>6.74268468437121e-05</v>
+        <v>6.742684684371203e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>5.580944467821362e-05</v>
+        <v>5.580944467821358e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>7.969118387797907e-05</v>
+        <v>7.969118387797901e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.384372614704155e-05</v>
+        <v>5.384372614704173e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.284485747442173e-05</v>
+        <v>7.284485747442183e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.915712154615398e-05</v>
+        <v>6.915712154615395e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.450745645859688e-05</v>
+        <v>9.450745645859689e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.401866047558418e-06</v>
+        <v>4.401866047558403e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.479184186631662e-06</v>
+        <v>4.479184186631663e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.459078446374704e-06</v>
+        <v>4.459078446374689e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.413237643069726e-06</v>
+        <v>4.413237643069708e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.484811388084553e-06</v>
+        <v>4.484811388084536e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.610618150289816e-06</v>
+        <v>4.6106181502898e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.399013038086922e-06</v>
+        <v>4.399013038086912e-06</v>
       </c>
       <c r="I2" t="n">
         <v>4.487862579982344e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.583198558084395e-06</v>
+        <v>4.583198558084338e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.965337329781423e-06</v>
+        <v>4.965337329781418e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.759783327412089e-06</v>
+        <v>4.759783327412081e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.589574262298084e-06</v>
+        <v>4.58957426229808e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.412062186607575e-06</v>
+        <v>4.412062186607544e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.048625973995045e-06</v>
+        <v>6.048625973995022e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.44218868613439e-06</v>
+        <v>4.442188686134296e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.471873516134053e-06</v>
+        <v>4.471873516134035e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.41851043811403e-06</v>
+        <v>4.418510438114026e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.772425812853817e-06</v>
+        <v>4.772425812853804e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.433939091044565e-06</v>
+        <v>4.433939091044549e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.861202449010436e-06</v>
+        <v>6.861202449010401e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.523240934066836e-06</v>
+        <v>4.523240934066812e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.444106434108603e-06</v>
+        <v>6.444106434108563e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>6.422293111537057e-06</v>
+        <v>6.422293111537056e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.645729194441415e-06</v>
+        <v>5.645729194441393e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.192618228323532e-06</v>
+        <v>5.192618228323522e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.606733076987551e-06</v>
+        <v>4.606733076987533e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.610797978038774e-06</v>
+        <v>4.610797978038771e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.376627496087461e-06</v>
+        <v>4.829156443664579e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.291392386241857e-06</v>
+        <v>4.876297008934682e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.722705115662852e-06</v>
+        <v>5.306200459792603e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.21497697394607e-06</v>
+        <v>4.533156090615795e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.333117322228263e-06</v>
+        <v>5.5128569359988e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.018387577779329e-05</v>
+        <v>6.44075123071968e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.324857890406205e-06</v>
+        <v>4.822781985218186e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.398292485897992e-06</v>
+        <v>5.538123985969372e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.581683902571531e-06</v>
+        <v>6.255798648525551e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.850008974771569e-05</v>
+        <v>9.228058464932225e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>1.366042440853938e-05</v>
+        <v>7.611784661100751e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>9.865838759175319e-06</v>
+        <v>6.386772313515142e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.619864785950981e-06</v>
+        <v>4.90786192548977e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.684838924408991e-06</v>
+        <v>6.682955045614307e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>6.302402946837734e-06</v>
+        <v>5.141812482976451e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.014228909569992e-06</v>
+        <v>5.391084537960776e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.778886993110092e-06</v>
+        <v>4.974079195446881e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.392673881360905e-05</v>
+        <v>7.682934406484913e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>6.135726381072581e-06</v>
+        <v>5.095136808850274e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.348371925664071e-05</v>
+        <v>1.202454205926217e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>8.176702033575268e-06</v>
+        <v>5.77602177603957e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.787844097323064e-06</v>
+        <v>7.612530281542069e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>5.246085333616675e-05</v>
+        <v>2.084886087961053e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.427333389097779e-05</v>
+        <v>1.483191778934764e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.892981758408508e-06</v>
+        <v>5.848428995037135e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.013616909276567e-05</v>
+        <v>6.468399013170413e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02515259406855e-05</v>
+        <v>6.556896439532812e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.451205819276197e-05</v>
+        <v>1.451205819276191e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.460304460634864e-05</v>
+        <v>1.460304460634863e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.724888174425884e-05</v>
+        <v>2.724888174425885e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.450011349217778e-05</v>
+        <v>1.450011349217776e-05</v>
       </c>
       <c r="F4" t="n">
         <v>3.243123882454705e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.235635749681583e-05</v>
+        <v>5.235635749681577e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.503972276777812e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.310880111508137e-05</v>
+        <v>3.31088011150813e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9146276042378e-05</v>
+        <v>4.914627604237795e-05</v>
       </c>
       <c r="K4" t="n">
         <v>0.000119762495691541</v>
       </c>
       <c r="L4" t="n">
-        <v>8.066010983268894e-05</v>
+        <v>8.066010983268895e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.477790014077321e-05</v>
+        <v>5.47779001407732e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.634684747698625e-05</v>
+        <v>1.634684747698624e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>2.030376700390112e-05</v>
+        <v>2.030376700390111e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.191900942969318e-05</v>
+        <v>2.191900942969316e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.862659788855834e-05</v>
+        <v>2.86265978885583e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.861941088190486e-05</v>
+        <v>1.861941088190483e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>8.118805785098456e-05</v>
+        <v>8.118805785098447e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.154667492740122e-05</v>
+        <v>2.154667492740121e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001413690673127236</v>
+        <v>0.0001413690673127233</v>
       </c>
       <c r="V4" t="n">
-        <v>3.707894167193596e-05</v>
+        <v>3.707894167193592e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>3.550130358452597e-05</v>
+        <v>3.550130358452594e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004086679167134035</v>
+        <v>0.0004086679167134041</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002668710900339978</v>
+        <v>0.0002668710900339977</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.099261384835339e-05</v>
+        <v>2.09926138483534e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.551485861526015e-05</v>
+        <v>5.551485861526007e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.029175054798798e-05</v>
+        <v>6.029175054798795e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.341878432520254e-05</v>
+        <v>1.341878432520251e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.932956822222483e-05</v>
+        <v>1.932956822222482e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.006408831853533e-05</v>
+        <v>2.006408831853532e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.635197093587822e-05</v>
+        <v>1.63519709358782e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.529027410417641e-05</v>
+        <v>1.529027410417639e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.301974390985343e-05</v>
+        <v>2.301974390985342e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.938562190047187e-05</v>
+        <v>1.938562190047185e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.038921834898921e-05</v>
+        <v>2.038921834898916e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.145068363932844e-05</v>
+        <v>2.14506836393284e-05</v>
       </c>
       <c r="K5" t="n">
         <v>2.578251529720653e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.346068828093222e-05</v>
+        <v>2.346068828093224e-05</v>
       </c>
       <c r="M5" t="n">
         <v>2.157990516743209e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.634684747698625e-05</v>
+        <v>1.488274010144952e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.638512779824454e-05</v>
+        <v>1.638512779824452e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.618771634888122e-05</v>
+        <v>1.618771634888118e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.303059796260913e-05</v>
+        <v>1.303059796260911e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.960585400302521e-05</v>
+        <v>1.96058540030252e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>2.360349096982698e-05</v>
+        <v>2.360349096982696e-05</v>
       </c>
       <c r="T5" t="n">
         <v>1.97801277354065e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.448777423508802e-05</v>
+        <v>2.4487774235088e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.905423746291555e-05</v>
+        <v>1.905423746291548e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.062272917380339e-05</v>
+        <v>2.062272917380337e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>3.561131063205951e-05</v>
+        <v>3.56113106320595e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.943952833263073e-05</v>
+        <v>3.943952833263076e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.367843526075532e-05</v>
+        <v>1.367843526075527e-05</v>
       </c>
       <c r="AA5" t="n">
         <v>2.173191529579328e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.80358774731918e-05</v>
+        <v>2.803587747319175e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.544581393939294e-05</v>
+        <v>1.544581393939292e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.852923318494661e-05</v>
+        <v>1.852923318494656e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.926375328125709e-05</v>
+        <v>1.926375328125705e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.801394523873253e-05</v>
@@ -1549,70 +1549,70 @@
         <v>1.224278673267825e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.097546408606479e-05</v>
+        <v>2.097546408606477e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.858528686319361e-05</v>
+        <v>1.85852868631936e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.958888331171093e-05</v>
+        <v>1.958888331171091e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.065034860205013e-05</v>
+        <v>2.065034860205014e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.498218025992827e-05</v>
+        <v>2.498218025992825e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.266035324365401e-05</v>
+        <v>2.266035324365398e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.077957013015466e-05</v>
+        <v>2.077957013015463e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.634684747698625e-05</v>
+        <v>1.873268299863918e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.000823101263653e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.035266829032438e-05</v>
+        <v>2.035266829032436e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.940827961759045e-05</v>
+        <v>1.940827961759042e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.880551896574695e-05</v>
+        <v>1.880551896574693e-05</v>
       </c>
       <c r="S6" t="n">
         <v>2.280315593254869e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.897979269812828e-05</v>
+        <v>1.897979269812824e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>2.661144440741862e-05</v>
+        <v>2.661144440741858e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.354913386184001e-05</v>
+        <v>2.354913386183998e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.982121514854514e-05</v>
+        <v>1.982121514854511e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.143916604763104e-05</v>
+        <v>4.143916604763099e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.266751936698438e-05</v>
+        <v>3.266751936698437e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.707634714917022e-05</v>
+        <v>1.707634714917019e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.093158025851504e-05</v>
+        <v>2.0931580258515e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.096901884110172e-05</v>
+        <v>2.096901884110169e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.364490944465744e-05</v>
+        <v>1.364490944465745e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.5061161839434e-06</v>
+        <v>7.506116183943424e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.57979273197448e-06</v>
+        <v>8.579792731974472e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.119044746848671e-06</v>
+        <v>9.119044746848667e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.117685594423576e-06</v>
+        <v>8.117685594423556e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.530126040192692e-06</v>
+        <v>8.530126040192663e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.64713248610341e-06</v>
+        <v>7.647132486103432e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.904014330001945e-06</v>
+        <v>7.904014330001935e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.416062225129347e-06</v>
+        <v>9.416062225129322e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.04505652903339e-06</v>
+        <v>8.045056529033372e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.833606125008907e-05</v>
+        <v>1.833606125008912e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.113592140313971e-05</v>
+        <v>1.113592140313973e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>7.873391584069872e-06</v>
+        <v>7.87339158406986e-06</v>
       </c>
       <c r="O2" t="n">
         <v>1.155013881611064e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.073899501345032e-05</v>
+        <v>1.073899501345028e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.71239944561388e-06</v>
+        <v>8.712399445613873e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>7.669623994366e-06</v>
+        <v>7.669623994365982e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.072453980538773e-05</v>
+        <v>1.072453980538776e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>8.725552650705779e-06</v>
+        <v>8.725552650705759e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.617126326617266e-05</v>
+        <v>1.617126326617267e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>8.462376244323647e-06</v>
+        <v>8.462376244323631e-06</v>
       </c>
       <c r="W2" t="n">
         <v>1.081411541635467e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.127124018446692e-05</v>
+        <v>1.127124018446693e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.503997410502429e-06</v>
+        <v>8.503997410502414e-06</v>
       </c>
       <c r="Z2" t="n">
         <v>1.238628228262277e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.410688330332563e-06</v>
+        <v>9.41068833033255e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.215634477565386e-05</v>
+        <v>1.215634477565388e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001484965635055494</v>
+        <v>5.48022992340382e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.88967845815809e-06</v>
+        <v>7.738987938634564e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.223304055280122e-05</v>
+        <v>1.593867298179124e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.389288411157553e-05</v>
+        <v>1.944042327737468e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.149833937649382e-05</v>
+        <v>1.218216889293542e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.076299870343931e-05</v>
+        <v>1.520078444568126e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.047691597780885e-05</v>
+        <v>8.350201011777315e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.647015430061381e-05</v>
+        <v>1.043745845161433e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.139885175095535e-05</v>
+        <v>2.234726031584392e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.972376589540973e-05</v>
+        <v>1.148835837067836e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002580071691097276</v>
+        <v>9.364042063543748e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>9.21239573522129e-05</v>
+        <v>3.688085880149459e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.57090469099724e-05</v>
+        <v>1.013836163739027e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.247914447795079e-05</v>
+        <v>1.770842354272168e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>8.150946311947256e-05</v>
+        <v>3.244408740863188e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52618766017867e-05</v>
+        <v>1.692058432000238e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.099543278612424e-05</v>
+        <v>8.52240001610039e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>8.147061787921218e-05</v>
+        <v>3.240884308697423e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>3.564946056185987e-05</v>
+        <v>1.712597486862251e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001572269286486983</v>
+        <v>6.003460741278651e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.920745339030445e-05</v>
+        <v>1.457351543094914e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>3.147564194040379e-05</v>
+        <v>1.711558128494026e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>9.497931286323525e-05</v>
+        <v>3.768973978964352e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.033713620808903e-05</v>
+        <v>1.514777030895773e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.099555968683623e-05</v>
+        <v>3.032992624095701e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.136819604059824e-05</v>
+        <v>2.242479671949524e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000115186933553115</v>
+        <v>4.558567955992295e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001214901475220814</v>
+        <v>0.00121490147522082</v>
       </c>
       <c r="C4" t="n">
-        <v>2.663176829515912e-05</v>
+        <v>2.663176829515915e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002505448779189139</v>
+        <v>0.000250544877918913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003471719393478263</v>
+        <v>0.0003471719393478313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001473578131933227</v>
+        <v>0.000147357813193323</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002155452544172921</v>
+        <v>0.0002155452544172912</v>
       </c>
       <c r="H4" t="n">
         <v>4.193646292885779e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.918486077229391e-05</v>
+        <v>9.918486077229404e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.0004092124286815852</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001237238325579211</v>
+        <v>0.0001237238325579215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002312965666779956</v>
+        <v>0.002312965666779988</v>
       </c>
       <c r="M4" t="n">
         <v>0.0008329271147746606</v>
       </c>
       <c r="N4" t="n">
-        <v>8.876134756871436e-05</v>
+        <v>8.876134756871461e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001951753354818432</v>
+        <v>0.0001951753354818434</v>
       </c>
       <c r="P4" t="n">
         <v>0.0006575978462746065</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002732173522362754</v>
+        <v>0.000273217352236276</v>
       </c>
       <c r="R4" t="n">
-        <v>4.618761497249741e-05</v>
+        <v>4.618761497249743e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0006598949844180298</v>
+        <v>0.0006598949844180295</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002832185126986504</v>
+        <v>0.000283218512698651</v>
       </c>
       <c r="U4" t="n">
         <v>0.001337497563802535</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001946631610080079</v>
+        <v>0.0001946631610080074</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002114625731581012</v>
+        <v>0.0002114625731581014</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008418144374286523</v>
+        <v>0.0008418144374286533</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002210657047624299</v>
+        <v>0.0002210657047624304</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0005488809441202328</v>
+        <v>0.0005488809441202361</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000416739878294162</v>
+        <v>0.0004167398782941627</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001098946544373153</v>
+        <v>0.001098946544373157</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.79301740885972e-05</v>
+        <v>8.793017408859732e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.788931680751655e-05</v>
+        <v>2.788931680751657e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.914558757447711e-05</v>
+        <v>3.91455875744771e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.074889965910933e-05</v>
+        <v>4.074889965910959e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.68106588459808e-05</v>
+        <v>2.681065884598079e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.033222925339929e-05</v>
+        <v>4.033222925339928e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.861076105245321e-05</v>
+        <v>2.861076105245322e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.151235965077359e-05</v>
+        <v>3.151235965077356e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.857193110618368e-05</v>
+        <v>4.857193110618369e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.310549617145088e-05</v>
+        <v>3.31054961714509e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001493471285918366</v>
+        <v>0.0001493471285918376</v>
       </c>
       <c r="M5" t="n">
-        <v>6.799585828226708e-05</v>
+        <v>6.799585828226701e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>8.876134756871436e-05</v>
+        <v>2.463316809606223e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.320074514477717e-05</v>
+        <v>3.320074514477716e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>5.83567855257696e-05</v>
+        <v>5.835678552576968e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.055886368161627e-05</v>
+        <v>3.055886368161638e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.886481298488411e-05</v>
+        <v>2.88648129848841e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>6.337149240107857e-05</v>
+        <v>6.337149240107861e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.079201290942246e-05</v>
+        <v>4.079201290942255e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>9.505145260234872e-05</v>
+        <v>9.505145260234886e-05</v>
       </c>
       <c r="V5" t="n">
         <v>3.538317974599004e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.770781490168033e-05</v>
+        <v>3.770781490168037e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>6.023461160394032e-05</v>
+        <v>6.023461160394044e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.666260164594128e-05</v>
+        <v>4.66626016459413e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.862770863579424e-05</v>
+        <v>4.862770863579437e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.853093558879115e-05</v>
+        <v>4.853093558879121e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.801701017146627e-05</v>
+        <v>8.80170101714662e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.615880634240486e-05</v>
+        <v>9.615880634240516e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.363380128185882e-05</v>
+        <v>3.363380128185884e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.48900720488193e-05</v>
+        <v>4.489007204881934e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.960930091786152e-05</v>
+        <v>4.960930091786171e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.596761045016241e-05</v>
+        <v>2.59676104501624e-05</v>
       </c>
       <c r="G6" t="n">
         <v>4.432906495599791e-05</v>
@@ -2151,64 +2151,64 @@
         <v>3.435524552679547e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.725684412511581e-05</v>
+        <v>3.725684412511586e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.431641558052603e-05</v>
+        <v>5.431641558052602e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.884998064579317e-05</v>
+        <v>3.884998064579324e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001550916130661791</v>
+        <v>0.0001550916130661793</v>
       </c>
       <c r="M6" t="n">
-        <v>7.374034275660949e-05</v>
+        <v>7.374034275660947e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.876134756871436e-05</v>
+        <v>3.691094612265407e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.565298208487888e-05</v>
+        <v>4.565298208487886e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>7.167753136066265e-05</v>
+        <v>7.167753136066268e-05</v>
       </c>
       <c r="Q6" t="n">
         <v>4.638792692013945e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.460929745922639e-05</v>
+        <v>3.460929745922641e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>6.911597687542088e-05</v>
+        <v>6.911597687542085e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.653649738376481e-05</v>
+        <v>4.653649738376489e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001049136493793969</v>
+        <v>0.000104913649379397</v>
       </c>
       <c r="V6" t="n">
-        <v>5.029498367071312e-05</v>
+        <v>5.029498367071314e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.345064298604648e-05</v>
+        <v>4.34506429860465e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>7.529120915171981e-05</v>
+        <v>7.529120915172027e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.403392902522206e-05</v>
+        <v>4.403392902522208e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.937323204797553e-05</v>
+        <v>5.937323204797555e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.427542006313351e-05</v>
+        <v>5.427542006313355e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.495749652506242e-05</v>
+        <v>8.495749652506241e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.291797728592633e-05</v>
+        <v>1.291797728592639e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.896464213325471e-06</v>
+        <v>7.896464213325476e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.384184635885421e-06</v>
+        <v>9.384184635885464e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.187882020338709e-06</v>
+        <v>9.187882020338752e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.869504405484788e-06</v>
+        <v>8.869504405484826e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.940046641095707e-06</v>
+        <v>8.940046641095748e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.952092288189639e-06</v>
+        <v>7.952092288189682e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.581397712842957e-06</v>
+        <v>9.581397712843006e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.913630836835583e-06</v>
+        <v>9.913630836835589e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.060571958614869e-05</v>
+        <v>1.060571958614873e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.763814986626276e-05</v>
+        <v>1.76381498662628e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.123569618636443e-05</v>
+        <v>1.123569618636445e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>8.424638994852138e-06</v>
+        <v>8.42463899485218e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.196699615783569e-05</v>
+        <v>1.196699615783574e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.11797415391358e-05</v>
+        <v>1.117974153913584e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.139770264663528e-06</v>
+        <v>9.139770264663569e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>8.045511010969449e-06</v>
+        <v>8.045511010969486e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.103694247547981e-05</v>
+        <v>1.103694247547985e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.324161432421287e-06</v>
+        <v>9.324161432421327e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.70425276128072e-05</v>
+        <v>1.704252761280723e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>9.430234323498121e-06</v>
+        <v>9.430234323498166e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.176154932148976e-05</v>
+        <v>1.17615493214898e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.313203912818561e-05</v>
+        <v>1.313203912818567e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.92494485484297e-06</v>
+        <v>9.924944854843012e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.297889350868899e-05</v>
+        <v>1.297889350868902e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.977238128771479e-06</v>
+        <v>9.977238128771518e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.236394655471016e-05</v>
+        <v>1.236394655471015e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000122956185171951</v>
+        <v>4.67116172143168e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>9.344585362911325e-06</v>
+        <v>8.183835236871737e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.204141541513371e-05</v>
+        <v>1.961354104379723e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>3.643805837673781e-05</v>
+        <v>1.706639959707584e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.010968184482041e-05</v>
+        <v>1.54294206239308e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.135963032895319e-05</v>
+        <v>1.565556788986587e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.616095716602592e-06</v>
+        <v>7.972087545753932e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.671201089443371e-05</v>
+        <v>2.130708033868396e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.405540835390304e-05</v>
+        <v>2.349166654446556e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.03757135476003e-05</v>
+        <v>2.868213544729083e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002329308424559434</v>
+        <v>8.514122062097203e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>8.556958224741103e-05</v>
+        <v>3.488739060581037e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.959969859686548e-05</v>
+        <v>1.177444968662489e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.186677991474452e-05</v>
+        <v>1.781710978893527e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>8.280536615097177e-05</v>
+        <v>3.306893738737488e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.626208634904245e-05</v>
+        <v>1.748323799419322e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08022400942539e-05</v>
+        <v>8.736770361405081e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.981135068290894e-05</v>
+        <v>3.20623475487123e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.066175195850341e-05</v>
+        <v>1.916882636938323e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001643143604985373</v>
+        <v>6.265148029979782e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.265910643007999e-05</v>
+        <v>1.930613698864232e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.001168247355388e-05</v>
+        <v>2.048347606822459e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001294112296034913</v>
+        <v>4.986396953240887e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.441639872587872e-05</v>
+        <v>2.372121576358348e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.327350250599793e-05</v>
+        <v>3.103709390234126e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.560799437006955e-05</v>
+        <v>2.418779964047309e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001111588269542189</v>
+        <v>4.448216785263889e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009461018276795272</v>
+        <v>0.0009461018276795288</v>
       </c>
       <c r="C4" t="n">
-        <v>2.68748286250274e-05</v>
+        <v>2.687482862502741e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003172421228735219</v>
+        <v>0.0003172421228735229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002600929211173588</v>
+        <v>0.0002600929211173585</v>
       </c>
       <c r="F4" t="n">
         <v>0.0002097027830454974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002013713951886606</v>
+        <v>0.0002013713951886612</v>
       </c>
       <c r="H4" t="n">
-        <v>1.841709381549272e-05</v>
+        <v>1.841709381549295e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003644480061396052</v>
+        <v>0.0003644480061396054</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000399225023327489</v>
+        <v>0.0003992250233274891</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005137279059323074</v>
+        <v>0.0005137279059323085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001935375202271077</v>
+        <v>0.001935375202271073</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007176664536588285</v>
+        <v>0.0007176664536588278</v>
       </c>
       <c r="N4" t="n">
         <v>0.0001144360936757271</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001736035653988382</v>
+        <v>0.000173603565398839</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0006159569277379088</v>
+        <v>0.0006159569277379093</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002565826427052102</v>
+        <v>0.0002565826427052101</v>
       </c>
       <c r="R4" t="n">
-        <v>3.826130516881994e-05</v>
+        <v>3.826130516881999e-05</v>
       </c>
       <c r="S4" t="n">
         <v>0.0005961460261983419</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003076287951550493</v>
+        <v>0.0003076287951550503</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001291170883482109</v>
+        <v>0.001291170883482107</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002810031144467807</v>
+        <v>0.0002810031144467804</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002671063488199218</v>
+        <v>0.0002671063488199214</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00108474113791736</v>
+        <v>0.001084741137917361</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00041082606301586</v>
+        <v>0.0004108260630158604</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004986040824008536</v>
+        <v>0.0004986040824008529</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004246090504142529</v>
+        <v>0.0004246090504142534</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009898433456973315</v>
+        <v>0.000989843345697333</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.506588133437598e-05</v>
+        <v>7.506588133437604e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.734361436893576e-05</v>
+        <v>2.734361436893578e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.312165759652306e-05</v>
+        <v>4.312165759652323e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.665969279214708e-05</v>
+        <v>3.665969279214715e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.057839829589991e-05</v>
+        <v>3.057839829589999e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.975787572124929e-05</v>
+        <v>3.975787572124934e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.694551573427141e-05</v>
+        <v>2.694551573427143e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.534927002325623e-05</v>
+        <v>4.534927002325632e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.908579514923044e-05</v>
+        <v>4.90857951492305e-05</v>
       </c>
       <c r="K5" t="n">
         <v>5.691945679358659e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001363539918852343</v>
+        <v>0.0001363539918852342</v>
       </c>
       <c r="M5" t="n">
-        <v>6.406443265870583e-05</v>
+        <v>6.406443265870585e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001144360936757271</v>
+        <v>2.610383240150501e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.235225000400219e-05</v>
+        <v>3.235225000400227e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>5.85058600715491e-05</v>
+        <v>5.850586007154923e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.082269561626955e-05</v>
+        <v>3.082269561626956e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.800072318280504e-05</v>
+        <v>2.80007231828051e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>6.179031770091125e-05</v>
+        <v>6.179031770091136e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.244366790135812e-05</v>
+        <v>4.24436679013582e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>9.789021180703696e-05</v>
+        <v>9.7890211807037e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.136114610316558e-05</v>
+        <v>4.13611461031657e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.099202701513335e-05</v>
+        <v>4.099202701513337e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>7.664782101520587e-05</v>
+        <v>7.664782101520596e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.715969463830536e-05</v>
+        <v>5.715969463830546e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.940840591478688e-05</v>
+        <v>4.94084059147869e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.982046961675657e-05</v>
+        <v>4.982046961675665e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.482029201800367e-05</v>
+        <v>8.482029201800365e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2726,82 +2726,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.185952973937352e-05</v>
+        <v>8.185952973937368e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.151415214197049e-05</v>
+        <v>3.151415214197051e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.729219536955788e-05</v>
+        <v>4.729219536955794e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.384046103611108e-05</v>
+        <v>4.384046103611112e-05</v>
       </c>
       <c r="F6" t="n">
         <v>2.914893897768829e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.227545397106327e-05</v>
+        <v>4.227545397106336e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.111605350730608e-05</v>
+        <v>3.111605350730611e-05</v>
       </c>
       <c r="I6" t="n">
         <v>4.951980779629102e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.325633292226527e-05</v>
+        <v>5.325633292226531e-05</v>
       </c>
       <c r="K6" t="n">
         <v>6.108999456662143e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001405245296582692</v>
+        <v>0.0001405245296582693</v>
       </c>
       <c r="M6" t="n">
-        <v>6.823497043174111e-05</v>
+        <v>6.823497043174117e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001144360936757271</v>
+        <v>3.645368594128405e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.277645501851208e-05</v>
+        <v>4.277645501851214e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>6.973180157830025e-05</v>
+        <v>6.97318015783003e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.453142417666811e-05</v>
+        <v>4.453142417666817e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.217126095583981e-05</v>
+        <v>3.217126095583984e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>6.596085547394602e-05</v>
+        <v>6.596085547394608e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.661420567439289e-05</v>
+        <v>4.661420567439296e-05</v>
       </c>
       <c r="U6" t="n">
         <v>0.0001059492781791683</v>
       </c>
       <c r="V6" t="n">
-        <v>5.387992782204268e-05</v>
+        <v>5.38799278220429e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.516099814278103e-05</v>
+        <v>4.516099814278106e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>8.962593595833512e-05</v>
+        <v>8.962593595833515e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.340033080467444e-05</v>
+        <v>5.34003308046745e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.847395317866593e-05</v>
+        <v>5.8473953178666e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.399100738979135e-05</v>
+        <v>5.399100738979139e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>8.06638375994765e-05</v>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.28322693650451e-05</v>
+        <v>1.283226936504508e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.594550333543025e-06</v>
+        <v>8.594550333543012e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.885095614696944e-06</v>
+        <v>9.88509561469693e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.499589511773152e-06</v>
+        <v>9.499589511773122e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.67307975719329e-06</v>
+        <v>9.673079757193261e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.565657393399134e-06</v>
+        <v>9.565657393399102e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.610721306833883e-06</v>
+        <v>8.610721306833853e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.042306480285847e-05</v>
+        <v>1.042306480285844e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.060132320072689e-05</v>
+        <v>1.060132320072686e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.170451864896971e-05</v>
+        <v>1.170451864896968e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655630602004341e-05</v>
+        <v>1.655630602004338e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.152871978751995e-05</v>
+        <v>1.152871978751996e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.007051285654809e-06</v>
+        <v>9.007051285654768e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22891514716744e-05</v>
+        <v>1.228915147167436e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.157615077807974e-05</v>
+        <v>1.157615077807971e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.016685841279151e-05</v>
+        <v>1.016685841279149e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>8.975000245366159e-06</v>
+        <v>8.97500024536613e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14972602696831e-05</v>
+        <v>1.149726026968307e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.001235689239289e-05</v>
+        <v>1.001235689239287e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.889057440498696e-05</v>
+        <v>1.889057440498693e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13235898359932e-05</v>
+        <v>1.132358983599317e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.301448007201736e-05</v>
+        <v>1.301448007201734e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.446619527235921e-05</v>
+        <v>1.446619527235919e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.182246859080768e-05</v>
+        <v>1.182246859080765e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.370110310679202e-05</v>
+        <v>1.3701103106792e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.076845351318066e-05</v>
+        <v>1.076845351318064e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.278725210282569e-05</v>
+        <v>1.278725210282568e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001067043983662912</v>
+        <v>4.135124314779587e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.169512403058192e-05</v>
+        <v>9.469624138049984e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.928014014839777e-05</v>
+        <v>1.900411354930469e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.910548266363364e-05</v>
+        <v>1.476014148376601e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.444244404832066e-05</v>
+        <v>1.740019814148499e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.152683427856004e-05</v>
+        <v>1.61423873204337e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.556546375597075e-06</v>
+        <v>8.791409889242501e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.191932615325186e-05</v>
+        <v>2.352841309245575e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.566806213869331e-05</v>
+        <v>2.438841051734548e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.156105608111363e-05</v>
+        <v>3.294227942744083e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000193441470961641</v>
+        <v>7.118453306714444e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>7.797083151531812e-05</v>
+        <v>3.236413467680364e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.876623870843357e-05</v>
+        <v>1.198150719493025e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.602571304765311e-05</v>
+        <v>1.635101257030988e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>7.76782654594583e-05</v>
+        <v>3.15747795953424e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.576520650747888e-05</v>
+        <v>2.114119324224344e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.808827562287731e-05</v>
+        <v>1.17905483177049e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>7.615752513189031e-05</v>
+        <v>3.122434590574784e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.229282314019726e-05</v>
+        <v>2.023536431882282e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001846500092746133</v>
+        <v>6.960090221656792e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>7.203396550984687e-05</v>
+        <v>2.950853945941675e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.700050319537744e-05</v>
+        <v>2.362670720550423e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001460329086023218</v>
+        <v>5.560068282552303e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.414606538213302e-05</v>
+        <v>3.461828352863796e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.252531262395991e-05</v>
+        <v>3.104000274852818e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.96285086783651e-05</v>
+        <v>2.610446210683218e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001066253936658997</v>
+        <v>4.316996933640091e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3146,31 +3146,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007844577704594464</v>
+        <v>0.0007844577704594461</v>
       </c>
       <c r="C4" t="n">
-        <v>4.166853951805554e-05</v>
+        <v>4.166853951805552e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002771094696214759</v>
+        <v>0.0002771094696214767</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001842803226935628</v>
+        <v>0.0001842803226935627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000240844576485253</v>
+        <v>0.0002408445764852529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001928563919528363</v>
+        <v>0.0001928563919528345</v>
       </c>
       <c r="H4" t="n">
-        <v>2.115469735171195e-05</v>
+        <v>2.1154697351712e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003995346209102988</v>
+        <v>0.0003995346209102989</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003972240498795276</v>
+        <v>0.0003972240498795278</v>
       </c>
       <c r="K4" t="n">
         <v>0.000599002114751044</v>
@@ -3179,52 +3179,52 @@
         <v>0.001531876627220593</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0006181006713594521</v>
+        <v>0.0006181006713594519</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001017596901612098</v>
+        <v>0.0001017596901612096</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001245663420029702</v>
+        <v>0.0001245663420029703</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005515053491208967</v>
+        <v>0.0005515053491208972</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003255948382965406</v>
+        <v>0.0003255948382965403</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970468392374544e-05</v>
+        <v>9.970468392374554e-05</v>
       </c>
       <c r="S4" t="n">
         <v>0.0005543674040765473</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003170030852201919</v>
+        <v>0.000317003085220192</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001401778997993864</v>
+        <v>0.001401778997993861</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0004974773813827839</v>
+        <v>0.0004974773813827836</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003196482317821594</v>
+        <v>0.000319648231782159</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001189465366430303</v>
+        <v>0.001189465366430302</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0006727330769835919</v>
+        <v>0.0006727330769835908</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004628285528396381</v>
+        <v>0.0004628285528396379</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004563666446057869</v>
+        <v>0.0004563666446057876</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009279931704724863</v>
+        <v>0.0009279931704724862</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.828310094957117e-05</v>
+        <v>6.828310094957105e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.985001059793851e-05</v>
+        <v>2.985001059793854e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.315172244543833e-05</v>
+        <v>4.315172244543826e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.44531970348382e-05</v>
+        <v>3.445319703483823e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.386956956528195e-05</v>
+        <v>3.386956956528182e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.123519842806727e-05</v>
+        <v>4.123519842806712e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.875707839697972e-05</v>
+        <v>2.875707839697975e-05</v>
       </c>
       <c r="I5" t="n">
         <v>4.922833190377588e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.123426067360318e-05</v>
+        <v>5.123426067360307e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.370294259349597e-05</v>
+        <v>6.370294259349598e-05</v>
       </c>
       <c r="L5" t="n">
         <v>0.0001185061128822338</v>
       </c>
       <c r="M5" t="n">
-        <v>6.178248290534668e-05</v>
+        <v>6.178248290534672e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001017596901612098</v>
+        <v>2.690975677466888e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.074971671091975e-05</v>
+        <v>3.07497167109198e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>5.72408192274768e-05</v>
+        <v>5.724081922747675e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65727650023628e-05</v>
+        <v>3.657276500236284e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.287177658429294e-05</v>
+        <v>3.287177658429287e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>6.136186385588891e-05</v>
+        <v>6.136186385588885e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.458919712009409e-05</v>
+        <v>4.458919712009407e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001089699852427955</v>
+        <v>0.0001089699852427954</v>
       </c>
       <c r="V5" t="n">
-        <v>5.714433884158e-05</v>
+        <v>5.714433884158003e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.557986136887409e-05</v>
+        <v>4.557986136887401e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>8.588347746662532e-05</v>
+        <v>8.588347746662523e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.317787402424754e-05</v>
+        <v>7.317787402424726e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.015726702384117e-05</v>
+        <v>5.015726702384108e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.312965627352179e-05</v>
+        <v>5.312965627352173e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.419506772829921e-05</v>
+        <v>8.419506772829913e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.476373238214804e-05</v>
+        <v>7.476373238214803e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.351551905358683e-05</v>
+        <v>3.351551905358679e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.681723090108666e-05</v>
+        <v>4.681723090108664e-05</v>
       </c>
       <c r="E6" t="n">
         <v>4.122957825572208e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.210492075029548e-05</v>
+        <v>3.210492075029547e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.320903014337608e-05</v>
+        <v>4.320903014337616e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.242258685262811e-05</v>
+        <v>3.242258685262807e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.289384035942422e-05</v>
+        <v>5.289384035942418e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.48997691292514e-05</v>
+        <v>5.489976912925137e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.736845104914444e-05</v>
+        <v>6.736845104914432e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001221716213378823</v>
+        <v>0.0001221716213378822</v>
       </c>
       <c r="M6" t="n">
-        <v>6.544799136099678e-05</v>
+        <v>6.544799136099676e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001017596901612098</v>
+        <v>3.689931628420826e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.077209673052734e-05</v>
+        <v>4.077209673052736e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>6.807430358038419e-05</v>
+        <v>6.807430358038426e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.999987222354599e-05</v>
+        <v>4.999987222354589e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.653728503994121e-05</v>
+        <v>3.653728503994112e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>6.502737231153741e-05</v>
+        <v>6.502737231153716e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.825470557574243e-05</v>
+        <v>4.825470557574234e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001165993229719998</v>
+        <v>0.0001165993229719997</v>
       </c>
       <c r="V6" t="n">
-        <v>6.918554993642391e-05</v>
+        <v>6.918554993642381e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.924376648462897e-05</v>
+        <v>4.924376648462886e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>9.856285894434201e-05</v>
+        <v>9.856285894434205e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.870074990185833e-05</v>
+        <v>6.870074990185809e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.891116182092666e-05</v>
+        <v>5.891116182092669e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.679516472917006e-05</v>
+        <v>5.679516472917001e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.933854466296266e-05</v>
+        <v>7.933854466296281e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3566,67 +3566,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.342672266325759e-06</v>
+        <v>5.342672266325758e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.841014118087617e-06</v>
+        <v>4.841014118087609e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.863891067061935e-06</v>
+        <v>4.863891067061938e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.945024120429984e-06</v>
+        <v>4.945024120429987e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.827436686471112e-06</v>
+        <v>4.827436686471119e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.152182329091498e-06</v>
+        <v>5.152182329091502e-06</v>
       </c>
       <c r="H2" t="n">
         <v>4.852039683424231e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.882291965204026e-06</v>
+        <v>4.882291965204028e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.254679676638076e-06</v>
+        <v>5.254679676638084e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.07160793804951e-06</v>
+        <v>5.071607938049515e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.107503568323871e-06</v>
+        <v>7.107503568323874e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.912010485993229e-06</v>
+        <v>5.912010485993227e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.813406691149944e-06</v>
+        <v>4.813406691149942e-06</v>
       </c>
       <c r="O2" t="n">
         <v>6.577029134085765e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.404754790967132e-06</v>
+        <v>5.404754790967137e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.923636698486228e-06</v>
+        <v>4.923636698486229e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.801308307174994e-06</v>
+        <v>4.801308307174999e-06</v>
       </c>
       <c r="S2" t="n">
         <v>5.154484590237609e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.885859814915884e-06</v>
+        <v>4.885859814915885e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>9.317624131368294e-06</v>
+        <v>9.317624131368301e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.973679109775073e-06</v>
+        <v>4.973679109775077e-06</v>
       </c>
       <c r="W2" t="n">
         <v>7.415306205538908e-06</v>
@@ -3635,16 +3635,16 @@
         <v>5.34866574994738e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.907114111889633e-06</v>
+        <v>4.907114111889641e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.202279233356807e-06</v>
+        <v>6.202279233356812e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.667787666901509e-06</v>
+        <v>5.667787666901511e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.277114641206164e-06</v>
+        <v>6.277114641206157e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.811602005327167e-05</v>
+        <v>9.328054373808427e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.385020939556168e-06</v>
+        <v>5.098471771294045e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.124431192050423e-06</v>
+        <v>5.657915013194086e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.511002342816449e-06</v>
+        <v>5.841275423351388e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.279537929674968e-06</v>
+        <v>5.37067546678001e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.373175116679021e-05</v>
+        <v>7.831495206837693e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>6.859360230112975e-06</v>
+        <v>5.575842768932221e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.558144430261588e-06</v>
+        <v>5.811289651881218e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.615019628459629e-05</v>
+        <v>8.676428046151942e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.195927512068085e-05</v>
+        <v>7.297564039601167e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.897164309863146e-05</v>
+        <v>2.277922143905212e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.158639367858949e-05</v>
+        <v>1.391773877884793e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.942367236684501e-06</v>
+        <v>5.244003916547434e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>8.92642951919497e-06</v>
+        <v>7.383625450365778e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.952683560628595e-05</v>
+        <v>9.834900312664113e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.509648549072656e-06</v>
+        <v>6.124039785190756e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.665366663179976e-06</v>
+        <v>5.146974157125436e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.379683607661877e-05</v>
+        <v>7.812104188061679e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.63946604289878e-06</v>
+        <v>5.843572410066132e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.905786954728242e-05</v>
+        <v>2.786179937528136e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>9.62998794909879e-06</v>
+        <v>6.487211547105649e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1807860325037e-05</v>
+        <v>1.202685186559355e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.842652116361621e-05</v>
+        <v>9.566125920978239e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.116927249807728e-06</v>
+        <v>5.992230208703721e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.703983629540789e-05</v>
+        <v>9.570726503625069e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.576791169841671e-05</v>
+        <v>1.207486577267878e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.981617786059118e-05</v>
+        <v>1.712498496705151e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3742,82 +3742,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001200967188004428</v>
+        <v>0.0001200967188004427</v>
       </c>
       <c r="C4" t="n">
         <v>1.288692905181378e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.919606537183451e-05</v>
+        <v>2.919606537183452e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>4.158817337872144e-05</v>
+        <v>4.15881733787214e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.171812778960296e-05</v>
+        <v>2.171812778960293e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>8.129180410437699e-05</v>
+        <v>8.129180410437691e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.757604799168214e-05</v>
+        <v>2.757604799168206e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.357187569696113e-05</v>
+        <v>3.357187569696112e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.0001049580892626009</v>
       </c>
       <c r="K4" t="n">
-        <v>7.198765572111072e-05</v>
+        <v>7.198765572111071e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004489528582168087</v>
+        <v>0.0004489528582168086</v>
       </c>
       <c r="M4" t="n">
         <v>0.0002445830819400098</v>
       </c>
       <c r="N4" t="n">
-        <v>1.768108256292963e-05</v>
+        <v>1.768108256292919e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>2.855585694309699e-05</v>
+        <v>2.855585694309675e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001341700892868144</v>
+        <v>0.0001341700892868143</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.111193960784346e-05</v>
+        <v>4.111193960784332e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.506931586330334e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>7.900063231086375e-05</v>
+        <v>7.900063231086397e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>3.461091079120778e-05</v>
+        <v>3.461091079120773e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000553176164988572</v>
+        <v>0.0005531761649885742</v>
       </c>
       <c r="V4" t="n">
-        <v>4.905910700910072e-05</v>
+        <v>4.905910700910053e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001453074910904364</v>
+        <v>0.0001453074910904365</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001349968366703526</v>
+        <v>0.0001349968366703529</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.762024357947993e-05</v>
+        <v>3.76202435794802e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001012276595900454</v>
+        <v>0.0001012276595900456</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002001282064130854</v>
+        <v>0.000200128206413085</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0003471160011422985</v>
@@ -3830,28 +3830,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.072689496143101e-05</v>
+        <v>2.0726894961431e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.110963005294724e-05</v>
+        <v>2.11096300529472e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.197815689083905e-05</v>
+        <v>2.197815689083901e-05</v>
       </c>
       <c r="E5" t="n">
         <v>1.93487028121907e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.594451564345104e-05</v>
+        <v>1.594451564345103e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66153918338029e-05</v>
+        <v>2.661539183380285e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.184429006074537e-05</v>
+        <v>2.18442900607453e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.218600350018531e-05</v>
+        <v>2.218600350018525e-05</v>
       </c>
       <c r="J5" t="n">
         <v>2.637579171954576e-05</v>
@@ -3860,13 +3860,13 @@
         <v>2.432441450312528e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.73207922053352e-05</v>
+        <v>4.732079220533515e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.379233409559376e-05</v>
+        <v>3.37923340955937e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.768108256292963e-05</v>
+        <v>1.624582879712437e-05</v>
       </c>
       <c r="O5" t="n">
         <v>1.829573891937227e-05</v>
@@ -3875,40 +3875,40 @@
         <v>2.399623350556206e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.468498790562567e-05</v>
+        <v>1.468498790562564e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.127125582842417e-05</v>
+        <v>2.127125582842415e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>2.526054441473349e-05</v>
+        <v>2.526054441473346e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.222630400397274e-05</v>
+        <v>2.222630400397272e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.808530932196997e-05</v>
+        <v>4.808530932196993e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>2.129431743479432e-05</v>
+        <v>2.129431743479429e-05</v>
       </c>
       <c r="W5" t="n">
         <v>2.816137822594606e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>2.009622609267986e-05</v>
+        <v>2.009622609267984e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.909227640384271e-05</v>
+        <v>2.909227640384268e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.960691944214238e-05</v>
+        <v>1.960691944214236e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.105853879673365e-05</v>
+        <v>3.105853879673363e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.473872115903118e-05</v>
+        <v>4.473872115903114e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3918,25 +3918,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.516446451729206e-05</v>
+        <v>2.516446451729202e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.301360813720077e-05</v>
+        <v>2.301360813720075e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.38821349750926e-05</v>
+        <v>2.388213497509261e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.384636896614455e-05</v>
+        <v>2.384636896614456e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395944671130654e-05</v>
+        <v>1.395944671130653e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.713851633750308e-05</v>
+        <v>2.71385163375031e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.374826814499886e-05</v>
+        <v>2.374826814499887e-05</v>
       </c>
       <c r="I6" t="n">
         <v>2.408998158443879e-05</v>
@@ -3945,58 +3945,58 @@
         <v>2.827976980379929e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.622839258737879e-05</v>
+        <v>2.62283925873788e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.922477028958872e-05</v>
+        <v>4.922477028958875e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.569631217984748e-05</v>
+        <v>3.569631217984745e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.768108256292963e-05</v>
+        <v>2.331189072520632e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.531047361916603e-05</v>
+        <v>2.531047361916605e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.165605321868398e-05</v>
+        <v>3.165605321868397e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.455698830363223e-05</v>
+        <v>2.455698830363225e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.31752339126777e-05</v>
+        <v>2.317523391267769e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.716452249898703e-05</v>
+        <v>2.716452249898706e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.413028208822626e-05</v>
+        <v>2.413028208822628e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.323686950047748e-05</v>
+        <v>5.323686950047749e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.97763564056287e-05</v>
+        <v>2.977635640562872e-05</v>
       </c>
       <c r="W6" t="n">
         <v>3.006404756361529e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.935788802565563e-05</v>
+        <v>2.935788802565564e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>2.437035915000445e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.580646822850214e-05</v>
+        <v>2.58064682285022e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>3.296251688098715e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.968648702063299e-05</v>
+        <v>3.968648702063298e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.187722180602674e-06</v>
+        <v>4.187722180602645e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.267366353192178e-06</v>
+        <v>4.267366353192107e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.173777879476665e-06</v>
+        <v>4.173777879476639e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.191718706819335e-06</v>
+        <v>4.191718706819307e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.196318130624668e-06</v>
+        <v>4.196318130624665e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.261267849669605e-06</v>
+        <v>4.261267849669574e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.177474793162844e-06</v>
+        <v>4.177474793162817e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.241013431415572e-06</v>
+        <v>4.24101343141556e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.258809151087581e-06</v>
+        <v>4.25880915108759e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.337370064993e-06</v>
+        <v>4.337370064992973e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.248843923270151e-06</v>
+        <v>4.248843923270127e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.258782026643944e-06</v>
+        <v>4.25878202664394e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.173262727970681e-06</v>
+        <v>4.173262727970655e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.655969345437356e-06</v>
+        <v>5.655969345437327e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.165191050259758e-06</v>
+        <v>4.165191050259746e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.176648609706949e-06</v>
+        <v>4.17664860970693e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.188201879267167e-06</v>
+        <v>4.188201879267142e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.335964023802286e-06</v>
+        <v>4.335964023802263e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.172823799834797e-06</v>
+        <v>4.17282379983478e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.906485871943294e-06</v>
+        <v>5.906485871943263e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.241380390159638e-06</v>
+        <v>4.241380390159611e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.181995984079738e-06</v>
+        <v>6.181995984079702e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.178359324161153e-06</v>
+        <v>5.178359324161124e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.624381549366095e-06</v>
+        <v>4.624381549366072e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.959918789726072e-06</v>
+        <v>4.959918789726053e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.341347788449365e-06</v>
+        <v>4.34134778844934e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.247049683873247e-06</v>
+        <v>4.24704968387324e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.325608879669179e-06</v>
+        <v>4.670679351628658e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.236415175998644e-06</v>
+        <v>4.722498756086317e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.015615024179857e-06</v>
+        <v>4.59246308254507e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.025463306488498e-06</v>
+        <v>4.33737930577556e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.544355549034851e-06</v>
+        <v>4.763181957079447e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.022463671075352e-06</v>
+        <v>5.260826418974923e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.103933617053185e-06</v>
+        <v>4.610562265550941e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.586087377601974e-06</v>
+        <v>5.122914495648304e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.977556526537552e-06</v>
+        <v>5.245735112132887e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.823508450852613e-06</v>
+        <v>5.875628973523738e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.74911814043008e-06</v>
+        <v>5.184772126541575e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.10501192301091e-06</v>
+        <v>5.312945169440684e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.998852120128882e-06</v>
+        <v>4.56665632711779e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.862181033465949e-06</v>
+        <v>6.171635560531338e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.806358905515879e-06</v>
+        <v>4.49640661503488e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.080670077042279e-06</v>
+        <v>4.610846676661298e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.353336798060564e-06</v>
+        <v>4.695871146841471e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>8.746644791992447e-06</v>
+        <v>5.805699485268095e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.993995249611435e-06</v>
+        <v>4.587516024106734e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>8.973487360005078e-06</v>
+        <v>7.000440523796575e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.56644975500371e-06</v>
+        <v>5.10522037829854e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0972289821333e-05</v>
+        <v>7.806477570971565e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.841558069526292e-05</v>
+        <v>1.250990466130179e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.547318870926187e-05</v>
+        <v>8.171451948879539e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.913755147978694e-06</v>
+        <v>5.699248873863645e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.89743379815127e-06</v>
+        <v>5.902934160227734e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.740164030948698e-06</v>
+        <v>5.183458949921455e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4338,85 +4338,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.53551683108324e-05</v>
+        <v>1.535516831083241e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.571130830020127e-05</v>
+        <v>1.571130830020125e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.481554157827882e-05</v>
+        <v>1.481554157827879e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.312642070407593e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.866248163170962e-05</v>
+        <v>1.866248163170958e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.02068558095828e-05</v>
+        <v>3.020685580958278e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.476949365454587e-05</v>
+        <v>1.476949365454585e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.774609349864197e-05</v>
+        <v>2.774609349864188e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.999286939092832e-05</v>
+        <v>2.999286939092829e-05</v>
       </c>
       <c r="K4" t="n">
         <v>4.578747444468155e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.928797464459857e-05</v>
+        <v>2.928797464459854e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.334013158971622e-05</v>
+        <v>3.33401315897162e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.324245718720616e-05</v>
+        <v>1.324245718720615e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.673390400091891e-05</v>
+        <v>1.67339040009189e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.124870524139308e-05</v>
+        <v>1.124870524139305e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>1.508014421304899e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68804725450518e-05</v>
+        <v>1.688047254505178e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.157627247714007e-05</v>
+        <v>4.157627247714008e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.480681141587832e-05</v>
+        <v>1.480681141587829e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.292083853210977e-05</v>
+        <v>3.292083853210974e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.635871479953997e-05</v>
+        <v>2.635871479953991e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.761976086515743e-05</v>
+        <v>4.761976086515736e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0002075580378958657</v>
+        <v>0.0002075580378958659</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001032114676308304</v>
+        <v>0.0001032114676308303</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.260175982876231e-05</v>
+        <v>2.260175982876227e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.630388269815055e-05</v>
+        <v>4.630388269815056e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.960502097817785e-05</v>
+        <v>2.960502097817786e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.30222022157993e-05</v>
+        <v>1.302220221579926e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.871468730827099e-05</v>
+        <v>1.87146873082709e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.864988891694232e-05</v>
+        <v>1.864988891694226e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.577209366406728e-05</v>
+        <v>1.577209366406723e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.402056303740419e-05</v>
+        <v>1.402056303740414e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.083772603997774e-05</v>
+        <v>2.083772603997763e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.869164725769212e-05</v>
+        <v>1.869164725769201e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.940934540597424e-05</v>
+        <v>1.940934540597417e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.959507088087434e-05</v>
+        <v>1.959507088087427e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.049773790847271e-05</v>
+        <v>2.049773790847262e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.949779441367595e-05</v>
+        <v>1.949779441367585e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.96593619185416e-05</v>
+        <v>1.965936191854151e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.324245718720616e-05</v>
+        <v>1.415957685414792e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.558993992032684e-05</v>
+        <v>1.558993992032677e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.499869566345174e-05</v>
+        <v>1.49986956634517e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.17601984773986e-05</v>
+        <v>1.176019847739854e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.881281462994377e-05</v>
+        <v>1.881281462994367e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>2.048185602641273e-05</v>
+        <v>2.048185602641265e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.863911214848915e-05</v>
+        <v>1.863911214848906e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.696947939811207e-05</v>
+        <v>1.6969479398112e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.773792930332931e-05</v>
+        <v>1.773792930332925e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.066524143346436e-05</v>
+        <v>2.066524143346428e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>2.360520633210312e-05</v>
+        <v>2.360520633210304e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.949841957503898e-05</v>
+        <v>2.949841957503886e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33320290641681e-05</v>
+        <v>1.333202906416803e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.054266812475557e-05</v>
+        <v>2.054266812475549e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.552819898228081e-05</v>
+        <v>2.552819898228069e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.555024700045661e-05</v>
+        <v>1.555024700045658e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.86747076993123e-05</v>
+        <v>1.867470769931228e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.860990930798364e-05</v>
+        <v>1.860990930798358e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.807004980156123e-05</v>
+        <v>1.807004980156121e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.144805745992334e-05</v>
+        <v>1.144805745992333e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.959814905136508e-05</v>
+        <v>1.959814905136499e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.865166764873343e-05</v>
+        <v>1.865166764873341e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.936936579701556e-05</v>
+        <v>1.936936579701554e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.955509127191565e-05</v>
+        <v>1.955509127191564e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.045775829951407e-05</v>
+        <v>2.045775829951402e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.945781480471729e-05</v>
+        <v>1.945781480471722e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.961938230958274e-05</v>
+        <v>1.961938230958272e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.324245718720616e-05</v>
+        <v>1.860409043474217e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.986824200460365e-05</v>
+        <v>1.98682420046036e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.981095608051838e-05</v>
+        <v>1.981095608051835e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86423358092133e-05</v>
+        <v>1.864233580921329e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.877283502098509e-05</v>
+        <v>1.877283502098504e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.044187641745405e-05</v>
+        <v>2.044187641745401e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.859913253953045e-05</v>
+        <v>1.859913253953044e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.974927784494315e-05</v>
+        <v>1.974927784494313e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.298737614002961e-05</v>
+        <v>2.298737614002957e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06241248680092e-05</v>
+        <v>2.062412486800918e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.99571188559912e-05</v>
+        <v>2.995711885599116e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.369968504731405e-05</v>
+        <v>2.369968504731401e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.724503932413576e-05</v>
+        <v>1.724503932413573e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.050268851579687e-05</v>
+        <v>2.050268851579686e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.944510049326787e-05</v>
+        <v>1.944510049326783e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.176953486215766e-06</v>
+        <v>4.176953486215741e-06</v>
       </c>
       <c r="C2" t="n">
         <v>4.248089932270893e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.218582053603687e-06</v>
+        <v>4.218582053603665e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.151449535382452e-06</v>
+        <v>4.15144953538243e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.172683788800065e-06</v>
+        <v>4.172683788800042e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.180387868623145e-06</v>
+        <v>4.180387868623133e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.154965019673048e-06</v>
+        <v>4.154965019673028e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.237830663384645e-06</v>
+        <v>4.237830663384629e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.21560323274215e-06</v>
+        <v>4.215603232742139e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.403516680386086e-06</v>
+        <v>4.403516680386066e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.197907372677167e-06</v>
+        <v>4.19790737267715e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.234611084119596e-06</v>
+        <v>4.234611084119598e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.149381728717319e-06</v>
+        <v>4.149381728717312e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>5.628290062715127e-06</v>
+        <v>5.628290062715097e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.145991155425461e-06</v>
+        <v>4.145991155425479e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.166907921770549e-06</v>
+        <v>4.166907921770524e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.173689296805546e-06</v>
+        <v>4.173689296805527e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.269022615315191e-06</v>
+        <v>4.269022615315169e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.16764110198643e-06</v>
+        <v>4.167641101986405e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.89658982704355e-06</v>
+        <v>5.89658982704356e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.259123800868036e-06</v>
+        <v>4.25912380086805e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.000310552474328e-06</v>
+        <v>6.000310552474313e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.236436023908015e-06</v>
+        <v>5.23643602390799e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.470280499067167e-06</v>
+        <v>4.470280499067152e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.908150082145751e-06</v>
+        <v>4.908150082145731e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.22900296081867e-06</v>
+        <v>4.229002960818648e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.36380602479889e-06</v>
+        <v>4.363806024798878e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.574632659464171e-06</v>
+        <v>4.749772399413101e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.280992145905991e-06</v>
+        <v>4.726903729175613e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.562866309826166e-06</v>
+        <v>5.107388823386777e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.594776963975646e-06</v>
+        <v>4.199976497438679e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.495862700144753e-06</v>
+        <v>4.736758899856822e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.656625255773344e-06</v>
+        <v>4.794675795304741e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.082609978266916e-06</v>
+        <v>4.599662624722822e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.015851144047103e-06</v>
+        <v>5.263422153599489e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.480750263402935e-06</v>
+        <v>5.071255529136504e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.086680450349955e-05</v>
+        <v>6.564442690115505e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.069438348624924e-06</v>
+        <v>4.946341185593404e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.035632464972697e-06</v>
+        <v>5.2755771158399e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.944802277316062e-06</v>
+        <v>4.537657490596025e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.857030901864228e-06</v>
+        <v>6.157042170079235e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.862046973481142e-06</v>
+        <v>4.516704138347842e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.354670344768792e-06</v>
+        <v>4.686589364936675e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.518389294582086e-06</v>
+        <v>4.74321900229103e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.702008648500812e-06</v>
+        <v>5.464124090319863e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.374865373513365e-06</v>
+        <v>4.698238134931426e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>9.503034461071199e-06</v>
+        <v>7.157258121548083e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>7.47182676117508e-06</v>
+        <v>5.395635516324934e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.792465924206798e-06</v>
+        <v>6.705493351699095e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>3.026543979848971e-05</v>
+        <v>1.308806526266804e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.239680445887307e-05</v>
+        <v>7.11225688827975e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.299320557824298e-06</v>
+        <v>5.489087360587051e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.790946573727877e-06</v>
+        <v>5.170012582779233e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.919236345072912e-06</v>
+        <v>6.292286440380658e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4934,34 +4934,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.755551524908919e-05</v>
+        <v>1.755551524908917e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.586120227656965e-05</v>
+        <v>1.586120227656963e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.752566361047144e-05</v>
+        <v>2.752566361047141e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.076196787375763e-05</v>
+        <v>1.07619678737576e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.811052383650911e-05</v>
+        <v>1.811052383650912e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.942651187381749e-05</v>
+        <v>1.942651187381808e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.488555872874782e-05</v>
+        <v>1.488555872874784e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15065677537392e-05</v>
+        <v>3.150656775373922e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.609668234560281e-05</v>
+        <v>2.609668234560271e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>6.29811488141612e-05</v>
+        <v>6.298114881416115e-05</v>
       </c>
       <c r="L4" t="n">
         <v>2.370635234921349e-05</v>
@@ -4970,10 +4970,10 @@
         <v>3.232538097439329e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.259984245270709e-05</v>
+        <v>1.259984245270708e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.667687983698429e-05</v>
+        <v>1.667687983698426e-05</v>
       </c>
       <c r="P4" t="n">
         <v>1.234814509726403e-05</v>
@@ -4982,13 +4982,13 @@
         <v>1.669590941128024e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.820503568338208e-05</v>
+        <v>1.820503568338203e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.447846493175364e-05</v>
+        <v>3.44784649317537e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.723172652030934e-05</v>
+        <v>1.723172652030933e-05</v>
       </c>
       <c r="U4" t="n">
         <v>3.685729089195134e-05</v>
@@ -4997,22 +4997,22 @@
         <v>3.313270093007332e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.174659471667419e-05</v>
+        <v>2.17465947166742e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0002200062482824923</v>
+        <v>0.000220006248282492</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.730268962541663e-05</v>
+        <v>7.730268962541669e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.821715973469867e-05</v>
+        <v>1.821715973469865e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.821860452370996e-05</v>
+        <v>2.821860452370997e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.857670179310273e-05</v>
+        <v>5.857670179310272e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5022,85 +5022,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.313715159593368e-05</v>
+        <v>1.313715159593367e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.870497429540064e-05</v>
+        <v>1.870497429540063e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.936829765491062e-05</v>
+        <v>1.936829765491061e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.554247849806024e-05</v>
+        <v>1.554247849806022e-05</v>
       </c>
       <c r="F5" t="n">
         <v>1.398640931307203e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.013144359436106e-05</v>
+        <v>2.013144359436105e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86497139913825e-05</v>
+        <v>1.864971399138251e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.958571955718456e-05</v>
+        <v>1.958571955718454e-05</v>
       </c>
       <c r="J5" t="n">
         <v>1.931988257170365e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.145721933854922e-05</v>
+        <v>2.14572193385492e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.913476762302242e-05</v>
+        <v>1.91347676230224e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.959471837572825e-05</v>
+        <v>1.959471837572824e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.259984245270709e-05</v>
+        <v>1.412096188245746e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.557285416225009e-05</v>
+        <v>1.55728541622501e-05</v>
       </c>
       <c r="P5" t="n">
         <v>1.500905449098146e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.189152765227986e-05</v>
+        <v>1.189152765227985e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.886121331518719e-05</v>
+        <v>1.886121331518718e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.993804700324681e-05</v>
+        <v>1.99380470032468e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.879289617239811e-05</v>
+        <v>1.87928961723981e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.721551027088293e-05</v>
+        <v>1.721551027088291e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.816150265483853e-05</v>
+        <v>1.816150265483854e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.909564603104133e-05</v>
+        <v>1.909564603104129e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>2.450034046013744e-05</v>
+        <v>2.450034046013743e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.794703827989335e-05</v>
+        <v>2.794703827989334e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.302555414588693e-05</v>
+        <v>1.302555414588691e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.948600659575804e-05</v>
+        <v>1.948600659575799e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.700787426646603e-05</v>
+        <v>2.700787426646601e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.498739571769719e-05</v>
+        <v>1.498739571769718e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.781344676819517e-05</v>
+        <v>1.781344676819514e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.847677012770512e-05</v>
+        <v>1.847677012770509e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.702166755202491e-05</v>
+        <v>1.702166755202487e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.099833885824569e-05</v>
+        <v>1.099833885824567e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.804534930270619e-05</v>
+        <v>1.804534930270623e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.775818646417702e-05</v>
+        <v>1.775818646417699e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.869419202997906e-05</v>
+        <v>1.869419202997904e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.842835504449817e-05</v>
+        <v>1.842835504449814e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.056569181134373e-05</v>
+        <v>2.05656918113437e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.824324009581692e-05</v>
+        <v>1.82432400958169e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.87031908485219e-05</v>
+        <v>1.870319084852187e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.259984245270709e-05</v>
+        <v>1.769512062439157e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.892034949515823e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.887497005614515e-05</v>
+        <v>1.887497005614511e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.789308710192414e-05</v>
+        <v>1.789308710192413e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.796968578798168e-05</v>
+        <v>1.796968578798164e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.90465194760413e-05</v>
+        <v>1.904651947604128e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.790136864519258e-05</v>
+        <v>1.790136864519256e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91312999824043e-05</v>
+        <v>1.913129998240428e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.232358940731164e-05</v>
+        <v>2.232358940731165e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.820298631554888e-05</v>
+        <v>1.820298631554886e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.997389895825216e-05</v>
+        <v>2.997389895825212e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.131981985622045e-05</v>
+        <v>2.131981985622044e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.618168579627098e-05</v>
+        <v>1.618168579627095e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.859447906855253e-05</v>
+        <v>1.859447906855252e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.009857129300572e-05</v>
+        <v>2.009857129300569e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.774876717879609e-06</v>
+        <v>9.774876717879564e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.567722317479806e-06</v>
+        <v>6.567722317479871e-06</v>
       </c>
       <c r="D2" t="n">
         <v>6.976920182026077e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.66819624008506e-06</v>
+        <v>7.668196240085009e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.814848004375809e-06</v>
+        <v>6.814848004375793e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.510687004475421e-06</v>
+        <v>7.510687004475439e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6587055400538e-06</v>
+        <v>6.658705540053856e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.752958883539054e-06</v>
+        <v>6.752958883539117e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.029928643850589e-06</v>
+        <v>8.02992864385053e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.705872282315976e-06</v>
+        <v>6.705872282315962e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.585395873903365e-05</v>
+        <v>1.585395873903376e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.992177245785362e-06</v>
+        <v>9.992177245785322e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>6.651510285473445e-06</v>
+        <v>6.651510285473561e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>9.227092356841269e-06</v>
+        <v>9.227092356841315e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>8.743560276186391e-06</v>
+        <v>8.743560276186369e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.056409156313371e-06</v>
+        <v>7.056409156313485e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.719954681040515e-06</v>
+        <v>6.719954681040551e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.198948893543584e-06</v>
+        <v>8.198948893543554e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>6.990391781329158e-06</v>
+        <v>6.990391781329263e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.432672174473771e-05</v>
+        <v>1.432672174473782e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>7.227442560828039e-06</v>
+        <v>7.227442560828018e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>9.656107191088883e-06</v>
+        <v>9.656107191088913e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.003795644222674e-05</v>
+        <v>1.00379564422268e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.510794830570493e-06</v>
+        <v>7.510794830570409e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.001572663920336e-05</v>
+        <v>1.001572663920335e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.128041783629963e-06</v>
+        <v>8.128041783629993e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.056925623284501e-05</v>
+        <v>1.056925623284504e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.074374958468798e-05</v>
+        <v>3.137930788252422e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.798000398694782e-06</v>
+        <v>6.851893061513638e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.647420898951903e-05</v>
+        <v>9.897201021032735e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>3.184759461140941e-05</v>
+        <v>1.480411167323704e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.271415288324539e-05</v>
+        <v>8.581654448717803e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.863046449343628e-05</v>
+        <v>1.384517879880321e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.060595435323549e-06</v>
+        <v>7.321523734270994e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.125295415417936e-05</v>
+        <v>8.076443856164246e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.07692898583317e-05</v>
+        <v>1.803636134250598e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.014277145302167e-05</v>
+        <v>7.690596400544599e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002218720191735766</v>
+        <v>7.969766734259658e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>8.674915664087558e-05</v>
+        <v>3.368974206586693e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>8.867927570963775e-06</v>
+        <v>7.231885859698348e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.681854495804942e-05</v>
+        <v>1.143037446354041e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>5.694759928696875e-05</v>
+        <v>2.354950433922233e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.829802216912234e-05</v>
+        <v>1.047565121809354e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.048849965532232e-05</v>
+        <v>7.814321507003259e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>4.454019804602526e-05</v>
+        <v>1.906896832168333e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.679373204228412e-05</v>
+        <v>1.000752404003687e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001399915927929372</v>
+        <v>5.337158937660449e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.212095229145588e-05</v>
+        <v>1.165540255475432e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>3.013249788124094e-05</v>
+        <v>1.599776189936381e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>8.785483985828183e-05</v>
+        <v>3.467109112886374e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.881533074060675e-05</v>
+        <v>1.408020680964427e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.96456399218496e-05</v>
+        <v>2.206432021910703e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.312955934434462e-05</v>
+        <v>1.904167237178341e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.97094080976478e-05</v>
+        <v>3.951265610483893e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006393437480258267</v>
+        <v>0.0006393437480258268</v>
       </c>
       <c r="C4" t="n">
-        <v>2.325359804700284e-05</v>
+        <v>2.325359804700287e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001056917915191495</v>
+        <v>0.0001056917915191496</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002431654275644638</v>
+        <v>0.0002431654275644646</v>
       </c>
       <c r="F4" t="n">
-        <v>6.963617447057314e-05</v>
+        <v>6.96361744705731e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001966894480945725</v>
+        <v>0.0001966894480945728</v>
       </c>
       <c r="H4" t="n">
         <v>3.548353176259643e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.570110232191888e-05</v>
+        <v>5.570110232191901e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003103119873684814</v>
+        <v>0.0003103119873684818</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4988836076698e-05</v>
+        <v>4.498883607669796e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001916579010011554</v>
+        <v>0.00191657901001156</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007290814803613007</v>
+        <v>0.0007290814803613006</v>
       </c>
       <c r="N4" t="n">
         <v>3.164163856150583e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>7.729098077171685e-05</v>
+        <v>7.729098077171678e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0004492823640934867</v>
+        <v>0.0004492823640934864</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0001185274352152629</v>
       </c>
       <c r="R4" t="n">
-        <v>4.877890441701103e-05</v>
+        <v>4.877890441701091e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003233696510857987</v>
+        <v>0.0003233696510857989</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001087484299258594</v>
+        <v>0.0001087484299258595</v>
       </c>
       <c r="U4" t="n">
         <v>0.001182905946838663</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001414459068422778</v>
+        <v>0.000141445906842278</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002077148878180282</v>
+        <v>0.0002077148878180287</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0007807546834457138</v>
+        <v>0.0007807546834457146</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002135326652087877</v>
+        <v>0.0002135326652087874</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003647041308878654</v>
+        <v>0.0003647041308878643</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0003472944125229094</v>
+        <v>0.0003472944125229104</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009468471373161116</v>
+        <v>0.0009468471373161098</v>
       </c>
     </row>
     <row r="5">
@@ -5618,85 +5618,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.349604396880221e-05</v>
+        <v>5.349604396880219e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.547674244200959e-05</v>
+        <v>2.547674244200963e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.965569973269309e-05</v>
+        <v>2.965569973269312e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.332995333710124e-05</v>
+        <v>3.332995333710127e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.127067692449947e-05</v>
+        <v>2.127067692449949e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.729472889138844e-05</v>
+        <v>3.729472889138845e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.606131896564847e-05</v>
+        <v>2.606131896564851e-05</v>
       </c>
       <c r="I5" t="n">
         <v>2.712595383899449e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.153102549992054e-05</v>
+        <v>4.153102549992057e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.659408901727243e-05</v>
+        <v>2.659408901727245e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001299259338735836</v>
+        <v>0.0001299259338735837</v>
       </c>
       <c r="M5" t="n">
-        <v>6.358380724029069e-05</v>
+        <v>6.358380724029076e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.164163856150583e-05</v>
+        <v>1.996175337042857e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.43886585967233e-05</v>
+        <v>2.438865859672332e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.484089359862949e-05</v>
+        <v>4.484089359862952e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.126392622743499e-05</v>
+        <v>2.126392622743501e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.675315618908955e-05</v>
+        <v>2.675315618908954e-05</v>
       </c>
       <c r="S5" t="n">
         <v>4.345907619026352e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.980786764406322e-05</v>
+        <v>2.980786764406323e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>8.519694808319068e-05</v>
+        <v>8.519694808319076e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>3.023933960401458e-05</v>
+        <v>3.023933960401459e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.527823765621973e-05</v>
+        <v>3.527823765621975e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.565344777701646e-05</v>
+        <v>5.565344777701655e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.34034122833996e-05</v>
+        <v>4.340341228339964e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.725485462150395e-05</v>
+        <v>3.725485462150397e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.265814776490754e-05</v>
+        <v>4.265814776490755e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.797784201817097e-05</v>
+        <v>7.797784201817087e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.053232641534728e-05</v>
+        <v>6.053232641534734e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.007433339292711e-05</v>
+        <v>3.007433339292714e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.42532906836106e-05</v>
+        <v>3.425329068361064e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.083254237361036e-05</v>
+        <v>4.083254237361039e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.014664258019118e-05</v>
+        <v>2.014664258019121e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.028243019180525e-05</v>
+        <v>4.028243019180531e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.065890991656599e-05</v>
+        <v>3.065890991656606e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1723544789912e-05</v>
+        <v>3.172354478991203e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.612861645083807e-05</v>
+        <v>4.612861645083809e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.119167996818996e-05</v>
+        <v>3.119167996818997e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001345235248245012</v>
+        <v>0.0001345235248245013</v>
       </c>
       <c r="M6" t="n">
-        <v>6.818139819120693e-05</v>
+        <v>6.818139819120697e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.164163856150583e-05</v>
+        <v>3.05776362061011e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.511541402846626e-05</v>
+        <v>3.511541402846627e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>5.635685836803601e-05</v>
+        <v>5.635685836803605e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.515115291868016e-05</v>
+        <v>3.51511529186802e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.135074714000711e-05</v>
+        <v>3.13507471400071e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.805666714118107e-05</v>
+        <v>4.80566671411811e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.440545859498079e-05</v>
+        <v>3.440545859498078e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>9.358519138535008e-05</v>
+        <v>9.358519138535011e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.310537029013135e-05</v>
+        <v>4.310537029013134e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.987430278576952e-05</v>
+        <v>3.987430278576953e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>6.882910338882703e-05</v>
+        <v>6.882910338882707e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.028365043339097e-05</v>
+        <v>4.0283650433391e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>4.654992008507237e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.725573871582506e-05</v>
+        <v>4.725573871582509e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.446542994833931e-05</v>
+        <v>7.446542994833926e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5950,85 +5950,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.842704377759884e-06</v>
+        <v>4.842704377759888e-06</v>
       </c>
       <c r="C2" t="n">
         <v>4.91227766900525e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.975177078623347e-06</v>
+        <v>4.975177078623351e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.896081145393978e-06</v>
+        <v>4.896081145393983e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.841090943647824e-06</v>
+        <v>4.841090943647829e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.514962461396111e-06</v>
+        <v>5.514962461396115e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.832669447824773e-06</v>
+        <v>4.832669447824775e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.953390821139646e-06</v>
+        <v>4.953390821139651e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.303025755709779e-06</v>
+        <v>5.303025755709781e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.351570426548545e-06</v>
+        <v>5.35157042654855e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.664962346427347e-06</v>
+        <v>7.664962346427351e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.330353347106845e-06</v>
+        <v>5.330353347106846e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.832669162337488e-06</v>
+        <v>4.832669162337494e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>6.609502258958847e-06</v>
+        <v>6.609502258958855e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>5.727625306807659e-06</v>
+        <v>5.727625306807657e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.843936342453084e-06</v>
+        <v>4.843936342453088e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>4.848095301510256e-06</v>
+        <v>4.848095301510257e-06</v>
       </c>
       <c r="S2" t="n">
         <v>5.217143561626463e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>4.839255636223668e-06</v>
+        <v>4.839255636223673e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>7.445169664897805e-06</v>
+        <v>7.445169664897803e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.915773770153654e-06</v>
+        <v>4.915773770153662e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>7.069682701980473e-06</v>
+        <v>7.069682701980481e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.001563227512743e-06</v>
+        <v>7.001563227512744e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.430219042733199e-06</v>
+        <v>6.430219042733204e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.835090745467728e-06</v>
+        <v>5.835090745467732e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.385942272671281e-06</v>
+        <v>5.385942272671284e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.369001833408558e-06</v>
+        <v>7.369001833408559e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.763089622913276e-06</v>
+        <v>5.178314078051513e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.678168993224618e-06</v>
+        <v>5.225879285032875e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.865747628574604e-06</v>
+        <v>6.262080336366169e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.539353294269874e-06</v>
+        <v>5.169726048251644e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.740510305159522e-06</v>
+        <v>5.186520828697012e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.123613421715758e-05</v>
+        <v>1.031214137128539e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.54264675449148e-06</v>
+        <v>5.107560999647465e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.362895860044605e-06</v>
+        <v>6.091780826158678e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.641136556404843e-05</v>
+        <v>8.757661069810803e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.761775424877331e-05</v>
+        <v>9.164618283874937e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.103455243046315e-05</v>
+        <v>2.694205137042721e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.724735544385682e-05</v>
+        <v>9.08685951620678e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.536605712989073e-06</v>
+        <v>5.098063339626063e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>8.395071851696734e-06</v>
+        <v>7.21988517744036e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.610224744509359e-05</v>
+        <v>1.202746821248204e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.802435733758004e-06</v>
+        <v>5.209546695654005e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.902450993100567e-06</v>
+        <v>5.2320360115699e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.440161592677713e-05</v>
+        <v>8.053089961346904e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.693919018155577e-06</v>
+        <v>5.162170107050703e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.687188747930118e-05</v>
+        <v>1.343596498573775e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>7.45109571877016e-06</v>
+        <v>5.762938857351786e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.380130881425005e-05</v>
+        <v>9.237146232609893e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>5.609487147819873e-05</v>
+        <v>2.246118176990932e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.262902753979588e-05</v>
+        <v>1.78452905075184e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.096649213615724e-05</v>
+        <v>7.451022486883566e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.837630784699842e-05</v>
+        <v>9.530047772913189e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.409941817389515e-05</v>
+        <v>2.573256592591975e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6126,85 +6126,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.479768747098292e-05</v>
+        <v>1.479768747098293e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.535822563757621e-05</v>
+        <v>1.535822563757622e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.289334927380754e-05</v>
+        <v>4.289334927380761e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.207269492028341e-05</v>
+        <v>2.207269492028346e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.589050820187158e-05</v>
+        <v>1.589050820187159e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001328607383191232</v>
+        <v>0.0001328607383191233</v>
       </c>
       <c r="H4" t="n">
-        <v>1.341979634738141e-05</v>
+        <v>1.341979634738143e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.880199907033417e-05</v>
+        <v>3.880199907033419e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>9.990154211598114e-05</v>
+        <v>9.990154211598119e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001107768053639508</v>
+        <v>0.0001107768053639507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000524343156266977</v>
+        <v>0.0005243431562669774</v>
       </c>
       <c r="M4" t="n">
         <v>0.0001118910769942771</v>
       </c>
       <c r="N4" t="n">
-        <v>1.278210748576918e-05</v>
+        <v>1.278210748576919e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>2.265125542979485e-05</v>
+        <v>2.265125542979492e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000176472130531758</v>
+        <v>0.0001764721305317581</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.648402491012814e-05</v>
+        <v>1.648402491012813e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.657619205182616e-05</v>
+        <v>1.657619205182618e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>8.156853107612255e-05</v>
+        <v>8.156853107612243e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.487076150636276e-05</v>
+        <v>1.487076150636275e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001685803628689423</v>
+        <v>0.0001685803628689422</v>
       </c>
       <c r="V4" t="n">
-        <v>2.931771719671499e-05</v>
+        <v>2.931771719671497e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>6.717337084855576e-05</v>
+        <v>6.717337084855575e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004472055152002938</v>
+        <v>0.0004472055152002941</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000330133046113122</v>
+        <v>0.0003301330461131213</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.917811307977227e-05</v>
+        <v>4.917811307977229e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001238765772122176</v>
+        <v>0.0001238765772122175</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005515902484519697</v>
+        <v>0.00055159024845197</v>
       </c>
     </row>
     <row r="5">
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.401690282601422e-05</v>
+        <v>1.401690282601424e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.02002920003355e-05</v>
+        <v>2.020029200033552e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.178143735390975e-05</v>
+        <v>2.178143735390981e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.755038376771396e-05</v>
+        <v>1.755038376771398e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.497518977996498e-05</v>
+        <v>1.497518977996501e-05</v>
       </c>
       <c r="G5" t="n">
         <v>2.917831251467591e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.01717481072908e-05</v>
+        <v>2.017174810729082e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.153535155345769e-05</v>
+        <v>2.153535155345774e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.546675632677008e-05</v>
+        <v>2.546675632677015e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.603297336821939e-05</v>
+        <v>2.603297336821941e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.21637993161115e-05</v>
+        <v>5.216379931611152e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.582680360809336e-05</v>
+        <v>2.582680360809338e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.278210748576918e-05</v>
+        <v>1.531284555235312e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.720532777486732e-05</v>
+        <v>1.720532777486735e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.642974824539571e-05</v>
+        <v>2.64297482453957e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.279897516367653e-05</v>
+        <v>1.279897516367655e-05</v>
       </c>
       <c r="R5" t="n">
         <v>2.034599022091164e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>2.451456008951137e-05</v>
+        <v>2.45145600895114e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02461421350527e-05</v>
+        <v>2.024614213505274e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.667729925294556e-05</v>
+        <v>2.667729925294555e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.928198452935015e-05</v>
+        <v>1.928198452935018e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32415487054923e-05</v>
+        <v>2.324154870549231e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>3.774485586257933e-05</v>
+        <v>3.774485586257932e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.445063658700168e-05</v>
+        <v>4.445063658700169e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.605885398025996e-05</v>
+        <v>1.605885398025999e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.642121918200615e-05</v>
+        <v>2.642121918200618e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.502151729277523e-05</v>
+        <v>5.502151729277525e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6305,82 +6305,82 @@
         <v>1.74260759641395e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.101234878927646e-05</v>
+        <v>2.101234878927649e-05</v>
       </c>
       <c r="D6" t="n">
         <v>2.259349414285071e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.085279932891731e-05</v>
+        <v>2.085279932891732e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.261609267962167e-05</v>
+        <v>1.26160926796217e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.869061833543702e-05</v>
+        <v>2.869061833543704e-05</v>
       </c>
       <c r="H6" t="n">
         <v>2.098380489623176e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.234740834239868e-05</v>
+        <v>2.234740834239869e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.627881311571107e-05</v>
+        <v>2.627881311571109e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.684503015716036e-05</v>
+        <v>2.684503015716035e-05</v>
       </c>
       <c r="L6" t="n">
         <v>5.297585610505246e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.663886039703481e-05</v>
+        <v>2.663886039703482e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.278210748576918e-05</v>
+        <v>2.098380167152157e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.27576066126684e-05</v>
+        <v>2.275760661266842e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.257392101974362e-05</v>
+        <v>3.257392101974361e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.11110696347101e-05</v>
+        <v>2.111106963471011e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.115804700985261e-05</v>
+        <v>2.115804700985262e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.532661687845237e-05</v>
+        <v>2.532661687845236e-05</v>
       </c>
       <c r="T6" t="n">
         <v>2.105819892399367e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.054789666695324e-05</v>
+        <v>3.054789666695326e-05</v>
       </c>
       <c r="V6" t="n">
         <v>2.604260469808853e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.405237361455302e-05</v>
+        <v>2.405237361455303e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.548245787823982e-05</v>
+        <v>4.548245787823986e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.902886247984468e-05</v>
+        <v>3.902886247984466e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.104220648389217e-05</v>
+        <v>2.104220648389219e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>2.723327597094712e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.928592086040257e-05</v>
+        <v>4.928592086040258e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.430856389596688e-05</v>
+        <v>4.812449584211382e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>9.097466421401017e-06</v>
+        <v>8.636599122710641e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.198991352238044e-05</v>
+        <v>1.065206925619566e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.251059138567302e-05</v>
+        <v>1.789170964047362e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.282227161395541e-05</v>
+        <v>1.11970232900743e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.597344424401384e-05</v>
+        <v>1.355820352130173e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.378912434304046e-05</v>
+        <v>1.183261190426594e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.281430510804168e-05</v>
+        <v>1.120590473096329e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.431970183919486e-05</v>
+        <v>1.937474436826594e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.150550300335831e-05</v>
+        <v>1.032576137405336e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.299487758037787e-05</v>
+        <v>6.733787277740422e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.92616019366471e-05</v>
+        <v>2.930677925393387e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>9.475767640599356e-06</v>
+        <v>8.934253253119811e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.864202307292147e-05</v>
+        <v>1.646934435823173e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.769211825886738e-05</v>
+        <v>2.190426957563038e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.812805698589278e-05</v>
+        <v>1.491639659856487e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.199029101749618e-05</v>
+        <v>1.062993518037664e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>3.235362481101732e-05</v>
+        <v>2.51424779249022e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.550522886037286e-05</v>
+        <v>1.306077537777879e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.212551152160093e-05</v>
+        <v>4.672625914561616e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.030568742213008e-05</v>
+        <v>1.667039120608047e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.109499097911753e-05</v>
+        <v>1.784013244332363e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.578078470114532e-05</v>
+        <v>2.707966324688358e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.708004786457389e-05</v>
+        <v>1.424109689116314e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.589204927732371e-05</v>
+        <v>2.843001278588134e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.798399836662235e-05</v>
+        <v>2.182015290318777e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.732966405964865e-05</v>
+        <v>3.457047552657653e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.829156443664579e-06</v>
+        <v>4.694394364950956e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.876297008934682e-06</v>
+        <v>4.739241751360671e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.306200459792603e-06</v>
+        <v>5.016775214864847e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.533156090615795e-06</v>
+        <v>4.400189912632178e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5128569359988e-06</v>
+        <v>5.160856998896009e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.44075123071968e-06</v>
+        <v>5.85204653435072e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.822781985218186e-06</v>
+        <v>4.680857765842007e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.538123985969372e-06</v>
+        <v>5.177897520752343e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.255798648525551e-06</v>
+        <v>5.703998540274478e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.228058464932225e-06</v>
+        <v>7.828346129619256e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.611784661100751e-06</v>
+        <v>6.682570530657553e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>6.386772313515142e-06</v>
+        <v>5.764585277678951e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.90786192548977e-06</v>
+        <v>4.751102417328915e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.682955045614307e-06</v>
+        <v>6.478449667790734e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.141812482976451e-06</v>
+        <v>4.918126718592074e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.391084537960776e-06</v>
+        <v>5.085884283794274e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.974079195446881e-06</v>
+        <v>4.789180696382641e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.682934406484913e-06</v>
+        <v>6.748793483415409e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.095136808850274e-06</v>
+        <v>4.875021960684639e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.202454205926217e-05</v>
+        <v>1.036927930274073e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.77602177603957e-06</v>
+        <v>5.36884902247567e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.612530281542069e-06</v>
+        <v>7.224670837467774e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.084886087961053e-05</v>
+        <v>1.596397855963543e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.483191778934764e-05</v>
+        <v>1.164869825975522e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.848428995037135e-06</v>
+        <v>5.635514373151676e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.468399013170413e-06</v>
+        <v>5.838729297476845e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.556896439532812e-06</v>
+        <v>5.866599469564794e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.48022992340382e-05</v>
+        <v>4.121106846837962e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.738987938634564e-06</v>
+        <v>7.495404965604917e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.593867298179124e-05</v>
+        <v>1.316029180160052e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.944042327737468e-05</v>
+        <v>1.558288379208728e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.218216889293542e-05</v>
+        <v>1.057152569668987e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.520078444568126e-05</v>
+        <v>1.283290001211118e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.350201011777315e-06</v>
+        <v>7.93279058443803e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.043745845161433e-05</v>
+        <v>9.372252401843954e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.234726031584392e-05</v>
+        <v>1.778997399177325e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.148835837067836e-05</v>
+        <v>1.014964565917033e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.364042063543748e-05</v>
+        <v>6.75922406751002e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.688085880149459e-05</v>
+        <v>2.750456220536447e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.013836163739027e-05</v>
+        <v>9.193277381405495e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.770842354272168e-05</v>
+        <v>1.557564224587855e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.244408740863188e-05</v>
+        <v>2.510448222948947e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.692058432000238e-05</v>
+        <v>1.388980876429817e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.52240001610039e-06</v>
+        <v>8.057345495816802e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.240884308697423e-05</v>
+        <v>2.50399105697949e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.712597486862251e-05</v>
+        <v>1.397775975646576e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.003460741278651e-05</v>
+        <v>4.501557562744543e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.457351543094914e-05</v>
+        <v>1.244388926998812e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.711558128494026e-05</v>
+        <v>1.478589055996708e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.768973978964352e-05</v>
+        <v>2.822599509510321e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.514777030895773e-05</v>
+        <v>1.271056604954885e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.032992624095701e-05</v>
+        <v>2.421083078386986e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.242479671949524e-05</v>
+        <v>1.777729706746587e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.558567955992295e-05</v>
+        <v>3.31722252808956e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.67116172143168e-05</v>
+        <v>3.540880568696942e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.183835236871737e-06</v>
+        <v>7.927370095910038e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.961354104379723e-05</v>
+        <v>1.584452052718646e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.706639959707584e-05</v>
+        <v>1.400006954093663e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.54294206239308e-05</v>
+        <v>1.296167999606325e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.565556788986587e-05</v>
+        <v>1.330459545231557e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.972087545753932e-06</v>
+        <v>7.818721554764645e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.130708033868396e-05</v>
+        <v>1.696269619645144e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.349166654446556e-05</v>
+        <v>1.875021133390289e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.868213544729083e-05</v>
+        <v>2.257616380315353e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.514122062097203e-05</v>
+        <v>6.186561603506918e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.488739060581037e-05</v>
+        <v>2.626402865537038e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.177444968662489e-05</v>
+        <v>1.046108444788627e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.781710978893527e-05</v>
+        <v>1.58050796109802e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.306893738737488e-05</v>
+        <v>2.573819002936489e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.748323799419322e-05</v>
+        <v>1.445485978312495e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.736770361405081e-06</v>
+        <v>8.343054770336773e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.20623475487123e-05</v>
+        <v>2.496438863007483e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.916882636938323e-05</v>
+        <v>1.551410701165003e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.265148029979782e-05</v>
+        <v>4.717427222639399e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.930613698864232e-05</v>
+        <v>1.600600491631024e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.048347606822459e-05</v>
+        <v>1.732853179007511e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.986396953240887e-05</v>
+        <v>3.681860926997467e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.372121576358348e-05</v>
+        <v>1.883320167049006e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.103709390234126e-05</v>
+        <v>2.513237217098083e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.418779964047309e-05</v>
+        <v>1.913102904255616e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.448216785263889e-05</v>
+        <v>3.253610001447074e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.135124314779587e-05</v>
+        <v>3.202566347048298e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>9.469624138049984e-06</v>
+        <v>9.04983171068054e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.900411354930469e-05</v>
+        <v>1.574270841376737e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.476014148376601e-05</v>
+        <v>1.263050754904073e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.740019814148499e-05</v>
+        <v>1.457206021804333e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.61423873204337e-05</v>
+        <v>1.391259428076371e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.791409889242501e-06</v>
+        <v>8.620050426547668e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.352841309245575e-05</v>
+        <v>1.877867330967297e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.438841051734548e-05</v>
+        <v>1.969388755212641e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.294227942744083e-05</v>
+        <v>2.582610416419759e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.118453306714444e-05</v>
+        <v>5.283603825128417e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.236413467680364e-05</v>
+        <v>2.497908341637973e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.198150719493025e-05</v>
+        <v>1.083631230432726e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.635101257030988e-05</v>
+        <v>1.494096375745745e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15747795953424e-05</v>
+        <v>2.504763651136378e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.114119324224344e-05</v>
+        <v>1.730027401041121e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17905483177049e-05</v>
+        <v>1.066701002287573e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>3.122434590574784e-05</v>
+        <v>2.464919227267877e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.023536431882282e-05</v>
+        <v>1.648202687338149e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>6.960090221656792e-05</v>
+        <v>5.28453398213815e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.950853945941675e-05</v>
+        <v>2.363544198962545e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.362670720550423e-05</v>
+        <v>1.985218505402786e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>5.560068282552303e-05</v>
+        <v>4.13303208038288e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.461828352863796e-05</v>
+        <v>2.657598201209404e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.104000274852818e-05</v>
+        <v>2.559878761609765e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.610446210683218e-05</v>
+        <v>2.067763095298422e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.316996933640091e-05</v>
+        <v>3.199845075398386e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.328054373808427e-06</v>
+        <v>8.018672962034687e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.098471771294045e-06</v>
+        <v>4.992180364192406e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.657915013194086e-06</v>
+        <v>5.367576718895318e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.841275423351388e-06</v>
+        <v>5.414150956961944e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.37067546678001e-06</v>
+        <v>5.164563532440001e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.831495206837693e-06</v>
+        <v>6.95900816306828e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.575842768932221e-06</v>
+        <v>5.303218890826742e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.811289651881218e-06</v>
+        <v>5.471270627768778e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.676428046151942e-06</v>
+        <v>7.535450165456082e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.297564039601167e-06</v>
+        <v>6.525130941952134e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.277922143905212e-05</v>
+        <v>1.778759864921709e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.391773877884793e-05</v>
+        <v>1.120088050513492e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.244003916547434e-06</v>
+        <v>5.084123235680659e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.383625450365778e-06</v>
+        <v>7.101646283859751e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>9.834900312664113e-06</v>
+        <v>8.366127716926913e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.124039785190756e-06</v>
+        <v>5.699712303888914e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.146974157125436e-06</v>
+        <v>5.016595956113375e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.812104188061679e-06</v>
+        <v>6.967237115809429e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.843572410066132e-06</v>
+        <v>5.491648804549522e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.786179937528136e-05</v>
+        <v>2.167569259599037e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>6.487211547105649e-06</v>
+        <v>5.973620162696552e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.202685186559355e-05</v>
+        <v>1.042619063837531e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>9.566125920978239e-06</v>
+        <v>8.079947051998623e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.992230208703721e-06</v>
+        <v>5.607298003565195e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.570726503625069e-06</v>
+        <v>8.474382682525317e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.207486577267878e-05</v>
+        <v>9.855308784602486e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.712498496705151e-05</v>
+        <v>1.323353022571922e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.670679351628658e-06</v>
+        <v>4.524364842741751e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.722498756086317e-06</v>
+        <v>4.570442556330398e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.59246308254507e-06</v>
+        <v>4.451036658957635e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.33737930577556e-06</v>
+        <v>4.22015248057289e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.763181957079447e-06</v>
+        <v>4.575802224987169e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.260826418974923e-06</v>
+        <v>4.935155355354249e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.610562265550941e-06</v>
+        <v>4.470259062793086e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.122914495648304e-06</v>
+        <v>4.825794990391026e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.245735112132887e-06</v>
+        <v>4.922250577304506e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.875628973523738e-06</v>
+        <v>5.36164624266939e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.184772126541575e-06</v>
+        <v>4.869060266152451e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>5.312945169440684e-06</v>
+        <v>4.947464751826569e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.56665632711779e-06</v>
+        <v>4.445278419265257e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.171635560531338e-06</v>
+        <v>6.00812757820493e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.49640661503488e-06</v>
+        <v>4.399366560101887e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.610846676661298e-06</v>
+        <v>4.466450244175648e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.695871146841471e-06</v>
+        <v>4.530114205020675e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.805699485268095e-06</v>
+        <v>5.345383436791298e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.587516024106734e-06</v>
+        <v>4.446063420262546e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.000440523796575e-06</v>
+        <v>6.641985346017227e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>5.10522037829854e-06</v>
+        <v>4.8246389797438e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.806477570971565e-06</v>
+        <v>7.271184334663272e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.250990466130179e-05</v>
+        <v>1.004806333694545e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.171451948879539e-06</v>
+        <v>6.964370314757105e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.699248873863645e-06</v>
+        <v>5.465573696696167e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.902934160227734e-06</v>
+        <v>5.382920265706709e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.183458949921455e-06</v>
+        <v>4.863528779740278e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.749772399413101e-06</v>
+        <v>4.57726986425397e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.726903729175613e-06</v>
+        <v>4.573604641218121e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.107388823386777e-06</v>
+        <v>4.81336279077818e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.199976497438679e-06</v>
+        <v>4.110692144819541e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>4.736758899856822e-06</v>
+        <v>4.556539738500008e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.794675795304741e-06</v>
+        <v>4.598735645904952e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.599662624722822e-06</v>
+        <v>4.458137111654586e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.263422153599489e-06</v>
+        <v>4.921253523538112e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.071255529136504e-06</v>
+        <v>4.794889747775209e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.564442690115505e-06</v>
+        <v>5.843590401112895e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.946341185593404e-06</v>
+        <v>4.698184592834678e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2755771158399e-06</v>
+        <v>4.923049311408667e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.537657490596025e-06</v>
+        <v>4.424564200235094e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.157042170079235e-06</v>
+        <v>5.99466942562921e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>4.516704138347842e-06</v>
+        <v>4.406340658973737e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.686589364936675e-06</v>
+        <v>4.523631435026581e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>4.74321900229103e-06</v>
+        <v>4.561936129843368e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.464124090319863e-06</v>
+        <v>5.088445831933097e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.698238134931426e-06</v>
+        <v>4.528531952299367e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>7.157258121548083e-06</v>
+        <v>6.752234352873166e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>5.395635516324934e-06</v>
+        <v>5.034524665123885e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>6.705493351699095e-06</v>
+        <v>6.481891119862392e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.308806526266804e-05</v>
+        <v>1.047889248503589e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.11225688827975e-06</v>
+        <v>6.217849777050817e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.489087360587051e-06</v>
+        <v>5.308062392118165e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.170012582779233e-06</v>
+        <v>4.868628162508506e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.292286440380658e-06</v>
+        <v>5.62180057075316e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.137930788252422e-05</v>
+        <v>2.425055237438805e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.851893061513638e-06</v>
+        <v>6.640202233125379e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.897201021032735e-06</v>
+        <v>8.752686340691368e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.480411167323704e-05</v>
+        <v>1.211402944346835e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.581654448717803e-06</v>
+        <v>7.845089543401414e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.384517879880321e-05</v>
+        <v>1.168786791560056e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.321523734270994e-06</v>
+        <v>6.971024153290509e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.076443856164246e-06</v>
+        <v>7.497647704522442e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.803636134250598e-05</v>
+        <v>1.459439244554934e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.690596400544599e-06</v>
+        <v>7.233147219990948e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.969766734259658e-05</v>
+        <v>5.816317184441041e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.368974206586693e-05</v>
+        <v>2.551904300514289e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>7.231885859698348e-06</v>
+        <v>6.926211601965824e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.143037446354041e-05</v>
+        <v>1.061362889895472e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.354950433922233e-05</v>
+        <v>1.854736231093056e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.047565121809354e-05</v>
+        <v>9.188842213303939e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.814321507003259e-06</v>
+        <v>7.31359201013545e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.906896832168333e-05</v>
+        <v>1.549433816963218e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.000752404003687e-05</v>
+        <v>8.828389045371701e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>5.337158937660449e-05</v>
+        <v>4.009425955626328e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.165540255475432e-05</v>
+        <v>1.011697687049745e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.599776189936381e-05</v>
+        <v>1.370416670272173e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.467109112886374e-05</v>
+        <v>2.589218524413987e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.408020680964427e-05</v>
+        <v>1.172214494411835e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.206432021910703e-05</v>
+        <v>1.801730634619363e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.904167237178341e-05</v>
+        <v>1.517232028804583e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.951265610483893e-05</v>
+        <v>2.88211669896761e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.178314078051513e-06</v>
+        <v>5.042131063769882e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.225879285032875e-06</v>
+        <v>5.081441014936278e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.262080336366169e-06</v>
+        <v>5.785637861453542e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.169726048251644e-06</v>
+        <v>4.948193394086707e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.186520828697012e-06</v>
+        <v>5.036125284917659e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.031214137128539e-05</v>
+        <v>8.762827513016695e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.107560999647465e-06</v>
+        <v>4.987554050856024e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.091780826158678e-06</v>
+        <v>5.664527108997526e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.757661069810803e-06</v>
+        <v>7.599110513251335e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.164618283874937e-06</v>
+        <v>7.874194044948457e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.694205137042721e-05</v>
+        <v>2.069553824295591e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>9.08685951620678e-06</v>
+        <v>7.779544144480986e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.098063339626063e-06</v>
+        <v>4.986213687974068e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>7.21988517744036e-06</v>
+        <v>6.988916944984575e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.202746821248204e-05</v>
+        <v>9.951003951566667e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.209546695654005e-06</v>
+        <v>5.051970002371079e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2320360115699e-06</v>
+        <v>5.073881248952845e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>8.053089961346904e-06</v>
+        <v>7.116875400246289e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>5.162170107050703e-06</v>
+        <v>5.024554011838016e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.343596498573775e-05</v>
+        <v>1.145348280107965e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.762938857351786e-06</v>
+        <v>5.450086034741843e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>9.237146232609893e-06</v>
+        <v>8.468774903692707e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.246118176990932e-05</v>
+        <v>1.710556025112506e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.78452905075184e-05</v>
+        <v>1.390470951919608e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.451022486883566e-06</v>
+        <v>6.902654007487192e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.530047772913189e-06</v>
+        <v>8.07701724499649e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.573256592591975e-05</v>
+        <v>1.909030525334036e-05</v>
       </c>
     </row>
     <row r="4">
